--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0A2A9B-3725-4E42-A5DD-07DF2D351C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F4A816-B579-4DC6-9DE1-5F9D38450F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="386">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -118,10 +118,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-  </si>
-  <si>
-    <t>Capitalization:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ST AR</t>
@@ -1532,10 +1528,6 @@
   </si>
   <si>
     <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target Buy Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3328,20 +3320,20 @@
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3647,22 +3639,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="293" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="294" t="s">
         <v>356</v>
-      </c>
-      <c r="F1" s="294" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="254" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3686,24 +3678,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="50">
         <v>7.9</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3719,7 +3711,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C8" s="287">
         <v>6</v>
@@ -3729,7 +3721,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3739,17 +3731,15 @@
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
-        <v>25</v>
+      <c r="B10" s="4" t="str">
+        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
+        <v>Capitalization (HKD):</v>
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
         <v>64557.851494399998</v>
       </c>
-      <c r="D10" s="32" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
@@ -3757,24 +3747,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="330" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="330"/>
-      <c r="D12" s="330"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="330"/>
+      <c r="B12" s="329" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="329"/>
+      <c r="D12" s="329"/>
+      <c r="E12" s="329"/>
+      <c r="F12" s="329"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3787,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3807,16 +3797,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C19" s="256">
         <v>0.2</v>
@@ -3824,15 +3814,16 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="2" t="s">
-        <v>288</v>
+      <c r="B20" s="2" t="str">
+        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
+        <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
         <f>C123</f>
         <v>7.4179368510878518</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E20" s="289">
         <f>Scenarios!C76</f>
@@ -3841,16 +3832,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
         <v>0.17349059186547722</v>
       </c>
-      <c r="D21" s="5" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
+      <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3859,7 +3847,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="254" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3868,26 +3856,26 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="330" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" s="330"/>
-      <c r="D25" s="330"/>
-      <c r="E25" s="330"/>
-      <c r="F25" s="330"/>
+      <c r="B25" s="329" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="329"/>
+      <c r="D25" s="329"/>
+      <c r="E25" s="329"/>
+      <c r="F25" s="329"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="331" t="s">
-        <v>257</v>
-      </c>
-      <c r="C26" s="331"/>
-      <c r="D26" s="331"/>
-      <c r="E26" s="331"/>
-      <c r="F26" s="331"/>
+      <c r="B26" s="333" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="333"/>
+      <c r="D26" s="333"/>
+      <c r="E26" s="333"/>
+      <c r="F26" s="333"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3895,17 +3883,17 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="329" t="s">
-        <v>239</v>
-      </c>
-      <c r="C29" s="329"/>
-      <c r="D29" s="329"/>
-      <c r="E29" s="329"/>
-      <c r="F29" s="329"/>
+      <c r="B29" s="331" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="331"/>
+      <c r="D29" s="331"/>
+      <c r="E29" s="331"/>
+      <c r="F29" s="331"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C30" s="192">
         <f>Normalized_FCF!C8</f>
@@ -3921,17 +3909,17 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="329" t="s">
-        <v>241</v>
-      </c>
-      <c r="C32" s="329"/>
-      <c r="D32" s="329"/>
-      <c r="E32" s="329"/>
-      <c r="F32" s="329"/>
+      <c r="B32" s="331" t="s">
+        <v>240</v>
+      </c>
+      <c r="C32" s="331"/>
+      <c r="D32" s="331"/>
+      <c r="E32" s="331"/>
+      <c r="F32" s="331"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C33" s="192">
         <f>Normalized_FCF!C9</f>
@@ -3944,7 +3932,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C34" s="192">
         <f>Normalized_FCF!C10</f>
@@ -3956,17 +3944,17 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="329" t="s">
-        <v>244</v>
-      </c>
-      <c r="C36" s="329"/>
-      <c r="D36" s="329"/>
-      <c r="E36" s="329"/>
-      <c r="F36" s="329"/>
+      <c r="B36" s="331" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="331"/>
+      <c r="D36" s="331"/>
+      <c r="E36" s="331"/>
+      <c r="F36" s="331"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C37" s="192">
         <f>Normalized_FCF!C11</f>
@@ -3978,17 +3966,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="329" t="s">
-        <v>248</v>
-      </c>
-      <c r="C39" s="329"/>
-      <c r="D39" s="329"/>
-      <c r="E39" s="329"/>
-      <c r="F39" s="329"/>
+      <c r="B39" s="331" t="s">
+        <v>247</v>
+      </c>
+      <c r="C39" s="331"/>
+      <c r="D39" s="331"/>
+      <c r="E39" s="331"/>
+      <c r="F39" s="331"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C40" s="192">
         <f>Normalized_FCF!C12</f>
@@ -4001,12 +3989,12 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B43" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C43" s="192">
         <f>Normalized_FCF!C15</f>
@@ -4018,17 +4006,17 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="329" t="s">
-        <v>249</v>
-      </c>
-      <c r="C45" s="329"/>
-      <c r="D45" s="329"/>
-      <c r="E45" s="329"/>
-      <c r="F45" s="329"/>
+      <c r="B45" s="331" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" s="331"/>
+      <c r="D45" s="331"/>
+      <c r="E45" s="331"/>
+      <c r="F45" s="331"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C46" s="192">
         <f>Normalized_FCF!C14</f>
@@ -4040,17 +4028,17 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="329" t="s">
-        <v>252</v>
-      </c>
-      <c r="C48" s="333"/>
-      <c r="D48" s="333"/>
-      <c r="E48" s="333"/>
-      <c r="F48" s="333"/>
+      <c r="B48" s="331" t="s">
+        <v>251</v>
+      </c>
+      <c r="C48" s="332"/>
+      <c r="D48" s="332"/>
+      <c r="E48" s="332"/>
+      <c r="F48" s="332"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C49" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4063,7 +4051,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C50" s="1">
         <f>Normalized_FCF!C18</f>
@@ -4075,17 +4063,17 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="330" t="s">
-        <v>273</v>
-      </c>
-      <c r="C52" s="330"/>
-      <c r="D52" s="330"/>
-      <c r="E52" s="330"/>
-      <c r="F52" s="330"/>
+      <c r="B52" s="329" t="s">
+        <v>272</v>
+      </c>
+      <c r="C52" s="329"/>
+      <c r="D52" s="329"/>
+      <c r="E52" s="329"/>
+      <c r="F52" s="329"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C53" s="192">
         <f>Normalized_FCF!G19</f>
@@ -4098,7 +4086,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B54" s="47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C54" s="192">
         <f>Normalized_FCF!C19</f>
@@ -4111,7 +4099,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B55" s="261" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
@@ -4120,7 +4108,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="261" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
@@ -4129,7 +4117,7 @@
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A58" s="254" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B58" s="36"/>
       <c r="C58" s="36"/>
@@ -4142,31 +4130,31 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="329" t="s">
-        <v>309</v>
-      </c>
-      <c r="C60" s="329"/>
-      <c r="D60" s="329"/>
-      <c r="E60" s="329"/>
-      <c r="F60" s="329"/>
+      <c r="B60" s="331" t="s">
+        <v>307</v>
+      </c>
+      <c r="C60" s="331"/>
+      <c r="D60" s="331"/>
+      <c r="E60" s="331"/>
+      <c r="F60" s="331"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="331" t="s">
-        <v>264</v>
-      </c>
-      <c r="C61" s="331"/>
-      <c r="D61" s="331"/>
-      <c r="E61" s="331"/>
-      <c r="F61" s="331"/>
+      <c r="B61" s="333" t="s">
+        <v>263</v>
+      </c>
+      <c r="C61" s="333"/>
+      <c r="D61" s="333"/>
+      <c r="E61" s="333"/>
+      <c r="F61" s="333"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C64" s="322">
         <v>0.08</v>
@@ -4174,31 +4162,31 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C65" s="271">
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D65" s="296" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C66" s="271">
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D66" s="296" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="82" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C67" s="271">
         <f>SUM(C64:C66)</f>
@@ -4209,26 +4197,26 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="330" t="s">
-        <v>317</v>
-      </c>
-      <c r="C69" s="330"/>
-      <c r="D69" s="330"/>
-      <c r="E69" s="330"/>
-      <c r="F69" s="330"/>
+      <c r="B69" s="329" t="s">
+        <v>315</v>
+      </c>
+      <c r="C69" s="329"/>
+      <c r="D69" s="329"/>
+      <c r="E69" s="329"/>
+      <c r="F69" s="329"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="330" t="s">
-        <v>263</v>
-      </c>
-      <c r="C70" s="330"/>
-      <c r="D70" s="330"/>
-      <c r="E70" s="330"/>
-      <c r="F70" s="330"/>
+      <c r="B70" s="329" t="s">
+        <v>262</v>
+      </c>
+      <c r="C70" s="329"/>
+      <c r="D70" s="329"/>
+      <c r="E70" s="329"/>
+      <c r="F70" s="329"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C71" s="271">
         <v>0</v>
@@ -4236,7 +4224,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B73" s="47" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C73" s="255">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4249,7 +4237,7 @@
     </row>
     <row r="75" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A75" s="254" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B75" s="36"/>
       <c r="C75" s="36"/>
@@ -4261,27 +4249,27 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="330" t="s">
-        <v>266</v>
-      </c>
-      <c r="C77" s="330"/>
-      <c r="D77" s="330"/>
-      <c r="E77" s="330"/>
-      <c r="F77" s="330"/>
+      <c r="B77" s="329" t="s">
+        <v>265</v>
+      </c>
+      <c r="C77" s="329"/>
+      <c r="D77" s="329"/>
+      <c r="E77" s="329"/>
+      <c r="F77" s="329"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B80" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C81" s="192">
         <f>Valuation_Model!C7</f>
@@ -4294,7 +4282,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="47" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C82" s="255">
         <f>C81*C28*Exchange_Rate/Common_Shares</f>
@@ -4307,12 +4295,12 @@
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B84" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C85" s="192">
         <f>BS!C66</f>
@@ -4325,7 +4313,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C86" s="192">
         <f>Valuation_Model!C8</f>
@@ -4338,7 +4326,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C87" s="255">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4351,12 +4339,12 @@
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C90" s="192">
         <f>Valuation_Model!C9</f>
@@ -4369,7 +4357,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C91" s="255">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
@@ -4381,17 +4369,17 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="330" t="s">
-        <v>272</v>
-      </c>
-      <c r="C93" s="330"/>
-      <c r="D93" s="330"/>
-      <c r="E93" s="330"/>
-      <c r="F93" s="330"/>
+      <c r="B93" s="329" t="s">
+        <v>271</v>
+      </c>
+      <c r="C93" s="329"/>
+      <c r="D93" s="329"/>
+      <c r="E93" s="329"/>
+      <c r="F93" s="329"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C95" s="255">
         <f>Valuation_Model!C12</f>
@@ -4404,7 +4392,7 @@
     </row>
     <row r="97" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A97" s="254" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B97" s="36"/>
       <c r="C97" s="36"/>
@@ -4413,29 +4401,29 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="329" t="s">
-        <v>376</v>
-      </c>
-      <c r="C99" s="329"/>
-      <c r="D99" s="329"/>
-      <c r="E99" s="329"/>
-      <c r="F99" s="329"/>
+      <c r="B99" s="331" t="s">
+        <v>374</v>
+      </c>
+      <c r="C99" s="331"/>
+      <c r="D99" s="331"/>
+      <c r="E99" s="331"/>
+      <c r="F99" s="331"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="267" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D101" s="267" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E101" s="267" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F101" s="267" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
@@ -4550,7 +4538,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B108" s="242" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C108" s="248">
         <f>Scenarios!C60</f>
@@ -4563,7 +4551,7 @@
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B110" s="334" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C110" s="334"/>
       <c r="D110" s="334"/>
@@ -4572,7 +4560,7 @@
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B112" s="36"/>
       <c r="C112" s="36"/>
@@ -4581,22 +4569,22 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="332" t="s">
-        <v>280</v>
-      </c>
-      <c r="C114" s="332"/>
-      <c r="D114" s="332"/>
-      <c r="E114" s="332"/>
-      <c r="F114" s="332"/>
+      <c r="B114" s="330" t="s">
+        <v>279</v>
+      </c>
+      <c r="C114" s="330"/>
+      <c r="D114" s="330"/>
+      <c r="E114" s="330"/>
+      <c r="F114" s="330"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B116" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C116" s="258">
         <f>E20</f>
@@ -4605,7 +4593,7 @@
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B117" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C117" s="257">
         <f>C19</f>
@@ -4614,7 +4602,7 @@
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B118" s="243" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C118" s="244">
         <f>Scenarios!C77</f>
@@ -4627,7 +4615,7 @@
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B120" s="241" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
@@ -4652,7 +4640,7 @@
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B123" s="82" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C123" s="246">
         <f>Scenarios!C83</f>
@@ -4665,7 +4653,7 @@
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B124" s="245" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C124" s="158">
         <f>Scenarios!F83</f>
@@ -4674,6 +4662,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4687,12 +4681,6 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4776,7 +4764,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4792,7 +4780,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="109">
         <v>1000000</v>
@@ -4826,7 +4814,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="194">
         <v>5344</v>
@@ -4852,7 +4840,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C6" s="194">
         <v>1084</v>
@@ -4876,7 +4864,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="195"/>
       <c r="D7" s="193"/>
@@ -4892,7 +4880,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="194"/>
       <c r="D8" s="185"/>
@@ -4908,7 +4896,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C9" s="194">
         <v>639</v>
@@ -4928,7 +4916,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C10" s="194"/>
       <c r="D10" s="185"/>
@@ -4944,7 +4932,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C11" s="194"/>
       <c r="D11" s="185"/>
@@ -4960,7 +4948,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="194">
         <v>43</v>
@@ -4984,7 +4972,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" s="194">
         <v>2340</v>
@@ -5008,7 +4996,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="194">
         <v>519</v>
@@ -5032,7 +5020,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="196">
         <v>4251</v>
@@ -5056,7 +5044,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="194">
         <v>-151</v>
@@ -5076,13 +5064,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="185">
         <v>160</v>
@@ -5106,7 +5094,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" s="185">
         <v>69</v>
@@ -5126,7 +5114,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C21" s="185">
         <v>910</v>
@@ -5171,13 +5159,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="187"/>
       <c r="D25" s="185">
@@ -5195,7 +5183,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="187"/>
       <c r="D26" s="185">
@@ -5213,7 +5201,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="186">
         <v>14028</v>
@@ -5233,7 +5221,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" s="186">
         <v>166316</v>
@@ -5253,7 +5241,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C29" s="185"/>
       <c r="D29" s="185"/>
@@ -5269,13 +5257,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="185"/>
       <c r="D32" s="185"/>
@@ -5291,7 +5279,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5307,7 +5295,7 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
@@ -5361,7 +5349,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="187">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5410,7 +5398,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="188">
         <f>IF(C36="","",C36+C37)</f>
@@ -5459,7 +5447,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C39" s="187">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5508,7 +5496,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C40" s="189">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5557,7 +5545,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C41" s="189">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5606,7 +5594,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="187">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5655,7 +5643,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C43" s="190">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5704,7 +5692,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C44" s="191">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5753,7 +5741,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="192">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5802,7 +5790,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C46" s="187">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5851,7 +5839,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="190">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5900,7 +5888,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="187">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -5949,12 +5937,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51" s="187">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6003,7 +5991,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" s="187">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6052,12 +6040,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="179" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C55" s="192">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6106,7 +6094,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C56" s="192">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6155,7 +6143,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C57" s="192">
         <f>IF(C$4="","",C11)</f>
@@ -6204,7 +6192,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="192">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6253,13 +6241,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C61" s="187">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6308,7 +6296,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" s="187">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6357,7 +6345,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C63" s="187">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6406,7 +6394,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6455,7 +6443,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6710,7 +6698,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6726,7 +6714,7 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" s="9"/>
     </row>
@@ -6781,7 +6769,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6815,7 +6803,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6849,7 +6837,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6898,7 +6886,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -6990,7 +6978,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7006,7 +6994,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7017,27 +7005,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="210" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="211" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="210" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="211" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>191</v>
-      </c>
       <c r="G3" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H3" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="19">
         <v>8029</v>
@@ -7047,7 +7035,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G4" s="19">
         <v>45665</v>
@@ -7058,7 +7046,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -7068,7 +7056,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="19">
         <v>2014</v>
@@ -7089,7 +7077,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G6" s="19">
         <v>156</v>
@@ -7100,7 +7088,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="19">
         <v>5466</v>
@@ -7110,7 +7098,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7121,7 +7109,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7131,7 +7119,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7142,7 +7130,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
@@ -7152,7 +7140,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7187,7 +7175,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7198,7 +7186,7 @@
         <v>13028</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7216,27 +7204,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C14" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G14" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H14" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="19">
         <v>2757</v>
@@ -7245,7 +7233,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7256,7 +7244,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -7265,7 +7253,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G16" s="19">
         <v>1373</v>
@@ -7276,7 +7264,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" s="19">
         <v>67668</v>
@@ -7285,7 +7273,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G17" s="19">
         <v>13024</v>
@@ -7296,7 +7284,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7305,7 +7293,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G18" s="19">
         <v>23696</v>
@@ -7316,7 +7304,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="19">
         <v>1284</v>
@@ -7325,7 +7313,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7345,7 +7333,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7365,7 +7353,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -7400,7 +7388,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7411,7 +7399,7 @@
         <v>41841</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7424,19 +7412,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F26" s="212" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G26" s="213" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H26" s="214" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7447,7 +7435,7 @@
         <v>967</v>
       </c>
       <c r="F27" s="215" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7466,7 +7454,7 @@
         <v>37</v>
       </c>
       <c r="F28" s="217" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G28" s="185">
         <v>519</v>
@@ -7481,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="218" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7510,14 +7498,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
       <c r="F31" s="218" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G31" s="219">
         <f>C31+C40</f>
@@ -7534,7 +7522,7 @@
         <v>8048</v>
       </c>
       <c r="F32" s="220" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" s="221">
         <f>G35+G40</f>
@@ -7560,24 +7548,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="224" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G34" s="225" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H34" s="226" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C35" s="210" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F35" s="227" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" s="221">
         <f>C12+C24</f>
@@ -7596,7 +7584,7 @@
         <v>832</v>
       </c>
       <c r="F36" s="218" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G36" s="219">
         <f>C4+C15</f>
@@ -7612,7 +7600,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="218" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G37" s="219">
         <f>C6</f>
@@ -7628,7 +7616,7 @@
         <v>1230</v>
       </c>
       <c r="F38" s="218" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G38" s="219">
         <f>C7+C17</f>
@@ -7644,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="218" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G39" s="219">
         <f>C7+C17+C19+C20</f>
@@ -7657,14 +7645,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
       <c r="F40" s="227" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G40" s="221">
         <f>G12+G24</f>
@@ -7684,7 +7672,7 @@
         <v>2748</v>
       </c>
       <c r="F41" s="218" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G41" s="219">
         <f>C70</f>
@@ -7703,7 +7691,7 @@
         <v>4837</v>
       </c>
       <c r="F42" s="229" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G42" s="230">
         <f>C82</f>
@@ -7716,7 +7704,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7727,21 +7715,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C45" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D45" s="210" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F45" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C46" s="192">
         <f>G29</f>
@@ -7773,20 +7761,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C49" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D49" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="292"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7800,7 +7788,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C51" s="209"/>
       <c r="D51" s="94">
@@ -7814,19 +7802,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C53" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D53" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F53" s="292"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7840,7 +7828,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7857,19 +7845,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C57" s="269" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D57" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F57" s="292"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7880,7 +7868,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7894,19 +7882,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C61" s="269" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D61" s="225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F61" s="292"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7917,12 +7905,12 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="292" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -7933,21 +7921,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C65" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D65" s="211" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F65" s="297" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -7958,12 +7946,12 @@
         <v>45106.841774682267</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -7973,7 +7961,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -7983,7 +7971,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -7993,7 +7981,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8006,19 +7994,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="295" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C72" s="268" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D72" s="210" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F72" s="292"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C73" s="192">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
@@ -8031,7 +8019,7 @@
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="298" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C74" s="299">
         <f>-$C$66/C73</f>
@@ -8042,12 +8030,12 @@
         <v>92.682867505381196</v>
       </c>
       <c r="F74" s="292" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C75" s="304"/>
       <c r="D75" s="303">
@@ -8055,12 +8043,12 @@
         <v>-2572.1582253177344</v>
       </c>
       <c r="F75" s="292" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="300" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C76" s="301"/>
       <c r="D76" s="302">
@@ -8068,7 +8056,7 @@
         <v>5</v>
       </c>
       <c r="F76" s="292" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8076,19 +8064,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C78" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D78" s="211" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F78" s="292"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8102,7 +8090,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8116,7 +8104,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8130,7 +8118,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8144,7 +8132,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8155,15 +8143,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D85" s="278" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="275" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C86" s="192">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8180,7 +8168,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="275" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C87" s="192">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8197,7 +8185,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="276" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C88" s="192">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8214,7 +8202,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C89" s="191">
         <f>SUM(C86:C88)</f>
@@ -8262,7 +8250,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8315,12 +8303,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8338,7 +8326,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8409,7 +8397,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="198">
         <f>C25</f>
@@ -8464,7 +8452,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="188">
         <f>C4+C5</f>
@@ -8519,7 +8507,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="198">
         <f>C35</f>
@@ -8574,7 +8562,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C8" s="199">
         <f>C6+C7</f>
@@ -8631,7 +8619,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="198">
         <f>BS!$G$39*BS!D58</f>
@@ -8686,7 +8674,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10" s="198">
         <f>-C4*C77</f>
@@ -8741,7 +8729,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C11" s="200">
         <f>C62</f>
@@ -8798,7 +8786,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="198">
         <f>C49</f>
@@ -8853,7 +8841,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C13" s="188">
         <f>SUM(C8:C12)</f>
@@ -8908,7 +8896,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="198">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -8963,7 +8951,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C15" s="198">
         <f>-C4*C82</f>
@@ -9020,7 +9008,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" s="201">
         <f>SUM(C13:C15)</f>
@@ -9077,7 +9065,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" s="198">
         <f>-C4*C84</f>
@@ -9085,7 +9073,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="312" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9103,7 +9091,7 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="198">
         <f>-C4*C85</f>
@@ -9111,7 +9099,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="312" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9129,7 +9117,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C19" s="188">
         <f>SUM(C16:C18)</f>
@@ -9205,12 +9193,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9228,7 +9216,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9249,7 +9237,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="204">
         <f>-C4*C28</f>
@@ -9306,7 +9294,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="198">
         <f>-C4*C29</f>
@@ -9363,7 +9351,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C25" s="188">
         <f>C23+C24</f>
@@ -9424,14 +9412,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E27" s="313"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
@@ -9439,7 +9427,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9499,7 +9487,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9550,7 +9538,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9609,21 +9597,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="313"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33" s="205">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
       <c r="E33" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9673,7 +9661,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="205">
         <f>AVERAGE(G34:J34)</f>
@@ -9681,7 +9669,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="311" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -9732,7 +9720,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="188">
         <f>C33+C34</f>
@@ -9793,7 +9781,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E37" s="313"/>
     </row>
@@ -9916,7 +9904,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -9975,21 +9963,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E42" s="313"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C43" s="307">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="310" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10043,12 +10031,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10066,14 +10054,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" s="313"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C47" s="198">
         <f>-BS!G31*Normalized_FCF!C53</f>
@@ -10128,7 +10116,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C48" s="198">
         <f>BS!$C$66*C52</f>
@@ -10183,7 +10171,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C49" s="188">
         <f>C47+C48</f>
@@ -10242,23 +10230,23 @@
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E51" s="313"/>
       <c r="G51" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C52" s="89">
         <v>0.03</v>
       </c>
       <c r="E52" s="310" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10278,14 +10266,14 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="84">
         <f>G53</f>
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E53" s="310" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10305,7 +10293,7 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C54" s="42">
         <f>-C8/C47</f>
@@ -10364,17 +10352,17 @@
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E56" s="313"/>
       <c r="G56" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C57" s="198">
         <f>BS!$C79*C65</f>
@@ -10429,7 +10417,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="198">
         <f>BS!$C68*C66</f>
@@ -10484,7 +10472,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="198">
         <f>BS!$C81*C67</f>
@@ -10539,7 +10527,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C60" s="188">
         <f>SUM(C57:C59)</f>
@@ -10594,13 +10582,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C61" s="308">
         <v>0</v>
       </c>
       <c r="E61" s="311" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -10650,7 +10638,7 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="31" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C62" s="188">
         <f>C60+C61</f>
@@ -10709,17 +10697,17 @@
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E64" s="313"/>
       <c r="G64" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C65" s="181">
         <f>G65</f>
@@ -10744,7 +10732,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C66" s="181">
         <f>G66</f>
@@ -10769,7 +10757,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C67" s="181">
         <f>G67</f>
@@ -10794,7 +10782,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C68" s="72">
         <f>C60/BS!C70</f>
@@ -10824,12 +10812,12 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A70" s="10"/>
       <c r="B70" s="54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C70" s="54"/>
       <c r="D70" s="56"/>
       <c r="E70" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F70" s="56"/>
       <c r="G70" s="37"/>
@@ -10847,7 +10835,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="10"/>
       <c r="B71" s="73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
@@ -10868,7 +10856,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C72" s="79">
         <f>ABS(C5/C$4)</f>
@@ -10925,7 +10913,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="31" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C73" s="80">
         <f>ABS(C6/C$4)</f>
@@ -10982,7 +10970,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11039,7 +11027,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C75" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11096,7 +11084,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C76" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11153,7 +11141,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C77" s="90">
         <f>MAX(AVERAGE(G77:J77),C76)</f>
@@ -11161,7 +11149,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="311" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
@@ -11212,7 +11200,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11269,7 +11257,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C79" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11326,7 +11314,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C80" s="80">
         <f>C13/C4</f>
@@ -11383,7 +11371,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C81" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11498,7 +11486,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="10"/>
       <c r="B83" s="41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C83" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11555,7 +11543,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C84" s="309">
         <v>0</v>
@@ -11581,7 +11569,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C85" s="309">
         <v>0</v>
@@ -11605,7 +11593,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="31" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C86" s="80">
         <f>ABS(C19/C$4)</f>
@@ -11666,7 +11654,7 @@
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E88" s="313"/>
     </row>
@@ -11785,7 +11773,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C91" s="23">
         <f>C89/(C19*$C$3/Common_Shares)</f>
@@ -11840,7 +11828,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
@@ -11899,7 +11887,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
       <c r="B94" s="162" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
@@ -11920,7 +11908,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C95" s="79">
         <f>C4/G4-1</f>
@@ -11977,7 +11965,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="71" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C96" s="79">
         <f>C13/G13-1</f>
@@ -12037,12 +12025,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A98" s="3"/>
       <c r="B98" s="54" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C98" s="54"/>
       <c r="D98" s="56"/>
       <c r="E98" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F98" s="56"/>
       <c r="G98" s="37"/>
@@ -12060,11 +12048,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="10"/>
       <c r="B99" s="65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E99" s="313"/>
       <c r="G99" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12127,7 +12115,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C101" s="207">
         <f>BS!C4</f>
@@ -12184,7 +12172,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" s="207">
         <f>BS!C6+BS!C7</f>
@@ -12241,7 +12229,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C103" s="206">
         <f>BS!G30</f>
@@ -12298,7 +12286,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C104" s="206">
         <f>BS!G27</f>
@@ -12359,14 +12347,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
       <c r="B106" s="93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
       <c r="E106" s="314"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -12382,7 +12370,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C107" s="97">
         <f>C101/C$4</f>
@@ -12439,7 +12427,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12496,7 +12484,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C109" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12527,7 +12515,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
       <c r="B111" s="93" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
@@ -12581,7 +12569,7 @@
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C112" s="23">
         <f>C80</f>
@@ -12635,7 +12623,7 @@
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B113" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C113" s="42">
         <f>C4/C100</f>
@@ -12689,7 +12677,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C114" s="15">
         <f>C100/C104</f>
@@ -12746,7 +12734,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="10"/>
       <c r="B115" s="71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C115" s="105">
         <f>C8/C104</f>
@@ -12822,12 +12810,12 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A117" s="10"/>
       <c r="B117" s="54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C117" s="54"/>
       <c r="D117" s="56"/>
       <c r="E117" s="67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F117" s="56"/>
       <c r="G117" s="37"/>
@@ -12845,7 +12833,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="10"/>
       <c r="B118" s="183" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
@@ -12924,7 +12912,7 @@
     <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="10"/>
       <c r="B120" s="27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13693,32 +13681,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13729,7 +13717,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C71</f>
@@ -13739,7 +13727,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="234" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="235">
         <f>Thesis!C67</f>
@@ -13750,7 +13738,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="239">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13761,14 +13749,14 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="335" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F6" s="335"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C7" s="233">
         <f>BS!G31</f>
@@ -13784,7 +13772,7 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C8" s="208">
         <f>BS!D66</f>
@@ -13800,7 +13788,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="234" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C9" s="236">
         <f>BS!H42</f>
@@ -13816,7 +13804,7 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C10" s="239">
         <f>C6-C7+C8+C9</f>
@@ -13830,7 +13818,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="237" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C11" s="238">
         <f>Exchange_Rate</f>
@@ -13844,7 +13832,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -13861,7 +13849,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -13871,13 +13859,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="166">
         <f>Scenarios!C65</f>
@@ -13887,7 +13875,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="167">
         <f>Scenarios!C64</f>
@@ -13897,7 +13885,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -13914,19 +13902,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>115</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>116</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14592,7 +14580,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14615,7 +14603,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14629,7 +14617,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14800,7 +14788,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15019,19 +15007,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="176" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C73" s="176" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D73" s="176" t="s">
+        <v>117</v>
+      </c>
+      <c r="E73" s="177" t="s">
         <v>118</v>
       </c>
-      <c r="E73" s="177" t="s">
-        <v>119</v>
-      </c>
       <c r="F73" s="177" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15156,20 +15144,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="160" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C80" s="160" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="160" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="160" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15221,20 +15209,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="285" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I2" s="286"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="164" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H3" s="284">
         <v>0</v>
@@ -15246,14 +15234,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="160" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4" s="160"/>
       <c r="H4" s="284">
@@ -15275,14 +15263,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="164" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="284">
@@ -15295,7 +15283,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15320,7 +15308,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15342,7 +15330,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="208">
         <f>Normalized_FCF!C19</f>
@@ -15375,7 +15363,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="164" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E11" s="337"/>
       <c r="F11" s="337"/>
@@ -15389,7 +15377,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="163">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15408,7 +15396,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C13" s="163">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15426,7 +15414,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15437,7 +15425,7 @@
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15446,21 +15434,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E17" s="164" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
       <c r="E18" s="337" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F18" s="338"/>
     </row>
@@ -15470,14 +15458,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E20" s="338"/>
       <c r="F20" s="338"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
@@ -15492,7 +15480,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C22" s="165">
         <f>Valuation_Model!C12</f>
@@ -15507,16 +15495,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E24" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F24" s="164"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C25" s="171">
         <f>C18</f>
@@ -15528,7 +15516,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C26" s="169">
         <v>0</v>
@@ -15539,7 +15527,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27" s="165">
         <f>Valuation_Model!E76</f>
@@ -15554,7 +15542,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C28" s="170">
         <v>0.55000000000000004</v>
@@ -15565,16 +15553,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F30" s="164"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C31" s="171">
         <f>C18</f>
@@ -15586,7 +15574,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C32" s="169">
         <v>-0.05</v>
@@ -15597,7 +15585,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33" s="165">
         <f>Valuation_Model!E77</f>
@@ -15612,7 +15600,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C34" s="170">
         <v>0.2</v>
@@ -15623,16 +15611,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E36" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F36" s="164"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C37" s="171">
         <f>C18</f>
@@ -15644,7 +15632,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C38" s="169">
         <v>0.02</v>
@@ -15655,7 +15643,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C39" s="165">
         <f>Valuation_Model!E75</f>
@@ -15670,7 +15658,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C40" s="172">
         <f>1-C28-C34</f>
@@ -15682,7 +15670,7 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="159">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15695,7 +15683,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15704,12 +15692,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15724,16 +15712,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="164" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E48" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F48" s="164"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C49" s="171">
         <f>C46</f>
@@ -15745,7 +15733,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C50" s="169">
         <v>-0.3</v>
@@ -15756,7 +15744,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="165">
         <f>Valuation_Model!E78</f>
@@ -15771,7 +15759,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="170">
         <v>0.05</v>
@@ -15782,16 +15770,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E54" s="164" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F54" s="164"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C55" s="171">
         <f>C46</f>
@@ -15803,7 +15791,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C56" s="169">
         <v>0.05</v>
@@ -15814,7 +15802,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C57" s="165">
         <f>Valuation_Model!E74</f>
@@ -15829,7 +15817,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C58" s="170">
         <v>0.05</v>
@@ -15840,7 +15828,7 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="159">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -15851,7 +15839,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F60" s="324">
         <v>3</v>
@@ -15859,7 +15847,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -15868,39 +15856,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E63" s="291" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C64" s="171">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="290" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C65" s="155">
         <v>-8.7951517171891095E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="290" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C66" s="165">
         <f>Valuation_Model!C18</f>
@@ -15911,20 +15899,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="290" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E68" s="291" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C69" s="281" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -15934,19 +15922,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C70" s="281" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="290" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C71" s="281" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -15956,7 +15944,7 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C72" s="280" t="str">
         <f>IF(E72&gt;50%,"Y","N")</f>
@@ -15969,7 +15957,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -15978,16 +15966,16 @@
     </row>
     <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B75" s="112" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E75" s="325" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F75" s="323"/>
     </row>
     <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B76" s="283" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C76" s="282">
         <f>F60</f>
@@ -15995,15 +15983,15 @@
       </c>
       <c r="D76" s="138"/>
       <c r="E76" s="326" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F76" s="323" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B77" s="103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C77" s="178">
         <f>Normalized_FCF!C89</f>
@@ -16014,28 +16002,28 @@
         <v>HKD</v>
       </c>
       <c r="E77" s="327" t="s">
+        <v>368</v>
+      </c>
+      <c r="F77" s="323" t="s">
         <v>370</v>
-      </c>
-      <c r="F77" s="323" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E78" s="328" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F78" s="323" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C80" s="172">
         <f>Thesis!C117</f>
@@ -16044,7 +16032,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16056,7 +16044,7 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16066,7 +16054,7 @@
     </row>
     <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16077,7 +16065,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F83" s="270">
         <f>(C83/C60-1)</f>
@@ -16089,12 +16077,12 @@
     </row>
     <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
@@ -16107,7 +16095,7 @@
     </row>
     <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F4A816-B579-4DC6-9DE1-5F9D38450F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE7CEF7-02F1-494C-A79C-17464CB55125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3692,7 +3692,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64557.851494399998</v>
+        <v>64966.445491200007</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17349059186547722</v>
+        <v>0.17086981192202799</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>5.401287075648549E-2</v>
+        <v>5.3673167166822057E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>7.3417721518987331E-2</v>
+        <v>7.2955974842767293E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -11832,20 +11832,20 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>7.3417721518987331E-2</v>
+        <v>7.2955974842767293E-2</v>
       </c>
       <c r="E92" s="313"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>7.3417721518987331E-2</v>
+        <v>7.2955974842767293E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
-        <v>7.3417721518987331E-2</v>
+        <v>7.2955974842767293E-2</v>
       </c>
       <c r="I92" s="23">
         <f t="shared" si="38"/>
-        <v>7.2151898734177211E-2</v>
+        <v>7.1698113207547168E-2</v>
       </c>
       <c r="J92" s="23">
         <f t="shared" si="38"/>
@@ -12916,30 +12916,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.401287075648549E-2</v>
+        <v>5.3673167166822057E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="310"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>7.5048965971556136E-2</v>
+        <v>7.4576959896263326E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>8.8838692401302988E-2</v>
+        <v>8.8279958486829388E-2</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>9.9448332439578013E-2</v>
+        <v>9.8822871229266196E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>0.16355862576863991</v>
+        <v>0.16252995516632143</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>5.3440440165504366E-2</v>
+        <v>5.3104336768237045E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-7.9</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>7.9</v>
+        <v>7.95</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16099,7 +16099,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17349059186547722</v>
+        <v>0.17086981192202799</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE7CEF7-02F1-494C-A79C-17464CB55125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC22CBB-2F66-42A2-B272-DCC21BB03826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3692,7 +3692,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>7.95</v>
+        <v>7.91</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64966.445491200007</v>
+        <v>64639.57029376</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17086981192202799</v>
+        <v>0.17296459645475393</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>5.3673167166822057E-2</v>
+        <v>5.3944586469814836E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>7.2955974842767293E-2</v>
+        <v>7.332490518331225E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -11832,20 +11832,20 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>7.2955974842767293E-2</v>
+        <v>7.332490518331225E-2</v>
       </c>
       <c r="E92" s="313"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>7.2955974842767293E-2</v>
+        <v>7.332490518331225E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
-        <v>7.2955974842767293E-2</v>
+        <v>7.332490518331225E-2</v>
       </c>
       <c r="I92" s="23">
         <f t="shared" si="38"/>
-        <v>7.1698113207547168E-2</v>
+        <v>7.20606826801517E-2</v>
       </c>
       <c r="J92" s="23">
         <f t="shared" si="38"/>
@@ -12916,30 +12916,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.3673167166822057E-2</v>
+        <v>5.3944586469814836E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="310"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>7.4576959896263326E-2</v>
+        <v>7.495408737993596E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>8.8279958486829388E-2</v>
+        <v>8.8726380527217902E-2</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>9.8822871229266196E-2</v>
+        <v>9.9322607619806103E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>0.16252995516632143</v>
+        <v>0.16335185127335719</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>5.3104336768237045E-2</v>
+        <v>5.3372879558468332E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-7.95</v>
+        <v>-7.91</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15469,7 +15469,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>7.95</v>
+        <v>7.91</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>7.95</v>
+        <v>7.91</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16099,7 +16099,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17086981192202799</v>
+        <v>0.17296459645475393</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC22CBB-2F66-42A2-B272-DCC21BB03826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39E0BA4-0773-4E05-A7BE-18515030294E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1986,7 +1986,7 @@
     <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="192" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2410,13 +2410,7 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <i/>
       <u/>
       <sz val="10"/>
@@ -2632,7 +2626,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3234,9 +3228,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3304,21 +3295,27 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="5"/>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3645,10 +3642,10 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="293" t="s">
+      <c r="E1" s="292" t="s">
         <v>354</v>
       </c>
-      <c r="F1" s="294" t="s">
+      <c r="F1" s="293" t="s">
         <v>356</v>
       </c>
     </row>
@@ -3747,13 +3744,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="329" t="s">
+      <c r="B12" s="332" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="329"/>
-      <c r="D12" s="329"/>
-      <c r="E12" s="329"/>
-      <c r="F12" s="329"/>
+      <c r="C12" s="332"/>
+      <c r="D12" s="332"/>
+      <c r="E12" s="332"/>
+      <c r="F12" s="332"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3819,15 +3816,15 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
-        <f>C123</f>
-        <v>7.4179368510878518</v>
+        <f ca="1">C123</f>
+        <v>7.3815066170863481</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="E20" s="289">
-        <f>Scenarios!C76</f>
-        <v>3</v>
+      <c r="E20" s="323">
+        <f ca="1">Scenarios!C76</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3836,7 +3833,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17296459645475393</v>
+        <v>0.17091086618081319</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3856,22 +3853,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="329" t="s">
+      <c r="B25" s="332" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="329"/>
-      <c r="D25" s="329"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="329"/>
+      <c r="C25" s="332"/>
+      <c r="D25" s="332"/>
+      <c r="E25" s="332"/>
+      <c r="F25" s="332"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="333" t="s">
+      <c r="B26" s="336" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="333"/>
-      <c r="D26" s="333"/>
-      <c r="E26" s="333"/>
-      <c r="F26" s="333"/>
+      <c r="C26" s="336"/>
+      <c r="D26" s="336"/>
+      <c r="E26" s="336"/>
+      <c r="F26" s="336"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3883,13 +3880,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="331" t="s">
+      <c r="B29" s="334" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="331"/>
-      <c r="D29" s="331"/>
-      <c r="E29" s="331"/>
-      <c r="F29" s="331"/>
+      <c r="C29" s="334"/>
+      <c r="D29" s="334"/>
+      <c r="E29" s="334"/>
+      <c r="F29" s="334"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3909,13 +3906,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="331" t="s">
+      <c r="B32" s="334" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="331"/>
-      <c r="D32" s="331"/>
-      <c r="E32" s="331"/>
-      <c r="F32" s="331"/>
+      <c r="C32" s="334"/>
+      <c r="D32" s="334"/>
+      <c r="E32" s="334"/>
+      <c r="F32" s="334"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3944,13 +3941,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="331" t="s">
+      <c r="B36" s="334" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="331"/>
-      <c r="D36" s="331"/>
-      <c r="E36" s="331"/>
-      <c r="F36" s="331"/>
+      <c r="C36" s="334"/>
+      <c r="D36" s="334"/>
+      <c r="E36" s="334"/>
+      <c r="F36" s="334"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3966,13 +3963,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="331" t="s">
+      <c r="B39" s="334" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
+      <c r="C39" s="334"/>
+      <c r="D39" s="334"/>
+      <c r="E39" s="334"/>
+      <c r="F39" s="334"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4006,13 +4003,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="331" t="s">
+      <c r="B45" s="334" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="331"/>
-      <c r="D45" s="331"/>
-      <c r="E45" s="331"/>
-      <c r="F45" s="331"/>
+      <c r="C45" s="334"/>
+      <c r="D45" s="334"/>
+      <c r="E45" s="334"/>
+      <c r="F45" s="334"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4028,13 +4025,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="331" t="s">
+      <c r="B48" s="334" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="332"/>
-      <c r="D48" s="332"/>
-      <c r="E48" s="332"/>
-      <c r="F48" s="332"/>
+      <c r="C48" s="335"/>
+      <c r="D48" s="335"/>
+      <c r="E48" s="335"/>
+      <c r="F48" s="335"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4063,13 +4060,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="329" t="s">
+      <c r="B52" s="332" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="329"/>
-      <c r="D52" s="329"/>
-      <c r="E52" s="329"/>
-      <c r="F52" s="329"/>
+      <c r="C52" s="332"/>
+      <c r="D52" s="332"/>
+      <c r="E52" s="332"/>
+      <c r="F52" s="332"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4130,22 +4127,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="331" t="s">
+      <c r="B60" s="334" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="331"/>
-      <c r="D60" s="331"/>
-      <c r="E60" s="331"/>
-      <c r="F60" s="331"/>
+      <c r="C60" s="334"/>
+      <c r="D60" s="334"/>
+      <c r="E60" s="334"/>
+      <c r="F60" s="334"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="333" t="s">
+      <c r="B61" s="336" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="333"/>
-      <c r="D61" s="333"/>
-      <c r="E61" s="333"/>
-      <c r="F61" s="333"/>
+      <c r="C61" s="336"/>
+      <c r="D61" s="336"/>
+      <c r="E61" s="336"/>
+      <c r="F61" s="336"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4156,7 +4153,7 @@
       <c r="B64" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C64" s="322">
+      <c r="C64" s="321">
         <v>0.08</v>
       </c>
     </row>
@@ -4168,7 +4165,7 @@
         <f>IF(D65="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D65" s="296" t="s">
+      <c r="D65" s="295" t="s">
         <v>311</v>
       </c>
     </row>
@@ -4180,7 +4177,7 @@
         <f>IF(D66="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D66" s="296" t="s">
+      <c r="D66" s="295" t="s">
         <v>362</v>
       </c>
     </row>
@@ -4197,22 +4194,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="329" t="s">
+      <c r="B69" s="332" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="329"/>
-      <c r="D69" s="329"/>
-      <c r="E69" s="329"/>
-      <c r="F69" s="329"/>
+      <c r="C69" s="332"/>
+      <c r="D69" s="332"/>
+      <c r="E69" s="332"/>
+      <c r="F69" s="332"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="329" t="s">
+      <c r="B70" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="329"/>
-      <c r="D70" s="329"/>
-      <c r="E70" s="329"/>
-      <c r="F70" s="329"/>
+      <c r="C70" s="332"/>
+      <c r="D70" s="332"/>
+      <c r="E70" s="332"/>
+      <c r="F70" s="332"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4249,13 +4246,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="329" t="s">
+      <c r="B77" s="332" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="329"/>
-      <c r="D77" s="329"/>
-      <c r="E77" s="329"/>
-      <c r="F77" s="329"/>
+      <c r="C77" s="332"/>
+      <c r="D77" s="332"/>
+      <c r="E77" s="332"/>
+      <c r="F77" s="332"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4369,13 +4366,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="329" t="s">
+      <c r="B93" s="332" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="329"/>
-      <c r="D93" s="329"/>
-      <c r="E93" s="329"/>
-      <c r="F93" s="329"/>
+      <c r="C93" s="332"/>
+      <c r="D93" s="332"/>
+      <c r="E93" s="332"/>
+      <c r="F93" s="332"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4401,13 +4398,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="334" t="s">
         <v>374</v>
       </c>
-      <c r="C99" s="331"/>
-      <c r="D99" s="331"/>
-      <c r="E99" s="331"/>
-      <c r="F99" s="331"/>
+      <c r="C99" s="334"/>
+      <c r="D99" s="334"/>
+      <c r="E99" s="334"/>
+      <c r="F99" s="334"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4550,13 +4547,13 @@
       </c>
     </row>
     <row r="110" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B110" s="334" t="s">
+      <c r="B110" s="337" t="s">
         <v>375</v>
       </c>
-      <c r="C110" s="334"/>
-      <c r="D110" s="334"/>
-      <c r="E110" s="334"/>
-      <c r="F110" s="334"/>
+      <c r="C110" s="337"/>
+      <c r="D110" s="337"/>
+      <c r="E110" s="337"/>
+      <c r="F110" s="337"/>
     </row>
     <row r="112" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A112" s="254" t="s">
@@ -4569,13 +4566,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="330" t="s">
+      <c r="B114" s="333" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="330"/>
-      <c r="D114" s="330"/>
-      <c r="E114" s="330"/>
-      <c r="F114" s="330"/>
+      <c r="C114" s="333"/>
+      <c r="D114" s="333"/>
+      <c r="E114" s="333"/>
+      <c r="F114" s="333"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4587,7 +4584,7 @@
         <v>280</v>
       </c>
       <c r="C116" s="258">
-        <f>E20</f>
+        <f ca="1">E20</f>
         <v>3</v>
       </c>
     </row>
@@ -4620,22 +4617,22 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B121" s="243" t="str">
-        <f>"PV("&amp;C116&amp;" yrs of Dividends)"</f>
+        <f ca="1">"PV("&amp;C116&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C121" s="247">
-        <f>Scenarios!C81</f>
+        <f ca="1">Scenarios!C81</f>
         <v>1.2217592592592592</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B122" s="243" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
+        <f ca="1">"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C122" s="247">
-        <f>Scenarios!C82</f>
-        <v>6.1961775918285928</v>
+        <f ca="1">Scenarios!C82</f>
+        <v>6.1597473578270892</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4643,8 +4640,8 @@
         <v>275</v>
       </c>
       <c r="C123" s="246">
-        <f>Scenarios!C83</f>
-        <v>7.4179368510878518</v>
+        <f ca="1">Scenarios!C83</f>
+        <v>7.3815066170863481</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4656,8 +4653,8 @@
         <v>277</v>
       </c>
       <c r="C124" s="158">
-        <f>Scenarios!F83</f>
-        <v>-0.30718778376753109</v>
+        <f ca="1">Scenarios!F83</f>
+        <v>-0.30651291845707263</v>
       </c>
     </row>
   </sheetData>
@@ -7030,7 +7027,7 @@
       <c r="C4" s="19">
         <v>8029</v>
       </c>
-      <c r="D4" s="305">
+      <c r="D4" s="304">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7040,7 +7037,7 @@
       <c r="G4" s="19">
         <v>45665</v>
       </c>
-      <c r="H4" s="305">
+      <c r="H4" s="304">
         <v>0.9</v>
       </c>
     </row>
@@ -7051,7 +7048,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="305">
+      <c r="D5" s="304">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7061,7 +7058,7 @@
       <c r="G5" s="19">
         <v>2014</v>
       </c>
-      <c r="H5" s="305">
+      <c r="H5" s="304">
         <v>0.7</v>
       </c>
     </row>
@@ -7072,7 +7069,7 @@
       <c r="C6" s="19">
         <v>9844</v>
       </c>
-      <c r="D6" s="305">
+      <c r="D6" s="304">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7082,7 +7079,7 @@
       <c r="G6" s="19">
         <v>156</v>
       </c>
-      <c r="H6" s="305">
+      <c r="H6" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7093,7 +7090,7 @@
       <c r="C7" s="19">
         <v>5466</v>
       </c>
-      <c r="D7" s="305">
+      <c r="D7" s="304">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7103,7 +7100,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="305">
+      <c r="H7" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7114,7 +7111,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="305">
+      <c r="D8" s="304">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7124,7 +7121,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="305">
+      <c r="H8" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7135,7 +7132,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="305">
+      <c r="D9" s="304">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7145,7 +7142,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="305">
+      <c r="H9" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7156,10 +7153,10 @@
       <c r="C10" s="19">
         <v>10</v>
       </c>
-      <c r="D10" s="305">
+      <c r="D10" s="304">
         <v>0.9</v>
       </c>
-      <c r="H10" s="306"/>
+      <c r="H10" s="305"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7168,10 +7165,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="305">
+      <c r="D11" s="304">
         <v>0.05</v>
       </c>
-      <c r="H11" s="306"/>
+      <c r="H11" s="305"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7229,7 +7226,7 @@
       <c r="C15" s="19">
         <v>2757</v>
       </c>
-      <c r="D15" s="305">
+      <c r="D15" s="304">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7238,7 +7235,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="305">
+      <c r="H15" s="304">
         <v>0.8</v>
       </c>
     </row>
@@ -7249,7 +7246,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="305">
+      <c r="D16" s="304">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7258,7 +7255,7 @@
       <c r="G16" s="19">
         <v>1373</v>
       </c>
-      <c r="H16" s="305">
+      <c r="H16" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7269,7 +7266,7 @@
       <c r="C17" s="19">
         <v>67668</v>
       </c>
-      <c r="D17" s="305">
+      <c r="D17" s="304">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7278,7 +7275,7 @@
       <c r="G17" s="19">
         <v>13024</v>
       </c>
-      <c r="H17" s="305">
+      <c r="H17" s="304">
         <v>0.6</v>
       </c>
     </row>
@@ -7289,7 +7286,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="305">
+      <c r="D18" s="304">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7298,7 +7295,7 @@
       <c r="G18" s="19">
         <v>23696</v>
       </c>
-      <c r="H18" s="305">
+      <c r="H18" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7309,7 +7306,7 @@
       <c r="C19" s="19">
         <v>1284</v>
       </c>
-      <c r="D19" s="305">
+      <c r="D19" s="304">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7318,7 +7315,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="305">
+      <c r="H19" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7329,7 +7326,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="305">
+      <c r="D20" s="304">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7338,7 +7335,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="305">
+      <c r="H20" s="304">
         <v>0.2</v>
       </c>
     </row>
@@ -7349,7 +7346,7 @@
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="305">
+      <c r="D21" s="304">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7358,7 +7355,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="305">
+      <c r="H21" s="304">
         <v>0.1</v>
       </c>
     </row>
@@ -7369,10 +7366,10 @@
       <c r="C22" s="19">
         <v>10</v>
       </c>
-      <c r="D22" s="305">
+      <c r="D22" s="304">
         <v>0.9</v>
       </c>
-      <c r="H22" s="306"/>
+      <c r="H22" s="305"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7381,10 +7378,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="305">
-        <v>0</v>
-      </c>
-      <c r="H23" s="306"/>
+      <c r="D23" s="304">
+        <v>0</v>
+      </c>
+      <c r="H23" s="305"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7723,7 +7720,7 @@
       <c r="D45" s="210" t="s">
         <v>292</v>
       </c>
-      <c r="F45" s="297" t="s">
+      <c r="F45" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7739,7 +7736,7 @@
         <f>H29</f>
         <v>94070.7</v>
       </c>
-      <c r="F46" s="292"/>
+      <c r="F46" s="291"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7754,10 +7751,10 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>11.511512740854835</v>
       </c>
-      <c r="F47" s="292"/>
+      <c r="F47" s="291"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="292"/>
+      <c r="F48" s="291"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="162" t="s">
@@ -7770,7 +7767,7 @@
         <v>100</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="292"/>
+      <c r="F49" s="291"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7784,7 +7781,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.3234916559691912</v>
       </c>
-      <c r="F50" s="292"/>
+      <c r="F50" s="291"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
@@ -7795,10 +7792,10 @@
         <f>G29/G32</f>
         <v>0.92039603085151056</v>
       </c>
-      <c r="F51" s="292"/>
+      <c r="F51" s="291"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="292"/>
+      <c r="F52" s="291"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="162" t="s">
@@ -7810,7 +7807,7 @@
       <c r="D53" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F53" s="292"/>
+      <c r="F53" s="291"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7824,7 +7821,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>2.4582404173854506E-2</v>
       </c>
-      <c r="F54" s="292"/>
+      <c r="F54" s="291"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7838,10 +7835,10 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>7.4364584303137507E-3</v>
       </c>
-      <c r="F55" s="292"/>
+      <c r="F55" s="291"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="292"/>
+      <c r="F56" s="291"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="162" t="s">
@@ -7853,7 +7850,7 @@
       <c r="D57" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="292"/>
+      <c r="F57" s="291"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7875,10 +7872,10 @@
         <f>G39/G32</f>
         <v>0.41115825764105285</v>
       </c>
-      <c r="F59" s="292"/>
+      <c r="F59" s="291"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="292"/>
+      <c r="F60" s="291"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="162" t="s">
@@ -7890,7 +7887,7 @@
       <c r="D61" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="F61" s="292"/>
+      <c r="F61" s="291"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7904,7 +7901,7 @@
         <f>G28/G29</f>
         <v>3.1154705020769802E-3</v>
       </c>
-      <c r="F62" s="292" t="s">
+      <c r="F62" s="291" t="s">
         <v>293</v>
       </c>
     </row>
@@ -7929,7 +7926,7 @@
       <c r="D65" s="211" t="s">
         <v>318</v>
       </c>
-      <c r="F65" s="297" t="s">
+      <c r="F65" s="296" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7957,7 +7954,7 @@
         <f>G6+G16</f>
         <v>1529</v>
       </c>
-      <c r="F67" s="292"/>
+      <c r="F67" s="291"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -7967,7 +7964,7 @@
         <f>G18</f>
         <v>23696</v>
       </c>
-      <c r="F68" s="292"/>
+      <c r="F68" s="291"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -7977,7 +7974,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="292"/>
+      <c r="F69" s="291"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -7987,13 +7984,13 @@
         <f>SUM(C66:C69)</f>
         <v>72904</v>
       </c>
-      <c r="F70" s="292"/>
+      <c r="F70" s="291"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="292"/>
+      <c r="F71" s="291"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="295" t="s">
+      <c r="B72" s="294" t="s">
         <v>359</v>
       </c>
       <c r="C72" s="268" t="s">
@@ -8002,7 +7999,7 @@
       <c r="D72" s="210" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="292"/>
+      <c r="F72" s="291"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
@@ -8018,18 +8015,18 @@
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="298" t="s">
+      <c r="B74" s="297" t="s">
         <v>364</v>
       </c>
-      <c r="C74" s="299">
+      <c r="C74" s="298">
         <f>-$C$66/C73</f>
         <v>89.008711885500944</v>
       </c>
-      <c r="D74" s="299">
+      <c r="D74" s="298">
         <f>-$C$66/D73</f>
         <v>92.682867505381196</v>
       </c>
-      <c r="F74" s="292" t="s">
+      <c r="F74" s="291" t="s">
         <v>360</v>
       </c>
     </row>
@@ -8037,30 +8034,30 @@
       <c r="B75" s="82" t="s">
         <v>361</v>
       </c>
-      <c r="C75" s="304"/>
-      <c r="D75" s="303">
+      <c r="C75" s="303"/>
+      <c r="D75" s="302">
         <f>MIN(D73*D76,-G5)</f>
         <v>-2572.1582253177344</v>
       </c>
-      <c r="F75" s="292" t="s">
+      <c r="F75" s="291" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="300" t="s">
+      <c r="B76" s="299" t="s">
         <v>365</v>
       </c>
-      <c r="C76" s="301"/>
-      <c r="D76" s="302">
+      <c r="C76" s="300"/>
+      <c r="D76" s="301">
         <f>IF(D74&lt;=3,1,IF(D74&gt;10,5,2))</f>
         <v>5</v>
       </c>
-      <c r="F76" s="292" t="s">
+      <c r="F76" s="291" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="292"/>
+      <c r="F77" s="291"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
@@ -8072,7 +8069,7 @@
       <c r="D78" s="211" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="292"/>
+      <c r="F78" s="291"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8086,7 +8083,7 @@
         <f>G7*H7+G17*H17</f>
         <v>7814.4</v>
       </c>
-      <c r="F79" s="292"/>
+      <c r="F79" s="291"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8100,7 +8097,7 @@
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="292"/>
+      <c r="F80" s="291"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8114,7 +8111,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="292"/>
+      <c r="F81" s="291"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8128,7 +8125,7 @@
         <f>SUM(D79:D81)</f>
         <v>7814.4</v>
       </c>
-      <c r="F82" s="292"/>
+      <c r="F82" s="291"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8333,7 +8330,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="313"/>
+      <c r="E3" s="312"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8347,7 +8344,7 @@
         <v>8765</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="311"/>
+      <c r="E4" s="310"/>
       <c r="F4" s="57"/>
       <c r="G4" s="187">
         <f>Data!C36</f>
@@ -8403,7 +8400,7 @@
         <f>C25</f>
         <v>-5066.6797407625618</v>
       </c>
-      <c r="E5" s="313"/>
+      <c r="E5" s="312"/>
       <c r="G5" s="187">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5344</v>
@@ -8458,7 +8455,7 @@
         <f>C4+C5</f>
         <v>3698.3202592374382</v>
       </c>
-      <c r="E6" s="313"/>
+      <c r="E6" s="312"/>
       <c r="G6" s="188">
         <f>IF(G4="","",G4+G5)</f>
         <v>3421</v>
@@ -8513,7 +8510,7 @@
         <f>C35</f>
         <v>-1106.5</v>
       </c>
-      <c r="E7" s="313"/>
+      <c r="E7" s="312"/>
       <c r="G7" s="198">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1084</v>
@@ -8569,7 +8566,7 @@
         <v>2591.8202592374382</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="319"/>
+      <c r="E8" s="318"/>
       <c r="F8" s="60"/>
       <c r="G8" s="188">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8625,7 +8622,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>159.99999999999997</v>
       </c>
-      <c r="E9" s="313"/>
+      <c r="E9" s="312"/>
       <c r="G9" s="198">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>160</v>
@@ -8680,7 +8677,7 @@
         <f>-C4*C77</f>
         <v>-159.99999999999997</v>
       </c>
-      <c r="E10" s="313"/>
+      <c r="E10" s="312"/>
       <c r="G10" s="198">
         <f>Data!C62</f>
         <v>-69</v>
@@ -8736,7 +8733,7 @@
         <v>639</v>
       </c>
       <c r="D11" s="173"/>
-      <c r="E11" s="312"/>
+      <c r="E11" s="311"/>
       <c r="F11" s="173"/>
       <c r="G11" s="190">
         <f>G60</f>
@@ -8792,7 +8789,7 @@
         <f>C49</f>
         <v>1387.37</v>
       </c>
-      <c r="E12" s="313"/>
+      <c r="E12" s="312"/>
       <c r="G12" s="198">
         <f t="shared" ref="G12:Q12" si="6">G49</f>
         <v>2297</v>
@@ -8847,7 +8844,7 @@
         <f>SUM(C8:C12)</f>
         <v>4618.1902592374381</v>
       </c>
-      <c r="E13" s="313"/>
+      <c r="E13" s="312"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>5364</v>
@@ -8902,7 +8899,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-1108.3656622169851</v>
       </c>
-      <c r="E14" s="313"/>
+      <c r="E14" s="312"/>
       <c r="G14" s="198">
         <f>Data!C46</f>
         <v>-519</v>
@@ -8958,7 +8955,7 @@
         <v>-22.869707937042335</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="320"/>
+      <c r="E15" s="319"/>
       <c r="F15" s="61"/>
       <c r="G15" s="187">
         <f>Data!C48</f>
@@ -9015,7 +9012,7 @@
         <v>3486.9548890834108</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="321"/>
+      <c r="E16" s="320"/>
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -9072,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="312" t="s">
+      <c r="E17" s="311" t="s">
         <v>378</v>
       </c>
       <c r="F17" s="59"/>
@@ -9098,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="312" t="s">
+      <c r="E18" s="311" t="s">
         <v>379</v>
       </c>
       <c r="F18" s="59"/>
@@ -9124,7 +9121,7 @@
         <v>3486.9548890834108</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="310"/>
+      <c r="E19" s="309"/>
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f t="shared" ref="G19:Q19" si="9">IF(G$4="","",SUM(G16:G18))</f>
@@ -9220,7 +9217,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="310"/>
+      <c r="E22" s="309"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9244,7 +9241,7 @@
         <v>-5066.6797407625618</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="312"/>
+      <c r="E23" s="311"/>
       <c r="F23" s="59"/>
       <c r="G23" s="187">
         <f>Data!C37</f>
@@ -9301,7 +9298,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="310"/>
+      <c r="E24" s="309"/>
       <c r="F24" s="27"/>
       <c r="G24" s="187">
         <f>Data!C40</f>
@@ -9358,7 +9355,7 @@
         <v>-5066.6797407625618</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="318"/>
+      <c r="E25" s="317"/>
       <c r="F25" s="9"/>
       <c r="G25" s="188">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9407,14 +9404,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="313"/>
+      <c r="E26" s="312"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="313"/>
+      <c r="E27" s="312"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9426,7 +9423,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="311" t="s">
+      <c r="E28" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F28" s="26"/>
@@ -9486,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="311" t="s">
+      <c r="E29" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F29" s="26"/>
@@ -9544,7 +9541,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.57805815639048053</v>
       </c>
-      <c r="E30" s="313"/>
+      <c r="E30" s="312"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.60969766115231028</v>
@@ -9592,14 +9589,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="313"/>
+      <c r="E31" s="312"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="313"/>
+      <c r="E32" s="312"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
@@ -9610,7 +9607,7 @@
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
-      <c r="E33" s="311" t="s">
+      <c r="E33" s="310" t="s">
         <v>380</v>
       </c>
       <c r="G33" s="198">
@@ -9668,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="311" t="s">
+      <c r="E34" s="310" t="s">
         <v>380</v>
       </c>
       <c r="F34" s="59"/>
@@ -9727,7 +9724,7 @@
         <v>-1106.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="312"/>
+      <c r="E35" s="311"/>
       <c r="F35" s="59"/>
       <c r="G35" s="188">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9776,14 +9773,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="313"/>
+      <c r="E36" s="312"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="313"/>
+      <c r="E37" s="312"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9796,7 +9793,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="310"/>
+      <c r="E38" s="309"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9854,7 +9851,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="310"/>
+      <c r="E39" s="309"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9910,7 +9907,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.1262407301768397</v>
       </c>
-      <c r="E40" s="313"/>
+      <c r="E40" s="312"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12367370222475756</v>
@@ -9958,25 +9955,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="313"/>
+      <c r="E41" s="312"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="313"/>
+      <c r="E42" s="312"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="307">
+      <c r="C43" s="306">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="310" t="s">
+      <c r="E43" s="309" t="s">
         <v>381</v>
       </c>
       <c r="F43" s="27"/>
@@ -10056,7 +10053,7 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="313"/>
+      <c r="E46" s="312"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
@@ -10067,7 +10064,7 @@
         <f>-BS!G31*Normalized_FCF!C53</f>
         <v>-43</v>
       </c>
-      <c r="E47" s="313"/>
+      <c r="E47" s="312"/>
       <c r="G47" s="198">
         <f>Data!C51</f>
         <v>-43</v>
@@ -10122,7 +10119,7 @@
         <f>BS!$C$66*C52</f>
         <v>1430.37</v>
       </c>
-      <c r="E48" s="313"/>
+      <c r="E48" s="312"/>
       <c r="G48" s="198">
         <f>Data!C52</f>
         <v>2340</v>
@@ -10177,7 +10174,7 @@
         <f>C47+C48</f>
         <v>1387.37</v>
       </c>
-      <c r="E49" s="313"/>
+      <c r="E49" s="312"/>
       <c r="G49" s="188">
         <f t="shared" ref="G49:Q49" si="19">IF(G4="","",G47+G48)</f>
         <v>2297</v>
@@ -10225,14 +10222,14 @@
     </row>
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
-      <c r="E50" s="313"/>
+      <c r="E50" s="312"/>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
       <c r="B51" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="313"/>
+      <c r="E51" s="312"/>
       <c r="G51" s="100" t="s">
         <v>224</v>
       </c>
@@ -10245,7 +10242,7 @@
       <c r="C52" s="89">
         <v>0.03</v>
       </c>
-      <c r="E52" s="310" t="s">
+      <c r="E52" s="309" t="s">
         <v>382</v>
       </c>
       <c r="G52" s="6">
@@ -10272,7 +10269,7 @@
         <f>G53</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="E53" s="310" t="s">
+      <c r="E53" s="309" t="s">
         <v>383</v>
       </c>
       <c r="G53" s="23">
@@ -10299,7 +10296,7 @@
         <f>-C8/C47</f>
         <v>60.274889749707867</v>
       </c>
-      <c r="E54" s="313"/>
+      <c r="E54" s="312"/>
       <c r="G54" s="42">
         <f>IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
@@ -10347,14 +10344,14 @@
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
-      <c r="E55" s="313"/>
+      <c r="E55" s="312"/>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
       <c r="B56" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E56" s="313"/>
+      <c r="E56" s="312"/>
       <c r="G56" s="100" t="s">
         <v>224</v>
       </c>
@@ -10368,7 +10365,7 @@
         <f>BS!$C79*C65</f>
         <v>0</v>
       </c>
-      <c r="E57" s="313"/>
+      <c r="E57" s="312"/>
       <c r="G57" s="198">
         <f>Data!C56</f>
         <v>0</v>
@@ -10423,7 +10420,7 @@
         <f>BS!$C68*C66</f>
         <v>639</v>
       </c>
-      <c r="E58" s="313"/>
+      <c r="E58" s="312"/>
       <c r="G58" s="198">
         <f>Data!C55</f>
         <v>639</v>
@@ -10478,7 +10475,7 @@
         <f>BS!$C81*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="313"/>
+      <c r="E59" s="312"/>
       <c r="G59" s="198">
         <f>Data!C57</f>
         <v>0</v>
@@ -10533,7 +10530,7 @@
         <f>SUM(C57:C59)</f>
         <v>639</v>
       </c>
-      <c r="E60" s="313"/>
+      <c r="E60" s="312"/>
       <c r="G60" s="188">
         <f t="shared" ref="G60:Q60" si="21">IF(G4="","",SUM(G57:G59))</f>
         <v>639</v>
@@ -10584,10 +10581,10 @@
       <c r="B61" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="308">
-        <v>0</v>
-      </c>
-      <c r="E61" s="311" t="s">
+      <c r="C61" s="307">
+        <v>0</v>
+      </c>
+      <c r="E61" s="310" t="s">
         <v>384</v>
       </c>
       <c r="G61" s="198">
@@ -10644,7 +10641,7 @@
         <f>C60+C61</f>
         <v>639</v>
       </c>
-      <c r="E62" s="313"/>
+      <c r="E62" s="312"/>
       <c r="G62" s="188">
         <f t="shared" ref="G62:Q62" si="22">IF(G4="","",G60+G61)</f>
         <v>136</v>
@@ -10692,14 +10689,14 @@
     </row>
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
-      <c r="E63" s="313"/>
+      <c r="E63" s="312"/>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
       <c r="B64" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="E64" s="313"/>
+      <c r="E64" s="312"/>
       <c r="G64" s="100" t="s">
         <v>224</v>
       </c>
@@ -10713,7 +10710,7 @@
         <f>G65</f>
         <v>0</v>
       </c>
-      <c r="E65" s="313"/>
+      <c r="E65" s="312"/>
       <c r="G65" s="23">
         <f>IFERROR(G57/BS!$C$67,0)</f>
         <v>0</v>
@@ -10738,7 +10735,7 @@
         <f>G66</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="E66" s="313"/>
+      <c r="E66" s="312"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$68,0)</f>
         <v>2.6966576637407157E-2</v>
@@ -10763,7 +10760,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="313"/>
+      <c r="E67" s="312"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$81,0)</f>
         <v>0</v>
@@ -10789,7 +10786,7 @@
         <v>8.7649511686601553E-3</v>
       </c>
       <c r="D68" s="9"/>
-      <c r="E68" s="318"/>
+      <c r="E68" s="317"/>
       <c r="F68" s="9"/>
       <c r="G68" s="72">
         <f>G60/BS!C70</f>
@@ -10839,7 +10836,7 @@
       </c>
       <c r="C71" s="63"/>
       <c r="D71" s="27"/>
-      <c r="E71" s="310"/>
+      <c r="E71" s="309"/>
       <c r="F71" s="27"/>
       <c r="G71" s="100"/>
       <c r="H71" s="12"/>
@@ -10863,7 +10860,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D72" s="27"/>
-      <c r="E72" s="310"/>
+      <c r="E72" s="309"/>
       <c r="F72" s="27"/>
       <c r="G72" s="6">
         <f t="shared" ref="G72:Q72" si="23">IF(G$4="","",ABS(G5/G$4))</f>
@@ -10920,7 +10917,7 @@
         <v>0.42194184360951947</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="310"/>
+      <c r="E73" s="309"/>
       <c r="F73" s="27"/>
       <c r="G73" s="66">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G6/G$4))</f>
@@ -10977,7 +10974,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="310"/>
+      <c r="E74" s="309"/>
       <c r="F74" s="27"/>
       <c r="G74" s="6">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11034,7 +11031,7 @@
         <v>0.2957011134326798</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="310"/>
+      <c r="E75" s="309"/>
       <c r="F75" s="27"/>
       <c r="G75" s="66">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11091,7 +11088,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="310"/>
+      <c r="E76" s="309"/>
       <c r="F76" s="27"/>
       <c r="G76" s="6">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",G9/G$4)</f>
@@ -11148,7 +11145,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="311" t="s">
+      <c r="E77" s="310" t="s">
         <v>385</v>
       </c>
       <c r="F77" s="27"/>
@@ -11207,7 +11204,7 @@
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="310"/>
+      <c r="E78" s="309"/>
       <c r="F78" s="27"/>
       <c r="G78" s="66">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",G11/G$4)</f>
@@ -11264,7 +11261,7 @@
         <v>0.15828522532800912</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="310"/>
+      <c r="E79" s="309"/>
       <c r="F79" s="27"/>
       <c r="G79" s="6">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11321,7 +11318,7 @@
         <v>0.52688993259982175</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="310"/>
+      <c r="E80" s="309"/>
       <c r="F80" s="27"/>
       <c r="G80" s="66">
         <f>IF(G$4="","",G13/G$4)</f>
@@ -11378,7 +11375,7 @@
         <v>0.12645358382395724</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="310"/>
+      <c r="E81" s="309"/>
       <c r="F81" s="27"/>
       <c r="G81" s="6">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11431,12 +11428,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C82" s="309">
+      <c r="C82" s="308">
         <f>MIN(BS!C62,MAX(G82:K82))</f>
         <v>2.6092079791263361E-3</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="310"/>
+      <c r="E82" s="309"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",-G15/G$4)</f>
@@ -11493,7 +11490,7 @@
         <v>0.39782714079673825</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="310"/>
+      <c r="E83" s="309"/>
       <c r="F83" s="27"/>
       <c r="G83" s="66">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11545,11 +11542,11 @@
       <c r="B84" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C84" s="309">
+      <c r="C84" s="308">
         <v>0</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="312" t="str">
+      <c r="E84" s="311" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11571,10 +11568,10 @@
       <c r="B85" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C85" s="309">
-        <v>0</v>
-      </c>
-      <c r="E85" s="312" t="str">
+      <c r="C85" s="308">
+        <v>0</v>
+      </c>
+      <c r="E85" s="311" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11600,7 +11597,7 @@
         <v>0.39782714079673825</v>
       </c>
       <c r="D86" s="77"/>
-      <c r="E86" s="310"/>
+      <c r="E86" s="309"/>
       <c r="F86" s="77"/>
       <c r="G86" s="66">
         <f t="shared" ref="G86:Q86" si="35">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11649,14 +11646,14 @@
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
-      <c r="E87" s="313"/>
+      <c r="E87" s="312"/>
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
       <c r="B88" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E88" s="313"/>
+      <c r="E88" s="312"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
@@ -11668,7 +11665,7 @@
         <f>G89</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E89" s="313"/>
+      <c r="E89" s="312"/>
       <c r="G89" s="116">
         <f>Data!C64</f>
         <v>0.57999999999999996</v>
@@ -11724,7 +11721,7 @@
         <f>C89*Common_Shares/$C$3</f>
         <v>4739.6903628800001</v>
       </c>
-      <c r="E90" s="313"/>
+      <c r="E90" s="312"/>
       <c r="G90" s="76">
         <f t="shared" ref="G90:Q90" si="36">IF(G$4="","",G89*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
@@ -11779,7 +11776,7 @@
         <f>C89/(C19*$C$3/Common_Shares)</f>
         <v>1.3592634587039025</v>
       </c>
-      <c r="E91" s="313"/>
+      <c r="E91" s="312"/>
       <c r="G91" s="175">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G89/(G19*$C$3/Common_Shares))</f>
         <v>0.97826426478431361</v>
@@ -11834,7 +11831,7 @@
         <f>C89/Market_Price</f>
         <v>7.332490518331225E-2</v>
       </c>
-      <c r="E92" s="313"/>
+      <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
         <v>7.332490518331225E-2</v>
@@ -11882,7 +11879,7 @@
     </row>
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
-      <c r="E93" s="313"/>
+      <c r="E93" s="312"/>
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
@@ -11891,7 +11888,7 @@
       </c>
       <c r="C94" s="63"/>
       <c r="D94" s="27"/>
-      <c r="E94" s="310"/>
+      <c r="E94" s="309"/>
       <c r="F94" s="27"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12"/>
@@ -11915,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="27"/>
-      <c r="E95" s="310"/>
+      <c r="E95" s="309"/>
       <c r="F95" s="27"/>
       <c r="G95" s="6">
         <f t="shared" ref="G95:Q95" si="39">IF(H4="","",G4/H4-1)</f>
@@ -11972,7 +11969,7 @@
         <v>-0.13903984727117114</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="310"/>
+      <c r="E96" s="309"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H5="","",G13/H13-1)</f>
@@ -12050,7 +12047,7 @@
       <c r="B99" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E99" s="313"/>
+      <c r="E99" s="312"/>
       <c r="G99" s="100" t="s">
         <v>224</v>
       </c>
@@ -12065,7 +12062,7 @@
         <v>180996</v>
       </c>
       <c r="D100" s="26"/>
-      <c r="E100" s="314"/>
+      <c r="E100" s="313"/>
       <c r="F100" s="26"/>
       <c r="G100" s="187">
         <f t="shared" ref="G100:Q100" si="41">IF(G$4="","",G104+G103)</f>
@@ -12122,7 +12119,7 @@
         <v>8029</v>
       </c>
       <c r="D101" s="91"/>
-      <c r="E101" s="315"/>
+      <c r="E101" s="314"/>
       <c r="F101" s="91"/>
       <c r="G101" s="189">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12179,7 +12176,7 @@
         <v>15310</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="315"/>
+      <c r="E102" s="314"/>
       <c r="F102" s="91"/>
       <c r="G102" s="189">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12236,7 +12233,7 @@
         <v>13889</v>
       </c>
       <c r="D103" s="26"/>
-      <c r="E103" s="314"/>
+      <c r="E103" s="313"/>
       <c r="F103" s="26"/>
       <c r="G103" s="187">
         <f>Data!C78</f>
@@ -12293,7 +12290,7 @@
         <v>167107</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="314"/>
+      <c r="E104" s="313"/>
       <c r="F104" s="26"/>
       <c r="G104" s="187">
         <f>Data!C79</f>
@@ -12342,7 +12339,7 @@
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
-      <c r="E105" s="313"/>
+      <c r="E105" s="312"/>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
@@ -12351,7 +12348,7 @@
       </c>
       <c r="C106" s="26"/>
       <c r="D106" s="26"/>
-      <c r="E106" s="314"/>
+      <c r="E106" s="313"/>
       <c r="F106" s="26"/>
       <c r="G106" s="100" t="s">
         <v>224</v>
@@ -12377,7 +12374,7 @@
         <v>0.91602966343411296</v>
       </c>
       <c r="D107" s="26"/>
-      <c r="E107" s="314"/>
+      <c r="E107" s="313"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97">
         <f t="shared" ref="G107:Q107" si="42">IF(G$4="","",G101/G$4)</f>
@@ -12434,7 +12431,7 @@
         <v>1.7467199087278951</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="314"/>
+      <c r="E108" s="313"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12491,7 +12488,7 @@
         <v>8.343867655447804</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="314"/>
+      <c r="E109" s="313"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12510,7 +12507,7 @@
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
-      <c r="E110" s="313"/>
+      <c r="E110" s="312"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
@@ -12519,7 +12516,7 @@
       </c>
       <c r="C111" s="55"/>
       <c r="D111" s="55"/>
-      <c r="E111" s="316"/>
+      <c r="E111" s="315"/>
       <c r="F111" s="55"/>
       <c r="G111" s="23" t="str">
         <f>IFERROR(IF(#REF!*G113*(1/#REF!)=G115,"","Error"),"")</f>
@@ -12575,7 +12572,7 @@
         <f>C80</f>
         <v>0.52688993259982175</v>
       </c>
-      <c r="E112" s="313"/>
+      <c r="E112" s="312"/>
       <c r="G112" s="23">
         <f t="shared" ref="G112:Q112" si="44">G80</f>
         <v>0.61197946377638335</v>
@@ -12629,7 +12626,7 @@
         <f>C4/C100</f>
         <v>4.8426484563194767E-2</v>
       </c>
-      <c r="E113" s="313"/>
+      <c r="E113" s="312"/>
       <c r="G113" s="42">
         <f t="shared" ref="G113:Q113" si="45">IF(G4="","",G4/G100)</f>
         <v>4.8601561460320276E-2</v>
@@ -12684,7 +12681,7 @@
         <v>1.0831144117242246</v>
       </c>
       <c r="D114" s="11"/>
-      <c r="E114" s="317"/>
+      <c r="E114" s="316"/>
       <c r="F114" s="11"/>
       <c r="G114" s="15">
         <f t="shared" ref="G114:Q114" si="46">IF(G$4="","",G100/G104)</f>
@@ -12741,7 +12738,7 @@
         <v>1.5509944282629921E-2</v>
       </c>
       <c r="D115" s="106"/>
-      <c r="E115" s="316"/>
+      <c r="E115" s="315"/>
       <c r="F115" s="106"/>
       <c r="G115" s="105">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G8/G104)</f>
@@ -12837,7 +12834,7 @@
       </c>
       <c r="C118" s="184"/>
       <c r="D118" s="27"/>
-      <c r="E118" s="310"/>
+      <c r="E118" s="309"/>
       <c r="F118" s="27"/>
       <c r="G118" s="12"/>
       <c r="H118" s="12"/>
@@ -12862,7 +12859,7 @@
         <v>0.42670167897623534</v>
       </c>
       <c r="D119" s="27"/>
-      <c r="E119" s="310"/>
+      <c r="E119" s="309"/>
       <c r="F119" s="27"/>
       <c r="G119" s="182">
         <f t="shared" ref="G119:Q119" si="48">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -12919,7 +12916,7 @@
         <v>5.3944586469814836E-2</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="310"/>
+      <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
@@ -13748,10 +13745,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="335" t="s">
+      <c r="E6" s="338" t="s">
         <v>259</v>
       </c>
-      <c r="F6" s="335"/>
+      <c r="F6" s="338"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -13766,8 +13763,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
+      <c r="E7" s="338"/>
+      <c r="F7" s="338"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -13782,8 +13779,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="335"/>
-      <c r="F8" s="335"/>
+      <c r="E8" s="338"/>
+      <c r="F8" s="338"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -13798,8 +13795,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="335"/>
-      <c r="F9" s="335"/>
+      <c r="E9" s="338"/>
+      <c r="F9" s="338"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15196,7 +15193,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I90"/>
+  <dimension ref="B2:I92"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -15248,7 +15245,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" ref="I4:I13" ca="1" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15257,7 +15254,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15277,8 +15274,8 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f t="shared" si="0"/>
-        <v>11.286994878679808</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>11.22404343432521</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15293,16 +15290,16 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="337" t="str">
+      <c r="E7" s="340" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="337"/>
+      <c r="F7" s="340"/>
       <c r="H7" s="284">
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15318,13 +15315,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="337"/>
-      <c r="F8" s="337"/>
+      <c r="E8" s="340"/>
+      <c r="F8" s="340"/>
       <c r="H8" s="284">
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15340,24 +15337,24 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="337"/>
-      <c r="F9" s="337"/>
+      <c r="E9" s="340"/>
+      <c r="F9" s="340"/>
       <c r="H9" s="284">
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="337"/>
-      <c r="F10" s="337"/>
+      <c r="E10" s="340"/>
+      <c r="F10" s="340"/>
       <c r="H10" s="284">
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15365,13 +15362,13 @@
       <c r="B11" s="164" t="s">
         <v>299</v>
       </c>
-      <c r="E11" s="337"/>
-      <c r="F11" s="337"/>
+      <c r="E11" s="340"/>
+      <c r="F11" s="340"/>
       <c r="H11" s="284">
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15384,13 +15381,13 @@
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="163"/>
-      <c r="E12" s="337"/>
-      <c r="F12" s="337"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
       <c r="H12" s="284">
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15402,13 +15399,13 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="337"/>
-      <c r="F13" s="337"/>
+      <c r="E13" s="340"/>
+      <c r="F13" s="340"/>
       <c r="H13" s="284">
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v/>
       </c>
     </row>
@@ -15420,8 +15417,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.22869925060693375</v>
       </c>
-      <c r="E14" s="337"/>
-      <c r="F14" s="337"/>
+      <c r="E14" s="340"/>
+      <c r="F14" s="340"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15447,21 +15444,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="337" t="s">
+      <c r="E18" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="F18" s="338"/>
+      <c r="F18" s="341"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="338"/>
-      <c r="F19" s="338"/>
+      <c r="E19" s="341"/>
+      <c r="F19" s="341"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="164" t="s">
         <v>337</v>
       </c>
-      <c r="E20" s="338"/>
-      <c r="F20" s="338"/>
+      <c r="E20" s="341"/>
+      <c r="F20" s="341"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -15475,8 +15472,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="338"/>
-      <c r="F21" s="338"/>
+      <c r="E21" s="341"/>
+      <c r="F21" s="341"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -15490,8 +15487,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="338"/>
-      <c r="F22" s="338"/>
+      <c r="E22" s="341"/>
+      <c r="F22" s="341"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="164" t="s">
@@ -15511,8 +15508,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="168"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15522,8 +15519,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="169"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15537,8 +15534,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="336"/>
-      <c r="F27" s="336"/>
+      <c r="E27" s="339"/>
+      <c r="F27" s="339"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15548,8 +15545,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="170"/>
-      <c r="E28" s="336"/>
-      <c r="F28" s="336"/>
+      <c r="E28" s="339"/>
+      <c r="F28" s="339"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="164" t="s">
@@ -15569,8 +15566,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="168"/>
-      <c r="E31" s="336"/>
-      <c r="F31" s="336"/>
+      <c r="E31" s="339"/>
+      <c r="F31" s="339"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15580,8 +15577,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="169"/>
-      <c r="E32" s="336"/>
-      <c r="F32" s="336"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15595,8 +15592,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="336"/>
-      <c r="F33" s="336"/>
+      <c r="E33" s="339"/>
+      <c r="F33" s="339"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15606,8 +15603,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="170"/>
-      <c r="E34" s="336"/>
-      <c r="F34" s="336"/>
+      <c r="E34" s="339"/>
+      <c r="F34" s="339"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="164" t="s">
@@ -15627,8 +15624,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="168"/>
-      <c r="E37" s="336"/>
-      <c r="F37" s="336"/>
+      <c r="E37" s="339"/>
+      <c r="F37" s="339"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15638,8 +15635,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="169"/>
-      <c r="E38" s="336"/>
-      <c r="F38" s="336"/>
+      <c r="E38" s="339"/>
+      <c r="F38" s="339"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -15653,8 +15650,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="336"/>
-      <c r="F39" s="336"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -15665,8 +15662,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="170"/>
-      <c r="E40" s="336"/>
-      <c r="F40" s="336"/>
+      <c r="E40" s="339"/>
+      <c r="F40" s="339"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -15728,8 +15725,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="168"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="336"/>
+      <c r="E49" s="339"/>
+      <c r="F49" s="339"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -15739,8 +15736,8 @@
         <v>-0.3</v>
       </c>
       <c r="D50" s="169"/>
-      <c r="E50" s="336"/>
-      <c r="F50" s="336"/>
+      <c r="E50" s="339"/>
+      <c r="F50" s="339"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -15754,8 +15751,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="336"/>
-      <c r="F51" s="336"/>
+      <c r="E51" s="339"/>
+      <c r="F51" s="339"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -15765,8 +15762,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="170"/>
-      <c r="E52" s="336"/>
-      <c r="F52" s="336"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="164" t="s">
@@ -15786,8 +15783,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="168"/>
-      <c r="E55" s="336"/>
-      <c r="F55" s="336"/>
+      <c r="E55" s="339"/>
+      <c r="F55" s="339"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -15797,8 +15794,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="169"/>
-      <c r="E56" s="336"/>
-      <c r="F56" s="336"/>
+      <c r="E56" s="339"/>
+      <c r="F56" s="339"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -15812,8 +15809,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="336"/>
-      <c r="F57" s="336"/>
+      <c r="E57" s="339"/>
+      <c r="F57" s="339"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -15823,8 +15820,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="170"/>
-      <c r="E58" s="336"/>
-      <c r="F58" s="336"/>
+      <c r="E58" s="339"/>
+      <c r="F58" s="339"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -15841,7 +15838,8 @@
       <c r="E60" s="103" t="s">
         <v>330</v>
       </c>
-      <c r="F60" s="324">
+      <c r="F60" s="322">
+        <f ca="1">Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
@@ -15858,7 +15856,7 @@
       <c r="B63" s="112" t="s">
         <v>338</v>
       </c>
-      <c r="E63" s="291" t="s">
+      <c r="E63" s="290" t="s">
         <v>348</v>
       </c>
     </row>
@@ -15870,7 +15868,7 @@
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="290" t="s">
+      <c r="E64" s="289" t="s">
         <v>349</v>
       </c>
     </row>
@@ -15882,7 +15880,7 @@
         <v>-8.7951517171891095E-3</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="290" t="s">
+      <c r="E65" s="289" t="s">
         <v>350</v>
       </c>
     </row>
@@ -15898,7 +15896,7 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="290" t="s">
+      <c r="E66" s="289" t="s">
         <v>351</v>
       </c>
     </row>
@@ -15906,7 +15904,7 @@
       <c r="B68" s="112" t="s">
         <v>325</v>
       </c>
-      <c r="E68" s="291" t="s">
+      <c r="E68" s="290" t="s">
         <v>352</v>
       </c>
     </row>
@@ -15928,7 +15926,7 @@
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
-      <c r="E70" s="290" t="s">
+      <c r="E70" s="289" t="s">
         <v>328</v>
       </c>
     </row>
@@ -15940,7 +15938,7 @@
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="290"/>
+      <c r="E71" s="289"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
@@ -15964,32 +15962,22 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
         <v>130</v>
       </c>
-      <c r="E75" s="325" t="s">
-        <v>367</v>
-      </c>
-      <c r="F75" s="323"/>
-    </row>
-    <row r="76" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="283" t="s">
         <v>331</v>
       </c>
       <c r="C76" s="282">
-        <f>F60</f>
+        <f ca="1">F60</f>
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
-      <c r="E76" s="326" t="s">
-        <v>368</v>
-      </c>
-      <c r="F76" s="323" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
         <v>116</v>
       </c>
@@ -16001,20 +15989,6 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E77" s="327" t="s">
-        <v>368</v>
-      </c>
-      <c r="F77" s="323" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E78" s="328" t="s">
-        <v>368</v>
-      </c>
-      <c r="F78" s="323" t="s">
-        <v>371</v>
-      </c>
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
@@ -16030,35 +16004,35 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
         <v>126</v>
       </c>
       <c r="C81" s="120">
-        <f>PV(C80, C76, -C77, 0)</f>
+        <f ca="1">PV(C80, C76, -C77, 0)</f>
         <v>1.2217592592592592</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
       <c r="F81" s="103"/>
     </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
         <v>127</v>
       </c>
       <c r="C82" s="120">
-        <f>C60/(1+C80)^C76</f>
-        <v>6.1961775918285928</v>
+        <f ca="1">C60/(1+C80)^C76</f>
+        <v>6.1597473578270892</v>
       </c>
       <c r="D82" s="120"/>
     </row>
-    <row r="83" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
         <v>106</v>
       </c>
       <c r="C83" s="115">
-        <f>C81+C82</f>
-        <v>7.4179368510878518</v>
+        <f ca="1">C81+C82</f>
+        <v>7.3815066170863481</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16068,19 +16042,19 @@
         <v>131</v>
       </c>
       <c r="F83" s="270">
-        <f>(C83/C60-1)</f>
-        <v>-0.30718778376753109</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <f ca="1">(C83/C60-1)</f>
+        <v>-0.30651291845707263</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E84" s="124"/>
     </row>
-    <row r="85" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
         <v>334</v>
       </c>
@@ -16093,20 +16067,55 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
         <v>332</v>
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17296459645475393</v>
-      </c>
-    </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+        <v>0.17091086618081319</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="103"/>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="C90" s="121"/>
+    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E89" s="331" t="s">
+        <v>367</v>
+      </c>
+      <c r="F89" s="328"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="327"/>
+    </row>
+    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E90" s="324" t="s">
+        <v>368</v>
+      </c>
+      <c r="F90" s="329" t="s">
+        <v>369</v>
+      </c>
+      <c r="G90" s="2"/>
+      <c r="H90" s="327"/>
+    </row>
+    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E91" s="325" t="s">
+        <v>368</v>
+      </c>
+      <c r="F91" s="329" t="s">
+        <v>370</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="327"/>
+    </row>
+    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E92" s="326" t="s">
+        <v>368</v>
+      </c>
+      <c r="F92" s="330" t="s">
+        <v>371</v>
+      </c>
+      <c r="G92" s="2"/>
+      <c r="H92" s="327"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39E0BA4-0773-4E05-A7BE-18515030294E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95F1479-1D2B-402B-B757-BBA8497E5A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3317,20 +3317,20 @@
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3744,13 +3744,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="332" t="s">
+      <c r="B12" s="333" t="s">
         <v>290</v>
       </c>
-      <c r="C12" s="332"/>
-      <c r="D12" s="332"/>
-      <c r="E12" s="332"/>
-      <c r="F12" s="332"/>
+      <c r="C12" s="333"/>
+      <c r="D12" s="333"/>
+      <c r="E12" s="333"/>
+      <c r="F12" s="333"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3816,15 +3816,14 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="259">
-        <f ca="1">C123</f>
-        <v>7.3815066170863481</v>
+        <f>C123</f>
+        <v>7.4179368510878518</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>344</v>
       </c>
       <c r="E20" s="323">
-        <f ca="1">Scenarios!C76</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3833,7 +3832,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17091086618081319</v>
+        <v>0.17296459645475393</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3853,22 +3852,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="332" t="s">
+      <c r="B25" s="333" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="332"/>
-      <c r="D25" s="332"/>
-      <c r="E25" s="332"/>
-      <c r="F25" s="332"/>
+      <c r="C25" s="333"/>
+      <c r="D25" s="333"/>
+      <c r="E25" s="333"/>
+      <c r="F25" s="333"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="336" t="s">
+      <c r="B26" s="334" t="s">
         <v>256</v>
       </c>
-      <c r="C26" s="336"/>
-      <c r="D26" s="336"/>
-      <c r="E26" s="336"/>
-      <c r="F26" s="336"/>
+      <c r="C26" s="334"/>
+      <c r="D26" s="334"/>
+      <c r="E26" s="334"/>
+      <c r="F26" s="334"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="241" t="s">
@@ -3880,13 +3879,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="334" t="s">
+      <c r="B29" s="332" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="334"/>
-      <c r="D29" s="334"/>
-      <c r="E29" s="334"/>
-      <c r="F29" s="334"/>
+      <c r="C29" s="332"/>
+      <c r="D29" s="332"/>
+      <c r="E29" s="332"/>
+      <c r="F29" s="332"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3906,13 +3905,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="334" t="s">
+      <c r="B32" s="332" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="334"/>
-      <c r="D32" s="334"/>
-      <c r="E32" s="334"/>
-      <c r="F32" s="334"/>
+      <c r="C32" s="332"/>
+      <c r="D32" s="332"/>
+      <c r="E32" s="332"/>
+      <c r="F32" s="332"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -3941,13 +3940,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="334" t="s">
+      <c r="B36" s="332" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="334"/>
-      <c r="D36" s="334"/>
-      <c r="E36" s="334"/>
-      <c r="F36" s="334"/>
+      <c r="C36" s="332"/>
+      <c r="D36" s="332"/>
+      <c r="E36" s="332"/>
+      <c r="F36" s="332"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -3963,13 +3962,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="334" t="s">
+      <c r="B39" s="332" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="334"/>
-      <c r="D39" s="334"/>
-      <c r="E39" s="334"/>
-      <c r="F39" s="334"/>
+      <c r="C39" s="332"/>
+      <c r="D39" s="332"/>
+      <c r="E39" s="332"/>
+      <c r="F39" s="332"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4003,13 +4002,13 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B45" s="334" t="s">
+      <c r="B45" s="332" t="s">
         <v>248</v>
       </c>
-      <c r="C45" s="334"/>
-      <c r="D45" s="334"/>
-      <c r="E45" s="334"/>
-      <c r="F45" s="334"/>
+      <c r="C45" s="332"/>
+      <c r="D45" s="332"/>
+      <c r="E45" s="332"/>
+      <c r="F45" s="332"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="47" t="s">
@@ -4025,13 +4024,13 @@
       </c>
     </row>
     <row r="48" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="334" t="s">
+      <c r="B48" s="332" t="s">
         <v>251</v>
       </c>
-      <c r="C48" s="335"/>
-      <c r="D48" s="335"/>
-      <c r="E48" s="335"/>
-      <c r="F48" s="335"/>
+      <c r="C48" s="336"/>
+      <c r="D48" s="336"/>
+      <c r="E48" s="336"/>
+      <c r="F48" s="336"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B49" s="47" t="s">
@@ -4060,13 +4059,13 @@
       </c>
     </row>
     <row r="52" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="332" t="s">
+      <c r="B52" s="333" t="s">
         <v>272</v>
       </c>
-      <c r="C52" s="332"/>
-      <c r="D52" s="332"/>
-      <c r="E52" s="332"/>
-      <c r="F52" s="332"/>
+      <c r="C52" s="333"/>
+      <c r="D52" s="333"/>
+      <c r="E52" s="333"/>
+      <c r="F52" s="333"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B53" s="47" t="s">
@@ -4127,22 +4126,22 @@
     </row>
     <row r="60" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="17"/>
-      <c r="B60" s="334" t="s">
+      <c r="B60" s="332" t="s">
         <v>307</v>
       </c>
-      <c r="C60" s="334"/>
-      <c r="D60" s="334"/>
-      <c r="E60" s="334"/>
-      <c r="F60" s="334"/>
+      <c r="C60" s="332"/>
+      <c r="D60" s="332"/>
+      <c r="E60" s="332"/>
+      <c r="F60" s="332"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B61" s="336" t="s">
+      <c r="B61" s="334" t="s">
         <v>263</v>
       </c>
-      <c r="C61" s="336"/>
-      <c r="D61" s="336"/>
-      <c r="E61" s="336"/>
-      <c r="F61" s="336"/>
+      <c r="C61" s="334"/>
+      <c r="D61" s="334"/>
+      <c r="E61" s="334"/>
+      <c r="F61" s="334"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B63" s="241" t="s">
@@ -4194,22 +4193,22 @@
       <c r="C68" s="125"/>
     </row>
     <row r="69" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="332" t="s">
+      <c r="B69" s="333" t="s">
         <v>315</v>
       </c>
-      <c r="C69" s="332"/>
-      <c r="D69" s="332"/>
-      <c r="E69" s="332"/>
-      <c r="F69" s="332"/>
+      <c r="C69" s="333"/>
+      <c r="D69" s="333"/>
+      <c r="E69" s="333"/>
+      <c r="F69" s="333"/>
     </row>
     <row r="70" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="332" t="s">
+      <c r="B70" s="333" t="s">
         <v>262</v>
       </c>
-      <c r="C70" s="332"/>
-      <c r="D70" s="332"/>
-      <c r="E70" s="332"/>
-      <c r="F70" s="332"/>
+      <c r="C70" s="333"/>
+      <c r="D70" s="333"/>
+      <c r="E70" s="333"/>
+      <c r="F70" s="333"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B71" s="47" t="s">
@@ -4246,13 +4245,13 @@
       <c r="A76" s="240"/>
     </row>
     <row r="77" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="332" t="s">
+      <c r="B77" s="333" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="332"/>
-      <c r="D77" s="332"/>
-      <c r="E77" s="332"/>
-      <c r="F77" s="332"/>
+      <c r="C77" s="333"/>
+      <c r="D77" s="333"/>
+      <c r="E77" s="333"/>
+      <c r="F77" s="333"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B78" s="1" t="s">
@@ -4366,13 +4365,13 @@
       </c>
     </row>
     <row r="93" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="332" t="s">
+      <c r="B93" s="333" t="s">
         <v>271</v>
       </c>
-      <c r="C93" s="332"/>
-      <c r="D93" s="332"/>
-      <c r="E93" s="332"/>
-      <c r="F93" s="332"/>
+      <c r="C93" s="333"/>
+      <c r="D93" s="333"/>
+      <c r="E93" s="333"/>
+      <c r="F93" s="333"/>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
@@ -4398,13 +4397,13 @@
       <c r="F97" s="36"/>
     </row>
     <row r="99" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B99" s="334" t="s">
+      <c r="B99" s="332" t="s">
         <v>374</v>
       </c>
-      <c r="C99" s="334"/>
-      <c r="D99" s="334"/>
-      <c r="E99" s="334"/>
-      <c r="F99" s="334"/>
+      <c r="C99" s="332"/>
+      <c r="D99" s="332"/>
+      <c r="E99" s="332"/>
+      <c r="F99" s="332"/>
     </row>
     <row r="101" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B101" s="267" t="s">
@@ -4566,13 +4565,13 @@
       <c r="F112" s="36"/>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B114" s="333" t="s">
+      <c r="B114" s="335" t="s">
         <v>279</v>
       </c>
-      <c r="C114" s="333"/>
-      <c r="D114" s="333"/>
-      <c r="E114" s="333"/>
-      <c r="F114" s="333"/>
+      <c r="C114" s="335"/>
+      <c r="D114" s="335"/>
+      <c r="E114" s="335"/>
+      <c r="F114" s="335"/>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B115" s="241" t="s">
@@ -4584,7 +4583,7 @@
         <v>280</v>
       </c>
       <c r="C116" s="258">
-        <f ca="1">E20</f>
+        <f>E20</f>
         <v>3</v>
       </c>
     </row>
@@ -4617,22 +4616,22 @@
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B121" s="243" t="str">
-        <f ca="1">"PV("&amp;C116&amp;" yrs of Dividends)"</f>
+        <f>"PV("&amp;C116&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C121" s="247">
-        <f ca="1">Scenarios!C81</f>
+        <f>Scenarios!C81</f>
         <v>1.2217592592592592</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B122" s="243" t="str">
-        <f ca="1">"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
+        <f>"+ PV(Equity Value realized at year "&amp;C116&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C122" s="247">
-        <f ca="1">Scenarios!C82</f>
-        <v>6.1597473578270892</v>
+        <f>Scenarios!C82</f>
+        <v>6.1961775918285928</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.35">
@@ -4640,8 +4639,8 @@
         <v>275</v>
       </c>
       <c r="C123" s="246">
-        <f ca="1">Scenarios!C83</f>
-        <v>7.3815066170863481</v>
+        <f>Scenarios!C83</f>
+        <v>7.4179368510878518</v>
       </c>
       <c r="D123" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4653,18 +4652,12 @@
         <v>277</v>
       </c>
       <c r="C124" s="158">
-        <f ca="1">Scenarios!F83</f>
-        <v>-0.30651291845707263</v>
+        <f>Scenarios!F83</f>
+        <v>-0.30718778376753109</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B70:F70"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B93:F93"/>
@@ -4678,6 +4671,12 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -15245,7 +15244,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="272">
-        <f t="shared" ref="I4:I13" ca="1" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
+        <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15254,7 +15253,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="272">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
@@ -15274,8 +15273,8 @@
         <v>3</v>
       </c>
       <c r="I6" s="272">
-        <f t="shared" ca="1" si="0"/>
-        <v>11.22404343432521</v>
+        <f t="shared" si="0"/>
+        <v>11.286994878679808</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -15299,7 +15298,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15321,7 +15320,7 @@
         <v>5</v>
       </c>
       <c r="I8" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15343,7 +15342,7 @@
         <v>6</v>
       </c>
       <c r="I9" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15354,7 +15353,7 @@
         <v>7</v>
       </c>
       <c r="I10" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15368,7 +15367,7 @@
         <v>8</v>
       </c>
       <c r="I11" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15387,7 +15386,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15405,7 +15404,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="272" t="str">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -15839,7 +15838,7 @@
         <v>330</v>
       </c>
       <c r="F60" s="322">
-        <f ca="1">Thesis!E20</f>
+        <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
@@ -15972,7 +15971,7 @@
         <v>331</v>
       </c>
       <c r="C76" s="282">
-        <f ca="1">F60</f>
+        <f>F60</f>
         <v>3</v>
       </c>
       <c r="D76" s="138"/>
@@ -16009,7 +16008,7 @@
         <v>126</v>
       </c>
       <c r="C81" s="120">
-        <f ca="1">PV(C80, C76, -C77, 0)</f>
+        <f>PV(C80, C76, -C77, 0)</f>
         <v>1.2217592592592592</v>
       </c>
       <c r="D81" s="120"/>
@@ -16021,8 +16020,8 @@
         <v>127</v>
       </c>
       <c r="C82" s="120">
-        <f ca="1">C60/(1+C80)^C76</f>
-        <v>6.1597473578270892</v>
+        <f>C60/(1+C80)^C76</f>
+        <v>6.1961775918285928</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16031,8 +16030,8 @@
         <v>106</v>
       </c>
       <c r="C83" s="115">
-        <f ca="1">C81+C82</f>
-        <v>7.3815066170863481</v>
+        <f>C81+C82</f>
+        <v>7.4179368510878518</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16042,8 +16041,8 @@
         <v>131</v>
       </c>
       <c r="F83" s="270">
-        <f ca="1">(C83/C60-1)</f>
-        <v>-0.30651291845707263</v>
+        <f>(C83/C60-1)</f>
+        <v>-0.30718778376753109</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16073,7 +16072,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17091086618081319</v>
+        <v>0.17296459645475393</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95F1479-1D2B-402B-B757-BBA8497E5A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E88B01A-4AE5-4291-A616-C5B4D8D52521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3689,7 +3689,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64639.57029376</v>
+        <v>64557.851494399998</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17296459645475393</v>
+        <v>0.17349059186547722</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C120</f>
-        <v>5.3944586469814836E-2</v>
+        <v>5.401287075648549E-2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="C56" s="94">
         <f>Normalized_FCF!C92</f>
-        <v>7.332490518331225E-2</v>
+        <v>7.3417721518987331E-2</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -11828,20 +11828,20 @@
       </c>
       <c r="C92" s="23">
         <f>C89/Market_Price</f>
-        <v>7.332490518331225E-2</v>
+        <v>7.3417721518987331E-2</v>
       </c>
       <c r="E92" s="312"/>
       <c r="G92" s="23">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G89/Market_Price)</f>
-        <v>7.332490518331225E-2</v>
+        <v>7.3417721518987331E-2</v>
       </c>
       <c r="H92" s="23">
         <f t="shared" si="38"/>
-        <v>7.332490518331225E-2</v>
+        <v>7.3417721518987331E-2</v>
       </c>
       <c r="I92" s="23">
         <f t="shared" si="38"/>
-        <v>7.20606826801517E-2</v>
+        <v>7.2151898734177211E-2</v>
       </c>
       <c r="J92" s="23">
         <f t="shared" si="38"/>
@@ -12912,30 +12912,30 @@
       </c>
       <c r="C120" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.3944586469814836E-2</v>
+        <v>5.401287075648549E-2</v>
       </c>
       <c r="D120" s="27"/>
       <c r="E120" s="309"/>
       <c r="F120" s="27"/>
       <c r="G120" s="79">
         <f t="shared" ref="G120" si="49">IF(G$4="","",G119/Market_Price)</f>
-        <v>7.495408737993596E-2</v>
+        <v>7.5048965971556136E-2</v>
       </c>
       <c r="H120" s="79">
         <f t="shared" ref="H120" si="50">IF(H$4="","",H119/Market_Price)</f>
-        <v>8.8726380527217902E-2</v>
+        <v>8.8838692401302988E-2</v>
       </c>
       <c r="I120" s="79">
         <f t="shared" ref="I120" si="51">IF(I$4="","",I119/Market_Price)</f>
-        <v>9.9322607619806103E-2</v>
+        <v>9.9448332439578013E-2</v>
       </c>
       <c r="J120" s="79">
         <f t="shared" ref="J120" si="52">IF(J$4="","",J119/Market_Price)</f>
-        <v>0.16335185127335719</v>
+        <v>0.16355862576863991</v>
       </c>
       <c r="K120" s="79">
         <f t="shared" ref="K120" si="53">IF(K$4="","",K119/Market_Price)</f>
-        <v>5.3372879558468332E-2</v>
+        <v>5.3440440165504366E-2</v>
       </c>
       <c r="L120" s="79" t="str">
         <f t="shared" ref="L120" si="54">IF(L$4="","",L119/Market_Price)</f>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-7.91</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15465,7 +15465,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16072,7 +16072,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17296459645475393</v>
+        <v>0.17349059186547722</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E88B01A-4AE5-4291-A616-C5B4D8D52521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EFF6A7-6D57-4CFA-AC5D-FC8B647B5CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="388">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1928,6 +1928,31 @@
   </si>
   <si>
     <t>Note that this model prioritizes fundamental analysis when combined with supplementary market signal analysis. While market signal analysis predicts future trends, fundamental analysis interprets these trends and identifies relevant factors and possibilities.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Prompt</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I need to categorize the balance sheet items from the provided financial statements into the exact structure below. Follow these steps:
+1.	Identify Line Items: Extract all assets, liabilities, and equity line items from the text. Preserve their exact wording (e.g., ‘Trade Receivables’ vs. ‘Accounts Receivable’).
+2.	Map to Categories: Classify each item into the pre-defined structure below. Use the descriptions to resolve ambiguities.
+3.	Flag Uncertainties: Note items that don’t fit cleanly or require assumptions.
+4.	Format Output: Provide a table with columns: PDF Line Item | Category | Subcategory | Amount. 
+STRUCTURE TO FOLLOW (use exact names):
+•	ST Operating Assets: ST AR, Operating ST Financial Assets, Inventory, Prepayments and Contract Assets, ST DTA, Other ST Assets, Operating ST Assets
+•	LT Operating Assets: LT AR, Operating LT Financial Assets, PP&amp;E &amp; Right of Use Assets, Biological assets, Intangible assets, LT DTA, Other assets &amp; Goodwill
+•	ST Non-Operating Assets: Cash and cash equivalents, Restricted cash, Securities with stable income, Other Securities, Properties with stable income, Other Properties
+•	LT Non-Operating Assets: LT Deposits, Securities with stable income, Other Securities, JV or associate with stable income, Other JV or associate, Properties with stable income, Other Properties
+•	ST Liabilities: ST Borrowing, ST Lease liabilities, ST SH Loan, ST Financial Liabilities, ST Interest-bearing Debt, Other ST liabilities
+•	LT Liabilities: LT Borrowing, LT Lease liabilities, LT SH Loan, LT Financial Liabilities, LT Interest-bearing Debt, Other LT liabilities
+•	Equity: Minority Interest (NCI), Common Equity
+EXAMPLE:
+•	If the PDF says “Property, Plant, and Equipment – $50M”, map to:
+PP&amp;E &amp; Right of Use Assets | LT Operating Assets | PP&amp;E &amp; Right of Use Assets | \$50,000,000
+•	If the PDF says “Marketable Securities – $10M”, map to:
+Other Securities | ST Non-Operating Assets | Other Securities | \$10,000,000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3678,10 +3703,10 @@
         <v>353</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -6960,7 +6985,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:H89"/>
+  <dimension ref="B1:H93"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
@@ -8213,7 +8238,38 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="91" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="81" t="s">
+        <v>376</v>
+      </c>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="37"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="37"/>
+      <c r="H91" s="37"/>
+    </row>
+    <row r="92" spans="2:8" ht="212" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="332" t="s">
+        <v>377</v>
+      </c>
+      <c r="C92" s="332"/>
+      <c r="D92" s="332"/>
+      <c r="E92" s="332"/>
+      <c r="F92" s="332"/>
+      <c r="G92" s="332"/>
+      <c r="H92" s="332"/>
+    </row>
+    <row r="93" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="1" t="str">
+        <f>"Please find the financial statement text below. The output should use a scaling factor of "&amp;H1</f>
+        <v>Please find the financial statement text below. The output should use a scaling factor of 1000000</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B92:H92"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="71" orientation="portrait" r:id="rId1"/>
@@ -9069,7 +9125,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="311" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="202"/>
@@ -9095,7 +9151,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="311" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="203"/>
@@ -9423,7 +9479,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9483,7 +9539,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9607,7 +9663,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G33" s="198">
         <f>Data!C41</f>
@@ -9665,7 +9721,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="310" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="187">
@@ -9973,7 +10029,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="309" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10242,7 +10298,7 @@
         <v>0.03</v>
       </c>
       <c r="E52" s="309" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G52" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G48/BS!$C$66)</f>
@@ -10269,7 +10325,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E53" s="309" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G53" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10584,7 +10640,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="310" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G61" s="198">
         <f>Data!C58</f>
@@ -11145,7 +11201,7 @@
       </c>
       <c r="D77" s="27"/>
       <c r="E77" s="310" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F77" s="27"/>
       <c r="G77" s="6">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6EFF6A7-6D57-4CFA-AC5D-FC8B647B5CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154528D6-F501-44D3-BF1C-0F4ACE606B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54350684-0AE1-484D-8F05-F093BFA89986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCAA11D-7024-4A74-A7A1-1E8F74F89D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1998,6 +1998,14 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Operating Interest Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Non-FCF Value is of the Expected Value, at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2026,7 +2034,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="58" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2459,13 +2467,6 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3369,15 +3370,17 @@
     <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3750,7 +3753,7 @@
         <v>99</v>
       </c>
       <c r="C6" s="50">
-        <v>7.9</v>
+        <v>7.79</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>43</v>
@@ -3795,7 +3798,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64557.851494399998</v>
+        <v>63658.944701439999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3893,7 +3896,7 @@
       </c>
       <c r="C21" s="288">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11614149089878545</v>
+        <v>0.12172735692567005</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4160,7 +4163,7 @@
       </c>
       <c r="C56" s="192">
         <f>Normalized_FCF!G19</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4186,7 +4189,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>3.9354193616452378E-2</v>
+        <v>3.9909901100125003E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,7 +4198,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>7.3417721518987331E-2</v>
+        <v>7.4454428754813853E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -8143,7 +8146,7 @@
         <v>360</v>
       </c>
       <c r="C76" s="300"/>
-      <c r="D76" s="339">
+      <c r="D76" s="337">
         <f>IF(D74&lt;=3,1,IF(D74&gt;12,IF(D74&gt;24,12,6),2))</f>
         <v>12</v>
       </c>
@@ -8886,48 +8889,48 @@
       </c>
       <c r="E12" s="311"/>
       <c r="G12" s="198">
-        <f t="shared" ref="G12:Q12" si="6">G50</f>
-        <v>0</v>
+        <f>G50</f>
+        <v>259.96861497481899</v>
       </c>
       <c r="H12" s="198">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" ref="H12:Q12" si="6">H50</f>
+        <v>139.30261332735768</v>
       </c>
       <c r="I12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-5.5315111914213588</v>
       </c>
       <c r="J12" s="198">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>-7.6802090667184899</v>
       </c>
       <c r="K12" s="198">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L12" s="198">
+      <c r="L12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="198">
+        <v/>
+      </c>
+      <c r="M12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="198">
+        <v/>
+      </c>
+      <c r="N12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="198">
+        <v/>
+      </c>
+      <c r="O12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="198">
+        <v/>
+      </c>
+      <c r="P12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="198">
+        <v/>
+      </c>
+      <c r="Q12" s="198" t="str">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -8942,19 +8945,19 @@
       <c r="E13" s="311"/>
       <c r="G13" s="188">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3067</v>
+        <v>3326.968614974819</v>
       </c>
       <c r="H13" s="188">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>5277</v>
+        <v>5416.3026133273579</v>
       </c>
       <c r="I13" s="188">
         <f t="shared" si="7"/>
-        <v>7481.2162740000003</v>
+        <v>7475.6847628085789</v>
       </c>
       <c r="J13" s="188">
         <f t="shared" si="7"/>
-        <v>12599.341036000002</v>
+        <v>12591.660826933283</v>
       </c>
       <c r="K13" s="188">
         <f t="shared" si="7"/>
@@ -9111,19 +9114,19 @@
       <c r="F16" s="62"/>
       <c r="G16" s="188">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="H16" s="188">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>4385.165172</v>
+        <v>4524.4677853273579</v>
       </c>
       <c r="I16" s="188">
         <f t="shared" si="8"/>
-        <v>6132.1087790000001</v>
+        <v>6126.5772678085787</v>
       </c>
       <c r="J16" s="188">
         <f t="shared" si="8"/>
-        <v>10068.571505000002</v>
+        <v>10060.891295933283</v>
       </c>
       <c r="K16" s="188">
         <f t="shared" si="8"/>
@@ -9219,19 +9222,19 @@
       <c r="F19" s="27"/>
       <c r="G19" s="190">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="H19" s="190">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>4385.165172</v>
+        <v>4524.4677853273579</v>
       </c>
       <c r="I19" s="190">
         <f t="shared" si="9"/>
-        <v>6132.1087790000001</v>
+        <v>6126.5772678085787</v>
       </c>
       <c r="J19" s="190">
         <f t="shared" si="9"/>
-        <v>10068.571505000002</v>
+        <v>10060.891295933283</v>
       </c>
       <c r="K19" s="190">
         <f t="shared" si="9"/>
@@ -10073,19 +10076,19 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.17439516129032259</v>
+        <v>0.16038474464748129</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.16596005937921729</v>
+        <v>0.16161958688679046</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18480422645572653</v>
+        <v>0.18494436262371075</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2038773843106306</v>
+        <v>0.2040036040672103</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10207,78 +10210,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>71</v>
+        <v>389</v>
       </c>
       <c r="C48" s="198">
         <f>BS!D75*C53</f>
         <v>185.19539222287685</v>
       </c>
       <c r="E48" s="311"/>
-      <c r="G48" s="333"/>
-      <c r="H48" s="333"/>
-      <c r="I48" s="333"/>
-      <c r="J48" s="333"/>
-      <c r="K48" s="333"/>
-      <c r="L48" s="333"/>
-      <c r="M48" s="333"/>
-      <c r="N48" s="333"/>
-      <c r="O48" s="333"/>
-      <c r="P48" s="333"/>
-      <c r="Q48" s="333"/>
+      <c r="G48" s="338">
+        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <v>302.96861497481899</v>
+      </c>
+      <c r="H48" s="338">
+        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <v>180.07798132735766</v>
+      </c>
+      <c r="I48" s="338">
+        <f t="shared" si="19"/>
+        <v>43.666282808578643</v>
+      </c>
+      <c r="J48" s="338">
+        <f t="shared" si="19"/>
+        <v>74.082965933281514</v>
+      </c>
+      <c r="K48" s="338">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="M48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="N48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="O48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="P48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="Q48" s="338" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="334" t="s">
+      <c r="B49" s="333" t="s">
         <v>384</v>
       </c>
-      <c r="C49" s="335">
+      <c r="C49" s="334">
         <f>BS!$C$66*C53</f>
         <v>1430.37</v>
       </c>
-      <c r="D49" s="336"/>
-      <c r="E49" s="337"/>
-      <c r="F49" s="336"/>
-      <c r="G49" s="335">
+      <c r="D49" s="335"/>
+      <c r="E49" s="336"/>
+      <c r="F49" s="335"/>
+      <c r="G49" s="334">
         <f>Data!C52</f>
         <v>2340</v>
       </c>
-      <c r="H49" s="335">
+      <c r="H49" s="334">
         <f>Data!D52</f>
         <v>1390.845307</v>
       </c>
-      <c r="I49" s="335">
+      <c r="I49" s="334">
         <f>Data!E52</f>
         <v>337.25969199999997</v>
       </c>
-      <c r="J49" s="335">
+      <c r="J49" s="334">
         <f>Data!F52</f>
         <v>572.18514300000004</v>
       </c>
-      <c r="K49" s="335">
+      <c r="K49" s="334">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="335" t="str">
+      <c r="L49" s="334" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="335" t="str">
+      <c r="M49" s="334" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="335" t="str">
+      <c r="N49" s="334" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="335" t="str">
+      <c r="O49" s="334" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="335" t="str">
+      <c r="P49" s="334" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="335" t="str">
+      <c r="Q49" s="334" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10293,17 +10329,50 @@
         <v>142.19539222287685</v>
       </c>
       <c r="E50" s="311"/>
-      <c r="G50" s="338"/>
-      <c r="H50" s="338"/>
-      <c r="I50" s="338"/>
-      <c r="J50" s="338"/>
-      <c r="K50" s="338"/>
-      <c r="L50" s="338"/>
-      <c r="M50" s="338"/>
-      <c r="N50" s="338"/>
-      <c r="O50" s="338"/>
-      <c r="P50" s="338"/>
-      <c r="Q50" s="338"/>
+      <c r="G50" s="188">
+        <f>IF(G$4="","",(G47+G48))</f>
+        <v>259.96861497481899</v>
+      </c>
+      <c r="H50" s="188">
+        <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
+        <v>139.30261332735768</v>
+      </c>
+      <c r="I50" s="188">
+        <f t="shared" si="20"/>
+        <v>-5.5315111914213588</v>
+      </c>
+      <c r="J50" s="188">
+        <f t="shared" si="20"/>
+        <v>-7.6802090667184899</v>
+      </c>
+      <c r="K50" s="188">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="L50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="M50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="N50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="O50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="P50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="Q50" s="188" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
@@ -10383,47 +10452,47 @@
       </c>
       <c r="E55" s="311"/>
       <c r="G55" s="42">
-        <f t="shared" ref="G55:Q55" si="19">IF(G4="","",-G8/G47)</f>
+        <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
       </c>
       <c r="H55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>104.47483882916765</v>
       </c>
       <c r="I55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>148.38466688160855</v>
       </c>
       <c r="J55" s="42">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>151.81888467516092</v>
       </c>
       <c r="K55" s="42" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="M55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="N55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="O55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="Q55" s="42" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -10617,47 +10686,47 @@
       </c>
       <c r="E61" s="311"/>
       <c r="G61" s="188">
-        <f t="shared" ref="G61:Q61" si="20">IF(G4="","",SUM(G58:G60))</f>
+        <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
       </c>
       <c r="H61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>927</v>
       </c>
       <c r="I61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="J61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="K61" s="188">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="L61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="M61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="N61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="O61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="P61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="Q61" s="188" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
     </row>
@@ -10728,47 +10797,47 @@
       </c>
       <c r="E63" s="311"/>
       <c r="G63" s="188">
-        <f t="shared" ref="G63:Q63" si="21">IF(G4="","",G61+G62)</f>
+        <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>136</v>
       </c>
       <c r="H63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1130.764889</v>
       </c>
       <c r="I63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-503.75612799999999</v>
       </c>
       <c r="J63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-726.80948300000091</v>
       </c>
       <c r="K63" s="188">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>-3450</v>
       </c>
       <c r="L63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="N63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="O63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="P63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="Q63" s="188" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
@@ -10948,47 +11017,47 @@
       <c r="E73" s="308"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
-        <f t="shared" ref="G73:Q73" si="22">IF(G$4="","",ABS(G5/G$4))</f>
+        <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
         <v>0.60969766115231028</v>
       </c>
       <c r="H73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.54641865162865078</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.47812220197752181</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.45826243510069942</v>
       </c>
       <c r="K73" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.4139629692542891</v>
       </c>
       <c r="L73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="M73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="O73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="P73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="Q73" s="6" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
@@ -11005,47 +11074,47 @@
       <c r="E74" s="308"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
-        <f t="shared" ref="G74:Q74" si="23">IF(G$4="","",ABS(G6/G$4))</f>
+        <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
         <v>0.39030233884768967</v>
       </c>
       <c r="H74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.45358134837134922</v>
       </c>
       <c r="I74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.52187779802247813</v>
       </c>
       <c r="J74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.54173756489930058</v>
       </c>
       <c r="K74" s="66">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0.5860370307457109</v>
       </c>
       <c r="L74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="M74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="N74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="P74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="Q74" s="66" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -11062,47 +11131,47 @@
       <c r="E75" s="308"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
-        <f t="shared" ref="G75:Q75" si="24">IF(G$4="","",ABS(G7/G$4))</f>
+        <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
         <v>0.12367370222475756</v>
       </c>
       <c r="H75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>9.5025671239794635E-2</v>
       </c>
       <c r="I75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.5428246134247773E-2</v>
       </c>
       <c r="J75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>3.3694951770082464E-2</v>
       </c>
       <c r="K75" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="L75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="M75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="N75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="O75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="Q75" s="6" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
     </row>
@@ -11119,47 +11188,47 @@
       <c r="E76" s="308"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
-        <f t="shared" ref="G76:Q76" si="25">IF(G$4="","",ABS(G8/G$4))</f>
+        <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
         <v>0.26662863662293212</v>
       </c>
       <c r="H76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.35855567713155456</v>
       </c>
       <c r="I76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.4664495518882304</v>
       </c>
       <c r="J76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.50804261312921806</v>
       </c>
       <c r="K76" s="66">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.5860370307457109</v>
       </c>
       <c r="L76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="M76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="N76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="O76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="P76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q76" s="66" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
     </row>
@@ -11176,47 +11245,47 @@
       <c r="E77" s="308"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
-        <f t="shared" ref="G77:Q77" si="26">IF(G$4="","",G9/G$4)</f>
+        <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
         <v>1.825442099258414E-2</v>
       </c>
       <c r="H77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.6665263866677889E-2</v>
       </c>
       <c r="I77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1.1566229000166427E-2</v>
       </c>
       <c r="J77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>7.6185555491919766E-3</v>
       </c>
       <c r="K77" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="L77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="M77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="N77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="O77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="P77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="Q77" s="6" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
     </row>
@@ -11231,51 +11300,51 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="309" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
-        <f t="shared" ref="G78:Q78" si="27">IF(G$4="","",-G10/G$4)</f>
+        <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
         <v>7.8722190530519116E-3</v>
       </c>
       <c r="H78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9.0901439272788494E-3</v>
       </c>
       <c r="I78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="J78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="K78" s="6">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="L78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="M78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="N78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="O78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="P78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="Q78" s="6" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
     </row>
@@ -11292,47 +11361,47 @@
       <c r="E79" s="308"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
-        <f t="shared" ref="G79:Q79" si="28">IF(G$4="","",G11/G$4)</f>
+        <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="H79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.8023735375810116E-2</v>
       </c>
       <c r="I79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K79" s="66">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="L79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="M79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="N79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="O79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="P79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="Q79" s="66" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
     </row>
@@ -11349,47 +11418,47 @@
       <c r="E80" s="308"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
-        <f t="shared" ref="G80:Q80" si="29">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>0</v>
+        <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
+        <v>2.9659853391308499E-2</v>
       </c>
       <c r="H80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>1.1724822264738463E-2</v>
       </c>
       <c r="I80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>3.534384710744946E-4</v>
       </c>
       <c r="J80" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
+        <f t="shared" si="31"/>
+        <v>3.1433275531812322E-4</v>
       </c>
       <c r="K80" s="6">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="L80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="M80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="N80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="O80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="P80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="Q80" s="6" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
     </row>
@@ -11406,47 +11475,47 @@
       <c r="E81" s="308"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
-        <f t="shared" ref="G81:Q81" si="30">IF(G$4="","",G13/G$4)</f>
-        <v>0.34991443240159725</v>
+        <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
+        <v>0.37957428579290575</v>
       </c>
       <c r="H81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.44415453244676373</v>
+        <f t="shared" si="32"/>
+        <v>0.4558793547115022</v>
       </c>
       <c r="I81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.47801578088839686</v>
+        <f t="shared" si="32"/>
+        <v>0.47766234241732236</v>
       </c>
       <c r="J81" s="66">
-        <f t="shared" si="30"/>
-        <v>0.51566116867841005</v>
+        <f t="shared" si="32"/>
+        <v>0.51534683592309194</v>
       </c>
       <c r="K81" s="66">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.5860370307457109</v>
       </c>
       <c r="L81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="N81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="O81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="P81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="Q81" s="66" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
     </row>
@@ -11463,47 +11532,47 @@
       <c r="E82" s="308"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
-        <f t="shared" ref="G82:Q82" si="31">IF(G$4="","",ABS(G14/G$4))</f>
+        <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
         <v>5.9212778094694808E-2</v>
       </c>
       <c r="H82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>7.2454745223466038E-2</v>
       </c>
       <c r="I82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>8.6201848617324689E-2</v>
       </c>
       <c r="J82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.10357839908312262</v>
       </c>
       <c r="K82" s="6">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="L82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="N82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="P82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Q82" s="6" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
     </row>
@@ -11521,47 +11590,47 @@
       <c r="E83" s="308"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
-        <f t="shared" ref="G83:Q83" si="32">IF(G$4="","",-G15/G$4)</f>
+        <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
         <v>0</v>
       </c>
       <c r="H83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>2.6092079791263361E-3</v>
       </c>
       <c r="I83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="J83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="K83" s="6">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="L83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="M83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="N83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="O83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="P83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q83" s="6" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
     </row>
@@ -11578,47 +11647,47 @@
       <c r="E84" s="308"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
-        <f t="shared" ref="G84:Q84" si="33">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.29070165430690248</v>
+        <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
+        <v>0.32036150769821098</v>
       </c>
       <c r="H84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.36909057924417138</v>
+        <f t="shared" si="35"/>
+        <v>0.38081540150890986</v>
       </c>
       <c r="I84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.39181393227107214</v>
+        <f t="shared" si="35"/>
+        <v>0.39146049379999764</v>
       </c>
       <c r="J84" s="66">
-        <f t="shared" si="33"/>
-        <v>0.4120827695952875</v>
+        <f t="shared" si="35"/>
+        <v>0.41176843683996933</v>
       </c>
       <c r="K84" s="66">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.5860370307457109</v>
       </c>
       <c r="L84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="M84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="N84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="O84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="P84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="Q84" s="66" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
     </row>
@@ -11685,47 +11754,47 @@
       <c r="E87" s="308"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
-        <f t="shared" ref="G87:Q87" si="34">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.29070165430690248</v>
+        <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
+        <v>0.32036150769821098</v>
       </c>
       <c r="H87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.36909057924417138</v>
+        <f t="shared" si="36"/>
+        <v>0.38081540150890986</v>
       </c>
       <c r="I87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.39181393227107214</v>
+        <f t="shared" si="36"/>
+        <v>0.39146049379999764</v>
       </c>
       <c r="J87" s="66">
-        <f t="shared" si="34"/>
-        <v>0.4120827695952875</v>
+        <f t="shared" si="36"/>
+        <v>0.41176843683996933</v>
       </c>
       <c r="K87" s="66">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.5860370307457109</v>
       </c>
       <c r="L87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="M87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="O87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="P87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="Q87" s="66" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
     </row>
@@ -11808,47 +11877,47 @@
       </c>
       <c r="E91" s="311"/>
       <c r="G91" s="76">
-        <f t="shared" ref="G91:Q91" si="35">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
       </c>
       <c r="H91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4739.6903628800001</v>
       </c>
       <c r="I91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4657.9715635199991</v>
       </c>
       <c r="J91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="K91" s="76">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="L91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="O91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Q91" s="76" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
@@ -11863,47 +11932,47 @@
       </c>
       <c r="E92" s="311"/>
       <c r="G92" s="175">
-        <f t="shared" ref="G92:Q92" si="36">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.8601610529356356</v>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <v>1.6879427845465798</v>
       </c>
       <c r="H92" s="175">
-        <f t="shared" si="36"/>
-        <v>1.0808464851321227</v>
+        <f t="shared" si="38"/>
+        <v>1.0475685954159291</v>
       </c>
       <c r="I92" s="175">
-        <f t="shared" si="36"/>
-        <v>0.75960354445630085</v>
+        <f t="shared" si="38"/>
+        <v>0.76028936874668918</v>
       </c>
       <c r="J92" s="175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="K92" s="175">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="L92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Q92" s="175" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
     </row>
@@ -11914,51 +11983,51 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.3417721518987331E-2</v>
+        <v>7.4454428754813853E-2</v>
       </c>
       <c r="E93" s="311"/>
       <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="37">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.3417721518987331E-2</v>
+        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
+        <v>7.4454428754813853E-2</v>
       </c>
       <c r="H93" s="23">
-        <f t="shared" si="37"/>
-        <v>7.3417721518987331E-2</v>
+        <f t="shared" si="39"/>
+        <v>7.4454428754813853E-2</v>
       </c>
       <c r="I93" s="23">
-        <f t="shared" si="37"/>
-        <v>7.2151898734177211E-2</v>
+        <f t="shared" si="39"/>
+        <v>7.3170731707317069E-2</v>
       </c>
       <c r="J93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="K93" s="23">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="L93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="M93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="N93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="O93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="P93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="Q93" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
@@ -12000,47 +12069,47 @@
       <c r="E96" s="308"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="38">IF(H4="","",G4/H4-1)</f>
+        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
         <v>-0.26226748590186011</v>
       </c>
       <c r="H96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.2408579989228844</v>
       </c>
       <c r="I96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>-0.35945953217712834</v>
       </c>
       <c r="J96" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>3.150394387463904</v>
       </c>
       <c r="K96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="L96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="M96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="N96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="O96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="P96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="Q96" s="6" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
     </row>
@@ -12051,53 +12120,53 @@
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>9.9776867121067703E-2</v>
+        <v>1.3840538284081383E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="308"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="39">IF(H5="","",G13/H13-1)</f>
-        <v>-0.41879855978775815</v>
+        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <v>-0.38574912583568022</v>
       </c>
       <c r="H97" s="6">
-        <f t="shared" si="39"/>
-        <v>-0.29463341163661705</v>
+        <f t="shared" si="41"/>
+        <v>-0.2754773930177763</v>
       </c>
       <c r="I97" s="6">
-        <f t="shared" si="39"/>
-        <v>-0.40622162281154406</v>
+        <f t="shared" si="41"/>
+        <v>-0.40629875077176036</v>
       </c>
       <c r="J97" s="6">
-        <f t="shared" si="39"/>
-        <v>2.6519829089855076</v>
+        <f t="shared" si="41"/>
+        <v>2.6497567614299369</v>
       </c>
       <c r="K97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="L97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="M97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="N97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="O97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="P97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="Q97" s="6" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
@@ -12150,47 +12219,47 @@
       <c r="E101" s="312"/>
       <c r="F101" s="26"/>
       <c r="G101" s="187">
-        <f t="shared" ref="G101:Q101" si="40">IF(G$4="","",G105+G104)</f>
+        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>180344</v>
       </c>
       <c r="H101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>174007</v>
       </c>
       <c r="I101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="J101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="K101" s="187">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="L101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="M101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="N101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="O101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="P101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
       <c r="Q101" s="187" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
@@ -12462,47 +12531,47 @@
       <c r="E108" s="312"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
-        <f t="shared" ref="G108:Q108" si="41">IF(G$4="","",G102/G$4)</f>
+        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
         <v>0.82726754135767255</v>
       </c>
       <c r="H108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J108" s="97">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="K108" s="97" t="e">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>#VALUE!</v>
       </c>
       <c r="L108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q108" s="97" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
@@ -12519,47 +12588,47 @@
       <c r="E109" s="312"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
-        <f t="shared" ref="G109:Q109" si="42">IF(G$4="","",G103/G$4)</f>
+        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
         <v>1.8698231602966344</v>
       </c>
       <c r="H109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="I109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="J109" s="97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="K109" s="97" t="e">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>#VALUE!</v>
       </c>
       <c r="L109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="M109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="N109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="O109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="P109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="Q109" s="97" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
     </row>
@@ -12659,47 +12728,47 @@
       </c>
       <c r="E113" s="311"/>
       <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="43">G81</f>
-        <v>0.34991443240159725</v>
+        <f t="shared" ref="G113:Q113" si="45">G81</f>
+        <v>0.37957428579290575</v>
       </c>
       <c r="H113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.44415453244676373</v>
+        <f t="shared" si="45"/>
+        <v>0.4558793547115022</v>
       </c>
       <c r="I113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.47801578088839686</v>
+        <f t="shared" si="45"/>
+        <v>0.47766234241732236</v>
       </c>
       <c r="J113" s="23">
-        <f t="shared" si="43"/>
-        <v>0.51566116867841005</v>
+        <f t="shared" si="45"/>
+        <v>0.51534683592309194</v>
       </c>
       <c r="K113" s="23">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.5860370307457109</v>
       </c>
       <c r="L113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="M113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="N113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="O113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="P113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="Q113" s="23" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
@@ -12713,47 +12782,47 @@
       </c>
       <c r="E114" s="311"/>
       <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="44">IF(G4="","",G4/G101)</f>
+        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>4.8601561460320276E-2</v>
       </c>
       <c r="H114" s="42">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>6.8278862344618316E-2</v>
       </c>
       <c r="I114" s="42" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J114" s="42" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K114" s="42" t="e">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="M114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="N114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="O114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="P114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="Q114" s="42" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
@@ -12769,47 +12838,47 @@
       <c r="E115" s="315"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="45">IF(G$4="","",G101/G105)</f>
+        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.0843454628538445</v>
       </c>
       <c r="H115" s="15">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>1.0668403788970295</v>
       </c>
       <c r="I115" s="15" t="e">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J115" s="15" t="e">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K115" s="15" t="e">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="M115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="N115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="O115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="P115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
       <c r="Q115" s="15" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
@@ -12826,47 +12895,47 @@
       <c r="E116" s="314"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="46">IF(G$4="","",G8/G105)</f>
+        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
         <v>1.4051564491690517E-2</v>
       </c>
       <c r="H116" s="105">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>2.6118144753379726E-2</v>
       </c>
       <c r="I116" s="105" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J116" s="105" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K116" s="105" t="e">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="M116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="O116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="P116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="Q116" s="105" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
@@ -12947,47 +13016,47 @@
       <c r="E120" s="308"/>
       <c r="F120" s="27"/>
       <c r="G120" s="182">
-        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.31180095889260018</v>
+        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.34361354265677985</v>
       </c>
       <c r="H120" s="182">
-        <f t="shared" si="47"/>
-        <v>0.53661644644114359</v>
+        <f t="shared" si="49"/>
+        <v>0.55366302745045104</v>
       </c>
       <c r="I120" s="182">
-        <f t="shared" si="47"/>
-        <v>0.7503914432205383</v>
+        <f t="shared" si="49"/>
+        <v>0.74971454742241805</v>
       </c>
       <c r="J120" s="182">
-        <f t="shared" si="47"/>
-        <v>1.2320997841199808</v>
+        <f t="shared" si="49"/>
+        <v>1.2311599503085606</v>
       </c>
       <c r="K120" s="182">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.42217947730748451</v>
       </c>
       <c r="L120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="M120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="N120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="O120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="P120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="Q120" s="182" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
@@ -12998,53 +13067,53 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9354193616452378E-2</v>
+        <v>3.9909901100125003E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="308"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
-        <f t="shared" ref="G121" si="48">IF(G$4="","",G120/Market_Price)</f>
-        <v>3.9468475809189892E-2</v>
+        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
+        <v>4.4109569018842082E-2</v>
       </c>
       <c r="H121" s="79">
-        <f t="shared" ref="H121" si="49">IF(H$4="","",H120/Market_Price)</f>
-        <v>6.7926132460904246E-2</v>
+        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
+        <v>7.1073559364627864E-2</v>
       </c>
       <c r="I121" s="79">
-        <f t="shared" ref="I121" si="50">IF(I$4="","",I120/Market_Price)</f>
-        <v>9.4986258635511175E-2</v>
+        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
+        <v>9.6240635099155078E-2</v>
       </c>
       <c r="J121" s="79">
-        <f t="shared" ref="J121" si="51">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.15596199798987098</v>
+        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
+        <v>0.15804363932073948</v>
       </c>
       <c r="K121" s="79">
-        <f t="shared" ref="K121" si="52">IF(K$4="","",K120/Market_Price)</f>
-        <v>5.3440440165504366E-2</v>
+        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
+        <v>5.4195054853335624E-2</v>
       </c>
       <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="53">IF(L$4="","",L120/Market_Price)</f>
+        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
         <v/>
       </c>
       <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="54">IF(M$4="","",M120/Market_Price)</f>
+        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
         <v/>
       </c>
       <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="55">IF(N$4="","",N120/Market_Price)</f>
+        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
         <v/>
       </c>
       <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="56">IF(O$4="","",O120/Market_Price)</f>
+        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
         <v/>
       </c>
       <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="57">IF(P$4="","",P120/Market_Price)</f>
+        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
         <v/>
       </c>
       <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="58">IF(Q$4="","",Q120/Market_Price)</f>
+        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
         <v/>
       </c>
     </row>
@@ -15311,7 +15380,7 @@
       </c>
       <c r="I3" s="272">
         <f>-Market_Price</f>
-        <v>-7.9</v>
+        <v>-7.79</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15394,7 +15463,7 @@
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>2548</v>
+        <v>2807.968614974819</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15500,7 +15569,7 @@
       </c>
       <c r="C14" s="163">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.36747573837633207</v>
+        <v>-0.34649046142280127</v>
       </c>
       <c r="E14" s="348"/>
       <c r="F14" s="348"/>
@@ -15551,7 +15620,7 @@
       </c>
       <c r="C21" s="165">
         <f>Market_Price</f>
-        <v>7.9</v>
+        <v>7.79</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16030,12 +16099,15 @@
         <v>312</v>
       </c>
       <c r="C72" s="280" t="str">
-        <f>IF(E72&gt;50%,"Y","N")</f>
+        <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="E72" s="138" t="str">
-        <f>"Non-FCF Value is "&amp;ROUND(BS!D89/C60*100,0)&amp;"% of the Expected Equity Value"</f>
-        <v>Non-FCF Value is 63% of the Expected Equity Value</v>
+      <c r="E72" s="138" t="s">
+        <v>390</v>
+      </c>
+      <c r="F72" s="339">
+        <f>BS!D89/C60</f>
+        <v>0.62612608991135499</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16145,7 +16217,7 @@
       </c>
       <c r="C86" s="274">
         <f>Market_Price</f>
-        <v>7.9</v>
+        <v>7.79</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16158,7 +16230,7 @@
       </c>
       <c r="C87" s="273">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11614149089878545</v>
+        <v>0.12172735692567005</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCAA11D-7024-4A74-A7A1-1E8F74F89D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D66181-D6A0-4D46-B420-5BB53141988F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2674,7 +2674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="350">
+  <cellXfs count="348">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3017,7 +3017,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3239,9 +3238,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3381,20 +3377,20 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3706,15 +3702,15 @@
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="292" t="s">
+      <c r="E1" s="290" t="s">
         <v>349</v>
       </c>
-      <c r="F1" s="293" t="s">
+      <c r="F1" s="291" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A2" s="254" t="s">
+      <c r="A2" s="253" t="s">
         <v>281</v>
       </c>
       <c r="B2" s="36"/>
@@ -3774,7 +3770,7 @@
       <c r="B8" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="287">
+      <c r="C8" s="285">
         <v>6</v>
       </c>
       <c r="D8" s="5"/>
@@ -3808,13 +3804,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="339" t="s">
         <v>286</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3869,7 +3865,7 @@
       <c r="B19" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C19" s="256">
+      <c r="C19" s="255">
         <v>0.2</v>
       </c>
       <c r="E19" s="5"/>
@@ -3879,14 +3875,14 @@
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="259">
+      <c r="C20" s="258">
         <f>C127</f>
         <v>6.4501768017717804</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="E20" s="322">
+      <c r="E20" s="320">
         <v>3</v>
       </c>
     </row>
@@ -3894,7 +3890,7 @@
       <c r="B21" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C21" s="288">
+      <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
         <v>0.12172735692567005</v>
       </c>
@@ -3906,7 +3902,7 @@
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A23" s="254" t="s">
+      <c r="A23" s="253" t="s">
         <v>235</v>
       </c>
       <c r="B23" s="36"/>
@@ -3916,25 +3912,25 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="339" t="s">
         <v>236</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="344" t="s">
+      <c r="B26" s="340" t="s">
         <v>381</v>
       </c>
-      <c r="C26" s="344"/>
-      <c r="D26" s="344"/>
-      <c r="E26" s="344"/>
-      <c r="F26" s="344"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B28" s="241" t="s">
+      <c r="B28" s="240" t="s">
         <v>237</v>
       </c>
       <c r="C28" s="111">
@@ -3943,19 +3939,19 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="342" t="s">
+      <c r="B29" s="338" t="s">
         <v>238</v>
       </c>
-      <c r="C29" s="342"/>
-      <c r="D29" s="342"/>
-      <c r="E29" s="342"/>
-      <c r="F29" s="342"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C30" s="192">
+      <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
         <v>2591.8202592374382</v>
       </c>
@@ -3969,19 +3965,19 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="342" t="s">
+      <c r="B32" s="338" t="s">
         <v>240</v>
       </c>
-      <c r="C32" s="342"/>
-      <c r="D32" s="342"/>
-      <c r="E32" s="342"/>
-      <c r="F32" s="342"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="192">
+      <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
         <v>159.99999999999997</v>
       </c>
@@ -3994,7 +3990,7 @@
       <c r="B34" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="C34" s="192">
+      <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
         <v>-159.99999999999997</v>
       </c>
@@ -4004,19 +4000,19 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="342" t="s">
+      <c r="B36" s="338" t="s">
         <v>243</v>
       </c>
-      <c r="C36" s="342"/>
-      <c r="D36" s="342"/>
-      <c r="E36" s="342"/>
-      <c r="F36" s="342"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="C37" s="192">
+      <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
         <v>639</v>
       </c>
@@ -4026,19 +4022,19 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="342" t="s">
+      <c r="B39" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C39" s="342"/>
-      <c r="D39" s="342"/>
-      <c r="E39" s="342"/>
-      <c r="F39" s="342"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
         <v>382</v>
       </c>
-      <c r="C40" s="332">
+      <c r="C40" s="330">
         <f>Normalized_FCF!C48</f>
         <v>185.19539222287685</v>
       </c>
@@ -4046,14 +4042,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="331"/>
-      <c r="F40" s="331"/>
+      <c r="E40" s="329"/>
+      <c r="F40" s="329"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
         <v>383</v>
       </c>
-      <c r="C41" s="332">
+      <c r="C41" s="330">
         <f>Normalized_FCF!C47</f>
         <v>-43</v>
       </c>
@@ -4061,14 +4057,14 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="331"/>
-      <c r="F41" s="331"/>
+      <c r="E41" s="329"/>
+      <c r="F41" s="329"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="C42" s="192">
+      <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
         <v>142.19539222287685</v>
       </c>
@@ -4086,7 +4082,7 @@
       <c r="B45" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
         <v>-22.869707937042335</v>
       </c>
@@ -4096,19 +4092,19 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="342" t="s">
+      <c r="B47" s="338" t="s">
         <v>248</v>
       </c>
-      <c r="C47" s="342"/>
-      <c r="D47" s="342"/>
-      <c r="E47" s="342"/>
-      <c r="F47" s="342"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="C48" s="192">
+      <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
         <v>-809.52375635047554</v>
       </c>
@@ -4118,13 +4114,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="342" t="s">
+      <c r="B50" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4140,28 +4136,28 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="339" t="s">
         <v>385</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="339" t="s">
         <v>268</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
         <v>2807.968614974819</v>
       </c>
@@ -4174,7 +4170,7 @@
       <c r="B57" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
         <v>2540.6221871727971</v>
       </c>
@@ -4184,7 +4180,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B58" s="261" t="s">
+      <c r="B58" s="260" t="s">
         <v>284</v>
       </c>
       <c r="C58" s="94">
@@ -4193,7 +4189,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B59" s="261" t="s">
+      <c r="B59" s="260" t="s">
         <v>340</v>
       </c>
       <c r="C59" s="94">
@@ -4202,7 +4198,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A61" s="254" t="s">
+      <c r="A61" s="253" t="s">
         <v>302</v>
       </c>
       <c r="B61" s="36"/>
@@ -4212,29 +4208,29 @@
       <c r="F61" s="36"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" s="240"/>
+      <c r="A62" s="239"/>
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="338" t="s">
         <v>303</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="344" t="s">
+      <c r="B64" s="340" t="s">
         <v>259</v>
       </c>
-      <c r="C64" s="344"/>
-      <c r="D64" s="344"/>
-      <c r="E64" s="344"/>
-      <c r="F64" s="344"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B66" s="241" t="s">
+      <c r="B66" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4242,7 +4238,7 @@
       <c r="B67" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C67" s="320">
+      <c r="C67" s="318">
         <v>0.08</v>
       </c>
     </row>
@@ -4250,11 +4246,11 @@
       <c r="B68" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C68" s="271">
+      <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D68" s="295" t="s">
+      <c r="D68" s="293" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4262,11 +4258,11 @@
       <c r="B69" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C69" s="271">
+      <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="295" t="s">
+      <c r="D69" s="293" t="s">
         <v>357</v>
       </c>
     </row>
@@ -4274,7 +4270,7 @@
       <c r="B70" s="82" t="s">
         <v>254</v>
       </c>
-      <c r="C70" s="271">
+      <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
         <v>0.09</v>
       </c>
@@ -4283,28 +4279,28 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="340" t="s">
+      <c r="B72" s="339" t="s">
         <v>386</v>
       </c>
-      <c r="C72" s="340"/>
-      <c r="D72" s="340"/>
-      <c r="E72" s="340"/>
-      <c r="F72" s="340"/>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="339" t="s">
         <v>387</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C75" s="271">
+      <c r="C75" s="269">
         <v>0</v>
       </c>
     </row>
@@ -4312,7 +4308,7 @@
       <c r="B76" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="C76" s="255">
+      <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
         <v>3.4544236618885975</v>
       </c>
@@ -4322,7 +4318,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="254" t="s">
+      <c r="A78" s="253" t="s">
         <v>260</v>
       </c>
       <c r="B78" s="36"/>
@@ -4332,16 +4328,16 @@
       <c r="F78" s="36"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="240"/>
+      <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="340" t="s">
+      <c r="B80" s="339" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="340"/>
-      <c r="D80" s="340"/>
-      <c r="E80" s="340"/>
-      <c r="F80" s="340"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4349,24 +4345,24 @@
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="241" t="s">
+      <c r="B83" s="240" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="340" t="s">
+      <c r="B84" s="339" t="s">
         <v>388</v>
       </c>
-      <c r="C84" s="340"/>
-      <c r="D84" s="340"/>
-      <c r="E84" s="340"/>
-      <c r="F84" s="340"/>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="C85" s="192">
+      <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
         <v>3093</v>
       </c>
@@ -4379,7 +4375,7 @@
       <c r="B86" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="C86" s="255">
+      <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
         <v>0.37849307922088393</v>
       </c>
@@ -4397,7 +4393,7 @@
       <c r="B89" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="C89" s="192">
+      <c r="C89" s="191">
         <f>BS!C66</f>
         <v>47679</v>
       </c>
@@ -4410,7 +4406,7 @@
       <c r="B90" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C90" s="192">
+      <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
         <v>41505.820259237436</v>
       </c>
@@ -4423,7 +4419,7 @@
       <c r="B91" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="C91" s="255">
+      <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
         <v>5.0791030441342784</v>
       </c>
@@ -4441,7 +4437,7 @@
       <c r="B94" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C94" s="192">
+      <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
         <v>7814.4</v>
       </c>
@@ -4454,7 +4450,7 @@
       <c r="B95" s="47" t="s">
         <v>306</v>
       </c>
-      <c r="C95" s="255">
+      <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
@@ -4464,19 +4460,19 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="340" t="s">
+      <c r="B97" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C97" s="340"/>
-      <c r="D97" s="340"/>
-      <c r="E97" s="340"/>
-      <c r="F97" s="340"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
         <v>300</v>
       </c>
-      <c r="C99" s="255">
+      <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
         <v>9.111288498532895</v>
       </c>
@@ -4486,7 +4482,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="254" t="s">
+      <c r="A101" s="253" t="s">
         <v>277</v>
       </c>
       <c r="B101" s="36"/>
@@ -4496,165 +4492,165 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="342" t="s">
+      <c r="B103" s="338" t="s">
         <v>369</v>
       </c>
-      <c r="C103" s="342"/>
-      <c r="D103" s="342"/>
-      <c r="E103" s="342"/>
-      <c r="F103" s="342"/>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="267" t="s">
+      <c r="B105" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="C105" s="267" t="s">
+      <c r="C105" s="266" t="s">
         <v>137</v>
       </c>
-      <c r="D105" s="267" t="s">
+      <c r="D105" s="266" t="s">
         <v>117</v>
       </c>
-      <c r="E105" s="267" t="s">
+      <c r="E105" s="266" t="s">
         <v>270</v>
       </c>
-      <c r="F105" s="267" t="s">
+      <c r="F105" s="266" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="262" t="str">
+      <c r="B106" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="263">
+      <c r="C106" s="262">
         <f>Valuation_Model!C74</f>
         <v>0.05</v>
       </c>
-      <c r="D106" s="264">
+      <c r="D106" s="263">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E106" s="265" t="str">
+      <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.16 HKD</v>
       </c>
-      <c r="F106" s="266">
+      <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="249" t="str">
+      <c r="B107" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="250">
+      <c r="C107" s="249">
         <f>Valuation_Model!C75</f>
         <v>0.02</v>
       </c>
-      <c r="D107" s="251">
+      <c r="D107" s="250">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E107" s="252" t="str">
+      <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>9.34 HKD</v>
       </c>
-      <c r="F107" s="253">
+      <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999992</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="249" t="str">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="250">
+      <c r="C108" s="249">
         <f>Valuation_Model!C76</f>
         <v>0</v>
       </c>
-      <c r="D108" s="251">
+      <c r="D108" s="250">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E108" s="252" t="str">
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>9.11 HKD</v>
       </c>
-      <c r="F108" s="253">
+      <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
         <v>0.495</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="249" t="str">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="250">
+      <c r="C109" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.05</v>
       </c>
-      <c r="D109" s="251">
+      <c r="D109" s="250">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E109" s="252" t="str">
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>8.62 HKD</v>
       </c>
-      <c r="F109" s="253">
+      <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="249" t="str">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="250">
+      <c r="C110" s="249">
         <f>Valuation_Model!C78</f>
         <v>-0.2</v>
       </c>
-      <c r="D110" s="251">
+      <c r="D110" s="250">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E110" s="252" t="str">
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>7.26 HKD</v>
       </c>
-      <c r="F110" s="253">
+      <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="242" t="s">
+      <c r="B112" s="241" t="s">
         <v>269</v>
       </c>
-      <c r="C112" s="248">
+      <c r="C112" s="247">
         <f>Scenarios!C60</f>
         <v>9.0347055134616365</v>
       </c>
-      <c r="D112" s="243" t="str">
+      <c r="D112" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="345" t="s">
+      <c r="B114" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C114" s="345"/>
-      <c r="D114" s="345"/>
-      <c r="E114" s="345"/>
-      <c r="F114" s="345"/>
+      <c r="C114" s="343"/>
+      <c r="D114" s="343"/>
+      <c r="E114" s="343"/>
+      <c r="F114" s="343"/>
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="254" t="s">
+      <c r="A116" s="253" t="s">
         <v>299</v>
       </c>
       <c r="B116" s="36"/>
@@ -4673,7 +4669,7 @@
       <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="241" t="s">
+      <c r="B119" s="240" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4681,7 +4677,7 @@
       <c r="B120" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C120" s="258">
+      <c r="C120" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
@@ -4690,45 +4686,45 @@
       <c r="B121" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C121" s="257">
+      <c r="C121" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="243" t="s">
+      <c r="B122" s="242" t="s">
         <v>272</v>
       </c>
-      <c r="C122" s="244">
+      <c r="C122" s="243">
         <f>Scenarios!C77</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="D122" s="243" t="str">
+      <c r="D122" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="241" t="s">
+      <c r="B124" s="240" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="243" t="str">
+      <c r="B125" s="242" t="str">
         <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="247">
+      <c r="C125" s="246">
         <f>Scenarios!C81</f>
         <v>1.2217592592592592</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="243" t="str">
+      <c r="B126" s="242" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="247">
+      <c r="C126" s="246">
         <f>Scenarios!C82</f>
         <v>5.2284175425125214</v>
       </c>
@@ -4737,7 +4733,7 @@
       <c r="B127" s="82" t="s">
         <v>271</v>
       </c>
-      <c r="C127" s="246">
+      <c r="C127" s="245">
         <f>Scenarios!C83</f>
         <v>6.4501768017717804</v>
       </c>
@@ -4747,22 +4743,16 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="245" t="s">
+      <c r="B128" s="244" t="s">
         <v>273</v>
       </c>
-      <c r="C128" s="158">
+      <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>-0.28606673541699057</v>
+        <v>0.28606673541699057</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4778,6 +4768,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4887,277 +4883,277 @@
       <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="194">
+      <c r="C4" s="193">
         <v>8765</v>
       </c>
-      <c r="D4" s="185">
+      <c r="D4" s="184">
         <v>11881</v>
       </c>
-      <c r="E4" s="185">
+      <c r="E4" s="184">
         <v>15650.563377</v>
       </c>
-      <c r="F4" s="185">
+      <c r="F4" s="184">
         <v>24433.371759000001</v>
       </c>
-      <c r="G4" s="185">
+      <c r="G4" s="184">
         <v>5887</v>
       </c>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="185"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="185"/>
+      <c r="H4" s="184"/>
+      <c r="I4" s="184"/>
+      <c r="J4" s="184"/>
+      <c r="K4" s="184"/>
+      <c r="L4" s="184"/>
+      <c r="M4" s="184"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="194">
+      <c r="C5" s="193">
         <v>5344</v>
       </c>
-      <c r="D5" s="185">
+      <c r="D5" s="184">
         <v>6492</v>
       </c>
-      <c r="E5" s="185">
+      <c r="E5" s="184">
         <v>7482.8818240000001</v>
       </c>
-      <c r="F5" s="185">
+      <c r="F5" s="184">
         <v>11196.89644</v>
       </c>
-      <c r="G5" s="185">
+      <c r="G5" s="184">
         <v>2437</v>
       </c>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="185"/>
-      <c r="M5" s="185"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
+      <c r="J5" s="184"/>
+      <c r="K5" s="184"/>
+      <c r="L5" s="184"/>
+      <c r="M5" s="184"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="194">
+      <c r="C6" s="193">
         <v>1084</v>
       </c>
-      <c r="D6" s="185">
+      <c r="D6" s="184">
         <v>1129</v>
       </c>
-      <c r="E6" s="185">
+      <c r="E6" s="184">
         <v>867.48327900000004</v>
       </c>
-      <c r="F6" s="185">
+      <c r="F6" s="184">
         <v>823.28128300000003</v>
       </c>
-      <c r="G6" s="185"/>
-      <c r="H6" s="185"/>
-      <c r="I6" s="185"/>
-      <c r="J6" s="185"/>
-      <c r="K6" s="185"/>
-      <c r="L6" s="185"/>
-      <c r="M6" s="185"/>
+      <c r="G6" s="184"/>
+      <c r="H6" s="184"/>
+      <c r="I6" s="184"/>
+      <c r="J6" s="184"/>
+      <c r="K6" s="184"/>
+      <c r="L6" s="184"/>
+      <c r="M6" s="184"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="195"/>
-      <c r="D7" s="193"/>
-      <c r="E7" s="193"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="193"/>
-      <c r="L7" s="193"/>
-      <c r="M7" s="193"/>
+      <c r="C7" s="194"/>
+      <c r="D7" s="192"/>
+      <c r="E7" s="192"/>
+      <c r="F7" s="192"/>
+      <c r="G7" s="192"/>
+      <c r="H7" s="192"/>
+      <c r="I7" s="192"/>
+      <c r="J7" s="192"/>
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="194"/>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
-      <c r="F8" s="185"/>
-      <c r="G8" s="185"/>
-      <c r="H8" s="185"/>
-      <c r="I8" s="185"/>
-      <c r="J8" s="185"/>
-      <c r="K8" s="185"/>
-      <c r="L8" s="185"/>
-      <c r="M8" s="185"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="184"/>
+      <c r="E8" s="184"/>
+      <c r="F8" s="184"/>
+      <c r="G8" s="184"/>
+      <c r="H8" s="184"/>
+      <c r="I8" s="184"/>
+      <c r="J8" s="184"/>
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="194">
+      <c r="C9" s="193">
         <v>639</v>
       </c>
-      <c r="D9" s="185">
+      <c r="D9" s="184">
         <v>927</v>
       </c>
-      <c r="E9" s="185"/>
-      <c r="F9" s="185"/>
-      <c r="G9" s="185"/>
-      <c r="H9" s="185"/>
-      <c r="I9" s="185"/>
-      <c r="J9" s="185"/>
-      <c r="K9" s="185"/>
-      <c r="L9" s="185"/>
-      <c r="M9" s="185"/>
+      <c r="E9" s="184"/>
+      <c r="F9" s="184"/>
+      <c r="G9" s="184"/>
+      <c r="H9" s="184"/>
+      <c r="I9" s="184"/>
+      <c r="J9" s="184"/>
+      <c r="K9" s="184"/>
+      <c r="L9" s="184"/>
+      <c r="M9" s="184"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="194"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="185"/>
-      <c r="G10" s="185"/>
-      <c r="H10" s="185"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="185"/>
+      <c r="C10" s="193"/>
+      <c r="D10" s="184"/>
+      <c r="E10" s="184"/>
+      <c r="F10" s="184"/>
+      <c r="G10" s="184"/>
+      <c r="H10" s="184"/>
+      <c r="I10" s="184"/>
+      <c r="J10" s="184"/>
+      <c r="K10" s="184"/>
+      <c r="L10" s="184"/>
+      <c r="M10" s="184"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="194"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
+      <c r="C11" s="193"/>
+      <c r="D11" s="184"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="184"/>
+      <c r="G11" s="184"/>
+      <c r="H11" s="184"/>
+      <c r="I11" s="184"/>
+      <c r="J11" s="184"/>
+      <c r="K11" s="184"/>
+      <c r="L11" s="184"/>
+      <c r="M11" s="184"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="194">
+      <c r="C12" s="193">
         <v>43</v>
       </c>
-      <c r="D12" s="185">
+      <c r="D12" s="184">
         <v>40.775368</v>
       </c>
-      <c r="E12" s="185">
+      <c r="E12" s="184">
         <v>49.197794000000002</v>
       </c>
-      <c r="F12" s="185">
+      <c r="F12" s="184">
         <v>81.763175000000004</v>
       </c>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
+      <c r="G12" s="184"/>
+      <c r="H12" s="184"/>
+      <c r="I12" s="184"/>
+      <c r="J12" s="184"/>
+      <c r="K12" s="184"/>
+      <c r="L12" s="184"/>
+      <c r="M12" s="184"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="194">
+      <c r="C13" s="193">
         <v>2340</v>
       </c>
-      <c r="D13" s="185">
+      <c r="D13" s="184">
         <v>1390.845307</v>
       </c>
-      <c r="E13" s="185">
+      <c r="E13" s="184">
         <v>337.25969199999997</v>
       </c>
-      <c r="F13" s="185">
+      <c r="F13" s="184">
         <v>572.18514300000004</v>
       </c>
-      <c r="G13" s="185"/>
-      <c r="H13" s="185"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="185"/>
-      <c r="K13" s="185"/>
-      <c r="L13" s="185"/>
-      <c r="M13" s="185"/>
+      <c r="G13" s="184"/>
+      <c r="H13" s="184"/>
+      <c r="I13" s="184"/>
+      <c r="J13" s="184"/>
+      <c r="K13" s="184"/>
+      <c r="L13" s="184"/>
+      <c r="M13" s="184"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="194">
+      <c r="C14" s="193">
         <v>519</v>
       </c>
-      <c r="D14" s="185">
+      <c r="D14" s="184">
         <v>860.83482800000002</v>
       </c>
-      <c r="E14" s="185">
+      <c r="E14" s="184">
         <v>1349.107495</v>
       </c>
-      <c r="F14" s="185">
+      <c r="F14" s="184">
         <v>2530.7695309999999</v>
       </c>
-      <c r="G14" s="185"/>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="185"/>
-      <c r="L14" s="185"/>
-      <c r="M14" s="185"/>
+      <c r="G14" s="184"/>
+      <c r="H14" s="184"/>
+      <c r="I14" s="184"/>
+      <c r="J14" s="184"/>
+      <c r="K14" s="184"/>
+      <c r="L14" s="184"/>
+      <c r="M14" s="184"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="196">
+      <c r="C15" s="195">
         <v>4251</v>
       </c>
-      <c r="D15" s="186">
+      <c r="D15" s="185">
         <v>5880</v>
       </c>
-      <c r="E15" s="186">
+      <c r="E15" s="185">
         <v>5735.3965490000001</v>
       </c>
-      <c r="F15" s="186">
+      <c r="F15" s="185">
         <v>9646.0369900000005</v>
       </c>
-      <c r="G15" s="186"/>
-      <c r="H15" s="186"/>
-      <c r="I15" s="186"/>
-      <c r="J15" s="186"/>
-      <c r="K15" s="186"/>
-      <c r="L15" s="186"/>
-      <c r="M15" s="186"/>
+      <c r="G15" s="185"/>
+      <c r="H15" s="185"/>
+      <c r="I15" s="185"/>
+      <c r="J15" s="185"/>
+      <c r="K15" s="185"/>
+      <c r="L15" s="185"/>
+      <c r="M15" s="185"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="194">
+      <c r="C16" s="193">
         <v>-151</v>
       </c>
-      <c r="D16" s="185">
+      <c r="D16" s="184">
         <v>31</v>
       </c>
-      <c r="E16" s="185"/>
-      <c r="F16" s="185"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="185"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="185"/>
+      <c r="E16" s="184"/>
+      <c r="F16" s="184"/>
+      <c r="G16" s="184"/>
+      <c r="H16" s="184"/>
+      <c r="I16" s="184"/>
+      <c r="J16" s="184"/>
+      <c r="K16" s="184"/>
+      <c r="L16" s="184"/>
+      <c r="M16" s="184"/>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
@@ -5169,65 +5165,65 @@
       <c r="B19" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="185">
+      <c r="C19" s="184">
         <v>160</v>
       </c>
-      <c r="D19" s="185">
+      <c r="D19" s="184">
         <v>198</v>
       </c>
-      <c r="E19" s="185">
+      <c r="E19" s="184">
         <v>181.018</v>
       </c>
-      <c r="F19" s="185">
+      <c r="F19" s="184">
         <v>186.14699999999999</v>
       </c>
-      <c r="G19" s="185"/>
-      <c r="H19" s="185"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="185"/>
-      <c r="L19" s="185"/>
-      <c r="M19" s="185"/>
+      <c r="G19" s="184"/>
+      <c r="H19" s="184"/>
+      <c r="I19" s="184"/>
+      <c r="J19" s="184"/>
+      <c r="K19" s="184"/>
+      <c r="L19" s="184"/>
+      <c r="M19" s="184"/>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="185">
+      <c r="C20" s="184">
         <v>69</v>
       </c>
-      <c r="D20" s="185">
+      <c r="D20" s="184">
         <v>108</v>
       </c>
-      <c r="E20" s="185"/>
-      <c r="F20" s="185"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="185"/>
-      <c r="L20" s="185"/>
-      <c r="M20" s="185"/>
+      <c r="E20" s="184"/>
+      <c r="F20" s="184"/>
+      <c r="G20" s="184"/>
+      <c r="H20" s="184"/>
+      <c r="I20" s="184"/>
+      <c r="J20" s="184"/>
+      <c r="K20" s="184"/>
+      <c r="L20" s="184"/>
+      <c r="M20" s="184"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="185">
+      <c r="C21" s="184">
         <v>910</v>
       </c>
-      <c r="D21" s="185">
+      <c r="D21" s="184">
         <v>2541</v>
       </c>
-      <c r="E21" s="185"/>
-      <c r="F21" s="185"/>
-      <c r="G21" s="185"/>
-      <c r="H21" s="185"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="185"/>
-      <c r="L21" s="185"/>
-      <c r="M21" s="185"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="184"/>
+      <c r="G21" s="184"/>
+      <c r="H21" s="184"/>
+      <c r="I21" s="184"/>
+      <c r="J21" s="184"/>
+      <c r="K21" s="184"/>
+      <c r="L21" s="184"/>
+      <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="24" t="str">
@@ -5262,93 +5258,93 @@
       <c r="B25" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="187"/>
-      <c r="D25" s="185">
+      <c r="C25" s="186"/>
+      <c r="D25" s="184">
         <v>7251</v>
       </c>
-      <c r="E25" s="185"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="185"/>
+      <c r="E25" s="184"/>
+      <c r="F25" s="184"/>
+      <c r="G25" s="184"/>
+      <c r="H25" s="184"/>
+      <c r="I25" s="184"/>
+      <c r="J25" s="184"/>
+      <c r="K25" s="184"/>
+      <c r="L25" s="184"/>
+      <c r="M25" s="184"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="187"/>
-      <c r="D26" s="185">
+      <c r="C26" s="186"/>
+      <c r="D26" s="184">
         <v>16389</v>
       </c>
-      <c r="E26" s="185"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="185"/>
-      <c r="M26" s="185"/>
+      <c r="E26" s="184"/>
+      <c r="F26" s="184"/>
+      <c r="G26" s="184"/>
+      <c r="H26" s="184"/>
+      <c r="I26" s="184"/>
+      <c r="J26" s="184"/>
+      <c r="K26" s="184"/>
+      <c r="L26" s="184"/>
+      <c r="M26" s="184"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="186">
+      <c r="C27" s="185">
         <v>14028</v>
       </c>
-      <c r="D27" s="186">
+      <c r="D27" s="185">
         <v>10902</v>
       </c>
-      <c r="E27" s="186"/>
-      <c r="F27" s="186"/>
-      <c r="G27" s="186"/>
-      <c r="H27" s="186"/>
-      <c r="I27" s="186"/>
-      <c r="J27" s="186"/>
-      <c r="K27" s="186"/>
-      <c r="L27" s="186"/>
-      <c r="M27" s="186"/>
+      <c r="E27" s="185"/>
+      <c r="F27" s="185"/>
+      <c r="G27" s="185"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="185"/>
+      <c r="J27" s="185"/>
+      <c r="K27" s="185"/>
+      <c r="L27" s="185"/>
+      <c r="M27" s="185"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="186">
+      <c r="C28" s="185">
         <v>166316</v>
       </c>
-      <c r="D28" s="186">
+      <c r="D28" s="185">
         <v>163105</v>
       </c>
-      <c r="E28" s="186"/>
-      <c r="F28" s="186"/>
-      <c r="G28" s="186"/>
-      <c r="H28" s="186"/>
-      <c r="I28" s="186"/>
-      <c r="J28" s="186"/>
-      <c r="K28" s="186"/>
-      <c r="L28" s="186"/>
-      <c r="M28" s="186"/>
+      <c r="E28" s="185"/>
+      <c r="F28" s="185"/>
+      <c r="G28" s="185"/>
+      <c r="H28" s="185"/>
+      <c r="I28" s="185"/>
+      <c r="J28" s="185"/>
+      <c r="K28" s="185"/>
+      <c r="L28" s="185"/>
+      <c r="M28" s="185"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="186"/>
-      <c r="H29" s="186"/>
-      <c r="I29" s="186"/>
-      <c r="J29" s="186"/>
-      <c r="K29" s="186"/>
-      <c r="L29" s="186"/>
-      <c r="M29" s="186"/>
+      <c r="C29" s="184"/>
+      <c r="D29" s="184"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="184"/>
+      <c r="G29" s="185"/>
+      <c r="H29" s="185"/>
+      <c r="I29" s="185"/>
+      <c r="J29" s="185"/>
+      <c r="K29" s="185"/>
+      <c r="L29" s="185"/>
+      <c r="M29" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
@@ -5360,17 +5356,17 @@
       <c r="B32" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="185"/>
-      <c r="D32" s="185"/>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="185"/>
+      <c r="C32" s="184"/>
+      <c r="D32" s="184"/>
+      <c r="E32" s="184"/>
+      <c r="F32" s="184"/>
+      <c r="G32" s="184"/>
+      <c r="H32" s="184"/>
+      <c r="I32" s="184"/>
+      <c r="J32" s="184"/>
+      <c r="K32" s="184"/>
+      <c r="L32" s="184"/>
+      <c r="M32" s="184"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
@@ -5397,47 +5393,47 @@
       <c r="B36" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="187">
+      <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>8765</v>
       </c>
-      <c r="D36" s="187">
+      <c r="D36" s="186">
         <f t="shared" si="1"/>
         <v>11881</v>
       </c>
-      <c r="E36" s="187">
+      <c r="E36" s="186">
         <f t="shared" si="1"/>
         <v>15650.563377</v>
       </c>
-      <c r="F36" s="187">
+      <c r="F36" s="186">
         <f t="shared" si="1"/>
         <v>24433.371759000001</v>
       </c>
-      <c r="G36" s="187">
+      <c r="G36" s="186">
         <f t="shared" si="1"/>
         <v>5887</v>
       </c>
-      <c r="H36" s="187" t="str">
+      <c r="H36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I36" s="187" t="str">
+      <c r="I36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J36" s="187" t="str">
+      <c r="J36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="K36" s="187" t="str">
+      <c r="K36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L36" s="187" t="str">
+      <c r="L36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M36" s="187" t="str">
+      <c r="M36" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5446,47 +5442,47 @@
       <c r="B37" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="187">
+      <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-5344</v>
       </c>
-      <c r="D37" s="187">
+      <c r="D37" s="186">
         <f t="shared" si="2"/>
         <v>-6492</v>
       </c>
-      <c r="E37" s="187">
+      <c r="E37" s="186">
         <f t="shared" si="2"/>
         <v>-7482.8818240000001</v>
       </c>
-      <c r="F37" s="187">
+      <c r="F37" s="186">
         <f t="shared" si="2"/>
         <v>-11196.89644</v>
       </c>
-      <c r="G37" s="187">
+      <c r="G37" s="186">
         <f t="shared" si="2"/>
         <v>-2437</v>
       </c>
-      <c r="H37" s="187" t="str">
+      <c r="H37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="I37" s="187" t="str">
+      <c r="I37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J37" s="187" t="str">
+      <c r="J37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="187" t="str">
+      <c r="K37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L37" s="187" t="str">
+      <c r="L37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M37" s="187" t="str">
+      <c r="M37" s="186" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -5495,47 +5491,47 @@
       <c r="B38" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
         <v>3421</v>
       </c>
-      <c r="D38" s="188">
+      <c r="D38" s="187">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>5389</v>
       </c>
-      <c r="E38" s="188">
+      <c r="E38" s="187">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>8167.6815530000003</v>
       </c>
-      <c r="F38" s="188">
+      <c r="F38" s="187">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>13236.475319000001</v>
       </c>
-      <c r="G38" s="188">
+      <c r="G38" s="187">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>3450</v>
       </c>
-      <c r="H38" s="188" t="str">
+      <c r="H38" s="187" t="str">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v/>
       </c>
-      <c r="I38" s="188" t="str">
+      <c r="I38" s="187" t="str">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v/>
       </c>
-      <c r="J38" s="188" t="str">
+      <c r="J38" s="187" t="str">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v/>
       </c>
-      <c r="K38" s="188" t="str">
+      <c r="K38" s="187" t="str">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v/>
       </c>
-      <c r="L38" s="188" t="str">
+      <c r="L38" s="187" t="str">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v/>
       </c>
-      <c r="M38" s="188" t="str">
+      <c r="M38" s="187" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -5544,47 +5540,47 @@
       <c r="B39" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="187">
+      <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-1084</v>
       </c>
-      <c r="D39" s="187">
+      <c r="D39" s="186">
         <f t="shared" si="13"/>
         <v>-1129</v>
       </c>
-      <c r="E39" s="187">
+      <c r="E39" s="186">
         <f t="shared" si="13"/>
         <v>-867.48327900000004</v>
       </c>
-      <c r="F39" s="187">
+      <c r="F39" s="186">
         <f t="shared" si="13"/>
         <v>-823.28128300000003</v>
       </c>
-      <c r="G39" s="187">
+      <c r="G39" s="186">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H39" s="187" t="str">
+      <c r="H39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="I39" s="187" t="str">
+      <c r="I39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J39" s="187" t="str">
+      <c r="J39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="K39" s="187" t="str">
+      <c r="K39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="L39" s="187" t="str">
+      <c r="L39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="M39" s="187" t="str">
+      <c r="M39" s="186" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -5593,47 +5589,47 @@
       <c r="B40" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="189">
+      <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>0</v>
       </c>
-      <c r="D40" s="189">
+      <c r="D40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="E40" s="189">
+      <c r="E40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="F40" s="189">
+      <c r="F40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="G40" s="189">
+      <c r="G40" s="188">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H40" s="189" t="str">
+      <c r="H40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="I40" s="189" t="str">
+      <c r="I40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J40" s="189" t="str">
+      <c r="J40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="K40" s="189" t="str">
+      <c r="K40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="L40" s="189" t="str">
+      <c r="L40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M40" s="189" t="str">
+      <c r="M40" s="188" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -5642,47 +5638,47 @@
       <c r="B41" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="189">
+      <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-1084</v>
       </c>
-      <c r="D41" s="189">
+      <c r="D41" s="188">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-1129</v>
       </c>
-      <c r="E41" s="189">
+      <c r="E41" s="188">
         <f t="shared" si="15"/>
         <v>-867.48327900000004</v>
       </c>
-      <c r="F41" s="189">
+      <c r="F41" s="188">
         <f t="shared" si="15"/>
         <v>-823.28128300000003</v>
       </c>
-      <c r="G41" s="189">
+      <c r="G41" s="188">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H41" s="189" t="str">
+      <c r="H41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="I41" s="189" t="str">
+      <c r="I41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="J41" s="189" t="str">
+      <c r="J41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="K41" s="189" t="str">
+      <c r="K41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="L41" s="189" t="str">
+      <c r="L41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="M41" s="189" t="str">
+      <c r="M41" s="188" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -5691,47 +5687,47 @@
       <c r="B42" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C42" s="187">
+      <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="187">
+      <c r="D42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="E42" s="187">
+      <c r="E42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="187">
+      <c r="F42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="187">
+      <c r="G42" s="186">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H42" s="187" t="str">
+      <c r="H42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="I42" s="187" t="str">
+      <c r="I42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="J42" s="187" t="str">
+      <c r="J42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="K42" s="187" t="str">
+      <c r="K42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="L42" s="187" t="str">
+      <c r="L42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="M42" s="187" t="str">
+      <c r="M42" s="186" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -5740,47 +5736,47 @@
       <c r="B43" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="C43" s="190">
+      <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>2337</v>
       </c>
-      <c r="D43" s="190">
+      <c r="D43" s="189">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>4260</v>
       </c>
-      <c r="E43" s="190">
+      <c r="E43" s="189">
         <f t="shared" si="17"/>
         <v>7300.1982740000003</v>
       </c>
-      <c r="F43" s="190">
+      <c r="F43" s="189">
         <f t="shared" si="17"/>
         <v>12413.194036000001</v>
       </c>
-      <c r="G43" s="190">
+      <c r="G43" s="189">
         <f t="shared" si="17"/>
         <v>3450</v>
       </c>
-      <c r="H43" s="190" t="str">
+      <c r="H43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I43" s="190" t="str">
+      <c r="I43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="J43" s="190" t="str">
+      <c r="J43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="K43" s="190" t="str">
+      <c r="K43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="L43" s="190" t="str">
+      <c r="L43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="M43" s="190" t="str">
+      <c r="M43" s="189" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -5789,47 +5785,47 @@
       <c r="B44" s="43" t="s">
         <v>173</v>
       </c>
-      <c r="C44" s="191">
+      <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
         <v>136</v>
       </c>
-      <c r="D44" s="191">
+      <c r="D44" s="190">
         <f t="shared" si="18"/>
         <v>1130.764889</v>
       </c>
-      <c r="E44" s="191">
+      <c r="E44" s="190">
         <f t="shared" si="18"/>
         <v>-503.75612799999999</v>
       </c>
-      <c r="F44" s="191">
+      <c r="F44" s="190">
         <f t="shared" si="18"/>
         <v>-726.80948300000091</v>
       </c>
-      <c r="G44" s="191">
+      <c r="G44" s="190">
         <f t="shared" si="18"/>
         <v>-3450</v>
       </c>
-      <c r="H44" s="191" t="str">
+      <c r="H44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="I44" s="191" t="str">
+      <c r="I44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="J44" s="191" t="str">
+      <c r="J44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="K44" s="191" t="str">
+      <c r="K44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="L44" s="191" t="str">
+      <c r="L44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="M44" s="191" t="str">
+      <c r="M44" s="190" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
@@ -5838,47 +5834,47 @@
       <c r="B45" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="192">
+      <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
         <v>2297</v>
       </c>
-      <c r="D45" s="192">
+      <c r="D45" s="191">
         <f t="shared" si="19"/>
         <v>1350.069939</v>
       </c>
-      <c r="E45" s="192">
+      <c r="E45" s="191">
         <f t="shared" si="19"/>
         <v>288.06189799999999</v>
       </c>
-      <c r="F45" s="192">
+      <c r="F45" s="191">
         <f t="shared" si="19"/>
         <v>490.42196800000005</v>
       </c>
-      <c r="G45" s="192">
+      <c r="G45" s="191">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H45" s="192" t="str">
+      <c r="H45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="I45" s="192" t="str">
+      <c r="I45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="J45" s="192" t="str">
+      <c r="J45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="K45" s="192" t="str">
+      <c r="K45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="L45" s="192" t="str">
+      <c r="L45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M45" s="192" t="str">
+      <c r="M45" s="191" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -5887,47 +5883,47 @@
       <c r="B46" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="187">
+      <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-519</v>
       </c>
-      <c r="D46" s="187">
+      <c r="D46" s="186">
         <f t="shared" si="20"/>
         <v>-860.83482800000002</v>
       </c>
-      <c r="E46" s="187">
+      <c r="E46" s="186">
         <f t="shared" si="20"/>
         <v>-1349.107495</v>
       </c>
-      <c r="F46" s="187">
+      <c r="F46" s="186">
         <f t="shared" si="20"/>
         <v>-2530.7695309999999</v>
       </c>
-      <c r="G46" s="187">
+      <c r="G46" s="186">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H46" s="187" t="str">
+      <c r="H46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="I46" s="187" t="str">
+      <c r="I46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="J46" s="187" t="str">
+      <c r="J46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="K46" s="187" t="str">
+      <c r="K46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="L46" s="187" t="str">
+      <c r="L46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M46" s="187" t="str">
+      <c r="M46" s="186" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -5936,47 +5932,47 @@
       <c r="B47" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C47" s="190">
+      <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>4251</v>
       </c>
-      <c r="D47" s="190">
+      <c r="D47" s="189">
         <f t="shared" si="21"/>
         <v>5880</v>
       </c>
-      <c r="E47" s="190">
+      <c r="E47" s="189">
         <f t="shared" si="21"/>
         <v>5735.3965490000001</v>
       </c>
-      <c r="F47" s="190">
+      <c r="F47" s="189">
         <f t="shared" si="21"/>
         <v>9646.0369900000005</v>
       </c>
-      <c r="G47" s="190">
+      <c r="G47" s="189">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H47" s="190" t="str">
+      <c r="H47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="I47" s="190" t="str">
+      <c r="I47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="J47" s="190" t="str">
+      <c r="J47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="K47" s="190" t="str">
+      <c r="K47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="L47" s="190" t="str">
+      <c r="L47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
-      <c r="M47" s="190" t="str">
+      <c r="M47" s="189" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -5985,47 +5981,47 @@
       <c r="B48" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C48" s="187">
+      <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="187">
+      <c r="D48" s="186">
         <f t="shared" si="22"/>
         <v>-31</v>
       </c>
-      <c r="E48" s="187">
+      <c r="E48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="187">
+      <c r="F48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="187">
+      <c r="G48" s="186">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="187" t="str">
+      <c r="H48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="I48" s="187" t="str">
+      <c r="I48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J48" s="187" t="str">
+      <c r="J48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="K48" s="187" t="str">
+      <c r="K48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="L48" s="187" t="str">
+      <c r="L48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M48" s="187" t="str">
+      <c r="M48" s="186" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -6039,47 +6035,47 @@
       <c r="B51" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="187">
+      <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-43</v>
       </c>
-      <c r="D51" s="187">
+      <c r="D51" s="186">
         <f t="shared" si="23"/>
         <v>-40.775368</v>
       </c>
-      <c r="E51" s="187">
+      <c r="E51" s="186">
         <f t="shared" si="23"/>
         <v>-49.197794000000002</v>
       </c>
-      <c r="F51" s="187">
+      <c r="F51" s="186">
         <f t="shared" si="23"/>
         <v>-81.763175000000004</v>
       </c>
-      <c r="G51" s="187">
+      <c r="G51" s="186">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H51" s="187" t="str">
+      <c r="H51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="I51" s="187" t="str">
+      <c r="I51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="J51" s="187" t="str">
+      <c r="J51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K51" s="187" t="str">
+      <c r="K51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="L51" s="187" t="str">
+      <c r="L51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M51" s="187" t="str">
+      <c r="M51" s="186" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -6088,53 +6084,53 @@
       <c r="B52" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="187">
+      <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>2340</v>
       </c>
-      <c r="D52" s="187">
+      <c r="D52" s="186">
         <f t="shared" si="24"/>
         <v>1390.845307</v>
       </c>
-      <c r="E52" s="187">
+      <c r="E52" s="186">
         <f t="shared" si="24"/>
         <v>337.25969199999997</v>
       </c>
-      <c r="F52" s="187">
+      <c r="F52" s="186">
         <f t="shared" si="24"/>
         <v>572.18514300000004</v>
       </c>
-      <c r="G52" s="187">
+      <c r="G52" s="186">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H52" s="187" t="str">
+      <c r="H52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="I52" s="187" t="str">
+      <c r="I52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="J52" s="187" t="str">
+      <c r="J52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="K52" s="187" t="str">
+      <c r="K52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="L52" s="187" t="str">
+      <c r="L52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
-      <c r="M52" s="187" t="str">
+      <c r="M52" s="186" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B54" s="179" t="s">
+      <c r="B54" s="178" t="s">
         <v>173</v>
       </c>
     </row>
@@ -6142,47 +6138,47 @@
       <c r="B55" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C55" s="192">
+      <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
         <v>639</v>
       </c>
-      <c r="D55" s="192">
+      <c r="D55" s="191">
         <f t="shared" si="25"/>
         <v>927</v>
       </c>
-      <c r="E55" s="192">
+      <c r="E55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="F55" s="192">
+      <c r="F55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="G55" s="192">
+      <c r="G55" s="191">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H55" s="192" t="str">
+      <c r="H55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="I55" s="192" t="str">
+      <c r="I55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="J55" s="192" t="str">
+      <c r="J55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="K55" s="192" t="str">
+      <c r="K55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="L55" s="192" t="str">
+      <c r="L55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="M55" s="192" t="str">
+      <c r="M55" s="191" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
@@ -6191,47 +6187,47 @@
       <c r="B56" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C56" s="192">
+      <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
         <v>0</v>
       </c>
-      <c r="D56" s="192">
+      <c r="D56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="E56" s="192">
+      <c r="E56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="F56" s="192">
+      <c r="F56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="G56" s="192">
+      <c r="G56" s="191">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H56" s="192" t="str">
+      <c r="H56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="I56" s="192" t="str">
+      <c r="I56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="J56" s="192" t="str">
+      <c r="J56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="K56" s="192" t="str">
+      <c r="K56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="L56" s="192" t="str">
+      <c r="L56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
-      <c r="M56" s="192" t="str">
+      <c r="M56" s="191" t="str">
         <f t="shared" si="26"/>
         <v/>
       </c>
@@ -6240,47 +6236,47 @@
       <c r="B57" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C57" s="192">
+      <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
-      <c r="D57" s="192">
+      <c r="D57" s="191">
         <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
         <v>0</v>
       </c>
-      <c r="E57" s="192">
+      <c r="E57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F57" s="192">
+      <c r="F57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="G57" s="192">
+      <c r="G57" s="191">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H57" s="192" t="str">
+      <c r="H57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="I57" s="192" t="str">
+      <c r="I57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="J57" s="192" t="str">
+      <c r="J57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="K57" s="192" t="str">
+      <c r="K57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="L57" s="192" t="str">
+      <c r="L57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
-      <c r="M57" s="192" t="str">
+      <c r="M57" s="191" t="str">
         <f t="shared" si="27"/>
         <v/>
       </c>
@@ -6289,47 +6285,47 @@
       <c r="B58" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="192">
+      <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
         <v>-503</v>
       </c>
-      <c r="D58" s="192">
+      <c r="D58" s="191">
         <f t="shared" ref="D58:M58" si="28">IF(D$4="","",D44-D55-D56-D57)</f>
         <v>203.76488900000004</v>
       </c>
-      <c r="E58" s="192">
+      <c r="E58" s="191">
         <f t="shared" si="28"/>
         <v>-503.75612799999999</v>
       </c>
-      <c r="F58" s="192">
+      <c r="F58" s="191">
         <f t="shared" si="28"/>
         <v>-726.80948300000091</v>
       </c>
-      <c r="G58" s="192">
+      <c r="G58" s="191">
         <f t="shared" si="28"/>
         <v>-3450</v>
       </c>
-      <c r="H58" s="192" t="str">
+      <c r="H58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="I58" s="192" t="str">
+      <c r="I58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="J58" s="192" t="str">
+      <c r="J58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="K58" s="192" t="str">
+      <c r="K58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="L58" s="192" t="str">
+      <c r="L58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="M58" s="192" t="str">
+      <c r="M58" s="191" t="str">
         <f t="shared" si="28"/>
         <v/>
       </c>
@@ -6344,47 +6340,47 @@
       <c r="B61" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C61" s="187">
+      <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
         <v>-160</v>
       </c>
-      <c r="D61" s="187">
+      <c r="D61" s="186">
         <f t="shared" si="29"/>
         <v>-198</v>
       </c>
-      <c r="E61" s="187">
+      <c r="E61" s="186">
         <f t="shared" si="29"/>
         <v>-181.018</v>
       </c>
-      <c r="F61" s="187">
+      <c r="F61" s="186">
         <f t="shared" si="29"/>
         <v>-186.14699999999999</v>
       </c>
-      <c r="G61" s="187">
+      <c r="G61" s="186">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H61" s="187" t="str">
+      <c r="H61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="I61" s="187" t="str">
+      <c r="I61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="J61" s="187" t="str">
+      <c r="J61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="K61" s="187" t="str">
+      <c r="K61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="L61" s="187" t="str">
+      <c r="L61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="M61" s="187" t="str">
+      <c r="M61" s="186" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -6393,47 +6389,47 @@
       <c r="B62" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="C62" s="187">
+      <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
         <v>-69</v>
       </c>
-      <c r="D62" s="187">
+      <c r="D62" s="186">
         <f t="shared" si="30"/>
         <v>-108</v>
       </c>
-      <c r="E62" s="187">
+      <c r="E62" s="186">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="187">
+      <c r="F62" s="186">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="G62" s="187">
+      <c r="G62" s="186">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H62" s="187" t="str">
+      <c r="H62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="I62" s="187" t="str">
+      <c r="I62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="J62" s="187" t="str">
+      <c r="J62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="K62" s="187" t="str">
+      <c r="K62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="L62" s="187" t="str">
+      <c r="L62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
-      <c r="M62" s="187" t="str">
+      <c r="M62" s="186" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -6442,47 +6438,47 @@
       <c r="B63" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C63" s="187">
+      <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
         <v>-910</v>
       </c>
-      <c r="D63" s="187">
+      <c r="D63" s="186">
         <f t="shared" si="31"/>
         <v>-2541</v>
       </c>
-      <c r="E63" s="187">
+      <c r="E63" s="186">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="187">
+      <c r="F63" s="186">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="187">
+      <c r="G63" s="186">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="187" t="str">
+      <c r="H63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="I63" s="187" t="str">
+      <c r="I63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="J63" s="187" t="str">
+      <c r="J63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="K63" s="187" t="str">
+      <c r="K63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="L63" s="187" t="str">
+      <c r="L63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
-      <c r="M63" s="187" t="str">
+      <c r="M63" s="186" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7102,19 +7098,19 @@
       <c r="B3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="211" t="s">
+      <c r="D3" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="G3" s="210" t="s">
+      <c r="G3" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="211" t="s">
+      <c r="H3" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7125,7 +7121,7 @@
       <c r="C4" s="19">
         <v>8029</v>
       </c>
-      <c r="D4" s="303">
+      <c r="D4" s="301">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -7135,7 +7131,7 @@
       <c r="G4" s="19">
         <v>45665</v>
       </c>
-      <c r="H4" s="303">
+      <c r="H4" s="301">
         <v>0.9</v>
       </c>
     </row>
@@ -7146,7 +7142,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="303">
+      <c r="D5" s="301">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -7156,7 +7152,7 @@
       <c r="G5" s="19">
         <v>2014</v>
       </c>
-      <c r="H5" s="303">
+      <c r="H5" s="301">
         <v>0.7</v>
       </c>
     </row>
@@ -7167,7 +7163,7 @@
       <c r="C6" s="19">
         <v>9844</v>
       </c>
-      <c r="D6" s="303">
+      <c r="D6" s="301">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -7177,7 +7173,7 @@
       <c r="G6" s="19">
         <v>156</v>
       </c>
-      <c r="H6" s="303">
+      <c r="H6" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7188,7 +7184,7 @@
       <c r="C7" s="19">
         <v>5466</v>
       </c>
-      <c r="D7" s="303">
+      <c r="D7" s="301">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -7198,7 +7194,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="303">
+      <c r="H7" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7209,7 +7205,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="303">
+      <c r="D8" s="301">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -7219,7 +7215,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="303">
+      <c r="H8" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7230,7 +7226,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="303">
+      <c r="D9" s="301">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -7240,7 +7236,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="303">
+      <c r="H9" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7251,10 +7247,10 @@
       <c r="C10" s="19">
         <v>10</v>
       </c>
-      <c r="D10" s="303">
+      <c r="D10" s="301">
         <v>0.9</v>
       </c>
-      <c r="H10" s="304"/>
+      <c r="H10" s="302"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
@@ -7263,10 +7259,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="303">
+      <c r="D11" s="301">
         <v>0.05</v>
       </c>
-      <c r="H11" s="304"/>
+      <c r="H11" s="302"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
@@ -7301,19 +7297,19 @@
       <c r="B14" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="210" t="s">
+      <c r="C14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="211" t="s">
+      <c r="D14" s="210" t="s">
         <v>36</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="G14" s="210" t="s">
+      <c r="G14" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="211" t="s">
+      <c r="H14" s="210" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7324,7 +7320,7 @@
       <c r="C15" s="19">
         <v>2757</v>
       </c>
-      <c r="D15" s="303">
+      <c r="D15" s="301">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -7333,7 +7329,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="303">
+      <c r="H15" s="301">
         <v>0.8</v>
       </c>
     </row>
@@ -7344,7 +7340,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="303">
+      <c r="D16" s="301">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -7353,7 +7349,7 @@
       <c r="G16" s="19">
         <v>1373</v>
       </c>
-      <c r="H16" s="303">
+      <c r="H16" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7364,7 +7360,7 @@
       <c r="C17" s="19">
         <v>67668</v>
       </c>
-      <c r="D17" s="303">
+      <c r="D17" s="301">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -7373,7 +7369,7 @@
       <c r="G17" s="19">
         <v>13024</v>
       </c>
-      <c r="H17" s="303">
+      <c r="H17" s="301">
         <v>0.6</v>
       </c>
     </row>
@@ -7384,7 +7380,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="303">
+      <c r="D18" s="301">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -7393,7 +7389,7 @@
       <c r="G18" s="19">
         <v>23696</v>
       </c>
-      <c r="H18" s="303">
+      <c r="H18" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7404,7 +7400,7 @@
       <c r="C19" s="19">
         <v>1284</v>
       </c>
-      <c r="D19" s="303">
+      <c r="D19" s="301">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -7413,7 +7409,7 @@
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="303">
+      <c r="H19" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7424,7 +7420,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="303">
+      <c r="D20" s="301">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -7433,7 +7429,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="303">
+      <c r="H20" s="301">
         <v>0.2</v>
       </c>
     </row>
@@ -7444,7 +7440,7 @@
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="303">
+      <c r="D21" s="301">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -7453,7 +7449,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="303">
+      <c r="H21" s="301">
         <v>0.1</v>
       </c>
     </row>
@@ -7464,10 +7460,10 @@
       <c r="C22" s="19">
         <v>10</v>
       </c>
-      <c r="D22" s="303">
+      <c r="D22" s="301">
         <v>0.9</v>
       </c>
-      <c r="H22" s="304"/>
+      <c r="H22" s="302"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
@@ -7476,10 +7472,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="303">
-        <v>0</v>
-      </c>
-      <c r="H23" s="304"/>
+      <c r="D23" s="301">
+        <v>0</v>
+      </c>
+      <c r="H23" s="302"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
@@ -7509,16 +7505,16 @@
       <c r="B26" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="C26" s="210" t="s">
+      <c r="C26" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F26" s="212" t="s">
+      <c r="F26" s="211" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="213" t="s">
+      <c r="G26" s="212" t="s">
         <v>141</v>
       </c>
-      <c r="H26" s="214" t="s">
+      <c r="H26" s="213" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7529,14 +7525,14 @@
       <c r="C27" s="19">
         <v>967</v>
       </c>
-      <c r="F27" s="215" t="s">
+      <c r="F27" s="214" t="s">
         <v>31</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
         <v>167107</v>
       </c>
-      <c r="H27" s="216">
+      <c r="H27" s="215">
         <f>H32-G30</f>
         <v>94589.7</v>
       </c>
@@ -7548,13 +7544,13 @@
       <c r="C28" s="19">
         <v>37</v>
       </c>
-      <c r="F28" s="217" t="s">
+      <c r="F28" s="216" t="s">
         <v>251</v>
       </c>
-      <c r="G28" s="185">
+      <c r="G28" s="184">
         <v>519</v>
       </c>
-      <c r="H28" s="216"/>
+      <c r="H28" s="215"/>
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
@@ -7563,14 +7559,14 @@
       <c r="C29" s="19">
         <v>0</v>
       </c>
-      <c r="F29" s="218" t="s">
+      <c r="F29" s="217" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
         <v>166588</v>
       </c>
-      <c r="H29" s="216">
+      <c r="H29" s="215">
         <f>H27-G28</f>
         <v>94070.7</v>
       </c>
@@ -7582,14 +7578,14 @@
       <c r="C30" s="19">
         <v>0</v>
       </c>
-      <c r="F30" s="215" t="s">
+      <c r="F30" s="214" t="s">
         <v>24</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
         <v>13889</v>
       </c>
-      <c r="H30" s="216"/>
+      <c r="H30" s="215"/>
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
@@ -7599,14 +7595,14 @@
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
-      <c r="F31" s="218" t="s">
+      <c r="F31" s="217" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="219">
+      <c r="G31" s="218">
         <f>C31+C40</f>
         <v>3093</v>
       </c>
-      <c r="H31" s="216"/>
+      <c r="H31" s="215"/>
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
@@ -7616,14 +7612,14 @@
         <f>C33-C31</f>
         <v>8048</v>
       </c>
-      <c r="F32" s="220" t="s">
+      <c r="F32" s="219" t="s">
         <v>79</v>
       </c>
-      <c r="G32" s="221">
+      <c r="G32" s="220">
         <f>G35+G40</f>
         <v>180996</v>
       </c>
-      <c r="H32" s="216">
+      <c r="H32" s="215">
         <f>H35+H40</f>
         <v>108478.7</v>
       </c>
@@ -7635,20 +7631,20 @@
       <c r="C33" s="86">
         <v>9052</v>
       </c>
-      <c r="F33" s="222"/>
+      <c r="F33" s="221"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="223"/>
+      <c r="H33" s="222"/>
     </row>
     <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
-      <c r="F34" s="224" t="s">
+      <c r="F34" s="223" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="225" t="s">
+      <c r="G34" s="224" t="s">
         <v>141</v>
       </c>
-      <c r="H34" s="226" t="s">
+      <c r="H34" s="225" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7656,17 +7652,17 @@
       <c r="B35" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="C35" s="210" t="s">
+      <c r="C35" s="209" t="s">
         <v>141</v>
       </c>
-      <c r="F35" s="227" t="s">
+      <c r="F35" s="226" t="s">
         <v>32</v>
       </c>
-      <c r="G35" s="221">
+      <c r="G35" s="220">
         <f>C12+C24</f>
         <v>95068</v>
       </c>
-      <c r="H35" s="228">
+      <c r="H35" s="227">
         <f>D12+D24</f>
         <v>54869</v>
       </c>
@@ -7678,14 +7674,14 @@
       <c r="C36" s="19">
         <v>832</v>
       </c>
-      <c r="F36" s="218" t="s">
+      <c r="F36" s="217" t="s">
         <v>202</v>
       </c>
-      <c r="G36" s="219">
+      <c r="G36" s="218">
         <f>C4+C15</f>
         <v>10786</v>
       </c>
-      <c r="H36" s="223"/>
+      <c r="H36" s="222"/>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
@@ -7694,14 +7690,14 @@
       <c r="C37" s="19">
         <v>27</v>
       </c>
-      <c r="F37" s="218" t="s">
+      <c r="F37" s="217" t="s">
         <v>203</v>
       </c>
-      <c r="G37" s="219">
+      <c r="G37" s="218">
         <f>C6</f>
         <v>9844</v>
       </c>
-      <c r="H37" s="223"/>
+      <c r="H37" s="222"/>
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
@@ -7710,14 +7706,14 @@
       <c r="C38" s="19">
         <v>1230</v>
       </c>
-      <c r="F38" s="218" t="s">
+      <c r="F38" s="217" t="s">
         <v>204</v>
       </c>
-      <c r="G38" s="219">
+      <c r="G38" s="218">
         <f>C7+C17</f>
         <v>73134</v>
       </c>
-      <c r="H38" s="223"/>
+      <c r="H38" s="222"/>
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
@@ -7726,14 +7722,14 @@
       <c r="C39" s="19">
         <v>0</v>
       </c>
-      <c r="F39" s="218" t="s">
+      <c r="F39" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="G39" s="219">
+      <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
         <v>74418</v>
       </c>
-      <c r="H39" s="216">
+      <c r="H39" s="215">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
         <v>44008.799999999996</v>
       </c>
@@ -7746,14 +7742,14 @@
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
-      <c r="F40" s="227" t="s">
+      <c r="F40" s="226" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="221">
+      <c r="G40" s="220">
         <f>G12+G24</f>
         <v>85928</v>
       </c>
-      <c r="H40" s="228">
+      <c r="H40" s="227">
         <f>H12+H24</f>
         <v>53609.7</v>
       </c>
@@ -7766,14 +7762,14 @@
         <f>C42-C40</f>
         <v>2748</v>
       </c>
-      <c r="F41" s="218" t="s">
+      <c r="F41" s="217" t="s">
         <v>196</v>
       </c>
-      <c r="G41" s="219">
+      <c r="G41" s="218">
         <f>C70</f>
         <v>72904</v>
       </c>
-      <c r="H41" s="228">
+      <c r="H41" s="227">
         <f>H40-H42</f>
         <v>45795.299999999996</v>
       </c>
@@ -7785,14 +7781,14 @@
       <c r="C42" s="86">
         <v>4837</v>
       </c>
-      <c r="F42" s="229" t="s">
+      <c r="F42" s="228" t="s">
         <v>197</v>
       </c>
-      <c r="G42" s="230">
+      <c r="G42" s="229">
         <f>C82</f>
         <v>13024</v>
       </c>
-      <c r="H42" s="231">
+      <c r="H42" s="230">
         <f>D82</f>
         <v>7814.4</v>
       </c>
@@ -7812,13 +7808,13 @@
       <c r="B45" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="268" t="s">
+      <c r="C45" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D45" s="210" t="s">
+      <c r="D45" s="209" t="s">
         <v>288</v>
       </c>
-      <c r="F45" s="296" t="s">
+      <c r="F45" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -7826,15 +7822,15 @@
       <c r="B46" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C46" s="192">
+      <c r="C46" s="191">
         <f>G29</f>
         <v>166588</v>
       </c>
-      <c r="D46" s="192">
+      <c r="D46" s="191">
         <f>H29</f>
         <v>94070.7</v>
       </c>
-      <c r="F46" s="291"/>
+      <c r="F46" s="289"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="str">
@@ -7849,23 +7845,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>11.511512740854835</v>
       </c>
-      <c r="F47" s="291"/>
+      <c r="F47" s="289"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F48" s="291"/>
+      <c r="F48" s="289"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="162" t="s">
+      <c r="B49" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="C49" s="269" t="s">
+      <c r="C49" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D49" s="225" t="s">
+      <c r="D49" s="224" t="s">
         <v>100</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="291"/>
+      <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
@@ -7879,33 +7875,33 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>1.3234916559691912</v>
       </c>
-      <c r="F50" s="291"/>
+      <c r="F50" s="289"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C51" s="209"/>
+      <c r="C51" s="208"/>
       <c r="D51" s="94">
         <f>G29/G32</f>
         <v>0.92039603085151056</v>
       </c>
-      <c r="F51" s="291"/>
+      <c r="F51" s="289"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F52" s="291"/>
+      <c r="F52" s="289"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="162" t="s">
+      <c r="B53" s="161" t="s">
         <v>147</v>
       </c>
-      <c r="C53" s="269" t="s">
+      <c r="C53" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="225" t="s">
+      <c r="D53" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F53" s="291"/>
+      <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
@@ -7919,7 +7915,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>2.4582404173854506E-2</v>
       </c>
-      <c r="F54" s="291"/>
+      <c r="F54" s="289"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
@@ -7933,22 +7929,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>7.4364584303137507E-3</v>
       </c>
-      <c r="F55" s="291"/>
+      <c r="F55" s="289"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F56" s="291"/>
+      <c r="F56" s="289"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="162" t="s">
+      <c r="B57" s="161" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="269" t="s">
+      <c r="C57" s="268" t="s">
         <v>61</v>
       </c>
-      <c r="D57" s="225" t="s">
+      <c r="D57" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="291"/>
+      <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
@@ -7970,22 +7966,22 @@
         <f>G39/G32</f>
         <v>0.41115825764105285</v>
       </c>
-      <c r="F59" s="291"/>
+      <c r="F59" s="289"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F60" s="291"/>
+      <c r="F60" s="289"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="162" t="s">
+      <c r="B61" s="161" t="s">
         <v>291</v>
       </c>
-      <c r="C61" s="269" t="s">
+      <c r="C61" s="268" t="s">
         <v>142</v>
       </c>
-      <c r="D61" s="225" t="s">
+      <c r="D61" s="224" t="s">
         <v>100</v>
       </c>
-      <c r="F61" s="291"/>
+      <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
@@ -7999,7 +7995,7 @@
         <f>G28/G29</f>
         <v>3.1154705020769802E-3</v>
       </c>
-      <c r="F62" s="291" t="s">
+      <c r="F62" s="289" t="s">
         <v>289</v>
       </c>
     </row>
@@ -8018,13 +8014,13 @@
       <c r="B65" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="C65" s="268" t="s">
+      <c r="C65" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="211" t="s">
+      <c r="D65" s="210" t="s">
         <v>313</v>
       </c>
-      <c r="F65" s="296" t="s">
+      <c r="F65" s="294" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8036,7 +8032,7 @@
         <f>G4+G5+G15</f>
         <v>47679</v>
       </c>
-      <c r="D66" s="192">
+      <c r="D66" s="191">
         <f>C66-D75</f>
         <v>41505.820259237436</v>
       </c>
@@ -8052,7 +8048,7 @@
         <f>G6+G16</f>
         <v>1529</v>
       </c>
-      <c r="F67" s="291"/>
+      <c r="F67" s="289"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
@@ -8062,7 +8058,7 @@
         <f>G18</f>
         <v>23696</v>
       </c>
-      <c r="F68" s="291"/>
+      <c r="F68" s="289"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
@@ -8072,7 +8068,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="291"/>
+      <c r="F69" s="289"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
@@ -8082,49 +8078,49 @@
         <f>SUM(C66:C69)</f>
         <v>72904</v>
       </c>
-      <c r="F70" s="291"/>
+      <c r="F70" s="289"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F71" s="291"/>
+      <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="294" t="s">
+      <c r="B72" s="292" t="s">
         <v>354</v>
       </c>
-      <c r="C72" s="268" t="s">
+      <c r="C72" s="267" t="s">
         <v>100</v>
       </c>
-      <c r="D72" s="210" t="s">
+      <c r="D72" s="209" t="s">
         <v>61</v>
       </c>
-      <c r="F72" s="291"/>
+      <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
         <v>353</v>
       </c>
-      <c r="C73" s="192">
+      <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
         <v>-535.66666666666663</v>
       </c>
-      <c r="D73" s="192">
+      <c r="D73" s="191">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
         <v>-514.43164506354685</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="297" t="s">
+      <c r="B74" s="295" t="s">
         <v>359</v>
       </c>
-      <c r="C74" s="298">
+      <c r="C74" s="296">
         <f>-$C$66/C73</f>
         <v>89.008711885500944</v>
       </c>
-      <c r="D74" s="298">
+      <c r="D74" s="296">
         <f>-$C$66/D73</f>
         <v>92.682867505381196</v>
       </c>
-      <c r="F74" s="291" t="s">
+      <c r="F74" s="289" t="s">
         <v>355</v>
       </c>
     </row>
@@ -8132,42 +8128,42 @@
       <c r="B75" s="82" t="s">
         <v>356</v>
       </c>
-      <c r="C75" s="302"/>
-      <c r="D75" s="301">
+      <c r="C75" s="300"/>
+      <c r="D75" s="299">
         <f>MAX(-D73*D76,G5)</f>
         <v>6173.1797407625618</v>
       </c>
-      <c r="F75" s="291" t="s">
+      <c r="F75" s="289" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="299" t="s">
+      <c r="B76" s="297" t="s">
         <v>360</v>
       </c>
-      <c r="C76" s="300"/>
-      <c r="D76" s="337">
+      <c r="C76" s="298"/>
+      <c r="D76" s="335">
         <f>IF(D74&lt;=3,1,IF(D74&gt;12,IF(D74&gt;24,12,6),2))</f>
         <v>12</v>
       </c>
-      <c r="F76" s="291" t="s">
+      <c r="F76" s="289" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F77" s="291"/>
+      <c r="F77" s="289"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C78" s="268" t="s">
+      <c r="C78" s="267" t="s">
         <v>141</v>
       </c>
-      <c r="D78" s="211" t="s">
+      <c r="D78" s="210" t="s">
         <v>36</v>
       </c>
-      <c r="F78" s="291"/>
+      <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
@@ -8177,11 +8173,11 @@
         <f>G7+G17</f>
         <v>13024</v>
       </c>
-      <c r="D79" s="192">
+      <c r="D79" s="191">
         <f>G7*H7+G17*H17</f>
         <v>7814.4</v>
       </c>
-      <c r="F79" s="291"/>
+      <c r="F79" s="289"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
@@ -8191,11 +8187,11 @@
         <f>G19</f>
         <v>0</v>
       </c>
-      <c r="D80" s="192">
+      <c r="D80" s="191">
         <f>G19*H19</f>
         <v>0</v>
       </c>
-      <c r="F80" s="291"/>
+      <c r="F80" s="289"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
@@ -8205,11 +8201,11 @@
         <f>G9+G21</f>
         <v>0</v>
       </c>
-      <c r="D81" s="192">
+      <c r="D81" s="191">
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="291"/>
+      <c r="F81" s="289"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
@@ -8223,7 +8219,7 @@
         <f>SUM(D79:D81)</f>
         <v>7814.4</v>
       </c>
-      <c r="F82" s="291"/>
+      <c r="F82" s="289"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
@@ -8240,57 +8236,57 @@
       <c r="B85" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="D85" s="278" t="s">
+      <c r="D85" s="276" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="275" t="s">
+      <c r="B86" s="273" t="s">
         <v>314</v>
       </c>
-      <c r="C86" s="192">
+      <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-3093</v>
       </c>
-      <c r="D86" s="255">
+      <c r="D86" s="254">
         <f>C86*$H$1/Common_Shares</f>
         <v>-0.37849307922088393</v>
       </c>
-      <c r="E86" s="277" t="str">
+      <c r="E86" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="275" t="s">
+      <c r="B87" s="273" t="s">
         <v>315</v>
       </c>
-      <c r="C87" s="192">
+      <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>41505.820259237436</v>
       </c>
-      <c r="D87" s="255">
+      <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
         <v>5.0791030441342784</v>
       </c>
-      <c r="E87" s="277" t="str">
+      <c r="E87" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="276" t="s">
+      <c r="B88" s="274" t="s">
         <v>194</v>
       </c>
-      <c r="C88" s="192">
+      <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>7814.4</v>
       </c>
-      <c r="D88" s="255">
+      <c r="D88" s="254">
         <f>C88*$H$1/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
-      <c r="E88" s="277" t="str">
+      <c r="E88" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8299,15 +8295,15 @@
       <c r="B89" s="82" t="s">
         <v>319</v>
       </c>
-      <c r="C89" s="191">
+      <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
         <v>46227.220259237438</v>
       </c>
-      <c r="D89" s="279">
+      <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
         <v>5.6568648366442948</v>
       </c>
-      <c r="E89" s="277" t="str">
+      <c r="E89" s="275" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -8428,7 +8424,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="311"/>
+      <c r="E3" s="309"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -8437,54 +8433,54 @@
       <c r="B4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="197">
+      <c r="C4" s="196">
         <f>G4</f>
         <v>8765</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="309"/>
+      <c r="E4" s="307"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="187">
+      <c r="G4" s="186">
         <f>Data!C36</f>
         <v>8765</v>
       </c>
-      <c r="H4" s="187">
+      <c r="H4" s="186">
         <f>Data!D36</f>
         <v>11881</v>
       </c>
-      <c r="I4" s="187">
+      <c r="I4" s="186">
         <f>Data!E36</f>
         <v>15650.563377</v>
       </c>
-      <c r="J4" s="187">
+      <c r="J4" s="186">
         <f>Data!F36</f>
         <v>24433.371759000001</v>
       </c>
-      <c r="K4" s="187">
+      <c r="K4" s="186">
         <f>Data!G36</f>
         <v>5887</v>
       </c>
-      <c r="L4" s="187" t="str">
+      <c r="L4" s="186" t="str">
         <f>Data!H36</f>
         <v/>
       </c>
-      <c r="M4" s="187" t="str">
+      <c r="M4" s="186" t="str">
         <f>Data!I36</f>
         <v/>
       </c>
-      <c r="N4" s="187" t="str">
+      <c r="N4" s="186" t="str">
         <f>Data!J36</f>
         <v/>
       </c>
-      <c r="O4" s="187" t="str">
+      <c r="O4" s="186" t="str">
         <f>Data!K36</f>
         <v/>
       </c>
-      <c r="P4" s="187" t="str">
+      <c r="P4" s="186" t="str">
         <f>Data!L36</f>
         <v/>
       </c>
-      <c r="Q4" s="187" t="str">
+      <c r="Q4" s="186" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -8494,52 +8490,52 @@
       <c r="B5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="198">
+      <c r="C5" s="197">
         <f>C25</f>
         <v>-5066.6797407625618</v>
       </c>
-      <c r="E5" s="311"/>
-      <c r="G5" s="187">
+      <c r="E5" s="309"/>
+      <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5344</v>
       </c>
-      <c r="H5" s="187">
+      <c r="H5" s="186">
         <f t="shared" si="1"/>
         <v>-6492</v>
       </c>
-      <c r="I5" s="187">
+      <c r="I5" s="186">
         <f t="shared" si="1"/>
         <v>-7482.8818240000001</v>
       </c>
-      <c r="J5" s="187">
+      <c r="J5" s="186">
         <f t="shared" si="1"/>
         <v>-11196.89644</v>
       </c>
-      <c r="K5" s="187">
+      <c r="K5" s="186">
         <f t="shared" si="1"/>
         <v>-2437</v>
       </c>
-      <c r="L5" s="187" t="str">
+      <c r="L5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="M5" s="187" t="str">
+      <c r="M5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N5" s="187" t="str">
+      <c r="N5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="O5" s="187" t="str">
+      <c r="O5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="P5" s="187" t="str">
+      <c r="P5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q5" s="187" t="str">
+      <c r="Q5" s="186" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8549,52 +8545,52 @@
       <c r="B6" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="188">
+      <c r="C6" s="187">
         <f>C4+C5</f>
         <v>3698.3202592374382</v>
       </c>
-      <c r="E6" s="311"/>
-      <c r="G6" s="188">
+      <c r="E6" s="309"/>
+      <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>3421</v>
       </c>
-      <c r="H6" s="188">
+      <c r="H6" s="187">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>5389</v>
       </c>
-      <c r="I6" s="188">
+      <c r="I6" s="187">
         <f t="shared" si="2"/>
         <v>8167.6815530000003</v>
       </c>
-      <c r="J6" s="188">
+      <c r="J6" s="187">
         <f t="shared" si="2"/>
         <v>13236.475319000001</v>
       </c>
-      <c r="K6" s="188">
+      <c r="K6" s="187">
         <f t="shared" si="2"/>
         <v>3450</v>
       </c>
-      <c r="L6" s="188" t="str">
+      <c r="L6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="M6" s="188" t="str">
+      <c r="M6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="N6" s="188" t="str">
+      <c r="N6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="O6" s="188" t="str">
+      <c r="O6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="P6" s="188" t="str">
+      <c r="P6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="Q6" s="188" t="str">
+      <c r="Q6" s="187" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -8604,52 +8600,52 @@
       <c r="B7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="198">
+      <c r="C7" s="197">
         <f>C35</f>
         <v>-1106.5</v>
       </c>
-      <c r="E7" s="311"/>
-      <c r="G7" s="198">
+      <c r="E7" s="309"/>
+      <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1084</v>
       </c>
-      <c r="H7" s="198">
+      <c r="H7" s="197">
         <f t="shared" si="3"/>
         <v>-1129</v>
       </c>
-      <c r="I7" s="198">
+      <c r="I7" s="197">
         <f t="shared" si="3"/>
         <v>-867.48327900000004</v>
       </c>
-      <c r="J7" s="198">
+      <c r="J7" s="197">
         <f t="shared" si="3"/>
         <v>-823.28128300000003</v>
       </c>
-      <c r="K7" s="198">
+      <c r="K7" s="197">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L7" s="198" t="str">
+      <c r="L7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M7" s="198" t="str">
+      <c r="M7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="N7" s="198" t="str">
+      <c r="N7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O7" s="198" t="str">
+      <c r="O7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="P7" s="198" t="str">
+      <c r="P7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="198" t="str">
+      <c r="Q7" s="197" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -8659,54 +8655,54 @@
       <c r="B8" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="199">
+      <c r="C8" s="198">
         <f>C6+C7</f>
         <v>2591.8202592374382</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="317"/>
+      <c r="E8" s="315"/>
       <c r="F8" s="60"/>
-      <c r="G8" s="188">
+      <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
         <v>2337</v>
       </c>
-      <c r="H8" s="188">
+      <c r="H8" s="187">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>4260</v>
       </c>
-      <c r="I8" s="188">
+      <c r="I8" s="187">
         <f t="shared" si="4"/>
         <v>7300.1982740000003</v>
       </c>
-      <c r="J8" s="188">
+      <c r="J8" s="187">
         <f t="shared" si="4"/>
         <v>12413.194036000001</v>
       </c>
-      <c r="K8" s="188">
+      <c r="K8" s="187">
         <f t="shared" si="4"/>
         <v>3450</v>
       </c>
-      <c r="L8" s="188" t="str">
+      <c r="L8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="M8" s="188" t="str">
+      <c r="M8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="N8" s="188" t="str">
+      <c r="N8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O8" s="188" t="str">
+      <c r="O8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="P8" s="188" t="str">
+      <c r="P8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="Q8" s="188" t="str">
+      <c r="Q8" s="187" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -8716,52 +8712,52 @@
       <c r="B9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="198">
+      <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
         <v>159.99999999999997</v>
       </c>
-      <c r="E9" s="311"/>
-      <c r="G9" s="198">
+      <c r="E9" s="309"/>
+      <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>160</v>
       </c>
-      <c r="H9" s="198">
+      <c r="H9" s="197">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>198</v>
       </c>
-      <c r="I9" s="198">
+      <c r="I9" s="197">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>181.018</v>
       </c>
-      <c r="J9" s="198">
+      <c r="J9" s="197">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>186.14699999999999</v>
       </c>
-      <c r="K9" s="198">
+      <c r="K9" s="197">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="198" t="str">
+      <c r="L9" s="197" t="str">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v/>
       </c>
-      <c r="M9" s="198" t="str">
+      <c r="M9" s="197" t="str">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v/>
       </c>
-      <c r="N9" s="198" t="str">
+      <c r="N9" s="197" t="str">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v/>
       </c>
-      <c r="O9" s="198" t="str">
+      <c r="O9" s="197" t="str">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v/>
       </c>
-      <c r="P9" s="198" t="str">
+      <c r="P9" s="197" t="str">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v/>
       </c>
-      <c r="Q9" s="198" t="str">
+      <c r="Q9" s="197" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -8771,52 +8767,52 @@
       <c r="B10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="198">
+      <c r="C10" s="197">
         <f>-C4*C78</f>
         <v>-159.99999999999997</v>
       </c>
-      <c r="E10" s="311"/>
-      <c r="G10" s="198">
+      <c r="E10" s="309"/>
+      <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-69</v>
       </c>
-      <c r="H10" s="198">
+      <c r="H10" s="197">
         <f>Data!D62</f>
         <v>-108</v>
       </c>
-      <c r="I10" s="198">
+      <c r="I10" s="197">
         <f>Data!E62</f>
         <v>0</v>
       </c>
-      <c r="J10" s="198">
+      <c r="J10" s="197">
         <f>Data!F62</f>
         <v>0</v>
       </c>
-      <c r="K10" s="198">
+      <c r="K10" s="197">
         <f>Data!G62</f>
         <v>0</v>
       </c>
-      <c r="L10" s="198" t="str">
+      <c r="L10" s="197" t="str">
         <f>Data!H62</f>
         <v/>
       </c>
-      <c r="M10" s="198" t="str">
+      <c r="M10" s="197" t="str">
         <f>Data!I62</f>
         <v/>
       </c>
-      <c r="N10" s="198" t="str">
+      <c r="N10" s="197" t="str">
         <f>Data!J62</f>
         <v/>
       </c>
-      <c r="O10" s="198" t="str">
+      <c r="O10" s="197" t="str">
         <f>Data!K62</f>
         <v/>
       </c>
-      <c r="P10" s="198" t="str">
+      <c r="P10" s="197" t="str">
         <f>Data!L62</f>
         <v/>
       </c>
-      <c r="Q10" s="198" t="str">
+      <c r="Q10" s="197" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -8826,54 +8822,54 @@
       <c r="B11" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C11" s="200">
+      <c r="C11" s="199">
         <f>C63</f>
         <v>639</v>
       </c>
-      <c r="D11" s="173"/>
-      <c r="E11" s="310"/>
-      <c r="F11" s="173"/>
-      <c r="G11" s="190">
+      <c r="D11" s="172"/>
+      <c r="E11" s="308"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="189">
         <f>G61</f>
         <v>639</v>
       </c>
-      <c r="H11" s="190">
+      <c r="H11" s="189">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>927</v>
       </c>
-      <c r="I11" s="190">
+      <c r="I11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="190">
+      <c r="J11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="190">
+      <c r="K11" s="189">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="190" t="str">
+      <c r="L11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="M11" s="190" t="str">
+      <c r="M11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="N11" s="190" t="str">
+      <c r="N11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="O11" s="190" t="str">
+      <c r="O11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P11" s="190" t="str">
+      <c r="P11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q11" s="190" t="str">
+      <c r="Q11" s="189" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -8883,52 +8879,52 @@
       <c r="B12" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="198">
+      <c r="C12" s="197">
         <f>C50</f>
         <v>142.19539222287685</v>
       </c>
-      <c r="E12" s="311"/>
-      <c r="G12" s="198">
+      <c r="E12" s="309"/>
+      <c r="G12" s="197">
         <f>G50</f>
         <v>259.96861497481899</v>
       </c>
-      <c r="H12" s="198">
+      <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>139.30261332735768</v>
       </c>
-      <c r="I12" s="198">
+      <c r="I12" s="197">
         <f t="shared" si="6"/>
         <v>-5.5315111914213588</v>
       </c>
-      <c r="J12" s="198">
+      <c r="J12" s="197">
         <f t="shared" si="6"/>
         <v>-7.6802090667184899</v>
       </c>
-      <c r="K12" s="198">
+      <c r="K12" s="197">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L12" s="198" t="str">
+      <c r="L12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="M12" s="198" t="str">
+      <c r="M12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="N12" s="198" t="str">
+      <c r="N12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="O12" s="198" t="str">
+      <c r="O12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="P12" s="198" t="str">
+      <c r="P12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Q12" s="198" t="str">
+      <c r="Q12" s="197" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -8938,52 +8934,52 @@
       <c r="B13" s="71" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="188">
+      <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
         <v>3373.015651460315</v>
       </c>
-      <c r="E13" s="311"/>
-      <c r="G13" s="188">
+      <c r="E13" s="309"/>
+      <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3326.968614974819</v>
       </c>
-      <c r="H13" s="188">
+      <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>5416.3026133273579</v>
       </c>
-      <c r="I13" s="188">
+      <c r="I13" s="187">
         <f t="shared" si="7"/>
         <v>7475.6847628085789</v>
       </c>
-      <c r="J13" s="188">
+      <c r="J13" s="187">
         <f t="shared" si="7"/>
         <v>12591.660826933283</v>
       </c>
-      <c r="K13" s="188">
+      <c r="K13" s="187">
         <f t="shared" si="7"/>
         <v>3450</v>
       </c>
-      <c r="L13" s="188" t="str">
+      <c r="L13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M13" s="188" t="str">
+      <c r="M13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N13" s="188" t="str">
+      <c r="N13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="O13" s="188" t="str">
+      <c r="O13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="P13" s="188" t="str">
+      <c r="P13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q13" s="188" t="str">
+      <c r="Q13" s="187" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8993,52 +8989,52 @@
       <c r="B14" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="198">
+      <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-809.52375635047554</v>
       </c>
-      <c r="E14" s="311"/>
-      <c r="G14" s="198">
+      <c r="E14" s="309"/>
+      <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-519</v>
       </c>
-      <c r="H14" s="198">
+      <c r="H14" s="197">
         <f>Data!D46</f>
         <v>-860.83482800000002</v>
       </c>
-      <c r="I14" s="198">
+      <c r="I14" s="197">
         <f>Data!E46</f>
         <v>-1349.107495</v>
       </c>
-      <c r="J14" s="198">
+      <c r="J14" s="197">
         <f>Data!F46</f>
         <v>-2530.7695309999999</v>
       </c>
-      <c r="K14" s="198">
+      <c r="K14" s="197">
         <f>Data!G46</f>
         <v>0</v>
       </c>
-      <c r="L14" s="198" t="str">
+      <c r="L14" s="197" t="str">
         <f>Data!H46</f>
         <v/>
       </c>
-      <c r="M14" s="198" t="str">
+      <c r="M14" s="197" t="str">
         <f>Data!I46</f>
         <v/>
       </c>
-      <c r="N14" s="198" t="str">
+      <c r="N14" s="197" t="str">
         <f>Data!J46</f>
         <v/>
       </c>
-      <c r="O14" s="198" t="str">
+      <c r="O14" s="197" t="str">
         <f>Data!K46</f>
         <v/>
       </c>
-      <c r="P14" s="198" t="str">
+      <c r="P14" s="197" t="str">
         <f>Data!L46</f>
         <v/>
       </c>
-      <c r="Q14" s="198" t="str">
+      <c r="Q14" s="197" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -9048,54 +9044,54 @@
       <c r="B15" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="C15" s="198">
+      <c r="C15" s="197">
         <f>-C4*C83</f>
         <v>-22.869707937042335</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="318"/>
+      <c r="E15" s="316"/>
       <c r="F15" s="61"/>
-      <c r="G15" s="187">
+      <c r="G15" s="186">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="187">
+      <c r="H15" s="186">
         <f>Data!D48</f>
         <v>-31</v>
       </c>
-      <c r="I15" s="187">
+      <c r="I15" s="186">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="187">
+      <c r="J15" s="186">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="187">
+      <c r="K15" s="186">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="187" t="str">
+      <c r="L15" s="186" t="str">
         <f>Data!H48</f>
         <v/>
       </c>
-      <c r="M15" s="187" t="str">
+      <c r="M15" s="186" t="str">
         <f>Data!I48</f>
         <v/>
       </c>
-      <c r="N15" s="187" t="str">
+      <c r="N15" s="186" t="str">
         <f>Data!J48</f>
         <v/>
       </c>
-      <c r="O15" s="187" t="str">
+      <c r="O15" s="186" t="str">
         <f>Data!K48</f>
         <v/>
       </c>
-      <c r="P15" s="187" t="str">
+      <c r="P15" s="186" t="str">
         <f>Data!L48</f>
         <v/>
       </c>
-      <c r="Q15" s="187" t="str">
+      <c r="Q15" s="186" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -9105,54 +9101,54 @@
       <c r="B16" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="201">
+      <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
         <v>2540.6221871727971</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="319"/>
+      <c r="E16" s="317"/>
       <c r="F16" s="62"/>
-      <c r="G16" s="188">
+      <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>2807.968614974819</v>
       </c>
-      <c r="H16" s="188">
+      <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>4524.4677853273579</v>
       </c>
-      <c r="I16" s="188">
+      <c r="I16" s="187">
         <f t="shared" si="8"/>
         <v>6126.5772678085787</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="187">
         <f t="shared" si="8"/>
         <v>10060.891295933283</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="187">
         <f t="shared" si="8"/>
         <v>3450</v>
       </c>
-      <c r="L16" s="188" t="str">
+      <c r="L16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="M16" s="188" t="str">
+      <c r="M16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N16" s="188" t="str">
+      <c r="N16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="O16" s="188" t="str">
+      <c r="O16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="P16" s="188" t="str">
+      <c r="P16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="Q16" s="188" t="str">
+      <c r="Q16" s="187" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -9162,105 +9158,105 @@
       <c r="B17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="198">
+      <c r="C17" s="197">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="310" t="s">
+      <c r="E17" s="308" t="s">
         <v>373</v>
       </c>
       <c r="F17" s="59"/>
-      <c r="G17" s="202"/>
-      <c r="H17" s="202"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="202"/>
-      <c r="K17" s="202"/>
-      <c r="L17" s="202"/>
-      <c r="M17" s="202"/>
-      <c r="N17" s="202"/>
-      <c r="O17" s="202"/>
-      <c r="P17" s="202"/>
-      <c r="Q17" s="202"/>
+      <c r="G17" s="201"/>
+      <c r="H17" s="201"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="201"/>
+      <c r="K17" s="201"/>
+      <c r="L17" s="201"/>
+      <c r="M17" s="201"/>
+      <c r="N17" s="201"/>
+      <c r="O17" s="201"/>
+      <c r="P17" s="201"/>
+      <c r="Q17" s="201"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C18" s="198">
+      <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="310" t="s">
+      <c r="E18" s="308" t="s">
         <v>374</v>
       </c>
       <c r="F18" s="59"/>
-      <c r="G18" s="203"/>
-      <c r="H18" s="203"/>
-      <c r="I18" s="203"/>
-      <c r="J18" s="203"/>
-      <c r="K18" s="203"/>
-      <c r="L18" s="203"/>
-      <c r="M18" s="203"/>
-      <c r="N18" s="203"/>
-      <c r="O18" s="203"/>
-      <c r="P18" s="203"/>
-      <c r="Q18" s="203"/>
+      <c r="G18" s="202"/>
+      <c r="H18" s="202"/>
+      <c r="I18" s="202"/>
+      <c r="J18" s="202"/>
+      <c r="K18" s="202"/>
+      <c r="L18" s="202"/>
+      <c r="M18" s="202"/>
+      <c r="N18" s="202"/>
+      <c r="O18" s="202"/>
+      <c r="P18" s="202"/>
+      <c r="Q18" s="202"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="188">
+      <c r="C19" s="187">
         <f>C16+C17</f>
         <v>2540.6221871727971</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="308"/>
+      <c r="E19" s="306"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="190">
+      <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
         <v>2807.968614974819</v>
       </c>
-      <c r="H19" s="190">
+      <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>4524.4677853273579</v>
       </c>
-      <c r="I19" s="190">
+      <c r="I19" s="189">
         <f t="shared" si="9"/>
         <v>6126.5772678085787</v>
       </c>
-      <c r="J19" s="190">
+      <c r="J19" s="189">
         <f t="shared" si="9"/>
         <v>10060.891295933283</v>
       </c>
-      <c r="K19" s="190">
+      <c r="K19" s="189">
         <f t="shared" si="9"/>
         <v>3450</v>
       </c>
-      <c r="L19" s="190" t="str">
+      <c r="L19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="M19" s="190" t="str">
+      <c r="M19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="N19" s="190" t="str">
+      <c r="N19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O19" s="190" t="str">
+      <c r="O19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="P19" s="190" t="str">
+      <c r="P19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="Q19" s="190" t="str">
+      <c r="Q19" s="189" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -9314,7 +9310,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="308"/>
+      <c r="E22" s="306"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9333,54 +9329,54 @@
       <c r="B23" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="204">
+      <c r="C23" s="203">
         <f>-C4*C28</f>
         <v>-5066.6797407625618</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="310"/>
+      <c r="E23" s="308"/>
       <c r="F23" s="59"/>
-      <c r="G23" s="187">
+      <c r="G23" s="186">
         <f>Data!C37</f>
         <v>-5344</v>
       </c>
-      <c r="H23" s="187">
+      <c r="H23" s="186">
         <f>Data!D37</f>
         <v>-6492</v>
       </c>
-      <c r="I23" s="187">
+      <c r="I23" s="186">
         <f>Data!E37</f>
         <v>-7482.8818240000001</v>
       </c>
-      <c r="J23" s="187">
+      <c r="J23" s="186">
         <f>Data!F37</f>
         <v>-11196.89644</v>
       </c>
-      <c r="K23" s="187">
+      <c r="K23" s="186">
         <f>Data!G37</f>
         <v>-2437</v>
       </c>
-      <c r="L23" s="187" t="str">
+      <c r="L23" s="186" t="str">
         <f>Data!H37</f>
         <v/>
       </c>
-      <c r="M23" s="187" t="str">
+      <c r="M23" s="186" t="str">
         <f>Data!I37</f>
         <v/>
       </c>
-      <c r="N23" s="187" t="str">
+      <c r="N23" s="186" t="str">
         <f>Data!J37</f>
         <v/>
       </c>
-      <c r="O23" s="187" t="str">
+      <c r="O23" s="186" t="str">
         <f>Data!K37</f>
         <v/>
       </c>
-      <c r="P23" s="187" t="str">
+      <c r="P23" s="186" t="str">
         <f>Data!L37</f>
         <v/>
       </c>
-      <c r="Q23" s="187" t="str">
+      <c r="Q23" s="186" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -9390,54 +9386,54 @@
       <c r="B24" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="198">
+      <c r="C24" s="197">
         <f>-C4*C29</f>
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="308"/>
+      <c r="E24" s="306"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="187">
+      <c r="G24" s="186">
         <f>Data!C40</f>
         <v>0</v>
       </c>
-      <c r="H24" s="187">
+      <c r="H24" s="186">
         <f>Data!D40</f>
         <v>0</v>
       </c>
-      <c r="I24" s="187">
+      <c r="I24" s="186">
         <f>Data!E40</f>
         <v>0</v>
       </c>
-      <c r="J24" s="187">
+      <c r="J24" s="186">
         <f>Data!F40</f>
         <v>0</v>
       </c>
-      <c r="K24" s="187">
+      <c r="K24" s="186">
         <f>Data!G40</f>
         <v>0</v>
       </c>
-      <c r="L24" s="187" t="str">
+      <c r="L24" s="186" t="str">
         <f>Data!H40</f>
         <v/>
       </c>
-      <c r="M24" s="187" t="str">
+      <c r="M24" s="186" t="str">
         <f>Data!I40</f>
         <v/>
       </c>
-      <c r="N24" s="187" t="str">
+      <c r="N24" s="186" t="str">
         <f>Data!J40</f>
         <v/>
       </c>
-      <c r="O24" s="187" t="str">
+      <c r="O24" s="186" t="str">
         <f>Data!K40</f>
         <v/>
       </c>
-      <c r="P24" s="187" t="str">
+      <c r="P24" s="186" t="str">
         <f>Data!L40</f>
         <v/>
       </c>
-      <c r="Q24" s="187" t="str">
+      <c r="Q24" s="186" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -9447,68 +9443,68 @@
       <c r="B25" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="188">
+      <c r="C25" s="187">
         <f>C23+C24</f>
         <v>-5066.6797407625618</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="316"/>
+      <c r="E25" s="314"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="188">
+      <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-5344</v>
       </c>
-      <c r="H25" s="188">
+      <c r="H25" s="187">
         <f t="shared" si="10"/>
         <v>-6492</v>
       </c>
-      <c r="I25" s="188">
+      <c r="I25" s="187">
         <f t="shared" si="10"/>
         <v>-7482.8818240000001</v>
       </c>
-      <c r="J25" s="188">
+      <c r="J25" s="187">
         <f t="shared" si="10"/>
         <v>-11196.89644</v>
       </c>
-      <c r="K25" s="188">
+      <c r="K25" s="187">
         <f t="shared" si="10"/>
         <v>-2437</v>
       </c>
-      <c r="L25" s="188" t="str">
+      <c r="L25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="M25" s="188" t="str">
+      <c r="M25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="N25" s="188" t="str">
+      <c r="N25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="O25" s="188" t="str">
+      <c r="O25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="P25" s="188" t="str">
+      <c r="P25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="Q25" s="188" t="str">
+      <c r="Q25" s="187" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="311"/>
+      <c r="E26" s="309"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
         <v>211</v>
       </c>
-      <c r="E27" s="311"/>
+      <c r="E27" s="309"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
@@ -9520,7 +9516,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="309" t="s">
+      <c r="E28" s="307" t="s">
         <v>375</v>
       </c>
       <c r="F28" s="26"/>
@@ -9580,7 +9576,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="309" t="s">
+      <c r="E29" s="307" t="s">
         <v>375</v>
       </c>
       <c r="F29" s="26"/>
@@ -9638,7 +9634,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.57805815639048053</v>
       </c>
-      <c r="E30" s="311"/>
+      <c r="E30" s="309"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.60969766115231028</v>
@@ -9686,68 +9682,68 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="311"/>
+      <c r="E31" s="309"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="311"/>
+      <c r="E32" s="309"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="205">
+      <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
-      <c r="E33" s="309" t="s">
+      <c r="E33" s="307" t="s">
         <v>375</v>
       </c>
-      <c r="G33" s="198">
+      <c r="G33" s="197">
         <f>Data!C41</f>
         <v>-1084</v>
       </c>
-      <c r="H33" s="198">
+      <c r="H33" s="197">
         <f>Data!D41</f>
         <v>-1129</v>
       </c>
-      <c r="I33" s="198">
+      <c r="I33" s="197">
         <f>Data!E41</f>
         <v>-867.48327900000004</v>
       </c>
-      <c r="J33" s="198">
+      <c r="J33" s="197">
         <f>Data!F41</f>
         <v>-823.28128300000003</v>
       </c>
-      <c r="K33" s="198">
+      <c r="K33" s="197">
         <f>Data!G41</f>
         <v>0</v>
       </c>
-      <c r="L33" s="198" t="str">
+      <c r="L33" s="197" t="str">
         <f>Data!H41</f>
         <v/>
       </c>
-      <c r="M33" s="198" t="str">
+      <c r="M33" s="197" t="str">
         <f>Data!I41</f>
         <v/>
       </c>
-      <c r="N33" s="198" t="str">
+      <c r="N33" s="197" t="str">
         <f>Data!J41</f>
         <v/>
       </c>
-      <c r="O33" s="198" t="str">
+      <c r="O33" s="197" t="str">
         <f>Data!K41</f>
         <v/>
       </c>
-      <c r="P33" s="198" t="str">
+      <c r="P33" s="197" t="str">
         <f>Data!L41</f>
         <v/>
       </c>
-      <c r="Q33" s="198" t="str">
+      <c r="Q33" s="197" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -9757,56 +9753,56 @@
       <c r="B34" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="205">
+      <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="309" t="s">
+      <c r="E34" s="307" t="s">
         <v>375</v>
       </c>
       <c r="F34" s="59"/>
-      <c r="G34" s="187">
+      <c r="G34" s="186">
         <f>Data!C42</f>
         <v>0</v>
       </c>
-      <c r="H34" s="187">
+      <c r="H34" s="186">
         <f>Data!D42</f>
         <v>0</v>
       </c>
-      <c r="I34" s="187">
+      <c r="I34" s="186">
         <f>Data!E42</f>
         <v>0</v>
       </c>
-      <c r="J34" s="187">
+      <c r="J34" s="186">
         <f>Data!F42</f>
         <v>0</v>
       </c>
-      <c r="K34" s="187">
+      <c r="K34" s="186">
         <f>Data!G42</f>
         <v>0</v>
       </c>
-      <c r="L34" s="187" t="str">
+      <c r="L34" s="186" t="str">
         <f>Data!H42</f>
         <v/>
       </c>
-      <c r="M34" s="187" t="str">
+      <c r="M34" s="186" t="str">
         <f>Data!I42</f>
         <v/>
       </c>
-      <c r="N34" s="187" t="str">
+      <c r="N34" s="186" t="str">
         <f>Data!J42</f>
         <v/>
       </c>
-      <c r="O34" s="187" t="str">
+      <c r="O34" s="186" t="str">
         <f>Data!K42</f>
         <v/>
       </c>
-      <c r="P34" s="187" t="str">
+      <c r="P34" s="186" t="str">
         <f>Data!L42</f>
         <v/>
       </c>
-      <c r="Q34" s="187" t="str">
+      <c r="Q34" s="186" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -9816,68 +9812,68 @@
       <c r="B35" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C35" s="187">
         <f>C33+C34</f>
         <v>-1106.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="310"/>
+      <c r="E35" s="308"/>
       <c r="F35" s="59"/>
-      <c r="G35" s="188">
+      <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-1084</v>
       </c>
-      <c r="H35" s="188">
+      <c r="H35" s="187">
         <f t="shared" si="14"/>
         <v>-1129</v>
       </c>
-      <c r="I35" s="188">
+      <c r="I35" s="187">
         <f t="shared" si="14"/>
         <v>-867.48327900000004</v>
       </c>
-      <c r="J35" s="188">
+      <c r="J35" s="187">
         <f t="shared" si="14"/>
         <v>-823.28128300000003</v>
       </c>
-      <c r="K35" s="188">
+      <c r="K35" s="187">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="L35" s="188" t="str">
+      <c r="L35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="M35" s="188" t="str">
+      <c r="M35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="N35" s="188" t="str">
+      <c r="N35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="O35" s="188" t="str">
+      <c r="O35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="P35" s="188" t="str">
+      <c r="P35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="Q35" s="188" t="str">
+      <c r="Q35" s="187" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="311"/>
+      <c r="E36" s="309"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="E37" s="311"/>
+      <c r="E37" s="309"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9890,7 +9886,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="308"/>
+      <c r="E38" s="306"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9948,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="308"/>
+      <c r="E39" s="306"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -10004,7 +10000,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>0.1262407301768397</v>
       </c>
-      <c r="E40" s="311"/>
+      <c r="E40" s="309"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12367370222475756</v>
@@ -10052,25 +10048,25 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="311"/>
+      <c r="E41" s="309"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
         <v>213</v>
       </c>
-      <c r="E42" s="311"/>
+      <c r="E42" s="309"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C43" s="305">
+      <c r="C43" s="303">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="308" t="s">
+      <c r="E43" s="306" t="s">
         <v>376</v>
       </c>
       <c r="F43" s="27"/>
@@ -10150,59 +10146,59 @@
       <c r="B46" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="311"/>
+      <c r="E46" s="309"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="198">
+      <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-43</v>
       </c>
-      <c r="E47" s="311"/>
-      <c r="G47" s="198">
+      <c r="E47" s="309"/>
+      <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-43</v>
       </c>
-      <c r="H47" s="198">
+      <c r="H47" s="197">
         <f>Data!D51</f>
         <v>-40.775368</v>
       </c>
-      <c r="I47" s="198">
+      <c r="I47" s="197">
         <f>Data!E51</f>
         <v>-49.197794000000002</v>
       </c>
-      <c r="J47" s="198">
+      <c r="J47" s="197">
         <f>Data!F51</f>
         <v>-81.763175000000004</v>
       </c>
-      <c r="K47" s="198">
+      <c r="K47" s="197">
         <f>Data!G51</f>
         <v>0</v>
       </c>
-      <c r="L47" s="198" t="str">
+      <c r="L47" s="197" t="str">
         <f>Data!H51</f>
         <v/>
       </c>
-      <c r="M47" s="198" t="str">
+      <c r="M47" s="197" t="str">
         <f>Data!I51</f>
         <v/>
       </c>
-      <c r="N47" s="198" t="str">
+      <c r="N47" s="197" t="str">
         <f>Data!J51</f>
         <v/>
       </c>
-      <c r="O47" s="198" t="str">
+      <c r="O47" s="197" t="str">
         <f>Data!K51</f>
         <v/>
       </c>
-      <c r="P47" s="198" t="str">
+      <c r="P47" s="197" t="str">
         <f>Data!L51</f>
         <v/>
       </c>
-      <c r="Q47" s="198" t="str">
+      <c r="Q47" s="197" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -10212,109 +10208,109 @@
       <c r="B48" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C48" s="198">
+      <c r="C48" s="197">
         <f>BS!D75*C53</f>
         <v>185.19539222287685</v>
       </c>
-      <c r="E48" s="311"/>
-      <c r="G48" s="338">
+      <c r="E48" s="309"/>
+      <c r="G48" s="336">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
         <v>302.96861497481899</v>
       </c>
-      <c r="H48" s="338">
+      <c r="H48" s="336">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
         <v>180.07798132735766</v>
       </c>
-      <c r="I48" s="338">
+      <c r="I48" s="336">
         <f t="shared" si="19"/>
         <v>43.666282808578643</v>
       </c>
-      <c r="J48" s="338">
+      <c r="J48" s="336">
         <f t="shared" si="19"/>
         <v>74.082965933281514</v>
       </c>
-      <c r="K48" s="338">
+      <c r="K48" s="336">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="338" t="str">
+      <c r="L48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="338" t="str">
+      <c r="M48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="338" t="str">
+      <c r="N48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="338" t="str">
+      <c r="O48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="338" t="str">
+      <c r="P48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="338" t="str">
+      <c r="Q48" s="336" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="333" t="s">
+      <c r="B49" s="331" t="s">
         <v>384</v>
       </c>
-      <c r="C49" s="334">
+      <c r="C49" s="332">
         <f>BS!$C$66*C53</f>
         <v>1430.37</v>
       </c>
-      <c r="D49" s="335"/>
-      <c r="E49" s="336"/>
-      <c r="F49" s="335"/>
-      <c r="G49" s="334">
+      <c r="D49" s="333"/>
+      <c r="E49" s="334"/>
+      <c r="F49" s="333"/>
+      <c r="G49" s="332">
         <f>Data!C52</f>
         <v>2340</v>
       </c>
-      <c r="H49" s="334">
+      <c r="H49" s="332">
         <f>Data!D52</f>
         <v>1390.845307</v>
       </c>
-      <c r="I49" s="334">
+      <c r="I49" s="332">
         <f>Data!E52</f>
         <v>337.25969199999997</v>
       </c>
-      <c r="J49" s="334">
+      <c r="J49" s="332">
         <f>Data!F52</f>
         <v>572.18514300000004</v>
       </c>
-      <c r="K49" s="334">
+      <c r="K49" s="332">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="334" t="str">
+      <c r="L49" s="332" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="334" t="str">
+      <c r="M49" s="332" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="334" t="str">
+      <c r="N49" s="332" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="334" t="str">
+      <c r="O49" s="332" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="334" t="str">
+      <c r="P49" s="332" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="334" t="str">
+      <c r="Q49" s="332" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10324,66 +10320,66 @@
       <c r="B50" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="188">
+      <c r="C50" s="187">
         <f>C47+C48</f>
         <v>142.19539222287685</v>
       </c>
-      <c r="E50" s="311"/>
-      <c r="G50" s="188">
+      <c r="E50" s="309"/>
+      <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>259.96861497481899</v>
       </c>
-      <c r="H50" s="188">
+      <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>139.30261332735768</v>
       </c>
-      <c r="I50" s="188">
+      <c r="I50" s="187">
         <f t="shared" si="20"/>
         <v>-5.5315111914213588</v>
       </c>
-      <c r="J50" s="188">
+      <c r="J50" s="187">
         <f t="shared" si="20"/>
         <v>-7.6802090667184899</v>
       </c>
-      <c r="K50" s="188">
+      <c r="K50" s="187">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="L50" s="188" t="str">
+      <c r="L50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="M50" s="188" t="str">
+      <c r="M50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="N50" s="188" t="str">
+      <c r="N50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="O50" s="188" t="str">
+      <c r="O50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="P50" s="188" t="str">
+      <c r="P50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="Q50" s="188" t="str">
+      <c r="Q50" s="187" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="311"/>
+      <c r="E51" s="309"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="E52" s="311"/>
+      <c r="E52" s="309"/>
       <c r="G52" s="100" t="s">
         <v>224</v>
       </c>
@@ -10396,23 +10392,23 @@
       <c r="C53" s="89">
         <v>0.03</v>
       </c>
-      <c r="E53" s="308" t="s">
+      <c r="E53" s="306" t="s">
         <v>377</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
         <v>4.907821053293903E-2</v>
       </c>
-      <c r="H53" s="174"/>
-      <c r="I53" s="174"/>
-      <c r="J53" s="174"/>
-      <c r="K53" s="174"/>
-      <c r="L53" s="174"/>
-      <c r="M53" s="174"/>
-      <c r="N53" s="174"/>
-      <c r="O53" s="174"/>
-      <c r="P53" s="174"/>
-      <c r="Q53" s="174"/>
+      <c r="H53" s="173"/>
+      <c r="I53" s="173"/>
+      <c r="J53" s="173"/>
+      <c r="K53" s="173"/>
+      <c r="L53" s="173"/>
+      <c r="M53" s="173"/>
+      <c r="N53" s="173"/>
+      <c r="O53" s="173"/>
+      <c r="P53" s="173"/>
+      <c r="Q53" s="173"/>
     </row>
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
@@ -10423,23 +10419,23 @@
         <f>G54</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="E54" s="308" t="s">
+      <c r="E54" s="306" t="s">
         <v>378</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="H54" s="174"/>
-      <c r="I54" s="174"/>
-      <c r="J54" s="174"/>
-      <c r="K54" s="174"/>
-      <c r="L54" s="174"/>
-      <c r="M54" s="174"/>
-      <c r="N54" s="174"/>
-      <c r="O54" s="174"/>
-      <c r="P54" s="174"/>
-      <c r="Q54" s="174"/>
+      <c r="H54" s="173"/>
+      <c r="I54" s="173"/>
+      <c r="J54" s="173"/>
+      <c r="K54" s="173"/>
+      <c r="L54" s="173"/>
+      <c r="M54" s="173"/>
+      <c r="N54" s="173"/>
+      <c r="O54" s="173"/>
+      <c r="P54" s="173"/>
+      <c r="Q54" s="173"/>
     </row>
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
@@ -10450,7 +10446,7 @@
         <f>-C8/C47</f>
         <v>60.274889749707867</v>
       </c>
-      <c r="E55" s="311"/>
+      <c r="E55" s="309"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
@@ -10498,14 +10494,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="311"/>
+      <c r="E56" s="309"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="E57" s="311"/>
+      <c r="E57" s="309"/>
       <c r="G57" s="100" t="s">
         <v>224</v>
       </c>
@@ -10515,52 +10511,52 @@
       <c r="B58" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C58" s="198">
+      <c r="C58" s="197">
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="311"/>
-      <c r="G58" s="198">
+      <c r="E58" s="309"/>
+      <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="198">
+      <c r="H58" s="197">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="198">
+      <c r="I58" s="197">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="198">
+      <c r="J58" s="197">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="198">
+      <c r="K58" s="197">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="198" t="str">
+      <c r="L58" s="197" t="str">
         <f>Data!H56</f>
         <v/>
       </c>
-      <c r="M58" s="198" t="str">
+      <c r="M58" s="197" t="str">
         <f>Data!I56</f>
         <v/>
       </c>
-      <c r="N58" s="198" t="str">
+      <c r="N58" s="197" t="str">
         <f>Data!J56</f>
         <v/>
       </c>
-      <c r="O58" s="198" t="str">
+      <c r="O58" s="197" t="str">
         <f>Data!K56</f>
         <v/>
       </c>
-      <c r="P58" s="198" t="str">
+      <c r="P58" s="197" t="str">
         <f>Data!L56</f>
         <v/>
       </c>
-      <c r="Q58" s="198" t="str">
+      <c r="Q58" s="197" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -10570,52 +10566,52 @@
       <c r="B59" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="198">
+      <c r="C59" s="197">
         <f>BS!$C68*C67</f>
         <v>639</v>
       </c>
-      <c r="E59" s="311"/>
-      <c r="G59" s="198">
+      <c r="E59" s="309"/>
+      <c r="G59" s="197">
         <f>Data!C55</f>
         <v>639</v>
       </c>
-      <c r="H59" s="198">
+      <c r="H59" s="197">
         <f>Data!D55</f>
         <v>927</v>
       </c>
-      <c r="I59" s="198">
+      <c r="I59" s="197">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="198">
+      <c r="J59" s="197">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="198">
+      <c r="K59" s="197">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="198" t="str">
+      <c r="L59" s="197" t="str">
         <f>Data!H55</f>
         <v/>
       </c>
-      <c r="M59" s="198" t="str">
+      <c r="M59" s="197" t="str">
         <f>Data!I55</f>
         <v/>
       </c>
-      <c r="N59" s="198" t="str">
+      <c r="N59" s="197" t="str">
         <f>Data!J55</f>
         <v/>
       </c>
-      <c r="O59" s="198" t="str">
+      <c r="O59" s="197" t="str">
         <f>Data!K55</f>
         <v/>
       </c>
-      <c r="P59" s="198" t="str">
+      <c r="P59" s="197" t="str">
         <f>Data!L55</f>
         <v/>
       </c>
-      <c r="Q59" s="198" t="str">
+      <c r="Q59" s="197" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -10625,52 +10621,52 @@
       <c r="B60" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="C60" s="198">
+      <c r="C60" s="197">
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="311"/>
-      <c r="G60" s="198">
+      <c r="E60" s="309"/>
+      <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="198">
+      <c r="H60" s="197">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="198">
+      <c r="I60" s="197">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="198">
+      <c r="J60" s="197">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="198">
+      <c r="K60" s="197">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="198" t="str">
+      <c r="L60" s="197" t="str">
         <f>Data!H57</f>
         <v/>
       </c>
-      <c r="M60" s="198" t="str">
+      <c r="M60" s="197" t="str">
         <f>Data!I57</f>
         <v/>
       </c>
-      <c r="N60" s="198" t="str">
+      <c r="N60" s="197" t="str">
         <f>Data!J57</f>
         <v/>
       </c>
-      <c r="O60" s="198" t="str">
+      <c r="O60" s="197" t="str">
         <f>Data!K57</f>
         <v/>
       </c>
-      <c r="P60" s="198" t="str">
+      <c r="P60" s="197" t="str">
         <f>Data!L57</f>
         <v/>
       </c>
-      <c r="Q60" s="198" t="str">
+      <c r="Q60" s="197" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -10680,52 +10676,52 @@
       <c r="B61" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C61" s="188">
+      <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
         <v>639</v>
       </c>
-      <c r="E61" s="311"/>
-      <c r="G61" s="188">
+      <c r="E61" s="309"/>
+      <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
       </c>
-      <c r="H61" s="188">
+      <c r="H61" s="187">
         <f t="shared" si="22"/>
         <v>927</v>
       </c>
-      <c r="I61" s="188">
+      <c r="I61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="188">
+      <c r="J61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="188">
+      <c r="K61" s="187">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="188" t="str">
+      <c r="L61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="M61" s="188" t="str">
+      <c r="M61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="N61" s="188" t="str">
+      <c r="N61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="O61" s="188" t="str">
+      <c r="O61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="P61" s="188" t="str">
+      <c r="P61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="Q61" s="188" t="str">
+      <c r="Q61" s="187" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -10735,53 +10731,53 @@
       <c r="B62" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C62" s="306">
-        <v>0</v>
-      </c>
-      <c r="E62" s="309" t="s">
+      <c r="C62" s="304">
+        <v>0</v>
+      </c>
+      <c r="E62" s="307" t="s">
         <v>379</v>
       </c>
-      <c r="G62" s="198">
+      <c r="G62" s="197">
         <f>Data!C58</f>
         <v>-503</v>
       </c>
-      <c r="H62" s="198">
+      <c r="H62" s="197">
         <f>Data!D58</f>
         <v>203.76488900000004</v>
       </c>
-      <c r="I62" s="198">
+      <c r="I62" s="197">
         <f>Data!E58</f>
         <v>-503.75612799999999</v>
       </c>
-      <c r="J62" s="198">
+      <c r="J62" s="197">
         <f>Data!F58</f>
         <v>-726.80948300000091</v>
       </c>
-      <c r="K62" s="198">
+      <c r="K62" s="197">
         <f>Data!G58</f>
         <v>-3450</v>
       </c>
-      <c r="L62" s="198" t="str">
+      <c r="L62" s="197" t="str">
         <f>Data!H58</f>
         <v/>
       </c>
-      <c r="M62" s="198" t="str">
+      <c r="M62" s="197" t="str">
         <f>Data!I58</f>
         <v/>
       </c>
-      <c r="N62" s="198" t="str">
+      <c r="N62" s="197" t="str">
         <f>Data!J58</f>
         <v/>
       </c>
-      <c r="O62" s="198" t="str">
+      <c r="O62" s="197" t="str">
         <f>Data!K58</f>
         <v/>
       </c>
-      <c r="P62" s="198" t="str">
+      <c r="P62" s="197" t="str">
         <f>Data!L58</f>
         <v/>
       </c>
-      <c r="Q62" s="198" t="str">
+      <c r="Q62" s="197" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -10791,66 +10787,66 @@
       <c r="B63" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="C63" s="188">
+      <c r="C63" s="187">
         <f>C61+C62</f>
         <v>639</v>
       </c>
-      <c r="E63" s="311"/>
-      <c r="G63" s="188">
+      <c r="E63" s="309"/>
+      <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>136</v>
       </c>
-      <c r="H63" s="188">
+      <c r="H63" s="187">
         <f t="shared" si="23"/>
         <v>1130.764889</v>
       </c>
-      <c r="I63" s="188">
+      <c r="I63" s="187">
         <f t="shared" si="23"/>
         <v>-503.75612799999999</v>
       </c>
-      <c r="J63" s="188">
+      <c r="J63" s="187">
         <f t="shared" si="23"/>
         <v>-726.80948300000091</v>
       </c>
-      <c r="K63" s="188">
+      <c r="K63" s="187">
         <f t="shared" si="23"/>
         <v>-3450</v>
       </c>
-      <c r="L63" s="188" t="str">
+      <c r="L63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="M63" s="188" t="str">
+      <c r="M63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="N63" s="188" t="str">
+      <c r="N63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="O63" s="188" t="str">
+      <c r="O63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="P63" s="188" t="str">
+      <c r="P63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q63" s="188" t="str">
+      <c r="Q63" s="187" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="311"/>
+      <c r="E64" s="309"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="311"/>
+      <c r="E65" s="309"/>
       <c r="G65" s="100" t="s">
         <v>224</v>
       </c>
@@ -10860,75 +10856,75 @@
       <c r="B66" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="C66" s="181">
+      <c r="C66" s="180">
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="311"/>
+      <c r="E66" s="309"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
       </c>
-      <c r="H66" s="180"/>
-      <c r="I66" s="180"/>
-      <c r="J66" s="180"/>
-      <c r="K66" s="180"/>
-      <c r="L66" s="180"/>
-      <c r="M66" s="180"/>
-      <c r="N66" s="180"/>
-      <c r="O66" s="180"/>
-      <c r="P66" s="180"/>
-      <c r="Q66" s="180"/>
+      <c r="H66" s="179"/>
+      <c r="I66" s="179"/>
+      <c r="J66" s="179"/>
+      <c r="K66" s="179"/>
+      <c r="L66" s="179"/>
+      <c r="M66" s="179"/>
+      <c r="N66" s="179"/>
+      <c r="O66" s="179"/>
+      <c r="P66" s="179"/>
+      <c r="Q66" s="179"/>
     </row>
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="C67" s="181">
+      <c r="C67" s="180">
         <f>G67</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="E67" s="311"/>
+      <c r="E67" s="309"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="H67" s="180"/>
-      <c r="I67" s="180"/>
-      <c r="J67" s="180"/>
-      <c r="K67" s="180"/>
-      <c r="L67" s="180"/>
-      <c r="M67" s="180"/>
-      <c r="N67" s="180"/>
-      <c r="O67" s="180"/>
-      <c r="P67" s="180"/>
-      <c r="Q67" s="180"/>
+      <c r="H67" s="179"/>
+      <c r="I67" s="179"/>
+      <c r="J67" s="179"/>
+      <c r="K67" s="179"/>
+      <c r="L67" s="179"/>
+      <c r="M67" s="179"/>
+      <c r="N67" s="179"/>
+      <c r="O67" s="179"/>
+      <c r="P67" s="179"/>
+      <c r="Q67" s="179"/>
     </row>
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
         <v>163</v>
       </c>
-      <c r="C68" s="181">
+      <c r="C68" s="180">
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="311"/>
+      <c r="E68" s="309"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
       </c>
-      <c r="H68" s="180"/>
-      <c r="I68" s="180"/>
-      <c r="J68" s="180"/>
-      <c r="K68" s="180"/>
-      <c r="L68" s="180"/>
-      <c r="M68" s="180"/>
-      <c r="N68" s="180"/>
-      <c r="O68" s="180"/>
-      <c r="P68" s="180"/>
-      <c r="Q68" s="180"/>
+      <c r="H68" s="179"/>
+      <c r="I68" s="179"/>
+      <c r="J68" s="179"/>
+      <c r="K68" s="179"/>
+      <c r="L68" s="179"/>
+      <c r="M68" s="179"/>
+      <c r="N68" s="179"/>
+      <c r="O68" s="179"/>
+      <c r="P68" s="179"/>
+      <c r="Q68" s="179"/>
     </row>
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
@@ -10940,22 +10936,22 @@
         <v>8.7649511686601553E-3</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="316"/>
+      <c r="E69" s="314"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
         <v>8.7649511686601553E-3</v>
       </c>
-      <c r="H69" s="180"/>
-      <c r="I69" s="180"/>
-      <c r="J69" s="180"/>
-      <c r="K69" s="180"/>
-      <c r="L69" s="180"/>
-      <c r="M69" s="180"/>
-      <c r="N69" s="180"/>
-      <c r="O69" s="180"/>
-      <c r="P69" s="180"/>
-      <c r="Q69" s="180"/>
+      <c r="H69" s="179"/>
+      <c r="I69" s="179"/>
+      <c r="J69" s="179"/>
+      <c r="K69" s="179"/>
+      <c r="L69" s="179"/>
+      <c r="M69" s="179"/>
+      <c r="N69" s="179"/>
+      <c r="O69" s="179"/>
+      <c r="P69" s="179"/>
+      <c r="Q69" s="179"/>
     </row>
     <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="10"/>
@@ -10990,7 +10986,7 @@
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="308"/>
+      <c r="E72" s="306"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -11014,7 +11010,7 @@
         <v>0.57805815639048053</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="308"/>
+      <c r="E73" s="306"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11071,7 +11067,7 @@
         <v>0.42194184360951947</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="308"/>
+      <c r="E74" s="306"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11128,7 +11124,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="308"/>
+      <c r="E75" s="306"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11185,7 +11181,7 @@
         <v>0.2957011134326798</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="308"/>
+      <c r="E76" s="306"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11242,7 +11238,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="308"/>
+      <c r="E77" s="306"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11299,7 +11295,7 @@
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="309" t="s">
+      <c r="E78" s="307" t="s">
         <v>391</v>
       </c>
       <c r="F78" s="27"/>
@@ -11358,7 +11354,7 @@
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="308"/>
+      <c r="E79" s="306"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11415,7 +11411,7 @@
         <v>1.6223090955262618E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="308"/>
+      <c r="E80" s="306"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -11472,7 +11468,7 @@
         <v>0.3848277982270753</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="308"/>
+      <c r="E81" s="306"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -11529,7 +11525,7 @@
         <v>9.2358671574498064E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="308"/>
+      <c r="E82" s="306"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11582,12 +11578,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="307">
+      <c r="C83" s="305">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>2.6092079791263361E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="308"/>
+      <c r="E83" s="306"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11644,7 +11640,7 @@
         <v>0.2898599186734509</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="308"/>
+      <c r="E84" s="306"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -11696,26 +11692,26 @@
       <c r="B85" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C85" s="307">
+      <c r="C85" s="305">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="310" t="str">
+      <c r="E85" s="308" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="260"/>
-      <c r="H85" s="260"/>
-      <c r="I85" s="260"/>
-      <c r="J85" s="260"/>
-      <c r="K85" s="260"/>
-      <c r="L85" s="260"/>
-      <c r="M85" s="260"/>
-      <c r="N85" s="260"/>
-      <c r="O85" s="260"/>
-      <c r="P85" s="260"/>
-      <c r="Q85" s="260"/>
+      <c r="G85" s="259"/>
+      <c r="H85" s="259"/>
+      <c r="I85" s="259"/>
+      <c r="J85" s="259"/>
+      <c r="K85" s="259"/>
+      <c r="L85" s="259"/>
+      <c r="M85" s="259"/>
+      <c r="N85" s="259"/>
+      <c r="O85" s="259"/>
+      <c r="P85" s="259"/>
+      <c r="Q85" s="259"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
@@ -11725,21 +11721,21 @@
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="310" t="str">
+      <c r="E86" s="308" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
-      <c r="G86" s="174"/>
-      <c r="H86" s="174"/>
-      <c r="I86" s="174"/>
-      <c r="J86" s="174"/>
-      <c r="K86" s="174"/>
-      <c r="L86" s="174"/>
-      <c r="M86" s="174"/>
-      <c r="N86" s="174"/>
-      <c r="O86" s="174"/>
-      <c r="P86" s="174"/>
-      <c r="Q86" s="174"/>
+      <c r="G86" s="173"/>
+      <c r="H86" s="173"/>
+      <c r="I86" s="173"/>
+      <c r="J86" s="173"/>
+      <c r="K86" s="173"/>
+      <c r="L86" s="173"/>
+      <c r="M86" s="173"/>
+      <c r="N86" s="173"/>
+      <c r="O86" s="173"/>
+      <c r="P86" s="173"/>
+      <c r="Q86" s="173"/>
     </row>
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
@@ -11751,7 +11747,7 @@
         <v>0.2898599186734509</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="308"/>
+      <c r="E87" s="306"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -11800,14 +11796,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="311"/>
+      <c r="E88" s="309"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
         <v>219</v>
       </c>
-      <c r="E89" s="311"/>
+      <c r="E89" s="309"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11819,7 +11815,7 @@
         <f>G90</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E90" s="311"/>
+      <c r="E90" s="309"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>0.57999999999999996</v>
@@ -11875,7 +11871,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>4739.6903628800001</v>
       </c>
-      <c r="E91" s="311"/>
+      <c r="E91" s="309"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
@@ -11930,48 +11926,48 @@
         <f>C90/(C19*$C$3/Common_Shares)</f>
         <v>1.8655628478763795</v>
       </c>
-      <c r="E92" s="311"/>
-      <c r="G92" s="175">
+      <c r="E92" s="309"/>
+      <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
         <v>1.6879427845465798</v>
       </c>
-      <c r="H92" s="175">
+      <c r="H92" s="174">
         <f t="shared" si="38"/>
         <v>1.0475685954159291</v>
       </c>
-      <c r="I92" s="175">
+      <c r="I92" s="174">
         <f t="shared" si="38"/>
         <v>0.76028936874668918</v>
       </c>
-      <c r="J92" s="175">
+      <c r="J92" s="174">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="K92" s="175">
+      <c r="K92" s="174">
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="L92" s="175" t="str">
+      <c r="L92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="M92" s="175" t="str">
+      <c r="M92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="N92" s="175" t="str">
+      <c r="N92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="O92" s="175" t="str">
+      <c r="O92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="P92" s="175" t="str">
+      <c r="P92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
-      <c r="Q92" s="175" t="str">
+      <c r="Q92" s="174" t="str">
         <f t="shared" si="38"/>
         <v/>
       </c>
@@ -11985,7 +11981,7 @@
         <f>C90/Market_Price</f>
         <v>7.4454428754813853E-2</v>
       </c>
-      <c r="E93" s="311"/>
+      <c r="E93" s="309"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>7.4454428754813853E-2</v>
@@ -12033,16 +12029,16 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="311"/>
+      <c r="E94" s="309"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
-      <c r="B95" s="162" t="s">
+      <c r="B95" s="161" t="s">
         <v>89</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="308"/>
+      <c r="E95" s="306"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12066,7 +12062,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="308"/>
+      <c r="E96" s="306"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12123,7 +12119,7 @@
         <v>1.3840538284081383E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="308"/>
+      <c r="E97" s="306"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -12201,7 +12197,7 @@
       <c r="B100" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E100" s="311"/>
+      <c r="E100" s="309"/>
       <c r="G100" s="100" t="s">
         <v>224</v>
       </c>
@@ -12211,54 +12207,54 @@
       <c r="B101" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C101" s="206">
+      <c r="C101" s="205">
         <f>BS!G32</f>
         <v>180996</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="312"/>
+      <c r="E101" s="310"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="187">
+      <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>180344</v>
       </c>
-      <c r="H101" s="187">
+      <c r="H101" s="186">
         <f t="shared" si="42"/>
         <v>174007</v>
       </c>
-      <c r="I101" s="187">
+      <c r="I101" s="186">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="J101" s="187">
+      <c r="J101" s="186">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="K101" s="187">
+      <c r="K101" s="186">
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="L101" s="187" t="str">
+      <c r="L101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="M101" s="187" t="str">
+      <c r="M101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="N101" s="187" t="str">
+      <c r="N101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="187" t="str">
+      <c r="O101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="187" t="str">
+      <c r="P101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="187" t="str">
+      <c r="Q101" s="186" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -12268,54 +12264,54 @@
       <c r="B102" s="95" t="s">
         <v>215</v>
       </c>
-      <c r="C102" s="207">
+      <c r="C102" s="206">
         <f>BS!C4</f>
         <v>8029</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="313"/>
+      <c r="E102" s="311"/>
       <c r="F102" s="91"/>
-      <c r="G102" s="189">
+      <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
         <v>7251</v>
       </c>
-      <c r="H102" s="189">
+      <c r="H102" s="188">
         <f>IF(H$4="","",Data!E76)</f>
         <v>0</v>
       </c>
-      <c r="I102" s="189">
+      <c r="I102" s="188">
         <f>IF(I$4="","",Data!F76)</f>
         <v>0</v>
       </c>
-      <c r="J102" s="189">
+      <c r="J102" s="188">
         <f>IF(J$4="","",Data!G76)</f>
         <v>0</v>
       </c>
-      <c r="K102" s="189" t="str">
+      <c r="K102" s="188" t="str">
         <f>IF(K$4="","",Data!H76)</f>
         <v/>
       </c>
-      <c r="L102" s="189" t="str">
+      <c r="L102" s="188" t="str">
         <f>IF(L$4="","",Data!I76)</f>
         <v/>
       </c>
-      <c r="M102" s="189" t="str">
+      <c r="M102" s="188" t="str">
         <f>IF(M$4="","",Data!J76)</f>
         <v/>
       </c>
-      <c r="N102" s="189" t="str">
+      <c r="N102" s="188" t="str">
         <f>IF(N$4="","",Data!K76)</f>
         <v/>
       </c>
-      <c r="O102" s="189" t="str">
+      <c r="O102" s="188" t="str">
         <f>IF(O$4="","",Data!L76)</f>
         <v/>
       </c>
-      <c r="P102" s="189" t="str">
+      <c r="P102" s="188" t="str">
         <f>IF(P$4="","",Data!M76)</f>
         <v/>
       </c>
-      <c r="Q102" s="189" t="str">
+      <c r="Q102" s="188" t="str">
         <f>IF(Q$4="","",Data!N76)</f>
         <v/>
       </c>
@@ -12325,54 +12321,54 @@
       <c r="B103" s="95" t="s">
         <v>216</v>
       </c>
-      <c r="C103" s="207">
+      <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
         <v>15310</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="313"/>
+      <c r="E103" s="311"/>
       <c r="F103" s="91"/>
-      <c r="G103" s="189">
+      <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
         <v>16389</v>
       </c>
-      <c r="H103" s="189">
+      <c r="H103" s="188">
         <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
-      <c r="I103" s="189">
+      <c r="I103" s="188">
         <f>IF(I$4="","",Data!F77)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="189">
+      <c r="J103" s="188">
         <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
-      <c r="K103" s="189" t="str">
+      <c r="K103" s="188" t="str">
         <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
-      <c r="L103" s="189" t="str">
+      <c r="L103" s="188" t="str">
         <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
-      <c r="M103" s="189" t="str">
+      <c r="M103" s="188" t="str">
         <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
-      <c r="N103" s="189" t="str">
+      <c r="N103" s="188" t="str">
         <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
-      <c r="O103" s="189" t="str">
+      <c r="O103" s="188" t="str">
         <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
-      <c r="P103" s="189" t="str">
+      <c r="P103" s="188" t="str">
         <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
-      <c r="Q103" s="189" t="str">
+      <c r="Q103" s="188" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -12382,54 +12378,54 @@
       <c r="B104" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C104" s="206">
+      <c r="C104" s="205">
         <f>BS!G30</f>
         <v>13889</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="312"/>
+      <c r="E104" s="310"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="187">
+      <c r="G104" s="186">
         <f>Data!C78</f>
         <v>14028</v>
       </c>
-      <c r="H104" s="187">
+      <c r="H104" s="186">
         <f>Data!D78</f>
         <v>10902</v>
       </c>
-      <c r="I104" s="187">
+      <c r="I104" s="186">
         <f>Data!E78</f>
         <v>0</v>
       </c>
-      <c r="J104" s="187">
+      <c r="J104" s="186">
         <f>Data!F78</f>
         <v>0</v>
       </c>
-      <c r="K104" s="187">
+      <c r="K104" s="186">
         <f>Data!G78</f>
         <v>0</v>
       </c>
-      <c r="L104" s="187" t="str">
+      <c r="L104" s="186" t="str">
         <f>Data!H78</f>
         <v/>
       </c>
-      <c r="M104" s="187" t="str">
+      <c r="M104" s="186" t="str">
         <f>Data!I78</f>
         <v/>
       </c>
-      <c r="N104" s="187" t="str">
+      <c r="N104" s="186" t="str">
         <f>Data!J78</f>
         <v/>
       </c>
-      <c r="O104" s="187" t="str">
+      <c r="O104" s="186" t="str">
         <f>Data!K78</f>
         <v/>
       </c>
-      <c r="P104" s="187" t="str">
+      <c r="P104" s="186" t="str">
         <f>Data!L78</f>
         <v/>
       </c>
-      <c r="Q104" s="187" t="str">
+      <c r="Q104" s="186" t="str">
         <f>Data!M78</f>
         <v/>
       </c>
@@ -12439,61 +12435,61 @@
       <c r="B105" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C105" s="206">
+      <c r="C105" s="205">
         <f>BS!G27</f>
         <v>167107</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="312"/>
+      <c r="E105" s="310"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="187">
+      <c r="G105" s="186">
         <f>Data!C79</f>
         <v>166316</v>
       </c>
-      <c r="H105" s="187">
+      <c r="H105" s="186">
         <f>Data!D79</f>
         <v>163105</v>
       </c>
-      <c r="I105" s="187">
+      <c r="I105" s="186">
         <f>Data!E79</f>
         <v>0</v>
       </c>
-      <c r="J105" s="187">
+      <c r="J105" s="186">
         <f>Data!F79</f>
         <v>0</v>
       </c>
-      <c r="K105" s="187">
+      <c r="K105" s="186">
         <f>Data!G79</f>
         <v>0</v>
       </c>
-      <c r="L105" s="187" t="str">
+      <c r="L105" s="186" t="str">
         <f>Data!H79</f>
         <v/>
       </c>
-      <c r="M105" s="187" t="str">
+      <c r="M105" s="186" t="str">
         <f>Data!I79</f>
         <v/>
       </c>
-      <c r="N105" s="187" t="str">
+      <c r="N105" s="186" t="str">
         <f>Data!J79</f>
         <v/>
       </c>
-      <c r="O105" s="187" t="str">
+      <c r="O105" s="186" t="str">
         <f>Data!K79</f>
         <v/>
       </c>
-      <c r="P105" s="187" t="str">
+      <c r="P105" s="186" t="str">
         <f>Data!L79</f>
         <v/>
       </c>
-      <c r="Q105" s="187" t="str">
+      <c r="Q105" s="186" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="311"/>
+      <c r="E106" s="309"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
@@ -12502,7 +12498,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="312"/>
+      <c r="E107" s="310"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
         <v>224</v>
@@ -12528,7 +12524,7 @@
         <v>0.91602966343411296</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="312"/>
+      <c r="E108" s="310"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12585,7 +12581,7 @@
         <v>1.7467199087278951</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="312"/>
+      <c r="E109" s="310"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12642,26 +12638,26 @@
         <v>8.343867655447804</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="312"/>
+      <c r="E110" s="310"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
         <v>8.343867655447804</v>
       </c>
-      <c r="H110" s="232"/>
-      <c r="I110" s="232"/>
-      <c r="J110" s="232"/>
-      <c r="K110" s="232"/>
-      <c r="L110" s="232"/>
-      <c r="M110" s="232"/>
-      <c r="N110" s="232"/>
-      <c r="O110" s="232"/>
-      <c r="P110" s="232"/>
-      <c r="Q110" s="232"/>
+      <c r="H110" s="231"/>
+      <c r="I110" s="231"/>
+      <c r="J110" s="231"/>
+      <c r="K110" s="231"/>
+      <c r="L110" s="231"/>
+      <c r="M110" s="231"/>
+      <c r="N110" s="231"/>
+      <c r="O110" s="231"/>
+      <c r="P110" s="231"/>
+      <c r="Q110" s="231"/>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="311"/>
+      <c r="E111" s="309"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
@@ -12670,7 +12666,7 @@
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="314"/>
+      <c r="E112" s="312"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12726,7 +12722,7 @@
         <f>C81</f>
         <v>0.3848277982270753</v>
       </c>
-      <c r="E113" s="311"/>
+      <c r="E113" s="309"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
         <v>0.37957428579290575</v>
@@ -12780,7 +12776,7 @@
         <f>C4/C101</f>
         <v>4.8426484563194767E-2</v>
       </c>
-      <c r="E114" s="311"/>
+      <c r="E114" s="309"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>4.8601561460320276E-2</v>
@@ -12835,7 +12831,7 @@
         <v>1.0831144117242246</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="315"/>
+      <c r="E115" s="313"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12892,7 +12888,7 @@
         <v>1.5509944282629921E-2</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="314"/>
+      <c r="E116" s="312"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -12983,12 +12979,12 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
-      <c r="B119" s="183" t="s">
+      <c r="B119" s="182" t="s">
         <v>175</v>
       </c>
-      <c r="C119" s="184"/>
+      <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="308"/>
+      <c r="E119" s="306"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -13008,54 +13004,54 @@
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="182">
+      <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
         <v>0.31089812956997381</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="308"/>
+      <c r="E120" s="306"/>
       <c r="F120" s="27"/>
-      <c r="G120" s="182">
+      <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>0.34361354265677985</v>
       </c>
-      <c r="H120" s="182">
+      <c r="H120" s="181">
         <f t="shared" si="49"/>
         <v>0.55366302745045104</v>
       </c>
-      <c r="I120" s="182">
+      <c r="I120" s="181">
         <f t="shared" si="49"/>
         <v>0.74971454742241805</v>
       </c>
-      <c r="J120" s="182">
+      <c r="J120" s="181">
         <f t="shared" si="49"/>
         <v>1.2311599503085606</v>
       </c>
-      <c r="K120" s="182">
+      <c r="K120" s="181">
         <f t="shared" si="49"/>
         <v>0.42217947730748451</v>
       </c>
-      <c r="L120" s="182" t="str">
+      <c r="L120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="182" t="str">
+      <c r="M120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="182" t="str">
+      <c r="N120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="182" t="str">
+      <c r="O120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="182" t="str">
+      <c r="P120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="182" t="str">
+      <c r="Q120" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
@@ -13070,7 +13066,7 @@
         <v>3.9909901100125003E-2</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="308"/>
+      <c r="E121" s="306"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
@@ -13877,10 +13873,10 @@
       <c r="H4" s="124"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B5" s="234" t="s">
+      <c r="B5" s="233" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="235">
+      <c r="C5" s="234">
         <f>Thesis!C70</f>
         <v>0.09</v>
       </c>
@@ -13891,7 +13887,7 @@
       <c r="B6" s="153" t="s">
         <v>233</v>
       </c>
-      <c r="C6" s="239">
+      <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>28229.135413031079</v>
       </c>
@@ -13899,17 +13895,17 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="346" t="s">
+      <c r="E6" s="344" t="s">
         <v>256</v>
       </c>
-      <c r="F6" s="346"/>
+      <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="233">
+      <c r="C7" s="232">
         <f>BS!G31</f>
         <v>3093</v>
       </c>
@@ -13917,15 +13913,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346"/>
-      <c r="F7" s="346"/>
+      <c r="E7" s="344"/>
+      <c r="F7" s="344"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
         <v>230</v>
       </c>
-      <c r="C8" s="208">
+      <c r="C8" s="207">
         <f>BS!D66</f>
         <v>41505.820259237436</v>
       </c>
@@ -13933,15 +13929,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="344"/>
+      <c r="F8" s="344"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B9" s="234" t="s">
+      <c r="B9" s="233" t="s">
         <v>195</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="235">
         <f>BS!H42</f>
         <v>7814.4</v>
       </c>
@@ -13949,15 +13945,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="344"/>
+      <c r="F9" s="344"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="239">
+      <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
         <v>74456.355672268517</v>
       </c>
@@ -13968,10 +13964,10 @@
       <c r="H10" s="124"/>
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="237" t="s">
+      <c r="B11" s="236" t="s">
         <v>171</v>
       </c>
-      <c r="C11" s="238">
+      <c r="C11" s="237">
         <f>Exchange_Rate</f>
         <v>1</v>
       </c>
@@ -14018,7 +14014,7 @@
       <c r="B16" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C16" s="166">
+      <c r="C16" s="165">
         <f>Scenarios!C65</f>
         <v>-7.3000000000000001E-3</v>
       </c>
@@ -14028,7 +14024,7 @@
       <c r="B17" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="167">
+      <c r="C17" s="166">
         <f>Scenarios!C64</f>
         <v>10</v>
       </c>
@@ -15157,19 +15153,19 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B73" s="176" t="s">
+      <c r="B73" s="175" t="s">
         <v>122</v>
       </c>
-      <c r="C73" s="176" t="s">
+      <c r="C73" s="175" t="s">
         <v>137</v>
       </c>
-      <c r="D73" s="176" t="s">
+      <c r="D73" s="175" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="177" t="s">
+      <c r="E73" s="176" t="s">
         <v>118</v>
       </c>
-      <c r="F73" s="177" t="s">
+      <c r="F73" s="176" t="s">
         <v>124</v>
       </c>
     </row>
@@ -15287,27 +15283,27 @@
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B79" s="160"/>
-      <c r="C79" s="160"/>
-      <c r="D79" s="160"/>
-      <c r="E79" s="160"/>
-      <c r="F79" s="161"/>
+      <c r="B79" s="159"/>
+      <c r="C79" s="159"/>
+      <c r="D79" s="159"/>
+      <c r="E79" s="159"/>
+      <c r="F79" s="160"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B80" s="160" t="s">
+      <c r="B80" s="159" t="s">
         <v>342</v>
       </c>
-      <c r="C80" s="160" t="s">
+      <c r="C80" s="159" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C81" s="160" t="s">
+      <c r="C81" s="159" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C82" s="160" t="s">
+      <c r="C82" s="159" t="s">
         <v>108</v>
       </c>
     </row>
@@ -15366,19 +15362,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="285" t="s">
+      <c r="H2" s="283" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="286"/>
+      <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B3" s="164" t="s">
+      <c r="B3" s="163" t="s">
         <v>153</v>
       </c>
-      <c r="H3" s="284">
-        <v>0</v>
-      </c>
-      <c r="I3" s="272">
+      <c r="H3" s="282">
+        <v>0</v>
+      </c>
+      <c r="I3" s="270">
         <f>-Market_Price</f>
         <v>-7.79</v>
       </c>
@@ -15391,29 +15387,29 @@
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
-      <c r="E4" s="160" t="s">
+      <c r="E4" s="159" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="160"/>
-      <c r="H4" s="284">
+      <c r="F4" s="159"/>
+      <c r="H4" s="282">
         <v>1</v>
       </c>
-      <c r="I4" s="272">
+      <c r="I4" s="270">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="H5" s="284">
+      <c r="H5" s="282">
         <v>2</v>
       </c>
-      <c r="I5" s="272">
+      <c r="I5" s="270">
         <f t="shared" si="0"/>
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B6" s="164" t="s">
+      <c r="B6" s="163" t="s">
         <v>100</v>
       </c>
       <c r="C6" s="110">
@@ -15424,10 +15420,10 @@
         <v>298</v>
       </c>
       <c r="F6" s="103"/>
-      <c r="H6" s="284">
+      <c r="H6" s="282">
         <v>3</v>
       </c>
-      <c r="I6" s="272">
+      <c r="I6" s="270">
         <f t="shared" si="0"/>
         <v>9.6147055134616366</v>
       </c>
@@ -15444,15 +15440,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="348" t="str">
+      <c r="E7" s="346" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="348"/>
-      <c r="H7" s="284">
+      <c r="F7" s="346"/>
+      <c r="H7" s="282">
         <v>4</v>
       </c>
-      <c r="I7" s="272" t="str">
+      <c r="I7" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15469,12 +15465,12 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
-      <c r="H8" s="284">
+      <c r="E8" s="346"/>
+      <c r="F8" s="346"/>
+      <c r="H8" s="282">
         <v>5</v>
       </c>
-      <c r="I8" s="272" t="str">
+      <c r="I8" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15483,7 +15479,7 @@
       <c r="B9" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="208">
+      <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
         <v>2540.6221871727971</v>
       </c>
@@ -15491,37 +15487,37 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
-      <c r="H9" s="284">
+      <c r="E9" s="346"/>
+      <c r="F9" s="346"/>
+      <c r="H9" s="282">
         <v>6</v>
       </c>
-      <c r="I9" s="272" t="str">
+      <c r="I9" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="348"/>
-      <c r="F10" s="348"/>
-      <c r="H10" s="284">
+      <c r="E10" s="346"/>
+      <c r="F10" s="346"/>
+      <c r="H10" s="282">
         <v>7</v>
       </c>
-      <c r="I10" s="272" t="str">
+      <c r="I10" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B11" s="164" t="s">
+      <c r="B11" s="163" t="s">
         <v>295</v>
       </c>
-      <c r="E11" s="348"/>
-      <c r="F11" s="348"/>
-      <c r="H11" s="284">
+      <c r="E11" s="346"/>
+      <c r="F11" s="346"/>
+      <c r="H11" s="282">
         <v>8</v>
       </c>
-      <c r="I11" s="272" t="str">
+      <c r="I11" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15530,17 +15526,17 @@
       <c r="B12" s="122" t="s">
         <v>149</v>
       </c>
-      <c r="C12" s="163">
+      <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.28945840615733698</v>
       </c>
-      <c r="D12" s="163"/>
-      <c r="E12" s="348"/>
-      <c r="F12" s="348"/>
-      <c r="H12" s="284">
+      <c r="D12" s="162"/>
+      <c r="E12" s="346"/>
+      <c r="F12" s="346"/>
+      <c r="H12" s="282">
         <v>9</v>
       </c>
-      <c r="I12" s="272" t="str">
+      <c r="I12" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15549,16 +15545,16 @@
       <c r="B13" s="152" t="s">
         <v>157</v>
       </c>
-      <c r="C13" s="163">
+      <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="348"/>
-      <c r="F13" s="348"/>
-      <c r="H13" s="284">
+      <c r="E13" s="346"/>
+      <c r="F13" s="346"/>
+      <c r="H13" s="282">
         <v>10</v>
       </c>
-      <c r="I13" s="272" t="str">
+      <c r="I13" s="270" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -15567,12 +15563,12 @@
       <c r="B14" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="163">
+      <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.34649046142280127</v>
       </c>
-      <c r="E14" s="348"/>
-      <c r="F14" s="348"/>
+      <c r="E14" s="346"/>
+      <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15587,7 +15583,7 @@
       <c r="B17" s="112" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="164" t="s">
+      <c r="E17" s="163" t="s">
         <v>367</v>
       </c>
     </row>
@@ -15598,27 +15594,27 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="348" t="s">
+      <c r="E18" s="346" t="s">
         <v>368</v>
       </c>
-      <c r="F18" s="349"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="349"/>
-      <c r="F19" s="349"/>
+      <c r="E19" s="347"/>
+      <c r="F19" s="347"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B20" s="164" t="s">
+      <c r="B20" s="163" t="s">
         <v>332</v>
       </c>
-      <c r="E20" s="349"/>
-      <c r="F20" s="349"/>
+      <c r="E20" s="347"/>
+      <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="165">
+      <c r="C21" s="164">
         <f>Market_Price</f>
         <v>7.79</v>
       </c>
@@ -15626,14 +15622,14 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="349"/>
-      <c r="F21" s="349"/>
+      <c r="E21" s="347"/>
+      <c r="F21" s="347"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
         <v>297</v>
       </c>
-      <c r="C22" s="165">
+      <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
         <v>9.111288498532895</v>
       </c>
@@ -15641,104 +15637,104 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="349"/>
-      <c r="F22" s="349"/>
+      <c r="E22" s="347"/>
+      <c r="F22" s="347"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B24" s="164" t="s">
+      <c r="B24" s="163" t="s">
         <v>120</v>
       </c>
-      <c r="E24" s="164" t="s">
+      <c r="E24" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="164"/>
+      <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="171">
+      <c r="C25" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D25" s="168"/>
-      <c r="E25" s="347"/>
-      <c r="F25" s="347"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="345"/>
+      <c r="F25" s="345"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="169">
-        <v>0</v>
-      </c>
-      <c r="D26" s="169"/>
-      <c r="E26" s="347"/>
-      <c r="F26" s="347"/>
+      <c r="C26" s="168">
+        <v>0</v>
+      </c>
+      <c r="D26" s="168"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="165">
+      <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
         <v>9.1112884985328897</v>
       </c>
-      <c r="D27" s="165" t="str">
+      <c r="D27" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="347"/>
-      <c r="F27" s="347"/>
+      <c r="E27" s="345"/>
+      <c r="F27" s="345"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C28" s="170">
+      <c r="C28" s="169">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D28" s="170"/>
-      <c r="E28" s="347"/>
-      <c r="F28" s="347"/>
+      <c r="D28" s="169"/>
+      <c r="E28" s="345"/>
+      <c r="F28" s="345"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B30" s="164" t="s">
+      <c r="B30" s="163" t="s">
         <v>121</v>
       </c>
-      <c r="E30" s="164" t="s">
+      <c r="E30" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F30" s="164"/>
+      <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="171">
+      <c r="C31" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D31" s="168"/>
-      <c r="E31" s="347"/>
-      <c r="F31" s="347"/>
+      <c r="D31" s="167"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="169">
+      <c r="C32" s="168">
         <v>-0.05</v>
       </c>
-      <c r="D32" s="169"/>
-      <c r="E32" s="347"/>
-      <c r="F32" s="347"/>
+      <c r="D32" s="168"/>
+      <c r="E32" s="345"/>
+      <c r="F32" s="345"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C33" s="165">
+      <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
         <v>8.6191954792579697</v>
       </c>
@@ -15746,57 +15742,57 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="347"/>
-      <c r="F33" s="347"/>
+      <c r="E33" s="345"/>
+      <c r="F33" s="345"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C34" s="170">
+      <c r="C34" s="169">
         <v>0.2</v>
       </c>
-      <c r="D34" s="170"/>
-      <c r="E34" s="347"/>
-      <c r="F34" s="347"/>
+      <c r="D34" s="169"/>
+      <c r="E34" s="345"/>
+      <c r="F34" s="345"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B36" s="164" t="s">
+      <c r="B36" s="163" t="s">
         <v>119</v>
       </c>
-      <c r="E36" s="164" t="s">
+      <c r="E36" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F36" s="164"/>
+      <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C37" s="171">
+      <c r="C37" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
-      <c r="D37" s="168"/>
-      <c r="E37" s="347"/>
-      <c r="F37" s="347"/>
+      <c r="D37" s="167"/>
+      <c r="E37" s="345"/>
+      <c r="F37" s="345"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="169">
+      <c r="C38" s="168">
         <v>0.02</v>
       </c>
-      <c r="D38" s="169"/>
-      <c r="E38" s="347"/>
-      <c r="F38" s="347"/>
+      <c r="D38" s="168"/>
+      <c r="E38" s="345"/>
+      <c r="F38" s="345"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="165">
+      <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
         <v>9.3427745886766083</v>
       </c>
@@ -15804,26 +15800,26 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="347"/>
-      <c r="F39" s="347"/>
+      <c r="E39" s="345"/>
+      <c r="F39" s="345"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C40" s="172">
+      <c r="C40" s="171">
         <f>1-C28-C34</f>
         <v>0.24999999999999994</v>
       </c>
-      <c r="D40" s="170"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="D40" s="169"/>
+      <c r="E40" s="345"/>
+      <c r="F40" s="345"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C42" s="159">
+      <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
         <v>9.070741417213835</v>
       </c>
@@ -15857,47 +15853,47 @@
       <c r="F46" s="103"/>
     </row>
     <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B47" s="164"/>
-      <c r="E47" s="164"/>
-      <c r="F47" s="164"/>
+      <c r="B47" s="163"/>
+      <c r="E47" s="163"/>
+      <c r="F47" s="163"/>
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B48" s="164" t="s">
+      <c r="B48" s="163" t="s">
         <v>170</v>
       </c>
-      <c r="E48" s="164" t="s">
+      <c r="E48" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F48" s="164"/>
+      <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="171">
+      <c r="C49" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
-      <c r="D49" s="168"/>
-      <c r="E49" s="347"/>
-      <c r="F49" s="347"/>
+      <c r="D49" s="167"/>
+      <c r="E49" s="345"/>
+      <c r="F49" s="345"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="169">
+      <c r="C50" s="168">
         <v>-0.2</v>
       </c>
-      <c r="D50" s="169"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="D50" s="168"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="165">
+      <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
         <v>7.2649269878396519</v>
       </c>
@@ -15905,57 +15901,57 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="347"/>
-      <c r="F51" s="347"/>
+      <c r="E51" s="345"/>
+      <c r="F51" s="345"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="170">
+      <c r="C52" s="169">
         <v>0.05</v>
       </c>
-      <c r="D52" s="170"/>
-      <c r="E52" s="347"/>
-      <c r="F52" s="347"/>
+      <c r="D52" s="169"/>
+      <c r="E52" s="345"/>
+      <c r="F52" s="345"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="B54" s="164" t="s">
+      <c r="B54" s="163" t="s">
         <v>350</v>
       </c>
-      <c r="E54" s="164" t="s">
+      <c r="E54" s="163" t="s">
         <v>154</v>
       </c>
-      <c r="F54" s="164"/>
+      <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C55" s="171">
+      <c r="C55" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
-      <c r="D55" s="168"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="D55" s="167"/>
+      <c r="E55" s="345"/>
+      <c r="F55" s="345"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
         <v>139</v>
       </c>
-      <c r="C56" s="169">
+      <c r="C56" s="168">
         <v>0.05</v>
       </c>
-      <c r="D56" s="169"/>
-      <c r="E56" s="347"/>
-      <c r="F56" s="347"/>
+      <c r="D56" s="168"/>
+      <c r="E56" s="345"/>
+      <c r="F56" s="345"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
         <v>118</v>
       </c>
-      <c r="C57" s="165">
+      <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
         <v>10.155837771544068</v>
       </c>
@@ -15963,25 +15959,25 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="347"/>
-      <c r="F57" s="347"/>
+      <c r="E57" s="345"/>
+      <c r="F57" s="345"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
         <v>152</v>
       </c>
-      <c r="C58" s="170">
+      <c r="C58" s="169">
         <v>0.05</v>
       </c>
-      <c r="D58" s="170"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="D58" s="169"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="159">
+      <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
         <v>9.0347055134616365</v>
       </c>
@@ -15992,7 +15988,7 @@
       <c r="E60" s="103" t="s">
         <v>325</v>
       </c>
-      <c r="F60" s="321">
+      <c r="F60" s="319">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
@@ -16010,7 +16006,7 @@
       <c r="B63" s="112" t="s">
         <v>333</v>
       </c>
-      <c r="E63" s="290" t="s">
+      <c r="E63" s="288" t="s">
         <v>343</v>
       </c>
     </row>
@@ -16018,11 +16014,11 @@
       <c r="B64" s="156" t="s">
         <v>138</v>
       </c>
-      <c r="C64" s="171">
+      <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
-      <c r="E64" s="289" t="s">
+      <c r="E64" s="287" t="s">
         <v>344</v>
       </c>
     </row>
@@ -16034,7 +16030,7 @@
         <v>-7.3000000000000001E-3</v>
       </c>
       <c r="D65" s="155"/>
-      <c r="E65" s="289" t="s">
+      <c r="E65" s="287" t="s">
         <v>345</v>
       </c>
     </row>
@@ -16042,15 +16038,15 @@
       <c r="B66" s="103" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="165">
+      <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
         <v>9.0321281164495559</v>
       </c>
-      <c r="D66" s="165" t="str">
+      <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="289" t="s">
+      <c r="E66" s="287" t="s">
         <v>346</v>
       </c>
     </row>
@@ -16058,7 +16054,7 @@
       <c r="B68" s="112" t="s">
         <v>320</v>
       </c>
-      <c r="E68" s="290" t="s">
+      <c r="E68" s="288" t="s">
         <v>347</v>
       </c>
     </row>
@@ -16066,7 +16062,7 @@
       <c r="B69" s="103" t="s">
         <v>334</v>
       </c>
-      <c r="C69" s="281" t="str">
+      <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>Y</v>
       </c>
@@ -16076,11 +16072,11 @@
       <c r="B70" s="103" t="s">
         <v>322</v>
       </c>
-      <c r="C70" s="281" t="str">
+      <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
-      <c r="E70" s="289" t="s">
+      <c r="E70" s="287" t="s">
         <v>323</v>
       </c>
     </row>
@@ -16088,24 +16084,24 @@
       <c r="B71" s="103" t="s">
         <v>321</v>
       </c>
-      <c r="C71" s="281" t="str">
+      <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="289"/>
+      <c r="E71" s="287"/>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
         <v>312</v>
       </c>
-      <c r="C72" s="280" t="str">
+      <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
         <v>390</v>
       </c>
-      <c r="F72" s="339">
+      <c r="F72" s="337">
         <f>BS!D89/C60</f>
         <v>0.62612608991135499</v>
       </c>
@@ -16125,10 +16121,10 @@
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B76" s="283" t="s">
+      <c r="B76" s="281" t="s">
         <v>326</v>
       </c>
-      <c r="C76" s="282">
+      <c r="C76" s="280">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -16138,7 +16134,7 @@
       <c r="B77" s="103" t="s">
         <v>116</v>
       </c>
-      <c r="C77" s="178">
+      <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
         <v>0.57999999999999996</v>
       </c>
@@ -16156,7 +16152,7 @@
       <c r="B80" s="152" t="s">
         <v>328</v>
       </c>
-      <c r="C80" s="172">
+      <c r="C80" s="171">
         <f>Thesis!C121</f>
         <v>0.2</v>
       </c>
@@ -16198,9 +16194,9 @@
       <c r="E83" s="150" t="s">
         <v>131</v>
       </c>
-      <c r="F83" s="270">
-        <f>(C83/C60-1)</f>
-        <v>-0.28606673541699057</v>
+      <c r="F83" s="337">
+        <f>(1-C83/C60)</f>
+        <v>0.28606673541699057</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16215,7 +16211,7 @@
       <c r="B86" s="152" t="s">
         <v>329</v>
       </c>
-      <c r="C86" s="274">
+      <c r="C86" s="272">
         <f>Market_Price</f>
         <v>7.79</v>
       </c>
@@ -16228,7 +16224,7 @@
       <c r="B87" s="103" t="s">
         <v>327</v>
       </c>
-      <c r="C87" s="273">
+      <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.12172735692567005</v>
       </c>
@@ -16237,42 +16233,42 @@
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="330" t="s">
+      <c r="E89" s="328" t="s">
         <v>362</v>
       </c>
-      <c r="F89" s="327"/>
+      <c r="F89" s="325"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="326"/>
+      <c r="H89" s="324"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="323" t="s">
+      <c r="E90" s="321" t="s">
         <v>363</v>
       </c>
-      <c r="F90" s="328" t="s">
+      <c r="F90" s="326" t="s">
         <v>364</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="326"/>
+      <c r="H90" s="324"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="324" t="s">
+      <c r="E91" s="322" t="s">
         <v>363</v>
       </c>
-      <c r="F91" s="328" t="s">
+      <c r="F91" s="326" t="s">
         <v>365</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="326"/>
+      <c r="H91" s="324"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="325" t="s">
+      <c r="E92" s="323" t="s">
         <v>363</v>
       </c>
-      <c r="F92" s="329" t="s">
+      <c r="F92" s="327" t="s">
         <v>366</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="326"/>
+      <c r="H92" s="324"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D66181-D6A0-4D46-B420-5BB53141988F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A56EB4F-905D-494D-A1AB-28014992666A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,12 +43,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
   <si>
     <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Reporting Currency:</t>
   </si>
   <si>
     <t>Exchange Rate:</t>
@@ -1570,10 +1567,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Categorize the investment</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1603,10 +1596,6 @@
   </si>
   <si>
     <t>Total Non-FCF Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Type of Investment</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1666,10 +1655,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Investment Type:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Valuation Overview</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1722,18 +1707,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Status in Portfolio:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Snowball Scenario</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Held</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>C0003</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1755,10 +1732,6 @@
   </si>
   <si>
     <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1x for stable businesses, 2x for for volatile ones</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2003,6 +1976,34 @@
   </si>
   <si>
     <t>The Non-FCF Value is of the Expected Value, at</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reporting Currency:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growth Classification</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type of Company</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Variable + Fixed Costs &amp; Dividends</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1x for stable businesses, 2x for for volatile ones, 6x for cash hoarders</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Selected:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3275,9 +3276,6 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3340,9 +3338,6 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3376,6 +3371,12 @@
     <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3696,22 +3697,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="290" t="s">
-        <v>349</v>
-      </c>
-      <c r="F1" s="291" t="s">
-        <v>351</v>
+      <c r="E1" s="337" t="s">
+        <v>390</v>
+      </c>
+      <c r="F1" s="290" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3735,24 +3736,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="50">
         <v>7.79</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3768,7 +3769,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3778,7 +3779,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3805,7 +3806,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="339" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C12" s="339"/>
       <c r="D12" s="339"/>
@@ -3814,14 +3815,14 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3831,17 +3832,17 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>384</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="50">
         <v>1</v>
@@ -3854,16 +3855,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3877,22 +3878,22 @@
       </c>
       <c r="C20" s="258">
         <f>C127</f>
-        <v>6.4501768017717804</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E20" s="320">
+        <v>335</v>
+      </c>
+      <c r="E20" s="336">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12172735692567005</v>
+        <v>0.12411921460409614</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3903,7 +3904,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3913,7 +3914,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B25" s="339" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C25" s="339"/>
       <c r="D25" s="339"/>
@@ -3922,7 +3923,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="340" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="C26" s="340"/>
       <c r="D26" s="340"/>
@@ -3931,7 +3932,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3940,7 +3941,7 @@
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="338" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C29" s="338"/>
       <c r="D29" s="338"/>
@@ -3949,7 +3950,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -3966,7 +3967,7 @@
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="338" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C32" s="338"/>
       <c r="D32" s="338"/>
@@ -3975,7 +3976,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -3988,7 +3989,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -4001,7 +4002,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="338" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C36" s="338"/>
       <c r="D36" s="338"/>
@@ -4010,7 +4011,7 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4023,7 +4024,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="338" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C39" s="338"/>
       <c r="D39" s="338"/>
@@ -4032,24 +4033,24 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>382</v>
-      </c>
-      <c r="C40" s="330">
+        <v>375</v>
+      </c>
+      <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
-        <v>185.19539222287685</v>
+        <v>163.69305155463843</v>
       </c>
       <c r="D40" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E40" s="329"/>
-      <c r="F40" s="329"/>
+      <c r="E40" s="327"/>
+      <c r="F40" s="327"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>383</v>
-      </c>
-      <c r="C41" s="330">
+        <v>376</v>
+      </c>
+      <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
         <v>-43</v>
       </c>
@@ -4057,16 +4058,16 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E41" s="329"/>
-      <c r="F41" s="329"/>
+      <c r="E41" s="327"/>
+      <c r="F41" s="327"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
-        <v>142.19539222287685</v>
+        <v>120.69305155463843</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4075,12 +4076,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4093,7 +4094,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B47" s="338" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C47" s="338"/>
       <c r="D47" s="338"/>
@@ -4102,11 +4103,11 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
-        <v>-809.52375635047554</v>
+        <v>-804.36319459009837</v>
       </c>
       <c r="D48" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4115,7 +4116,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="338" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="C50" s="342"/>
       <c r="D50" s="342"/>
@@ -4124,7 +4125,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4137,7 +4138,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="339" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C53" s="339"/>
       <c r="D53" s="339"/>
@@ -4146,7 +4147,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="339" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C54" s="339"/>
       <c r="D54" s="339"/>
@@ -4155,11 +4156,11 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4168,11 +4169,11 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D57" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4181,16 +4182,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>3.9909901100125003E-2</v>
+        <v>3.9653192809019897E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4199,7 +4200,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4213,7 +4214,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="338" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="338"/>
@@ -4222,7 +4223,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B64" s="340" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C64" s="340"/>
       <c r="D64" s="340"/>
@@ -4231,44 +4232,44 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C67" s="318">
+        <v>307</v>
+      </c>
+      <c r="C67" s="317">
         <v>0.08</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D68" s="293" t="s">
-        <v>307</v>
+      <c r="D68" s="292" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
-      <c r="D69" s="293" t="s">
-        <v>357</v>
+      <c r="D69" s="292" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4280,7 +4281,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="339" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C72" s="339"/>
       <c r="D72" s="339"/>
@@ -4289,7 +4290,7 @@
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="339" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C73" s="339"/>
       <c r="D73" s="339"/>
@@ -4298,7 +4299,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="269">
         <v>0</v>
@@ -4306,11 +4307,11 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C76" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>3.4544236618885975</v>
+        <v>3.432204133136278</v>
       </c>
       <c r="D76" s="1" t="str">
         <f>Market_currency</f>
@@ -4319,7 +4320,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A78" s="253" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4332,7 +4333,7 @@
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="339" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C80" s="339"/>
       <c r="D80" s="339"/>
@@ -4341,17 +4342,17 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B83" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="339" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="C84" s="339"/>
       <c r="D84" s="339"/>
@@ -4360,7 +4361,7 @@
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C85" s="191">
         <f>Valuation_Model!C7</f>
@@ -4373,7 +4374,7 @@
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C86" s="254">
         <f>C85*C28*Exchange_Rate/Common_Shares</f>
@@ -4386,12 +4387,12 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B88" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B89" s="47" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C89" s="191">
         <f>BS!C66</f>
@@ -4404,11 +4405,11 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C90" s="191">
         <f>Valuation_Model!C8</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4417,11 +4418,11 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C91" s="254">
         <f>C90*C28*Exchange_Rate/Common_Shares</f>
-        <v>5.0791030441342784</v>
+        <v>5.1668117102618574</v>
       </c>
       <c r="D91" s="1" t="str">
         <f>Market_currency</f>
@@ -4430,12 +4431,12 @@
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B93" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B94" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C94" s="191">
         <f>Valuation_Model!C9</f>
@@ -4448,7 +4449,7 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B95" s="47" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C95" s="254">
         <f>C94*C28*Exchange_Rate/Common_Shares</f>
@@ -4461,7 +4462,7 @@
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B97" s="339" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C97" s="339"/>
       <c r="D97" s="339"/>
@@ -4470,11 +4471,11 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C99" s="254">
         <f>Valuation_Model!C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4483,7 +4484,7 @@
     </row>
     <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A101" s="253" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B101" s="36"/>
       <c r="C101" s="36"/>
@@ -4493,7 +4494,7 @@
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B103" s="338" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C103" s="338"/>
       <c r="D103" s="338"/>
@@ -4502,19 +4503,19 @@
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C105" s="266" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D105" s="266" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E105" s="266" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F105" s="266" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
@@ -4532,7 +4533,7 @@
       </c>
       <c r="E106" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>10.16 HKD</v>
+        <v>10.21 HKD</v>
       </c>
       <c r="F106" s="265">
         <f>Valuation_Model!F74</f>
@@ -4554,7 +4555,7 @@
       </c>
       <c r="E107" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>9.34 HKD</v>
+        <v>9.41 HKD</v>
       </c>
       <c r="F107" s="252">
         <f>Valuation_Model!F75</f>
@@ -4576,7 +4577,7 @@
       </c>
       <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>9.11 HKD</v>
+        <v>9.18 HKD</v>
       </c>
       <c r="F108" s="252">
         <f>Valuation_Model!F76</f>
@@ -4598,7 +4599,7 @@
       </c>
       <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>8.62 HKD</v>
+        <v>8.69 HKD</v>
       </c>
       <c r="F109" s="252">
         <f>Valuation_Model!F77</f>
@@ -4620,7 +4621,7 @@
       </c>
       <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.26 HKD</v>
+        <v>7.34 HKD</v>
       </c>
       <c r="F110" s="252">
         <f>Valuation_Model!F78</f>
@@ -4629,11 +4630,11 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B112" s="241" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C112" s="247">
         <f>Scenarios!C60</f>
-        <v>9.0347055134616365</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="D112" s="242" t="str">
         <f>Market_currency</f>
@@ -4642,7 +4643,7 @@
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="343" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="C114" s="343"/>
       <c r="D114" s="343"/>
@@ -4651,7 +4652,7 @@
     </row>
     <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A116" s="253" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -4661,7 +4662,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B118" s="341" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C118" s="341"/>
       <c r="D118" s="341"/>
@@ -4670,12 +4671,12 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B120" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C120" s="257">
         <f>E20</f>
@@ -4684,7 +4685,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C121" s="256">
         <f>C19</f>
@@ -4693,7 +4694,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="242" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C122" s="243">
         <f>Scenarios!C77</f>
@@ -4706,7 +4707,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B124" s="240" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.35">
@@ -4726,16 +4727,16 @@
       </c>
       <c r="C126" s="246">
         <f>Scenarios!C82</f>
-        <v>5.2284175425125214</v>
+        <v>5.2666014164225361</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B127" s="82" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C127" s="245">
         <f>Scenarios!C83</f>
-        <v>6.4501768017717804</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="D127" s="47" t="str">
         <f>Reporting_currency</f>
@@ -4744,11 +4745,11 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B128" s="244" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C128" s="94">
         <f>Scenarios!F83</f>
-        <v>0.28606673541699057</v>
+        <v>0.28704717576043881</v>
       </c>
     </row>
   </sheetData>
@@ -4781,7 +4782,7 @@
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
-      <formula1>"Not Held, Held"</formula1>
+      <formula1>"Y, N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
@@ -4857,7 +4858,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4873,7 +4874,7 @@
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="109">
         <v>1000000</v>
@@ -4881,7 +4882,7 @@
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B4" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="193">
         <v>8765</v>
@@ -4907,7 +4908,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="193">
         <v>5344</v>
@@ -4933,7 +4934,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="193">
         <v>1084</v>
@@ -4957,7 +4958,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="194"/>
       <c r="D7" s="192"/>
@@ -4973,7 +4974,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -4989,7 +4990,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C9" s="193">
         <v>639</v>
@@ -5009,7 +5010,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5025,7 +5026,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5041,7 +5042,7 @@
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B12" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="193">
         <v>43</v>
@@ -5065,7 +5066,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="193">
         <v>2340</v>
@@ -5089,7 +5090,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="193">
         <v>519</v>
@@ -5113,7 +5114,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="195">
         <v>4251</v>
@@ -5137,7 +5138,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="193">
         <v>-151</v>
@@ -5157,13 +5158,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C19" s="184">
         <v>160</v>
@@ -5187,7 +5188,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" s="184">
         <v>69</v>
@@ -5207,7 +5208,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C21" s="184">
         <v>910</v>
@@ -5250,13 +5251,13 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C24" s="9"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B25" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="186"/>
       <c r="D25" s="184">
@@ -5274,7 +5275,7 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B26" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="186"/>
       <c r="D26" s="184">
@@ -5292,7 +5293,7 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B27" s="29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="185">
         <v>14028</v>
@@ -5312,7 +5313,7 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="185">
         <v>166316</v>
@@ -5332,7 +5333,7 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29" s="184"/>
       <c r="D29" s="184"/>
@@ -5348,13 +5349,13 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="9"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="184"/>
       <c r="D32" s="184"/>
@@ -5370,7 +5371,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5386,12 +5387,12 @@
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B36" s="32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" s="186">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -5440,7 +5441,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5489,7 +5490,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
@@ -5538,7 +5539,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5587,7 +5588,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5636,7 +5637,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5685,7 +5686,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5734,7 +5735,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5783,7 +5784,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5832,7 +5833,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5881,7 +5882,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5930,7 +5931,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5979,7 +5980,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6028,12 +6029,12 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B51" s="40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" s="186">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -6082,7 +6083,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6131,12 +6132,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6185,7 +6186,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6234,7 +6235,7 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C57" s="191">
         <f>IF(C$4="","",C11)</f>
@@ -6283,7 +6284,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6332,13 +6333,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6387,7 +6388,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6436,7 +6437,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6485,7 +6486,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C64" s="75">
         <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
@@ -6534,7 +6535,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6789,7 +6790,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6805,13 +6806,13 @@
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B74" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C74" s="9"/>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B75" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" s="78">
         <f>IF(C$4="","",C78+C79)</f>
@@ -6860,7 +6861,7 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
@@ -6894,7 +6895,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6928,7 +6929,7 @@
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B78" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C78" s="58">
         <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
@@ -6977,7 +6978,7 @@
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
@@ -7069,7 +7070,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B1" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C1" s="102">
         <v>45473</v>
@@ -7085,7 +7086,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7096,177 +7097,177 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="210" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="209" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="210" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>190</v>
-      </c>
       <c r="G3" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H3" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="19">
         <v>8029</v>
       </c>
-      <c r="D4" s="301">
+      <c r="D4" s="300">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G4" s="19">
         <v>45665</v>
       </c>
-      <c r="H4" s="301">
+      <c r="H4" s="300">
         <v>0.9</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="301">
+      <c r="D5" s="300">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="19">
         <v>2014</v>
       </c>
-      <c r="H5" s="301">
+      <c r="H5" s="300">
         <v>0.7</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="19">
         <v>9844</v>
       </c>
-      <c r="D6" s="301">
+      <c r="D6" s="300">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G6" s="19">
         <v>156</v>
       </c>
-      <c r="H6" s="301">
+      <c r="H6" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="19">
         <v>5466</v>
       </c>
-      <c r="D7" s="301">
+      <c r="D7" s="300">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="301">
+      <c r="H7" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="301">
+      <c r="D8" s="300">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="301">
+      <c r="H8" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="301">
+      <c r="D9" s="300">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="301">
+      <c r="H9" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="19">
         <v>10</v>
       </c>
-      <c r="D10" s="301">
+      <c r="D10" s="300">
         <v>0.9</v>
       </c>
-      <c r="H10" s="302"/>
+      <c r="H10" s="301"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="301">
+      <c r="D11" s="300">
         <v>0.05</v>
       </c>
-      <c r="H11" s="302"/>
+      <c r="H11" s="301"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7277,7 +7278,7 @@
         <v>13028</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7295,191 +7296,191 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H14" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C15" s="19">
         <v>2757</v>
       </c>
-      <c r="D15" s="301">
+      <c r="D15" s="300">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="301">
+      <c r="H15" s="300">
         <v>0.8</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="301">
+      <c r="D16" s="300">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="19">
         <v>1373</v>
       </c>
-      <c r="H16" s="301">
+      <c r="H16" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="19">
         <v>67668</v>
       </c>
-      <c r="D17" s="301">
+      <c r="D17" s="300">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G17" s="19">
         <v>13024</v>
       </c>
-      <c r="H17" s="301">
+      <c r="H17" s="300">
         <v>0.6</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="301">
+      <c r="D18" s="300">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G18" s="19">
         <v>23696</v>
       </c>
-      <c r="H18" s="301">
+      <c r="H18" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="19">
         <v>1284</v>
       </c>
-      <c r="D19" s="301">
+      <c r="D19" s="300">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
       </c>
-      <c r="H19" s="301">
+      <c r="H19" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="301">
+      <c r="D20" s="300">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="301">
+      <c r="H20" s="300">
         <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
       </c>
-      <c r="D21" s="301">
+      <c r="D21" s="300">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="301">
+      <c r="H21" s="300">
         <v>0.1</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="19">
         <v>10</v>
       </c>
-      <c r="D22" s="301">
+      <c r="D22" s="300">
         <v>0.9</v>
       </c>
-      <c r="H22" s="302"/>
+      <c r="H22" s="301"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="301">
-        <v>0</v>
-      </c>
-      <c r="H23" s="302"/>
+      <c r="D23" s="300">
+        <v>0</v>
+      </c>
+      <c r="H23" s="301"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7490,7 +7491,7 @@
         <v>41841</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7503,30 +7504,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H26" s="213" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="19">
         <v>967</v>
       </c>
       <c r="F27" s="214" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" s="87">
         <f>G32-G30</f>
@@ -7539,13 +7540,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="19">
         <v>37</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G28" s="184">
         <v>519</v>
@@ -7554,13 +7555,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7573,13 +7574,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30" s="87">
         <f>C33+C42</f>
@@ -7589,14 +7590,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
@@ -7606,14 +7607,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>8048</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
@@ -7626,7 +7627,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="86">
         <v>9052</v>
@@ -7639,24 +7640,24 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H34" s="225" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F35" s="226" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G35" s="220">
         <f>C12+C24</f>
@@ -7669,13 +7670,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C36" s="19">
         <v>832</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
@@ -7685,13 +7686,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="19">
         <v>27</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
@@ -7701,13 +7702,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C38" s="19">
         <v>1230</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
@@ -7717,13 +7718,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
@@ -7736,14 +7737,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
@@ -7756,14 +7757,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>2748</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
@@ -7776,13 +7777,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="86">
         <v>4837</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
@@ -7795,7 +7796,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7806,21 +7807,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" s="267" t="s">
+        <v>140</v>
+      </c>
+      <c r="D45" s="209" t="s">
         <v>287</v>
       </c>
-      <c r="C45" s="267" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="209" t="s">
-        <v>288</v>
-      </c>
-      <c r="F45" s="294" t="s">
-        <v>63</v>
+      <c r="F45" s="293" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -7852,20 +7853,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7879,7 +7880,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
@@ -7893,19 +7894,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7919,7 +7920,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7936,19 +7937,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7959,7 +7960,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7973,19 +7974,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7996,12 +7997,12 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8012,21 +8013,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>313</v>
-      </c>
-      <c r="F65" s="294" t="s">
-        <v>63</v>
+        <v>311</v>
+      </c>
+      <c r="F65" s="293" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8034,15 +8035,15 @@
       </c>
       <c r="D66" s="191">
         <f>C66-D75</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8052,7 +8053,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8062,7 +8063,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8072,7 +8073,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8084,70 +8085,73 @@
       <c r="F71" s="289"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="292" t="s">
-        <v>354</v>
+      <c r="B72" s="291" t="s">
+        <v>348</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C73" s="191">
-        <f>(Normalized_FCF!G25+Normalized_FCF!G35)/12</f>
-        <v>-535.66666666666663</v>
+        <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
+        <v>-930.64086357333326</v>
       </c>
       <c r="D73" s="191">
-        <f>(Normalized_FCF!C25+Normalized_FCF!C35)/12</f>
-        <v>-514.43164506354685</v>
+        <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
+        <v>-909.4058419702136</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="295" t="s">
-        <v>359</v>
-      </c>
-      <c r="C74" s="296">
+      <c r="B74" s="294" t="s">
+        <v>352</v>
+      </c>
+      <c r="C74" s="295">
         <f>-$C$66/C73</f>
-        <v>89.008711885500944</v>
-      </c>
-      <c r="D74" s="296">
+        <v>51.232437631128107</v>
+      </c>
+      <c r="D74" s="295">
         <f>-$C$66/D73</f>
-        <v>92.682867505381196</v>
+        <v>52.428737313479523</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>356</v>
-      </c>
-      <c r="C75" s="300"/>
-      <c r="D75" s="299">
+        <v>350</v>
+      </c>
+      <c r="C75" s="299"/>
+      <c r="D75" s="298">
         <f>MAX(-D73*D76,G5)</f>
-        <v>6173.1797407625618</v>
+        <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="297" t="s">
-        <v>360</v>
-      </c>
-      <c r="C76" s="298"/>
-      <c r="D76" s="335">
-        <f>IF(D74&lt;=3,1,IF(D74&gt;12,IF(D74&gt;24,12,6),2))</f>
-        <v>12</v>
+      <c r="B76" s="296" t="s">
+        <v>353</v>
+      </c>
+      <c r="C76" s="297"/>
+      <c r="D76" s="333">
+        <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
+        <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8155,19 +8159,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D78" s="210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" s="289"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8181,7 +8185,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8195,7 +8199,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8209,7 +8213,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8223,7 +8227,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8234,15 +8238,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8259,15 +8263,15 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="D87" s="254">
         <f>C87*$H$1/Common_Shares</f>
-        <v>5.0791030441342784</v>
+        <v>5.1668117102618574</v>
       </c>
       <c r="E87" s="275" t="str">
         <f>Market_currency</f>
@@ -8276,7 +8280,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8293,15 +8297,15 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
-        <v>46227.220259237438</v>
+        <v>46943.96494817872</v>
       </c>
       <c r="D89" s="277">
         <f>SUM(D86:D88)</f>
-        <v>5.6568648366442948</v>
+        <v>5.7445735027718738</v>
       </c>
       <c r="E89" s="275" t="str">
         <f>Market_currency</f>
@@ -8341,7 +8345,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8394,12 +8398,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8417,28 +8421,28 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="309"/>
+      <c r="E3" s="308"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="196">
         <f>G4</f>
         <v>8765</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="307"/>
+      <c r="E4" s="306"/>
       <c r="F4" s="57"/>
       <c r="G4" s="186">
         <f>Data!C36</f>
@@ -8488,13 +8492,13 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
         <v>-5066.6797407625618</v>
       </c>
-      <c r="E5" s="309"/>
+      <c r="E5" s="308"/>
       <c r="G5" s="186">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-5344</v>
@@ -8543,13 +8547,13 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
         <v>3698.3202592374382</v>
       </c>
-      <c r="E6" s="309"/>
+      <c r="E6" s="308"/>
       <c r="G6" s="187">
         <f>IF(G4="","",G4+G5)</f>
         <v>3421</v>
@@ -8598,13 +8602,13 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
         <v>-1106.5</v>
       </c>
-      <c r="E7" s="309"/>
+      <c r="E7" s="308"/>
       <c r="G7" s="197">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-1084</v>
@@ -8653,14 +8657,14 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
         <v>2591.8202592374382</v>
       </c>
       <c r="D8" s="60"/>
-      <c r="E8" s="315"/>
+      <c r="E8" s="314"/>
       <c r="F8" s="60"/>
       <c r="G8" s="187">
         <f>IF(G$4="","",G6+G7)</f>
@@ -8710,13 +8714,13 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
         <v>159.99999999999997</v>
       </c>
-      <c r="E9" s="309"/>
+      <c r="E9" s="308"/>
       <c r="G9" s="197">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>160</v>
@@ -8765,13 +8769,13 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
         <v>-159.99999999999997</v>
       </c>
-      <c r="E10" s="309"/>
+      <c r="E10" s="308"/>
       <c r="G10" s="197">
         <f>Data!C62</f>
         <v>-69</v>
@@ -8820,14 +8824,14 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
         <v>639</v>
       </c>
       <c r="D11" s="172"/>
-      <c r="E11" s="308"/>
+      <c r="E11" s="307"/>
       <c r="F11" s="172"/>
       <c r="G11" s="189">
         <f>G61</f>
@@ -8877,28 +8881,28 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
-        <v>142.19539222287685</v>
-      </c>
-      <c r="E12" s="309"/>
+        <v>120.69305155463843</v>
+      </c>
+      <c r="E12" s="308"/>
       <c r="G12" s="197">
         <f>G50</f>
-        <v>259.96861497481899</v>
+        <v>224.79206823259295</v>
       </c>
       <c r="H12" s="197">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>139.30261332735768</v>
+        <v>118.39443599706225</v>
       </c>
       <c r="I12" s="197">
         <f t="shared" si="6"/>
-        <v>-5.5315111914213588</v>
+        <v>-10.601439105911425</v>
       </c>
       <c r="J12" s="197">
         <f t="shared" si="6"/>
-        <v>-7.6802090667184899</v>
+        <v>-16.281703694046172</v>
       </c>
       <c r="K12" s="197">
         <f t="shared" si="6"/>
@@ -8932,28 +8936,28 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
-        <v>3373.015651460315</v>
-      </c>
-      <c r="E13" s="309"/>
+        <v>3351.5133107920765</v>
+      </c>
+      <c r="E13" s="308"/>
       <c r="G13" s="187">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3326.968614974819</v>
+        <v>3291.792068232593</v>
       </c>
       <c r="H13" s="187">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>5416.3026133273579</v>
+        <v>5395.3944359970619</v>
       </c>
       <c r="I13" s="187">
         <f t="shared" si="7"/>
-        <v>7475.6847628085789</v>
+        <v>7470.6148348940887</v>
       </c>
       <c r="J13" s="187">
         <f t="shared" si="7"/>
-        <v>12591.660826933283</v>
+        <v>12583.059332305955</v>
       </c>
       <c r="K13" s="187">
         <f t="shared" si="7"/>
@@ -8987,13 +8991,13 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-809.52375635047554</v>
-      </c>
-      <c r="E14" s="309"/>
+        <v>-804.36319459009837</v>
+      </c>
+      <c r="E14" s="308"/>
       <c r="G14" s="197">
         <f>Data!C46</f>
         <v>-519</v>
@@ -9042,14 +9046,14 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
         <v>-22.869707937042335</v>
       </c>
       <c r="D15" s="61"/>
-      <c r="E15" s="316"/>
+      <c r="E15" s="315"/>
       <c r="F15" s="61"/>
       <c r="G15" s="186">
         <f>Data!C48</f>
@@ -9099,30 +9103,30 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D16" s="62"/>
-      <c r="E16" s="317"/>
+      <c r="E16" s="316"/>
       <c r="F16" s="62"/>
       <c r="G16" s="187">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="H16" s="187">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>4524.4677853273579</v>
+        <v>4503.5596079970619</v>
       </c>
       <c r="I16" s="187">
         <f t="shared" si="8"/>
-        <v>6126.5772678085787</v>
+        <v>6121.5073398940885</v>
       </c>
       <c r="J16" s="187">
         <f t="shared" si="8"/>
-        <v>10060.891295933283</v>
+        <v>10052.289801305955</v>
       </c>
       <c r="K16" s="187">
         <f t="shared" si="8"/>
@@ -9156,15 +9160,15 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
       <c r="D17" s="59"/>
-      <c r="E17" s="308" t="s">
-        <v>373</v>
+      <c r="E17" s="307" t="s">
+        <v>366</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9182,14 +9186,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
-      <c r="E18" s="308" t="s">
-        <v>374</v>
+      <c r="E18" s="307" t="s">
+        <v>367</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9207,30 +9211,30 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="306"/>
+      <c r="E19" s="305"/>
       <c r="F19" s="27"/>
       <c r="G19" s="189">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="H19" s="189">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>4524.4677853273579</v>
+        <v>4503.5596079970619</v>
       </c>
       <c r="I19" s="189">
         <f t="shared" si="9"/>
-        <v>6126.5772678085787</v>
+        <v>6121.5073398940885</v>
       </c>
       <c r="J19" s="189">
         <f t="shared" si="9"/>
-        <v>10060.891295933283</v>
+        <v>10052.289801305955</v>
       </c>
       <c r="K19" s="189">
         <f t="shared" si="9"/>
@@ -9283,12 +9287,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9306,11 +9310,11 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="306"/>
+      <c r="E22" s="305"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -9327,14 +9331,14 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
         <v>-5066.6797407625618</v>
       </c>
       <c r="D23" s="59"/>
-      <c r="E23" s="308"/>
+      <c r="E23" s="307"/>
       <c r="F23" s="59"/>
       <c r="G23" s="186">
         <f>Data!C37</f>
@@ -9384,14 +9388,14 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
         <v>0</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="306"/>
+      <c r="E24" s="305"/>
       <c r="F24" s="27"/>
       <c r="G24" s="186">
         <f>Data!C40</f>
@@ -9441,14 +9445,14 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
         <v>-5066.6797407625618</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="314"/>
+      <c r="E25" s="313"/>
       <c r="F25" s="9"/>
       <c r="G25" s="187">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -9497,27 +9501,27 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
-      <c r="E26" s="309"/>
+      <c r="E26" s="308"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="309"/>
+        <v>210</v>
+      </c>
+      <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
         <v>0.57805815639048053</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="307" t="s">
-        <v>375</v>
+      <c r="E28" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9576,8 +9580,8 @@
         <v>0</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="307" t="s">
-        <v>375</v>
+      <c r="E29" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9628,13 +9632,13 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
         <v>0.57805815639048053</v>
       </c>
-      <c r="E30" s="309"/>
+      <c r="E30" s="308"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.60969766115231028</v>
@@ -9682,26 +9686,26 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="10"/>
-      <c r="E31" s="309"/>
+      <c r="E31" s="308"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32" s="309"/>
+        <v>47</v>
+      </c>
+      <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
-      <c r="E33" s="307" t="s">
-        <v>375</v>
+      <c r="E33" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9751,15 +9755,15 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
         <v>0</v>
       </c>
       <c r="D34" s="59"/>
-      <c r="E34" s="307" t="s">
-        <v>375</v>
+      <c r="E34" s="306" t="s">
+        <v>368</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -9810,14 +9814,14 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
         <v>-1106.5</v>
       </c>
       <c r="D35" s="59"/>
-      <c r="E35" s="308"/>
+      <c r="E35" s="307"/>
       <c r="F35" s="59"/>
       <c r="G35" s="187">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -9866,14 +9870,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="10"/>
-      <c r="E36" s="309"/>
+      <c r="E36" s="308"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>212</v>
-      </c>
-      <c r="E37" s="309"/>
+        <v>211</v>
+      </c>
+      <c r="E37" s="308"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="10"/>
@@ -9886,7 +9890,7 @@
         <v>0.1262407301768397</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="306"/>
+      <c r="E38" s="305"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -9944,7 +9948,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="306"/>
+      <c r="E39" s="305"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -9994,13 +9998,13 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
         <v>0.1262407301768397</v>
       </c>
-      <c r="E40" s="309"/>
+      <c r="E40" s="308"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>0.12367370222475756</v>
@@ -10048,43 +10052,43 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="10"/>
-      <c r="E41" s="309"/>
+      <c r="E41" s="308"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>213</v>
-      </c>
-      <c r="E42" s="309"/>
+        <v>212</v>
+      </c>
+      <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="C43" s="303">
+        <v>175</v>
+      </c>
+      <c r="C43" s="302">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="306" t="s">
-        <v>376</v>
+      <c r="E43" s="305" t="s">
+        <v>369</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.16038474464748129</v>
+        <v>0.16214736506972799</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.16161958688679046</v>
+        <v>0.16225651803742283</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18494436262371075</v>
+        <v>0.18507299176575123</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.2040036040672103</v>
+        <v>0.20414515027301566</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
@@ -10121,12 +10125,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10144,20 +10148,20 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="309"/>
+        <v>63</v>
+      </c>
+      <c r="E46" s="308"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" s="197">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-43</v>
       </c>
-      <c r="E47" s="309"/>
+      <c r="E47" s="308"/>
       <c r="G47" s="197">
         <f>Data!C51</f>
         <v>-43</v>
@@ -10206,111 +10210,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
-        <v>185.19539222287685</v>
-      </c>
-      <c r="E48" s="309"/>
-      <c r="G48" s="336">
+        <v>163.69305155463843</v>
+      </c>
+      <c r="E48" s="308"/>
+      <c r="G48" s="334">
         <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
-        <v>302.96861497481899</v>
-      </c>
-      <c r="H48" s="336">
+        <v>267.79206823259295</v>
+      </c>
+      <c r="H48" s="334">
         <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
-        <v>180.07798132735766</v>
-      </c>
-      <c r="I48" s="336">
+        <v>159.16980399706225</v>
+      </c>
+      <c r="I48" s="334">
         <f t="shared" si="19"/>
-        <v>43.666282808578643</v>
-      </c>
-      <c r="J48" s="336">
+        <v>38.596354894088577</v>
+      </c>
+      <c r="J48" s="334">
         <f t="shared" si="19"/>
-        <v>74.082965933281514</v>
-      </c>
-      <c r="K48" s="336">
+        <v>65.481471305953832</v>
+      </c>
+      <c r="K48" s="334">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="336" t="str">
+      <c r="L48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="M48" s="336" t="str">
+      <c r="M48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="N48" s="336" t="str">
+      <c r="N48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="O48" s="336" t="str">
+      <c r="O48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="P48" s="336" t="str">
+      <c r="P48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="336" t="str">
+      <c r="Q48" s="334" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
-      <c r="B49" s="331" t="s">
-        <v>384</v>
-      </c>
-      <c r="C49" s="332">
+      <c r="B49" s="329" t="s">
+        <v>377</v>
+      </c>
+      <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
         <v>1430.37</v>
       </c>
-      <c r="D49" s="333"/>
-      <c r="E49" s="334"/>
-      <c r="F49" s="333"/>
-      <c r="G49" s="332">
+      <c r="D49" s="331"/>
+      <c r="E49" s="332"/>
+      <c r="F49" s="331"/>
+      <c r="G49" s="330">
         <f>Data!C52</f>
         <v>2340</v>
       </c>
-      <c r="H49" s="332">
+      <c r="H49" s="330">
         <f>Data!D52</f>
         <v>1390.845307</v>
       </c>
-      <c r="I49" s="332">
+      <c r="I49" s="330">
         <f>Data!E52</f>
         <v>337.25969199999997</v>
       </c>
-      <c r="J49" s="332">
+      <c r="J49" s="330">
         <f>Data!F52</f>
         <v>572.18514300000004</v>
       </c>
-      <c r="K49" s="332">
+      <c r="K49" s="330">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="332" t="str">
+      <c r="L49" s="330" t="str">
         <f>Data!H52</f>
         <v/>
       </c>
-      <c r="M49" s="332" t="str">
+      <c r="M49" s="330" t="str">
         <f>Data!I52</f>
         <v/>
       </c>
-      <c r="N49" s="332" t="str">
+      <c r="N49" s="330" t="str">
         <f>Data!J52</f>
         <v/>
       </c>
-      <c r="O49" s="332" t="str">
+      <c r="O49" s="330" t="str">
         <f>Data!K52</f>
         <v/>
       </c>
-      <c r="P49" s="332" t="str">
+      <c r="P49" s="330" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="332" t="str">
+      <c r="Q49" s="330" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -10318,28 +10322,28 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
-        <v>142.19539222287685</v>
-      </c>
-      <c r="E50" s="309"/>
+        <v>120.69305155463843</v>
+      </c>
+      <c r="E50" s="308"/>
       <c r="G50" s="187">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>259.96861497481899</v>
+        <v>224.79206823259295</v>
       </c>
       <c r="H50" s="187">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>139.30261332735768</v>
+        <v>118.39443599706225</v>
       </c>
       <c r="I50" s="187">
         <f t="shared" si="20"/>
-        <v>-5.5315111914213588</v>
+        <v>-10.601439105911425</v>
       </c>
       <c r="J50" s="187">
         <f t="shared" si="20"/>
-        <v>-7.6802090667184899</v>
+        <v>-16.281703694046172</v>
       </c>
       <c r="K50" s="187">
         <f t="shared" si="20"/>
@@ -10372,28 +10376,28 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="10"/>
-      <c r="E51" s="309"/>
+      <c r="E51" s="308"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>160</v>
-      </c>
-      <c r="E52" s="309"/>
+        <v>159</v>
+      </c>
+      <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C53" s="89">
         <v>0.03</v>
       </c>
-      <c r="E53" s="306" t="s">
-        <v>377</v>
+      <c r="E53" s="305" t="s">
+        <v>370</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10413,14 +10417,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
         <v>1.3902360168121564E-2</v>
       </c>
-      <c r="E54" s="306" t="s">
-        <v>378</v>
+      <c r="E54" s="305" t="s">
+        <v>371</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10440,13 +10444,13 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
         <v>60.274889749707867</v>
       </c>
-      <c r="E55" s="309"/>
+      <c r="E55" s="308"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>54.348837209302324</v>
@@ -10494,28 +10498,28 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="10"/>
-      <c r="E56" s="309"/>
+      <c r="E56" s="308"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="E57" s="309"/>
+        <v>172</v>
+      </c>
+      <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="309"/>
+      <c r="E58" s="308"/>
       <c r="G58" s="197">
         <f>Data!C56</f>
         <v>0</v>
@@ -10564,13 +10568,13 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
         <v>639</v>
       </c>
-      <c r="E59" s="309"/>
+      <c r="E59" s="308"/>
       <c r="G59" s="197">
         <f>Data!C55</f>
         <v>639</v>
@@ -10619,13 +10623,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="309"/>
+      <c r="E60" s="308"/>
       <c r="G60" s="197">
         <f>Data!C57</f>
         <v>0</v>
@@ -10674,13 +10678,13 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
         <v>639</v>
       </c>
-      <c r="E61" s="309"/>
+      <c r="E61" s="308"/>
       <c r="G61" s="187">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>639</v>
@@ -10729,13 +10733,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="C62" s="304">
-        <v>0</v>
-      </c>
-      <c r="E62" s="307" t="s">
-        <v>379</v>
+        <v>164</v>
+      </c>
+      <c r="C62" s="303">
+        <v>0</v>
+      </c>
+      <c r="E62" s="306" t="s">
+        <v>372</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -10785,13 +10789,13 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
         <v>639</v>
       </c>
-      <c r="E63" s="309"/>
+      <c r="E63" s="308"/>
       <c r="G63" s="187">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>136</v>
@@ -10839,28 +10843,28 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="10"/>
-      <c r="E64" s="309"/>
+      <c r="E64" s="308"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>174</v>
-      </c>
-      <c r="E65" s="309"/>
+        <v>173</v>
+      </c>
+      <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="309"/>
+      <c r="E66" s="308"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -10879,13 +10883,13 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
         <v>2.6966576637407157E-2</v>
       </c>
-      <c r="E67" s="309"/>
+      <c r="E67" s="308"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>2.6966576637407157E-2</v>
@@ -10904,13 +10908,13 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="309"/>
+      <c r="E68" s="308"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$81,0)</f>
         <v>0</v>
@@ -10929,14 +10933,14 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
         <v>8.7649511686601553E-3</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="314"/>
+      <c r="E69" s="313"/>
       <c r="F69" s="9"/>
       <c r="G69" s="72">
         <f>G61/BS!C70</f>
@@ -10959,12 +10963,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -10982,11 +10986,11 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="306"/>
+      <c r="E72" s="305"/>
       <c r="F72" s="27"/>
       <c r="G72" s="100"/>
       <c r="H72" s="12"/>
@@ -11003,14 +11007,14 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
         <v>0.57805815639048053</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="306"/>
+      <c r="E73" s="305"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -11060,14 +11064,14 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
         <v>0.42194184360951947</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="306"/>
+      <c r="E74" s="305"/>
       <c r="F74" s="27"/>
       <c r="G74" s="66">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -11117,14 +11121,14 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
         <v>0.1262407301768397</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="306"/>
+      <c r="E75" s="305"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -11174,14 +11178,14 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
         <v>0.2957011134326798</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="306"/>
+      <c r="E76" s="305"/>
       <c r="F76" s="27"/>
       <c r="G76" s="66">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -11231,14 +11235,14 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="306"/>
+      <c r="E77" s="305"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -11288,14 +11292,14 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
         <v>1.8254420992584137E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="307" t="s">
+      <c r="E78" s="306" t="s">
         <v>391</v>
       </c>
       <c r="F78" s="27"/>
@@ -11347,14 +11351,14 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
         <v>7.2903593839132919E-2</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="306"/>
+      <c r="E79" s="305"/>
       <c r="F79" s="27"/>
       <c r="G79" s="66">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -11404,30 +11408,30 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
-        <v>1.6223090955262618E-2</v>
+        <v>1.3769886087237698E-2</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="306"/>
+      <c r="E80" s="305"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>2.9659853391308499E-2</v>
+        <v>2.5646556558196573E-2</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>1.1724822264738463E-2</v>
+        <v>9.9650228092805528E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>3.534384710744946E-4</v>
+        <v>6.7738386475538973E-4</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>3.1433275531812322E-4</v>
+        <v>6.6637154522272712E-4</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
@@ -11461,30 +11465,30 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
-        <v>0.3848277982270753</v>
+        <v>0.38237459335905039</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="306"/>
+      <c r="E81" s="305"/>
       <c r="F81" s="27"/>
       <c r="G81" s="66">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.37957428579290575</v>
+        <v>0.37556098895979384</v>
       </c>
       <c r="H81" s="66">
         <f t="shared" si="32"/>
-        <v>0.4558793547115022</v>
+        <v>0.45411955525604425</v>
       </c>
       <c r="I81" s="66">
         <f t="shared" si="32"/>
-        <v>0.47766234241732236</v>
+        <v>0.47733839702364145</v>
       </c>
       <c r="J81" s="66">
         <f t="shared" si="32"/>
-        <v>0.51534683592309194</v>
+        <v>0.5149947971331873</v>
       </c>
       <c r="K81" s="66">
         <f t="shared" si="32"/>
@@ -11518,14 +11522,14 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
-        <v>9.2358671574498064E-2</v>
+        <v>9.1769902406172096E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="306"/>
+      <c r="E82" s="305"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -11578,12 +11582,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="305">
+      <c r="C83" s="304">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>2.6092079791263361E-3</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="306"/>
+      <c r="E83" s="305"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -11633,30 +11637,30 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
-        <v>0.2898599186734509</v>
+        <v>0.28799548297375194</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="306"/>
+      <c r="E84" s="305"/>
       <c r="F84" s="27"/>
       <c r="G84" s="66">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.32036150769821098</v>
+        <v>0.31634821086509901</v>
       </c>
       <c r="H84" s="66">
         <f t="shared" si="35"/>
-        <v>0.38081540150890986</v>
+        <v>0.3790556020534519</v>
       </c>
       <c r="I84" s="66">
         <f t="shared" si="35"/>
-        <v>0.39146049379999764</v>
+        <v>0.39113654840631673</v>
       </c>
       <c r="J84" s="66">
         <f t="shared" si="35"/>
-        <v>0.41176843683996933</v>
+        <v>0.41141639805006475</v>
       </c>
       <c r="K84" s="66">
         <f t="shared" si="35"/>
@@ -11690,13 +11694,13 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="C85" s="305">
+        <v>54</v>
+      </c>
+      <c r="C85" s="304">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="308" t="str">
+      <c r="E85" s="307" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
@@ -11716,12 +11720,12 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
       </c>
-      <c r="E86" s="308" t="str">
+      <c r="E86" s="307" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -11740,30 +11744,30 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
-        <v>0.2898599186734509</v>
+        <v>0.28799548297375194</v>
       </c>
       <c r="D87" s="77"/>
-      <c r="E87" s="306"/>
+      <c r="E87" s="305"/>
       <c r="F87" s="77"/>
       <c r="G87" s="66">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.32036150769821098</v>
+        <v>0.31634821086509901</v>
       </c>
       <c r="H87" s="66">
         <f t="shared" si="36"/>
-        <v>0.38081540150890986</v>
+        <v>0.3790556020534519</v>
       </c>
       <c r="I87" s="66">
         <f t="shared" si="36"/>
-        <v>0.39146049379999764</v>
+        <v>0.39113654840631673</v>
       </c>
       <c r="J87" s="66">
         <f t="shared" si="36"/>
-        <v>0.41176843683996933</v>
+        <v>0.41141639805006475</v>
       </c>
       <c r="K87" s="66">
         <f t="shared" si="36"/>
@@ -11796,14 +11800,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="10"/>
-      <c r="E88" s="309"/>
+      <c r="E88" s="308"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>219</v>
-      </c>
-      <c r="E89" s="309"/>
+        <v>218</v>
+      </c>
+      <c r="E89" s="308"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="10"/>
@@ -11815,7 +11819,7 @@
         <f>G90</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E90" s="309"/>
+      <c r="E90" s="308"/>
       <c r="G90" s="116">
         <f>Data!C64</f>
         <v>0.57999999999999996</v>
@@ -11871,7 +11875,7 @@
         <f>C90*Common_Shares/$C$3</f>
         <v>4739.6903628800001</v>
       </c>
-      <c r="E91" s="309"/>
+      <c r="E91" s="308"/>
       <c r="G91" s="76">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
         <v>4739.6903628800001</v>
@@ -11920,24 +11924,24 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
-        <v>1.8655628478763795</v>
-      </c>
-      <c r="E92" s="309"/>
+        <v>1.8776401969295582</v>
+      </c>
+      <c r="E92" s="308"/>
       <c r="G92" s="174">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
-        <v>1.6879427845465798</v>
+        <v>1.7093565785843898</v>
       </c>
       <c r="H92" s="174">
         <f t="shared" si="38"/>
-        <v>1.0475685954159291</v>
+        <v>1.0524320260941227</v>
       </c>
       <c r="I92" s="174">
         <f t="shared" si="38"/>
-        <v>0.76028936874668918</v>
+        <v>0.76091905226737666</v>
       </c>
       <c r="J92" s="174">
         <f t="shared" si="38"/>
@@ -11975,13 +11979,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>7.4454428754813853E-2</v>
       </c>
-      <c r="E93" s="309"/>
+      <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>7.4454428754813853E-2</v>
@@ -12029,16 +12033,16 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="10"/>
-      <c r="E94" s="309"/>
+      <c r="E94" s="308"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="306"/>
+      <c r="E95" s="305"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -12055,14 +12059,14 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
         <v>0</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="306"/>
+      <c r="E96" s="305"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -12112,30 +12116,30 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
-        <v>1.3840538284081383E-2</v>
+        <v>1.8142471128666626E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="306"/>
+      <c r="E97" s="305"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-0.38574912583568022</v>
+        <v>-0.38988852302060206</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.2754773930177763</v>
+        <v>-0.27778441865373549</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>-0.40629875077176036</v>
+        <v>-0.40629582698430833</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>2.6497567614299369</v>
+        <v>2.6472635745814364</v>
       </c>
       <c r="K97" s="6" t="str">
         <f t="shared" si="41"/>
@@ -12172,12 +12176,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12195,24 +12199,24 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="10"/>
       <c r="B100" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="E100" s="309"/>
+        <v>28</v>
+      </c>
+      <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C101" s="205">
         <f>BS!G32</f>
         <v>180996</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="310"/>
+      <c r="E101" s="309"/>
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -12262,14 +12266,14 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
         <v>8029</v>
       </c>
       <c r="D102" s="91"/>
-      <c r="E102" s="311"/>
+      <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
         <f>IF(G$4="","",Data!D76)</f>
@@ -12319,14 +12323,14 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
         <v>15310</v>
       </c>
       <c r="D103" s="91"/>
-      <c r="E103" s="311"/>
+      <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
         <f>IF(G$4="","",Data!D77)</f>
@@ -12376,14 +12380,14 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" s="205">
         <f>BS!G30</f>
         <v>13889</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="310"/>
+      <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C78</f>
@@ -12433,14 +12437,14 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C105" s="205">
         <f>BS!G27</f>
         <v>167107</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="310"/>
+      <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C79</f>
@@ -12489,19 +12493,19 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="10"/>
-      <c r="E106" s="309"/>
+      <c r="E106" s="308"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="310"/>
+      <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12517,14 +12521,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
         <v>0.91602966343411296</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="310"/>
+      <c r="E108" s="309"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -12574,14 +12578,14 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
         <v>1.7467199087278951</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="310"/>
+      <c r="E109" s="309"/>
       <c r="F109" s="26"/>
       <c r="G109" s="97">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -12631,14 +12635,14 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
         <v>8.343867655447804</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="310"/>
+      <c r="E110" s="309"/>
       <c r="F110" s="26"/>
       <c r="G110" s="97">
         <f>BS!$G$38/G$4</f>
@@ -12657,16 +12661,16 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="10"/>
-      <c r="E111" s="309"/>
+      <c r="E111" s="308"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
       <c r="B112" s="93" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" s="55"/>
       <c r="D112" s="55"/>
-      <c r="E112" s="312"/>
+      <c r="E112" s="311"/>
       <c r="F112" s="55"/>
       <c r="G112" s="23" t="str">
         <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
@@ -12716,28 +12720,28 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
-        <v>0.3848277982270753</v>
-      </c>
-      <c r="E113" s="309"/>
+        <v>0.38237459335905039</v>
+      </c>
+      <c r="E113" s="308"/>
       <c r="G113" s="23">
         <f t="shared" ref="G113:Q113" si="45">G81</f>
-        <v>0.37957428579290575</v>
+        <v>0.37556098895979384</v>
       </c>
       <c r="H113" s="23">
         <f t="shared" si="45"/>
-        <v>0.4558793547115022</v>
+        <v>0.45411955525604425</v>
       </c>
       <c r="I113" s="23">
         <f t="shared" si="45"/>
-        <v>0.47766234241732236</v>
+        <v>0.47733839702364145</v>
       </c>
       <c r="J113" s="23">
         <f t="shared" si="45"/>
-        <v>0.51534683592309194</v>
+        <v>0.5149947971331873</v>
       </c>
       <c r="K113" s="23">
         <f t="shared" si="45"/>
@@ -12770,13 +12774,13 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
         <v>4.8426484563194767E-2</v>
       </c>
-      <c r="E114" s="309"/>
+      <c r="E114" s="308"/>
       <c r="G114" s="42">
         <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
         <v>4.8601561460320276E-2</v>
@@ -12824,14 +12828,14 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
         <v>1.0831144117242246</v>
       </c>
       <c r="D115" s="11"/>
-      <c r="E115" s="313"/>
+      <c r="E115" s="312"/>
       <c r="F115" s="11"/>
       <c r="G115" s="15">
         <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
@@ -12881,14 +12885,14 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
         <v>1.5509944282629921E-2</v>
       </c>
       <c r="D116" s="106"/>
-      <c r="E116" s="312"/>
+      <c r="E116" s="311"/>
       <c r="F116" s="106"/>
       <c r="G116" s="105">
         <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
@@ -12957,12 +12961,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -12980,11 +12984,11 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="305"/>
       <c r="F119" s="27"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -13006,26 +13010,26 @@
       </c>
       <c r="C120" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.31089812956997381</v>
+        <v>0.308898371982265</v>
       </c>
       <c r="D120" s="27"/>
-      <c r="E120" s="306"/>
+      <c r="E120" s="305"/>
       <c r="F120" s="27"/>
       <c r="G120" s="181">
         <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.34361354265677985</v>
+        <v>0.33930895827500729</v>
       </c>
       <c r="H120" s="181">
         <f t="shared" si="49"/>
-        <v>0.55366302745045104</v>
+        <v>0.55110447574704324</v>
       </c>
       <c r="I120" s="181">
         <f t="shared" si="49"/>
-        <v>0.74971454742241805</v>
+        <v>0.7490941359682366</v>
       </c>
       <c r="J120" s="181">
         <f t="shared" si="49"/>
-        <v>1.2311599503085606</v>
+        <v>1.2301073779880305</v>
       </c>
       <c r="K120" s="181">
         <f t="shared" si="49"/>
@@ -13059,30 +13063,30 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9909901100125003E-2</v>
+        <v>3.9653192809019897E-2</v>
       </c>
       <c r="D121" s="27"/>
-      <c r="E121" s="306"/>
+      <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>4.4109569018842082E-2</v>
+        <v>4.355699079268386E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>7.1073559364627864E-2</v>
+        <v>7.0745118837874613E-2</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>9.6240635099155078E-2</v>
+        <v>9.6160993063958478E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.15804363932073948</v>
+        <v>0.15790852092272536</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
@@ -13828,43 +13832,43 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F4" s="138">
         <f>Thesis!C75</f>
@@ -13874,7 +13878,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
@@ -13885,25 +13889,25 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>28229.135413031079</v>
+        <v>28047.560091832624</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
       <c r="E6" s="344" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F6" s="344"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
@@ -13919,11 +13923,11 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
-        <v>41505.820259237436</v>
+        <v>42222.564948178719</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -13935,7 +13939,7 @@
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
@@ -13951,11 +13955,11 @@
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
-        <v>74456.355672268517</v>
+        <v>74991.525040011329</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -13965,7 +13969,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
@@ -13979,11 +13983,11 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -13996,7 +14000,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14006,13 +14010,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
@@ -14022,7 +14026,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -14032,11 +14036,11 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>9.0321281164495559</v>
+        <v>9.0981264288878361</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14049,19 +14053,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>112</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="D20" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="D20" s="132" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>114</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>115</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14071,7 +14075,7 @@
       </c>
       <c r="C21" s="127">
         <f>C4*(1+D21)</f>
-        <v>2522.0756452064356</v>
+        <v>2505.8531612846018</v>
       </c>
       <c r="D21" s="142">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
@@ -14083,7 +14087,7 @@
       </c>
       <c r="F21" s="129">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2313.8308671618674</v>
+        <v>2298.947854389543</v>
       </c>
       <c r="H21" s="124"/>
     </row>
@@ -14093,7 +14097,7 @@
       </c>
       <c r="C22" s="127">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2503.6644929964286</v>
+        <v>2487.5604332072244</v>
       </c>
       <c r="D22" s="142">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
@@ -14105,7 +14109,7 @@
       </c>
       <c r="F22" s="129">
         <f t="shared" si="1"/>
-        <v>2107.2843136069591</v>
+        <v>2093.7298486720174</v>
       </c>
       <c r="H22" s="124"/>
     </row>
@@ -14115,7 +14119,7 @@
       </c>
       <c r="C23" s="127">
         <f t="shared" si="2"/>
-        <v>2485.3877421975549</v>
+        <v>2469.4012420448116</v>
       </c>
       <c r="D23" s="142">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
@@ -14127,7 +14131,7 @@
       </c>
       <c r="F23" s="129">
         <f t="shared" si="1"/>
-        <v>1919.1753560712189</v>
+        <v>1906.830844749277</v>
       </c>
       <c r="H23" s="124"/>
     </row>
@@ -14137,7 +14141,7 @@
       </c>
       <c r="C24" s="127">
         <f t="shared" si="2"/>
-        <v>2467.2444116795127</v>
+        <v>2451.3746129778847</v>
       </c>
       <c r="D24" s="142">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
@@ -14149,7 +14153,7 @@
       </c>
       <c r="F24" s="129">
         <f t="shared" si="1"/>
-        <v>1747.8581430934851</v>
+        <v>1736.6155775987222</v>
       </c>
       <c r="H24" s="124"/>
     </row>
@@ -14159,7 +14163,7 @@
       </c>
       <c r="C25" s="127">
         <f t="shared" si="2"/>
-        <v>2449.2335274742522</v>
+        <v>2433.4795783031459</v>
       </c>
       <c r="D25" s="142">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
@@ -14171,7 +14175,7 @@
       </c>
       <c r="F25" s="129">
         <f t="shared" si="1"/>
-        <v>1591.8337418797271</v>
+        <v>1581.5947558552762</v>
       </c>
       <c r="H25" s="124"/>
     </row>
@@ -14181,7 +14185,7 @@
       </c>
       <c r="C26" s="127">
         <f t="shared" si="2"/>
-        <v>2431.3541227236901</v>
+        <v>2415.7151773815331</v>
       </c>
       <c r="D26" s="142">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
@@ -14193,7 +14197,7 @@
       </c>
       <c r="F26" s="129">
         <f t="shared" si="1"/>
-        <v>1449.7370234532154</v>
+        <v>1440.4120313188373</v>
       </c>
       <c r="H26" s="124"/>
     </row>
@@ -14203,7 +14207,7 @@
       </c>
       <c r="C27" s="127">
         <f t="shared" si="2"/>
-        <v>2413.6052376278076</v>
+        <v>2398.0804565866479</v>
       </c>
       <c r="D27" s="142">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
@@ -14215,7 +14219,7 @@
       </c>
       <c r="F27" s="129">
         <f t="shared" si="1"/>
-        <v>1320.3247185156031</v>
+        <v>1311.8321316423944</v>
       </c>
       <c r="H27" s="124"/>
     </row>
@@ -14225,7 +14229,7 @@
       </c>
       <c r="C28" s="127">
         <f t="shared" si="2"/>
-        <v>2395.9859193931243</v>
+        <v>2380.5744692535654</v>
       </c>
       <c r="D28" s="142">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
@@ -14237,7 +14241,7 @@
       </c>
       <c r="F28" s="129">
         <f t="shared" si="1"/>
-        <v>1202.464539514164</v>
+        <v>1194.7300523682613</v>
       </c>
       <c r="H28" s="124"/>
     </row>
@@ -14247,7 +14251,7 @@
       </c>
       <c r="C29" s="127">
         <f t="shared" si="2"/>
-        <v>2378.4952221815547</v>
+        <v>2363.1962756280145</v>
       </c>
       <c r="D29" s="142">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
@@ -14259,7 +14263,7 @@
       </c>
       <c r="F29" s="129">
         <f t="shared" si="1"/>
-        <v>1095.1252737391842</v>
+        <v>1088.0812137485991</v>
       </c>
       <c r="H29" s="124"/>
     </row>
@@ -14269,7 +14273,7 @@
       </c>
       <c r="C30" s="127">
         <f t="shared" si="2"/>
-        <v>2361.1322070596293</v>
+        <v>2345.9449428159301</v>
       </c>
       <c r="D30" s="142">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
@@ -14281,7 +14285,7 @@
       </c>
       <c r="F30" s="129">
         <f t="shared" si="1"/>
-        <v>997.36776077145691</v>
+        <v>990.95249622773781</v>
       </c>
       <c r="H30" s="124"/>
     </row>
@@ -14727,11 +14731,11 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>28023.062724515952</v>
+        <v>27842.812903162245</v>
       </c>
       <c r="D51" s="143">
         <f>Terminal_Growth</f>
@@ -14743,18 +14747,18 @@
       </c>
       <c r="F51" s="129">
         <f t="shared" si="1"/>
-        <v>11837.244537151286</v>
+        <v>11761.105064670463</v>
       </c>
       <c r="H51" s="124"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
-        <v>27582.246274958168</v>
+        <v>27404.831871241127</v>
       </c>
       <c r="H52" s="124"/>
     </row>
@@ -14764,7 +14768,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14775,7 +14779,7 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="137">
         <f>F52</f>
-        <v>27582.246274958168</v>
+        <v>27404.831871241127</v>
       </c>
       <c r="B55" s="135">
         <f>C78</f>
@@ -14805,19 +14809,19 @@
       </c>
       <c r="B56" s="127">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>20193.592912324937</v>
+        <v>20063.703772414767</v>
       </c>
       <c r="C56" s="127">
-        <v>25999.545497513922</v>
+        <v>25832.311334807477</v>
       </c>
       <c r="D56" s="127">
-        <v>28229.135413031072</v>
+        <v>28047.560091832616</v>
       </c>
       <c r="E56" s="127">
-        <v>29169.388943080252</v>
+        <v>28981.765727242848</v>
       </c>
       <c r="F56" s="127">
-        <v>30635.527109280756</v>
+        <v>30438.473405950401</v>
       </c>
       <c r="H56" s="124"/>
     </row>
@@ -14826,19 +14830,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="127">
-        <v>16230.163670980823</v>
+        <v>16125.768083282397</v>
       </c>
       <c r="C57" s="127">
-        <v>24207.81034217267</v>
+        <v>24052.100970487048</v>
       </c>
       <c r="D57" s="127">
-        <v>28229.135413031065</v>
+        <v>28047.560091832609</v>
       </c>
       <c r="E57" s="127">
-        <v>30120.811948539595</v>
+        <v>29927.068993812412</v>
       </c>
       <c r="F57" s="127">
-        <v>33324.021051394309</v>
+        <v>33109.67442910144</v>
       </c>
       <c r="H57" s="124"/>
     </row>
@@ -14847,19 +14851,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="127">
-        <v>13140.890829194326</v>
+        <v>13056.366048742024</v>
       </c>
       <c r="C58" s="127">
-        <v>22409.643349910642</v>
+        <v>22265.500140079126</v>
       </c>
       <c r="D58" s="127">
-        <v>28229.135413031065</v>
+        <v>28047.560091832613</v>
       </c>
       <c r="E58" s="127">
-        <v>31246.686937184058</v>
+        <v>31045.702134284722</v>
       </c>
       <c r="F58" s="127">
-        <v>36765.0666593145</v>
+        <v>36528.586558529481</v>
       </c>
       <c r="H58" s="124"/>
     </row>
@@ -14868,19 +14872,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="127">
-        <v>11023.754834817611</v>
+        <v>10952.84788723816</v>
       </c>
       <c r="C59" s="127">
-        <v>20922.286661863869</v>
+        <v>20787.710421208605</v>
       </c>
       <c r="D59" s="127">
-        <v>28229.135413031061</v>
+        <v>28047.560091832613</v>
       </c>
       <c r="E59" s="127">
-        <v>32342.609628836006</v>
+        <v>32134.575636798087</v>
       </c>
       <c r="F59" s="127">
-        <v>40406.434113458046</v>
+        <v>40146.532024878717</v>
       </c>
       <c r="H59" s="124"/>
     </row>
@@ -14889,19 +14893,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="127">
-        <v>9624.4797447577112</v>
+        <v>9562.5732082856211</v>
       </c>
       <c r="C60" s="127">
-        <v>19795.345519715876</v>
+        <v>19668.01798494067</v>
       </c>
       <c r="D60" s="127">
-        <v>28229.135413031061</v>
+        <v>28047.560091832605</v>
       </c>
       <c r="E60" s="127">
-        <v>33316.212150828149</v>
+        <v>33101.915756911323</v>
       </c>
       <c r="F60" s="127">
-        <v>43938.451096733559</v>
+        <v>43655.830383979846</v>
       </c>
       <c r="H60" s="124"/>
     </row>
@@ -14910,19 +14914,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="127">
-        <v>8710.0885982663494</v>
+        <v>8654.0636045229312</v>
       </c>
       <c r="C61" s="127">
-        <v>18982.314945066366</v>
+        <v>18860.216981993442</v>
       </c>
       <c r="D61" s="127">
-        <v>28229.135413031065</v>
+        <v>28047.560091832605</v>
       </c>
       <c r="E61" s="127">
-        <v>34136.509865863532</v>
+        <v>33916.937156575856</v>
       </c>
       <c r="F61" s="127">
-        <v>47200.695522272283</v>
+        <v>46897.091415208801</v>
       </c>
       <c r="H61" s="124"/>
     </row>
@@ -14935,7 +14939,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -14972,23 +14976,23 @@
       </c>
       <c r="B65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="C65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E65" s="145">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="F65" s="128">
         <f>C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="H65" s="124"/>
     </row>
@@ -14999,23 +15003,23 @@
       </c>
       <c r="B66" s="128">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.1279722281473283</v>
+        <v>8.1997862481313746</v>
       </c>
       <c r="C66" s="128">
         <f t="shared" si="4"/>
-        <v>8.8384516564624356</v>
+        <v>8.9056957337786056</v>
       </c>
       <c r="D66" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328915</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E66" s="128">
         <f t="shared" si="4"/>
-        <v>9.2263481344322198</v>
+        <v>9.2910971857212523</v>
       </c>
       <c r="F66" s="128">
         <f t="shared" si="4"/>
-        <v>9.4057607270893442</v>
+        <v>9.4693557614854704</v>
       </c>
       <c r="H66" s="124"/>
     </row>
@@ -15026,23 +15030,23 @@
       </c>
       <c r="B67" s="128">
         <f t="shared" si="4"/>
-        <v>7.6429639714934581</v>
+        <v>7.7178976594622748</v>
       </c>
       <c r="C67" s="128">
         <f t="shared" si="4"/>
-        <v>8.6191954792579697</v>
+        <v>8.6878498551971095</v>
       </c>
       <c r="D67" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E67" s="128">
         <f t="shared" si="4"/>
-        <v>9.3427745886766083</v>
+        <v>9.4067747622364397</v>
       </c>
       <c r="F67" s="128">
         <f t="shared" si="4"/>
-        <v>9.7347540509229198</v>
+        <v>9.7962329359020277</v>
       </c>
       <c r="H67" s="124"/>
     </row>
@@ -15053,23 +15057,23 @@
       </c>
       <c r="B68" s="128">
         <f t="shared" si="4"/>
-        <v>7.2649269878396519</v>
+        <v>7.3422922836394369</v>
       </c>
       <c r="C68" s="128">
         <f t="shared" si="4"/>
-        <v>8.3991522326189099</v>
+        <v>8.4692219697655933</v>
       </c>
       <c r="D68" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E68" s="128">
         <f t="shared" si="4"/>
-        <v>9.480548882653272</v>
+        <v>9.5436628650026503</v>
       </c>
       <c r="F68" s="128">
         <f t="shared" si="4"/>
-        <v>10.155837771544068</v>
+        <v>10.214608163659173</v>
       </c>
       <c r="H68" s="124"/>
     </row>
@@ -15080,23 +15084,23 @@
       </c>
       <c r="B69" s="128">
         <f t="shared" si="4"/>
-        <v>7.0058512291454997</v>
+        <v>7.0848829509059597</v>
       </c>
       <c r="C69" s="128">
         <f t="shared" si="4"/>
-        <v>8.2171431111321347</v>
+        <v>8.2883835665530903</v>
       </c>
       <c r="D69" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="E69" s="128">
         <f t="shared" si="4"/>
-        <v>9.614657888198499</v>
+        <v>9.6769092551896243</v>
       </c>
       <c r="F69" s="128">
         <f t="shared" si="4"/>
-        <v>10.601435049362856</v>
+        <v>10.65733927261868</v>
       </c>
       <c r="H69" s="124"/>
     </row>
@@ -15107,23 +15111,23 @@
       </c>
       <c r="B70" s="128">
         <f t="shared" si="4"/>
-        <v>6.8346207288177103</v>
+        <v>6.9147538386526222</v>
       </c>
       <c r="C70" s="128">
         <f t="shared" si="4"/>
-        <v>8.0792383510311669</v>
+        <v>8.1513658368462085</v>
       </c>
       <c r="D70" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081488</v>
       </c>
       <c r="E70" s="128">
         <f t="shared" si="4"/>
-        <v>9.7337984690216537</v>
+        <v>9.7952835004904841</v>
       </c>
       <c r="F70" s="128">
         <f t="shared" si="4"/>
-        <v>11.03365101569341</v>
+        <v>11.086775141303123</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15133,40 +15137,40 @@
       </c>
       <c r="B71" s="128">
         <f t="shared" si="4"/>
-        <v>6.7227258951132729</v>
+        <v>6.8035787344075898</v>
       </c>
       <c r="C71" s="128">
         <f t="shared" si="4"/>
-        <v>7.97974709797594</v>
+        <v>8.0525145309932462</v>
       </c>
       <c r="D71" s="128">
         <f t="shared" si="4"/>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081488</v>
       </c>
       <c r="E71" s="128">
         <f t="shared" si="4"/>
-        <v>9.8341790083173546</v>
+        <v>9.8950183725208571</v>
       </c>
       <c r="F71" s="128">
         <f t="shared" si="4"/>
-        <v>11.43285468132332</v>
+        <v>11.483411050862937</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C73" s="175" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D73" s="175" t="s">
+        <v>116</v>
+      </c>
+      <c r="E73" s="176" t="s">
         <v>117</v>
       </c>
-      <c r="E73" s="176" t="s">
-        <v>118</v>
-      </c>
       <c r="F73" s="176" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15184,7 +15188,7 @@
       </c>
       <c r="E74" s="139">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>10.155837771544068</v>
+        <v>10.214608163659173</v>
       </c>
       <c r="F74" s="146">
         <f>Scenarios!C58</f>
@@ -15206,7 +15210,7 @@
       </c>
       <c r="E75" s="139">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>9.3427745886766083</v>
+        <v>9.4067747622364397</v>
       </c>
       <c r="F75" s="146">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -15229,7 +15233,7 @@
       </c>
       <c r="E76" s="139">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="F76" s="146">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -15252,7 +15256,7 @@
       </c>
       <c r="E77" s="139">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>8.6191954792579697</v>
+        <v>8.6878498551971095</v>
       </c>
       <c r="F77" s="146">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -15275,7 +15279,7 @@
       </c>
       <c r="E78" s="139">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.2649269878396519</v>
+        <v>7.3422922836394369</v>
       </c>
       <c r="F78" s="146">
         <f>Scenarios!C52</f>
@@ -15291,20 +15295,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15356,20 +15360,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
@@ -15381,14 +15385,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15410,14 +15414,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15425,12 +15429,12 @@
       </c>
       <c r="I6" s="270">
         <f t="shared" si="0"/>
-        <v>9.6147055134616366</v>
+        <v>9.6806872475781418</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15455,11 +15459,11 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
-        <v>2807.968614974819</v>
+        <v>2772.792068232593</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15477,11 +15481,11 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
-        <v>2540.6221871727971</v>
+        <v>2524.2804082649359</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -15510,7 +15514,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E11" s="346"/>
       <c r="F11" s="346"/>
@@ -15524,7 +15528,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15543,7 +15547,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -15561,18 +15565,18 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-0.34649046142280127</v>
+        <v>-0.34904529928871464</v>
       </c>
       <c r="E14" s="346"/>
       <c r="F14" s="346"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15581,21 +15585,21 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -15605,14 +15609,14 @@
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E20" s="347"/>
       <c r="F20" s="347"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15627,11 +15631,11 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
-        <v>9.111288498532895</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -15642,16 +15646,16 @@
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
@@ -15663,7 +15667,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C26" s="168">
         <v>0</v>
@@ -15674,11 +15678,11 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
-        <v>9.1112884985328897</v>
+        <v>9.1767776359081505</v>
       </c>
       <c r="D27" s="164" t="str">
         <f>Market_currency</f>
@@ -15689,7 +15693,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28" s="169">
         <v>0.55000000000000004</v>
@@ -15700,16 +15704,16 @@
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
@@ -15721,7 +15725,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C32" s="168">
         <v>-0.05</v>
@@ -15732,11 +15736,11 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
-        <v>8.6191954792579697</v>
+        <v>8.6878498551971095</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -15747,7 +15751,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C34" s="169">
         <v>0.2</v>
@@ -15758,16 +15762,16 @@
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
@@ -15779,7 +15783,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C38" s="168">
         <v>0.02</v>
@@ -15790,11 +15794,11 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
-        <v>9.3427745886766083</v>
+        <v>9.4067747622364397</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -15805,7 +15809,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
@@ -15817,11 +15821,11 @@
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>9.070741417213835</v>
+        <v>9.1364913613480141</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -15830,7 +15834,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15839,12 +15843,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15859,16 +15863,16 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
@@ -15880,7 +15884,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C50" s="168">
         <v>-0.2</v>
@@ -15891,11 +15895,11 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
-        <v>7.2649269878396519</v>
+        <v>7.3422922836394369</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -15906,7 +15910,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C52" s="169">
         <v>0.05</v>
@@ -15917,16 +15921,16 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
@@ -15938,7 +15942,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C56" s="168">
         <v>0.05</v>
@@ -15949,11 +15953,11 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
-        <v>10.155837771544068</v>
+        <v>10.214608163659173</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -15964,7 +15968,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C58" s="169">
         <v>0.05</v>
@@ -15975,27 +15979,27 @@
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>9.0347055134616365</v>
+        <v>9.1006872475781417</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>325</v>
-      </c>
-      <c r="F60" s="319">
+        <v>322</v>
+      </c>
+      <c r="F60" s="318">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>311</v>
+        <v>386</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16004,63 +16008,63 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C65" s="155">
         <v>-7.3000000000000001E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
-        <v>9.0321281164495559</v>
+        <v>9.0981264288878361</v>
       </c>
       <c r="D66" s="164" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>320</v>
+        <v>387</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16070,19 +16074,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16092,23 +16096,23 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>390</v>
-      </c>
-      <c r="F72" s="337">
+        <v>383</v>
+      </c>
+      <c r="F72" s="335">
         <f>BS!D89/C60</f>
-        <v>0.62612608991135499</v>
+        <v>0.63122414236360114</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16117,12 +16121,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16132,7 +16136,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
@@ -16145,12 +16149,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C121</f>
@@ -16159,7 +16163,7 @@
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16171,32 +16175,32 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2284175425125214</v>
+        <v>5.2666014164225361</v>
       </c>
       <c r="D82" s="120"/>
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>6.4501768017717804</v>
+        <v>6.4883606756817951</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>131</v>
-      </c>
-      <c r="F83" s="337">
+        <v>130</v>
+      </c>
+      <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.28606673541699057</v>
+        <v>0.28704717576043881</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16204,12 +16208,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16222,53 +16226,53 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12172735692567005</v>
+        <v>0.12411921460409614</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="103"/>
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="328" t="s">
-        <v>362</v>
-      </c>
-      <c r="F89" s="325"/>
+      <c r="E89" s="326" t="s">
+        <v>355</v>
+      </c>
+      <c r="F89" s="323"/>
       <c r="G89" s="2"/>
-      <c r="H89" s="324"/>
+      <c r="H89" s="322"/>
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="321" t="s">
-        <v>363</v>
-      </c>
-      <c r="F90" s="326" t="s">
-        <v>364</v>
+      <c r="E90" s="319" t="s">
+        <v>356</v>
+      </c>
+      <c r="F90" s="324" t="s">
+        <v>357</v>
       </c>
       <c r="G90" s="2"/>
-      <c r="H90" s="324"/>
+      <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="322" t="s">
-        <v>363</v>
-      </c>
-      <c r="F91" s="326" t="s">
-        <v>365</v>
+      <c r="E91" s="320" t="s">
+        <v>356</v>
+      </c>
+      <c r="F91" s="324" t="s">
+        <v>358</v>
       </c>
       <c r="G91" s="2"/>
-      <c r="H91" s="324"/>
+      <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="323" t="s">
-        <v>363</v>
-      </c>
-      <c r="F92" s="327" t="s">
-        <v>366</v>
+      <c r="E92" s="321" t="s">
+        <v>356</v>
+      </c>
+      <c r="F92" s="325" t="s">
+        <v>359</v>
       </c>
       <c r="G92" s="2"/>
-      <c r="H92" s="324"/>
+      <c r="H92" s="322"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A56EB4F-905D-494D-A1AB-28014992666A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E133D2EB-8C4B-4A8A-A0B2-D42FD6711B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1711,10 +1711,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>C0003</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Monthly Operating Expenses</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2004,6 +2000,10 @@
   </si>
   <si>
     <t>Selected:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3690,7 +3690,7 @@
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.59765625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F1" s="290" t="s">
         <v>306</v>
@@ -3739,10 +3739,10 @@
         <v>344</v>
       </c>
       <c r="C5" s="48" t="s">
+        <v>363</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>364</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="338" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3822,7 +3822,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>42</v>
@@ -3858,7 +3858,7 @@
         <v>59</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>346</v>
+        <v>390</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="338" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
-        <v>374</v>
-      </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="B26" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="340" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,17 +4023,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="340" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="340" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
-        <v>373</v>
-      </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="B50" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="338" t="s">
+        <v>377</v>
+      </c>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="340" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="342" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4264,7 +4264,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
+      <c r="B72" s="338" t="s">
+        <v>378</v>
+      </c>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
+    </row>
+    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
-        <v>380</v>
-      </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
+      <c r="B80" s="338" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
-        <v>381</v>
-      </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="B84" s="338" t="s">
+        <v>380</v>
+      </c>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
+      <c r="B97" s="338" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
-        <v>362</v>
-      </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="B103" s="340" t="s">
+        <v>361</v>
+      </c>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4643,7 +4643,7 @@
     </row>
     <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="343" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C114" s="343"/>
       <c r="D114" s="343"/>
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
+      <c r="B118" s="339" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4754,6 +4754,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4769,12 +4775,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8086,7 +8086,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>99</v>
@@ -8098,7 +8098,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8109,12 +8109,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8125,12 +8125,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8138,12 +8138,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8151,7 +8151,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9705,7 +9705,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10210,7 +10210,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10265,7 +10265,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10397,7 +10397,7 @@
         <v>0.03</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10424,7 +10424,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -15588,7 +15588,7 @@
         <v>155</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15599,7 +15599,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -15999,7 +15999,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16056,7 +16056,7 @@
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E68" s="288" t="s">
         <v>343</v>
@@ -16103,7 +16103,7 @@
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16238,7 +16238,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16246,30 +16246,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
+        <v>355</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>356</v>
-      </c>
-      <c r="F90" s="324" t="s">
-        <v>357</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E133D2EB-8C4B-4A8A-A0B2-D42FD6711B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC533427-2FAD-4EC6-B452-F9E0E3134102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC533427-2FAD-4EC6-B452-F9E0E3134102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB024F5B-257B-4A82-8250-F0577D45538E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3750,7 +3750,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="50">
-        <v>7.79</v>
+        <v>7.77</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>42</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>63658.944701439999</v>
+        <v>63495.507102719996</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="339" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12411921460409614</v>
+        <v>0.12514862916378067</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="340"/>
+      <c r="D26" s="340"/>
+      <c r="E26" s="340"/>
+      <c r="F26" s="340"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="338" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="338"/>
+      <c r="D29" s="338"/>
+      <c r="E29" s="338"/>
+      <c r="F29" s="338"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="338" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="338"/>
+      <c r="D32" s="338"/>
+      <c r="E32" s="338"/>
+      <c r="F32" s="338"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="338" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="338"/>
+      <c r="D36" s="338"/>
+      <c r="E36" s="338"/>
+      <c r="F36" s="338"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="338" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="338"/>
+      <c r="D39" s="338"/>
+      <c r="E39" s="338"/>
+      <c r="F39" s="338"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="338" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="338"/>
+      <c r="D47" s="338"/>
+      <c r="E47" s="338"/>
+      <c r="F47" s="338"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="338" t="s">
         <v>372</v>
       </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="C50" s="342"/>
+      <c r="D50" s="342"/>
+      <c r="E50" s="342"/>
+      <c r="F50" s="342"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="339" t="s">
         <v>377</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="339" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>3.9653192809019897E-2</v>
+        <v>3.975526022937774E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>7.4454428754813853E-2</v>
+        <v>7.4646074646074645E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="338" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="340" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="340"/>
+      <c r="D64" s="340"/>
+      <c r="E64" s="340"/>
+      <c r="F64" s="340"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="338" t="s">
+      <c r="B72" s="339" t="s">
         <v>378</v>
       </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+      <c r="C72" s="339"/>
+      <c r="D72" s="339"/>
+      <c r="E72" s="339"/>
+      <c r="F72" s="339"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="339" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
+      <c r="B80" s="339" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+      <c r="C80" s="339"/>
+      <c r="D80" s="339"/>
+      <c r="E80" s="339"/>
+      <c r="F80" s="339"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
+      <c r="B84" s="339" t="s">
         <v>380</v>
       </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
+      <c r="C84" s="339"/>
+      <c r="D84" s="339"/>
+      <c r="E84" s="339"/>
+      <c r="F84" s="339"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
+      <c r="B97" s="339" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
+      <c r="C97" s="339"/>
+      <c r="D97" s="339"/>
+      <c r="E97" s="339"/>
+      <c r="F97" s="339"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
+      <c r="B103" s="338" t="s">
         <v>361</v>
       </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
+      <c r="C103" s="338"/>
+      <c r="D103" s="338"/>
+      <c r="E103" s="338"/>
+      <c r="F103" s="338"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
+      <c r="B118" s="341" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+      <c r="C118" s="341"/>
+      <c r="D118" s="341"/>
+      <c r="E118" s="341"/>
+      <c r="F118" s="341"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4754,12 +4754,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4775,6 +4769,12 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -11983,20 +11983,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.4454428754813853E-2</v>
+        <v>7.4646074646074645E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.4454428754813853E-2</v>
+        <v>7.4646074646074645E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4454428754813853E-2</v>
+        <v>7.4646074646074645E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3170731707317069E-2</v>
+        <v>7.3359073359073351E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13067,30 +13067,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9653192809019897E-2</v>
+        <v>3.975526022937774E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>4.355699079268386E-2</v>
+        <v>4.366910659910004E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>7.0745118837874613E-2</v>
+        <v>7.0927216955861419E-2</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>9.6160993063958478E-2</v>
+        <v>9.6408511707623767E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.15790852092272536</v>
+        <v>0.15831497786203738</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>5.4195054853335624E-2</v>
+        <v>5.433455306402632E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-7.79</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>7.79</v>
+        <v>7.77</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>7.79</v>
+        <v>7.77</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12411921460409614</v>
+        <v>0.12514862916378067</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB024F5B-257B-4A82-8250-F0577D45538E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A46492-EDAA-4A2D-8E18-D9148FEBE336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3378,20 +3378,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3750,7 +3750,7 @@
         <v>98</v>
       </c>
       <c r="C6" s="50">
-        <v>7.77</v>
+        <v>7.88</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>42</v>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>63495.507102719996</v>
+        <v>64394.413895680002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3805,13 +3805,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="338" t="s">
         <v>285</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12514862916378067</v>
+        <v>0.11953198379323582</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -3913,22 +3913,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="338" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="340" t="s">
+      <c r="B26" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C26" s="340"/>
-      <c r="D26" s="340"/>
-      <c r="E26" s="340"/>
-      <c r="F26" s="340"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -3940,13 +3940,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="338" t="s">
+      <c r="B29" s="340" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="338"/>
-      <c r="D29" s="338"/>
-      <c r="E29" s="338"/>
-      <c r="F29" s="338"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -3966,13 +3966,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="338" t="s">
+      <c r="B32" s="340" t="s">
         <v>239</v>
       </c>
-      <c r="C32" s="338"/>
-      <c r="D32" s="338"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="338"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4001,13 +4001,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="338" t="s">
+      <c r="B36" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="338"/>
-      <c r="D36" s="338"/>
-      <c r="E36" s="338"/>
-      <c r="F36" s="338"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4023,13 +4023,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="338" t="s">
+      <c r="B39" s="340" t="s">
         <v>246</v>
       </c>
-      <c r="C39" s="338"/>
-      <c r="D39" s="338"/>
-      <c r="E39" s="338"/>
-      <c r="F39" s="338"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4093,13 +4093,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="338" t="s">
+      <c r="B47" s="340" t="s">
         <v>247</v>
       </c>
-      <c r="C47" s="338"/>
-      <c r="D47" s="338"/>
-      <c r="E47" s="338"/>
-      <c r="F47" s="338"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4115,13 +4115,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="338" t="s">
+      <c r="B50" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C50" s="342"/>
-      <c r="D50" s="342"/>
-      <c r="E50" s="342"/>
-      <c r="F50" s="342"/>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4137,22 +4137,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="338" t="s">
         <v>267</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>3.975526022937774E-2</v>
+        <v>3.9200301012977792E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>7.4646074646074645E-2</v>
+        <v>7.3604060913705582E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4213,22 +4213,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="340" t="s">
         <v>302</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="340" t="s">
+      <c r="B64" s="342" t="s">
         <v>258</v>
       </c>
-      <c r="C64" s="340"/>
-      <c r="D64" s="340"/>
-      <c r="E64" s="340"/>
-      <c r="F64" s="340"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4280,22 +4280,22 @@
       <c r="C71" s="125"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B72" s="339" t="s">
+      <c r="B72" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C72" s="339"/>
-      <c r="D72" s="339"/>
-      <c r="E72" s="339"/>
-      <c r="F72" s="339"/>
+      <c r="C72" s="338"/>
+      <c r="D72" s="338"/>
+      <c r="E72" s="338"/>
+      <c r="F72" s="338"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B75" s="47" t="s">
@@ -4332,13 +4332,13 @@
       <c r="A79" s="239"/>
     </row>
     <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="339" t="s">
+      <c r="B80" s="338" t="s">
         <v>260</v>
       </c>
-      <c r="C80" s="339"/>
-      <c r="D80" s="339"/>
-      <c r="E80" s="339"/>
-      <c r="F80" s="339"/>
+      <c r="C80" s="338"/>
+      <c r="D80" s="338"/>
+      <c r="E80" s="338"/>
+      <c r="F80" s="338"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="1" t="s">
@@ -4351,13 +4351,13 @@
       </c>
     </row>
     <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="339" t="s">
+      <c r="B84" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C84" s="339"/>
-      <c r="D84" s="339"/>
-      <c r="E84" s="339"/>
-      <c r="F84" s="339"/>
+      <c r="C84" s="338"/>
+      <c r="D84" s="338"/>
+      <c r="E84" s="338"/>
+      <c r="F84" s="338"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B85" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="339" t="s">
+      <c r="B97" s="338" t="s">
         <v>266</v>
       </c>
-      <c r="C97" s="339"/>
-      <c r="D97" s="339"/>
-      <c r="E97" s="339"/>
-      <c r="F97" s="339"/>
+      <c r="C97" s="338"/>
+      <c r="D97" s="338"/>
+      <c r="E97" s="338"/>
+      <c r="F97" s="338"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B99" s="47" t="s">
@@ -4493,13 +4493,13 @@
       <c r="F101" s="36"/>
     </row>
     <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="338" t="s">
+      <c r="B103" s="340" t="s">
         <v>361</v>
       </c>
-      <c r="C103" s="338"/>
-      <c r="D103" s="338"/>
-      <c r="E103" s="338"/>
-      <c r="F103" s="338"/>
+      <c r="C103" s="340"/>
+      <c r="D103" s="340"/>
+      <c r="E103" s="340"/>
+      <c r="F103" s="340"/>
     </row>
     <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B105" s="266" t="s">
@@ -4661,13 +4661,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="341" t="s">
+      <c r="B118" s="339" t="s">
         <v>274</v>
       </c>
-      <c r="C118" s="341"/>
-      <c r="D118" s="341"/>
-      <c r="E118" s="341"/>
-      <c r="F118" s="341"/>
+      <c r="C118" s="339"/>
+      <c r="D118" s="339"/>
+      <c r="E118" s="339"/>
+      <c r="F118" s="339"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="240" t="s">
@@ -4754,6 +4754,12 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B80:F80"/>
     <mergeCell ref="B97:F97"/>
@@ -4769,12 +4775,6 @@
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -11983,20 +11983,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.4646074646074645E-2</v>
+        <v>7.3604060913705582E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.4646074646074645E-2</v>
+        <v>7.3604060913705582E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4646074646074645E-2</v>
+        <v>7.3604060913705582E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3359073359073351E-2</v>
+        <v>7.2335025380710655E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13067,30 +13067,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.975526022937774E-2</v>
+        <v>3.9200301012977792E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>4.366910659910004E-2</v>
+        <v>4.3059512471447625E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>7.0927216955861419E-2</v>
+        <v>6.9937116211553713E-2</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>9.6408511707623767E-2</v>
+        <v>9.5062707610182304E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.15831497786203738</v>
+        <v>0.15610499720660287</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>5.433455306402632E-2</v>
+        <v>5.3576075800442199E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -15380,7 +15380,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-7.77</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>7.77</v>
+        <v>7.88</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16217,7 +16217,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>7.77</v>
+        <v>7.88</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12514862916378067</v>
+        <v>0.11953198379323582</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A46492-EDAA-4A2D-8E18-D9148FEBE336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BC1A2E-9867-4EEE-855A-6D7F0BF81681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="395">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -183,10 +183,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Contingent Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -240,10 +236,6 @@
   </si>
   <si>
     <t>CAPX</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Other Data</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -952,14 +944,6 @@
   </si>
   <si>
     <t>Implied Growth Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 1: Calculate FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>FCFE represents the cash available to equity holders after accounting for operating expenses, reinvestments, taxes, and interest obligations.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1254,14 +1238,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 3: Calculate Equity Value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Equity Value adjusts the stable income value for debt and incorporates non-operating resources available to equity holders. The formula is:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1325,58 +1301,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Purpose:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> This step ensures the equity value reflects all resources available to shareholders by deducting debt and adding excess cash and non-operating assets, avoiding double-counting of income-generating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Purpose: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Expected Equity Value =</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1401,18 +1325,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Assume the Equity Value will be realized over the holding period.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Step 4: Scenario Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Total Cash =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1445,32 +1361,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This valuation method estimates the equity value of a company through a five-step process. Each step is designed to systematically derive cash flows available to equity holders, discount them appropriately, and adjust for debt and non-operating assets.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Value Stress Test</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1519,23 +1409,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Calculate Target Buy Price</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>No Growth SIV Per Share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 2: Calculate Stable Income Value (SIV) Using FCFE</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Stable Income Value (SIV) represents the present value of FCFE, assuming it grows at a constant rate indefinitely. This is calculated using the Gordon Growth Model:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1663,10 +1541,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1768,22 +1642,6 @@
   </si>
   <si>
     <t>Fundamental analysis and market signal analysis should be combined, with fundamental analysis given priority and market signal analysis serving as a supplement. Market signal analysis predicts a company's future trend, while fundamental analysis interprets the trend and identifies relevant fundamental factors and possibilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Based on fundamental research, the following scenarios have been developed, considering driving factors of high growth periods (HGP) and high growth rates (HGR), along with their associated probabilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Note that this model prioritizes fundamental analysis when combined with supplementary market signal analysis. While market signal analysis predicts future trends, fundamental analysis interprets these trends and identifies relevant factors and possibilities.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SINO LAND</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>0083.HK</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1899,58 +1757,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Note on Cost of Equity:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile, while target annual return is the investor’s hurdle rate.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Note on Terminal Growth Rate:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Setting g=0 can be a conservative assumption to avoid overestimating the stock’s value, especially if future growth is uncertain or unreliable.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t xml:space="preserve">Note on debt: </t>
     </r>
     <r>
@@ -2003,11 +1809,369 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Historical Average or D&amp;A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Note:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Implied Market Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Insight: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This step ensures a comprehensive measure of cash flow by incorporating both operating and stable non-operating sources while accounting for taxes and reinvestment needs.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Cost of Equity reflects the company’s risk profile and represents the minimum return the investor requires for taking on the general risk of owning this type of business, while the target annual return serves as the investor’s hurdle rate.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Setting g=0% is a conservative assumption, valuing the company based only on its current demonstrated earning power without relying on potentially optimistic future growth projections.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To refine the Stable Income Value (SIV) by incorporating the company’s balance sheet structure. </t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The No Growth Equity Value per share represents an estimate of the company’s intrinsic worth based on its current sustainable operations and net financial position, before factoring in any future growth potential. It serves as a fundamentally anchored valuation baseline.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To translate our estimate of the company’s intrinsic value (from Step 4) into a concrete buy price that meets the specific investment requirements.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFF</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SINO LAND</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0083.HK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>RES_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2675,7 +2839,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3378,23 +3542,24 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3684,7 +3849,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3697,22 +3862,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="253" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -3736,24 +3901,24 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>363</v>
+        <v>392</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C6" s="50">
         <v>7.88</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -3769,7 +3934,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3779,7 +3944,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -3805,24 +3970,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>285</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="341" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3832,10 +3997,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -3855,16 +4020,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -3877,11 +4042,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="258">
-        <f>C127</f>
+        <f>C129</f>
         <v>6.4883606756817951</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -3889,7 +4054,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
@@ -3904,7 +4069,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>234</v>
+        <v>370</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -3912,27 +4077,27 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>235</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="341" t="s">
+        <v>378</v>
+      </c>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="339" t="s">
+        <v>354</v>
+      </c>
+      <c r="C26" s="339"/>
+      <c r="D26" s="339"/>
+      <c r="E26" s="339"/>
+      <c r="F26" s="339"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C28" s="111">
         <f>Data!C3</f>
@@ -3941,7 +4106,7 @@
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="340" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C29" s="340"/>
       <c r="D29" s="340"/>
@@ -3950,7 +4115,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C30" s="191">
         <f>Normalized_FCF!C8</f>
@@ -3967,7 +4132,7 @@
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="340" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C32" s="340"/>
       <c r="D32" s="340"/>
@@ -3976,7 +4141,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C33" s="191">
         <f>Normalized_FCF!C9</f>
@@ -3989,7 +4154,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="52" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C34" s="191">
         <f>Normalized_FCF!C10</f>
@@ -4002,7 +4167,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B36" s="340" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C36" s="340"/>
       <c r="D36" s="340"/>
@@ -4011,7 +4176,7 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C37" s="191">
         <f>Normalized_FCF!C11</f>
@@ -4024,7 +4189,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="340" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C39" s="340"/>
       <c r="D39" s="340"/>
@@ -4033,7 +4198,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4048,7 +4213,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4063,7 +4228,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B42" s="47" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C42" s="191">
         <f>Normalized_FCF!C12</f>
@@ -4076,12 +4241,12 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="C45" s="191">
         <f>Normalized_FCF!C15</f>
@@ -4094,7 +4259,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B47" s="340" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C47" s="340"/>
       <c r="D47" s="340"/>
@@ -4103,7 +4268,7 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C48" s="191">
         <f>Normalized_FCF!C14</f>
@@ -4116,16 +4281,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="340" t="s">
-        <v>372</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+        <v>353</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4137,26 +4302,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>377</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="341" t="s">
+        <v>358</v>
+      </c>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>267</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="341" t="s">
+        <v>379</v>
+      </c>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4169,7 +4334,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B57" s="47" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C57" s="191">
         <f>Normalized_FCF!C19</f>
@@ -4182,7 +4347,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
@@ -4191,7 +4356,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
@@ -4200,7 +4365,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4213,31 +4378,31 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
-        <v>302</v>
-      </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="B63" s="341" t="s">
+        <v>380</v>
+      </c>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
-        <v>258</v>
-      </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="B64" s="339" t="s">
+        <v>254</v>
+      </c>
+      <c r="C64" s="339"/>
+      <c r="D64" s="339"/>
+      <c r="E64" s="339"/>
+      <c r="F64" s="339"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4245,31 +4410,31 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C70" s="269">
         <f>SUM(C67:C69)</f>
@@ -4281,135 +4446,128 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>378</v>
-      </c>
-      <c r="C72" s="338"/>
-      <c r="D72" s="338"/>
-      <c r="E72" s="338"/>
-      <c r="F72" s="338"/>
+        <v>372</v>
+      </c>
+      <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>379</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B75" s="47" t="s">
-        <v>257</v>
-      </c>
-      <c r="C75" s="269">
-        <v>0</v>
-      </c>
+      <c r="B73" s="341" t="s">
+        <v>381</v>
+      </c>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="341" t="s">
+        <v>382</v>
+      </c>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="254">
+        <v>253</v>
+      </c>
+      <c r="C76" s="269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B77" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
         <v>3.432204133136278</v>
       </c>
-      <c r="D76" s="1" t="str">
+      <c r="D77" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A78" s="253" t="s">
-        <v>259</v>
-      </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="239"/>
-    </row>
-    <row r="80" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="338" t="s">
-        <v>260</v>
-      </c>
-      <c r="C80" s="338"/>
-      <c r="D80" s="338"/>
-      <c r="E80" s="338"/>
-      <c r="F80" s="338"/>
+    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A79" s="253" t="s">
+        <v>373</v>
+      </c>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="36"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="83" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B83" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B84" s="338" t="s">
-        <v>380</v>
-      </c>
-      <c r="C84" s="338"/>
-      <c r="D84" s="338"/>
-      <c r="E84" s="338"/>
-      <c r="F84" s="338"/>
-    </row>
-    <row r="85" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B85" s="47" t="s">
-        <v>263</v>
-      </c>
-      <c r="C85" s="191">
+      <c r="B81" s="341" t="s">
+        <v>383</v>
+      </c>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B82" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B84" s="240" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" s="341" t="s">
+        <v>359</v>
+      </c>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
+    </row>
+    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B86" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="C86" s="191">
         <f>Valuation_Model!C7</f>
         <v>3093</v>
       </c>
-      <c r="D85" s="1" t="str">
+      <c r="D86" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B86" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="254">
-        <f>C85*C28*Exchange_Rate/Common_Shares</f>
+    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B87" s="47" t="s">
+        <v>289</v>
+      </c>
+      <c r="C87" s="254">
+        <f>C86*C28*Exchange_Rate/Common_Shares</f>
         <v>0.37849307922088393</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B88" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="47" t="s">
-        <v>277</v>
-      </c>
-      <c r="C89" s="191">
+      <c r="B89" s="1" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="47" t="s">
+        <v>267</v>
+      </c>
+      <c r="C90" s="191">
         <f>BS!C66</f>
         <v>47679</v>
-      </c>
-      <c r="D89" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
-        <v>279</v>
-      </c>
-      <c r="C90" s="191">
-        <f>Valuation_Model!C8</f>
-        <v>42222.564948178719</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4418,363 +4576,386 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>304</v>
-      </c>
-      <c r="C91" s="254">
-        <f>C90*C28*Exchange_Rate/Common_Shares</f>
+        <v>269</v>
+      </c>
+      <c r="C91" s="191">
+        <f>Valuation_Model!C8</f>
+        <v>42222.564948178719</v>
+      </c>
+      <c r="D91" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="47" t="s">
+        <v>290</v>
+      </c>
+      <c r="C92" s="254">
+        <f>C91*C28*Exchange_Rate/Common_Shares</f>
         <v>5.1668117102618574</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B93" s="1" t="s">
-        <v>264</v>
-      </c>
-    </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="C94" s="191">
+      <c r="B94" s="1" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="C95" s="191">
         <f>Valuation_Model!C9</f>
         <v>7814.4</v>
       </c>
-      <c r="D94" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="C95" s="254">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B96" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="C96" s="254">
+        <f>C95*C28*Exchange_Rate/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B97" s="338" t="s">
-        <v>266</v>
-      </c>
-      <c r="C97" s="338"/>
-      <c r="D97" s="338"/>
-      <c r="E97" s="338"/>
-      <c r="F97" s="338"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B99" s="47" t="s">
-        <v>299</v>
-      </c>
-      <c r="C99" s="254">
+    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B98" s="341" t="s">
+        <v>384</v>
+      </c>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B100" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
         <v>9.1767776359081505</v>
       </c>
-      <c r="D99" s="1" t="str">
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A101" s="253" t="s">
-        <v>276</v>
-      </c>
-      <c r="B101" s="36"/>
-      <c r="C101" s="36"/>
-      <c r="D101" s="36"/>
-      <c r="E101" s="36"/>
-      <c r="F101" s="36"/>
-    </row>
-    <row r="103" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="340" t="s">
-        <v>361</v>
-      </c>
-      <c r="C103" s="340"/>
-      <c r="D103" s="340"/>
-      <c r="E103" s="340"/>
-      <c r="F103" s="340"/>
-    </row>
-    <row r="105" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B105" s="266" t="s">
-        <v>121</v>
-      </c>
-      <c r="C105" s="266" t="s">
-        <v>136</v>
-      </c>
-      <c r="D105" s="266" t="s">
-        <v>116</v>
-      </c>
-      <c r="E105" s="266" t="s">
-        <v>269</v>
-      </c>
-      <c r="F105" s="266" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B106" s="261" t="str">
+    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A102" s="253" t="s">
+        <v>374</v>
+      </c>
+      <c r="B102" s="36"/>
+      <c r="C102" s="36"/>
+      <c r="D102" s="36"/>
+      <c r="E102" s="36"/>
+      <c r="F102" s="36"/>
+    </row>
+    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B104" s="340" t="s">
+        <v>385</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
+    </row>
+    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B106" s="266" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" s="266" t="s">
+        <v>134</v>
+      </c>
+      <c r="D106" s="266" t="s">
+        <v>114</v>
+      </c>
+      <c r="E106" s="266" t="s">
+        <v>261</v>
+      </c>
+      <c r="F106" s="266" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B107" s="261" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C106" s="262">
+      <c r="C107" s="262">
         <f>Valuation_Model!C74</f>
         <v>0.05</v>
       </c>
-      <c r="D106" s="263">
+      <c r="D107" s="263">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E106" s="264" t="str">
+      <c r="E107" s="264" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.21 HKD</v>
       </c>
-      <c r="F106" s="265">
+      <c r="F107" s="265">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="248" t="str">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B108" s="248" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C107" s="249">
+      <c r="C108" s="249">
         <f>Valuation_Model!C75</f>
         <v>0.02</v>
       </c>
-      <c r="D107" s="250">
+      <c r="D108" s="250">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E107" s="251" t="str">
+      <c r="E108" s="251" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>9.41 HKD</v>
       </c>
-      <c r="F107" s="252">
+      <c r="F108" s="252">
         <f>Valuation_Model!F75</f>
         <v>0.22499999999999992</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="248" t="str">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B109" s="248" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C108" s="249">
+      <c r="C109" s="249">
         <f>Valuation_Model!C76</f>
         <v>0</v>
       </c>
-      <c r="D108" s="250">
+      <c r="D109" s="250">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E108" s="251" t="str">
+      <c r="E109" s="251" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>9.18 HKD</v>
       </c>
-      <c r="F108" s="252">
+      <c r="F109" s="252">
         <f>Valuation_Model!F76</f>
         <v>0.495</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="248" t="str">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B110" s="248" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C109" s="249">
+      <c r="C110" s="249">
         <f>Valuation_Model!C77</f>
         <v>-0.05</v>
       </c>
-      <c r="D109" s="250">
+      <c r="D110" s="250">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E109" s="251" t="str">
+      <c r="E110" s="251" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>8.69 HKD</v>
       </c>
-      <c r="F109" s="252">
+      <c r="F110" s="252">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="248" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="248" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C110" s="249">
+      <c r="C111" s="249">
         <f>Valuation_Model!C78</f>
         <v>-0.2</v>
       </c>
-      <c r="D110" s="250">
+      <c r="D111" s="250">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E110" s="251" t="str">
+      <c r="E111" s="251" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>7.34 HKD</v>
       </c>
-      <c r="F110" s="252">
+      <c r="F111" s="252">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="241" t="s">
-        <v>268</v>
-      </c>
-      <c r="C112" s="247">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="241" t="s">
+        <v>260</v>
+      </c>
+      <c r="C113" s="247">
         <f>Scenarios!C60</f>
         <v>9.1006872475781417</v>
       </c>
-      <c r="D112" s="242" t="str">
+      <c r="D113" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="343" t="s">
-        <v>362</v>
-      </c>
-      <c r="C114" s="343"/>
-      <c r="D114" s="343"/>
-      <c r="E114" s="343"/>
-      <c r="F114" s="343"/>
-    </row>
-    <row r="116" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A116" s="253" t="s">
-        <v>298</v>
-      </c>
-      <c r="B116" s="36"/>
-      <c r="C116" s="36"/>
-      <c r="D116" s="36"/>
-      <c r="E116" s="36"/>
-      <c r="F116" s="36"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B118" s="339" t="s">
-        <v>274</v>
-      </c>
-      <c r="C118" s="339"/>
-      <c r="D118" s="339"/>
-      <c r="E118" s="339"/>
-      <c r="F118" s="339"/>
+    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B115" s="342" t="s">
+        <v>388</v>
+      </c>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
+    </row>
+    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A117" s="253" t="s">
+        <v>375</v>
+      </c>
+      <c r="B117" s="36"/>
+      <c r="C117" s="36"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="240" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B120" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C120" s="257">
+      <c r="B119" s="343" t="s">
+        <v>386</v>
+      </c>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="341" t="s">
+        <v>387</v>
+      </c>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B121" s="240" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B122" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C122" s="257">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="C121" s="256">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C123" s="256">
         <f>C19</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="242" t="s">
-        <v>271</v>
-      </c>
-      <c r="C122" s="243">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B124" s="242" t="s">
+        <v>263</v>
+      </c>
+      <c r="C124" s="243">
         <f>Scenarios!C77</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="D122" s="242" t="str">
+      <c r="D124" s="242" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="240" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B125" s="242" t="str">
-        <f>"PV("&amp;C120&amp;" yrs of Dividends)"</f>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="240" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="242" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C125" s="246">
+      <c r="C127" s="246">
         <f>Scenarios!C81</f>
         <v>1.2217592592592592</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="242" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C120&amp;")"</f>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="242" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C126" s="246">
+      <c r="C128" s="246">
         <f>Scenarios!C82</f>
         <v>5.2666014164225361</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="82" t="s">
-        <v>270</v>
-      </c>
-      <c r="C127" s="245">
+    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B129" s="82" t="s">
+        <v>262</v>
+      </c>
+      <c r="C129" s="245">
         <f>Scenarios!C83</f>
         <v>6.4883606756817951</v>
       </c>
-      <c r="D127" s="47" t="str">
+      <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="244" t="s">
-        <v>272</v>
-      </c>
-      <c r="C128" s="94">
+    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B130" s="244" t="s">
+        <v>264</v>
+      </c>
+      <c r="C130" s="94">
         <f>Scenarios!F83</f>
         <v>0.28704717576043881</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
+    <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B72:F72"/>
-    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
     <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -4858,7 +5039,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -4908,7 +5089,7 @@
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B5" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="193">
         <v>5344</v>
@@ -4934,7 +5115,7 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" s="193">
         <v>1084</v>
@@ -4958,7 +5139,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" s="70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="194"/>
       <c r="D7" s="192"/>
@@ -4974,7 +5155,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="193"/>
       <c r="D8" s="184"/>
@@ -4990,7 +5171,7 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B9" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C9" s="193">
         <v>639</v>
@@ -5010,7 +5191,7 @@
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C10" s="193"/>
       <c r="D10" s="184"/>
@@ -5026,7 +5207,7 @@
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B11" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C11" s="193"/>
       <c r="D11" s="184"/>
@@ -5066,7 +5247,7 @@
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B13" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="193">
         <v>2340</v>
@@ -5090,7 +5271,7 @@
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B14" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="193">
         <v>519</v>
@@ -5114,7 +5295,7 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B15" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="195">
         <v>4251</v>
@@ -5138,7 +5319,7 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B16" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="193">
         <v>-151</v>
@@ -5158,13 +5339,13 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B19" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="184">
         <v>160</v>
@@ -5188,7 +5369,7 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B20" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="184">
         <v>69</v>
@@ -5208,7 +5389,7 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B21" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C21" s="184">
         <v>910</v>
@@ -5227,151 +5408,177 @@
       <c r="M21" s="184"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="24" t="str">
+      <c r="B22" s="27" t="s">
+        <v>389</v>
+      </c>
+      <c r="C22" s="184"/>
+      <c r="D22" s="184"/>
+      <c r="E22" s="184"/>
+      <c r="F22" s="184"/>
+      <c r="G22" s="184"/>
+      <c r="H22" s="184"/>
+      <c r="I22" s="184"/>
+      <c r="J22" s="184"/>
+      <c r="K22" s="184"/>
+      <c r="L22" s="184"/>
+      <c r="M22" s="184"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="27" t="s">
+        <v>391</v>
+      </c>
+      <c r="C23" s="184"/>
+      <c r="D23" s="184"/>
+      <c r="E23" s="184"/>
+      <c r="F23" s="184"/>
+      <c r="G23" s="184"/>
+      <c r="H23" s="184"/>
+      <c r="I23" s="184"/>
+      <c r="J23" s="184"/>
+      <c r="K23" s="184"/>
+      <c r="L23" s="184"/>
+      <c r="M23" s="184"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="184"/>
+      <c r="D24" s="184"/>
+      <c r="E24" s="184"/>
+      <c r="F24" s="184"/>
+      <c r="G24" s="184"/>
+      <c r="H24" s="184"/>
+      <c r="I24" s="184"/>
+      <c r="J24" s="184"/>
+      <c r="K24" s="184"/>
+      <c r="L24" s="184"/>
+      <c r="M24" s="184"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C25" s="39">
         <v>0.57999999999999996</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D25" s="39">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E25" s="39">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="39"/>
-      <c r="M22" s="39"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="16" t="s">
+      <c r="F25" s="39"/>
+      <c r="G25" s="39"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="39"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="9"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="26" t="s">
+      <c r="C27" s="9"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="186"/>
-      <c r="D25" s="184">
+      <c r="C28" s="186"/>
+      <c r="D28" s="184">
         <v>7251</v>
       </c>
-      <c r="E25" s="184"/>
-      <c r="F25" s="184"/>
-      <c r="G25" s="184"/>
-      <c r="H25" s="184"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="184"/>
-      <c r="K25" s="184"/>
-      <c r="L25" s="184"/>
-      <c r="M25" s="184"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B26" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" s="186"/>
-      <c r="D26" s="184">
-        <v>16389</v>
-      </c>
-      <c r="E26" s="184"/>
-      <c r="F26" s="184"/>
-      <c r="G26" s="184"/>
-      <c r="H26" s="184"/>
-      <c r="I26" s="184"/>
-      <c r="J26" s="184"/>
-      <c r="K26" s="184"/>
-      <c r="L26" s="184"/>
-      <c r="M26" s="184"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B27" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="185">
-        <v>14028</v>
-      </c>
-      <c r="D27" s="185">
-        <v>10902</v>
-      </c>
-      <c r="E27" s="185"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="185"/>
-      <c r="H27" s="185"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="185"/>
-      <c r="M27" s="185"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B28" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C28" s="185">
-        <v>166316</v>
-      </c>
-      <c r="D28" s="185">
-        <v>163105</v>
-      </c>
-      <c r="E28" s="185"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="185"/>
-      <c r="H28" s="185"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="185"/>
-      <c r="M28" s="185"/>
+      <c r="E28" s="184"/>
+      <c r="F28" s="184"/>
+      <c r="G28" s="184"/>
+      <c r="H28" s="184"/>
+      <c r="I28" s="184"/>
+      <c r="J28" s="184"/>
+      <c r="K28" s="184"/>
+      <c r="L28" s="184"/>
+      <c r="M28" s="184"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B29" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="C29" s="184"/>
-      <c r="D29" s="184"/>
+        <v>32</v>
+      </c>
+      <c r="C29" s="186"/>
+      <c r="D29" s="184">
+        <v>16389</v>
+      </c>
       <c r="E29" s="184"/>
       <c r="F29" s="184"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="185"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="185"/>
+      <c r="G29" s="184"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="184"/>
+      <c r="J29" s="184"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="184"/>
+      <c r="M29" s="184"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="185">
+        <v>14028</v>
+      </c>
+      <c r="D30" s="185">
+        <v>10902</v>
+      </c>
+      <c r="E30" s="185"/>
+      <c r="F30" s="185"/>
+      <c r="G30" s="185"/>
+      <c r="H30" s="185"/>
+      <c r="I30" s="185"/>
+      <c r="J30" s="185"/>
+      <c r="K30" s="185"/>
+      <c r="L30" s="185"/>
+      <c r="M30" s="185"/>
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B31" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="9"/>
+      <c r="B31" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="185">
+        <v>166316</v>
+      </c>
+      <c r="D31" s="185">
+        <v>163105</v>
+      </c>
+      <c r="E31" s="185"/>
+      <c r="F31" s="185"/>
+      <c r="G31" s="185"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="185"/>
+      <c r="J31" s="185"/>
+      <c r="K31" s="185"/>
+      <c r="L31" s="185"/>
+      <c r="M31" s="185"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B32" s="26" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="C32" s="184"/>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="184"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="184"/>
-      <c r="L32" s="184"/>
-      <c r="M32" s="184"/>
+      <c r="G32" s="185"/>
+      <c r="H32" s="185"/>
+      <c r="I32" s="185"/>
+      <c r="J32" s="185"/>
+      <c r="K32" s="185"/>
+      <c r="L32" s="185"/>
+      <c r="M32" s="185"/>
     </row>
     <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B34" s="36" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -5441,7 +5648,7 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B37" s="40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="186">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -5490,7 +5697,7 @@
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B38" s="31" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38" s="187">
         <f>IF(C36="","",C36+C37)</f>
@@ -5539,7 +5746,7 @@
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B39" s="40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" s="186">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -5588,7 +5795,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B40" s="70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C40" s="188">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -5637,7 +5844,7 @@
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B41" s="70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C41" s="188">
         <f>IF(C$4="","",C39-C40)</f>
@@ -5686,7 +5893,7 @@
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B42" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="186">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -5735,7 +5942,7 @@
     </row>
     <row r="43" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B43" s="43" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C43" s="189">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -5784,7 +5991,7 @@
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B44" s="43" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C44" s="190">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -5833,7 +6040,7 @@
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B45" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C45" s="191">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -5882,7 +6089,7 @@
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B46" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="186">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -5931,7 +6138,7 @@
     </row>
     <row r="47" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B47" s="43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47" s="189">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -5980,7 +6187,7 @@
     </row>
     <row r="48" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B48" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="186">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6029,7 +6236,7 @@
     </row>
     <row r="50" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.35">
@@ -6083,7 +6290,7 @@
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B52" s="40" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C52" s="186">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6132,12 +6339,12 @@
     </row>
     <row r="54" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B54" s="178" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B55" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C55" s="191">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6186,7 +6393,7 @@
     </row>
     <row r="56" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B56" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C56" s="191">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6235,14 +6442,14 @@
     </row>
     <row r="57" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B57" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C57" s="191">
-        <f>IF(C$4="","",C11)</f>
+        <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
         <v>0</v>
       </c>
       <c r="D57" s="191">
-        <f t="shared" ref="D57:M57" si="27">IF(D$4="","",D11)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="E57" s="191">
@@ -6284,7 +6491,7 @@
     </row>
     <row r="58" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B58" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C58" s="191">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6333,13 +6540,13 @@
     </row>
     <row r="60" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B60" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B61" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="186">
         <f t="shared" ref="C61:M61" si="29">IF(C$4="","",-C19)</f>
@@ -6388,7 +6595,7 @@
     </row>
     <row r="62" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B62" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C62" s="186">
         <f t="shared" ref="C62:M62" si="30">IF(C$4="","",-C20)</f>
@@ -6437,7 +6644,7 @@
     </row>
     <row r="63" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B63" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C63" s="186">
         <f t="shared" ref="C63:M63" si="31">IF(C$4="","",-C21)</f>
@@ -6489,7 +6696,7 @@
         <v>36</v>
       </c>
       <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C22)</f>
+        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="D64" s="75">
@@ -6535,7 +6742,7 @@
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B66" s="93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
@@ -6790,7 +6997,7 @@
     </row>
     <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B73" s="36" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
@@ -6861,10 +7068,10 @@
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B76" s="95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C25)</f>
+        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
       <c r="D76" s="74">
@@ -6895,7 +7102,7 @@
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C77" s="74">
         <f t="shared" si="39"/>
@@ -6932,7 +7139,7 @@
         <v>40</v>
       </c>
       <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C27)</f>
+        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
         <v>14028</v>
       </c>
       <c r="D78" s="58">
@@ -6981,7 +7188,7 @@
         <v>30</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C28)</f>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
         <v>166316</v>
       </c>
       <c r="D79" s="58">
@@ -7027,14 +7234,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M22 C32:M32 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:M29">
+  <conditionalFormatting sqref="C28:M32">
     <cfRule type="expression" dxfId="4" priority="1">
-      <formula>ISBLANK(C25)</formula>
+      <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M64">
@@ -7086,7 +7293,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7097,19 +7304,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D3" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G3" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H3" s="210" t="s">
         <v>35</v>
@@ -7127,7 +7334,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G4" s="19">
         <v>45665</v>
@@ -7169,7 +7376,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G6" s="19">
         <v>156</v>
@@ -7180,7 +7387,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" s="19">
         <v>5466</v>
@@ -7190,7 +7397,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7201,7 +7408,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7211,7 +7418,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7232,7 +7439,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7267,7 +7474,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="82" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C12" s="83">
         <f>SUM(C4:C11)</f>
@@ -7278,7 +7485,7 @@
         <v>13028</v>
       </c>
       <c r="F12" s="82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G12" s="83">
         <f>SUM(G4:G9)</f>
@@ -7296,19 +7503,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D14" s="210" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H14" s="210" t="s">
         <v>35</v>
@@ -7316,7 +7523,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C15" s="19">
         <v>2757</v>
@@ -7325,7 +7532,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -7345,7 +7552,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G16" s="19">
         <v>1373</v>
@@ -7356,7 +7563,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" s="19">
         <v>67668</v>
@@ -7365,7 +7572,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G17" s="19">
         <v>13024</v>
@@ -7376,7 +7583,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -7385,7 +7592,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G18" s="19">
         <v>23696</v>
@@ -7405,7 +7612,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -7425,7 +7632,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -7445,7 +7652,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -7480,7 +7687,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="82" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C24" s="83">
         <f>SUM(C15:C23)</f>
@@ -7491,7 +7698,7 @@
         <v>41841</v>
       </c>
       <c r="F24" s="82" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G24" s="83">
         <f>SUM(G15:G21)</f>
@@ -7504,16 +7711,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F26" s="211" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G26" s="212" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H26" s="213" t="s">
         <v>35</v>
@@ -7546,7 +7753,7 @@
         <v>37</v>
       </c>
       <c r="F28" s="216" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G28" s="184">
         <v>519</v>
@@ -7561,7 +7768,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="217" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -7590,14 +7797,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="82" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C31" s="83">
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
       <c r="F31" s="217" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="G31" s="218">
         <f>C31+C40</f>
@@ -7614,7 +7821,7 @@
         <v>8048</v>
       </c>
       <c r="F32" s="219" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G32" s="220">
         <f>G35+G40</f>
@@ -7640,10 +7847,10 @@
       <c r="B34" s="85"/>
       <c r="C34" s="86"/>
       <c r="F34" s="223" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G34" s="224" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H34" s="225" t="s">
         <v>35</v>
@@ -7651,10 +7858,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C35" s="209" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F35" s="226" t="s">
         <v>31</v>
@@ -7676,7 +7883,7 @@
         <v>832</v>
       </c>
       <c r="F36" s="217" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G36" s="218">
         <f>C4+C15</f>
@@ -7692,7 +7899,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="217" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G37" s="218">
         <f>C6</f>
@@ -7708,7 +7915,7 @@
         <v>1230</v>
       </c>
       <c r="F38" s="217" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G38" s="218">
         <f>C7+C17</f>
@@ -7724,7 +7931,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="217" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G39" s="218">
         <f>C7+C17+C19+C20</f>
@@ -7737,14 +7944,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="82" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C40" s="83">
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
       <c r="F40" s="226" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G40" s="220">
         <f>G12+G24</f>
@@ -7764,7 +7971,7 @@
         <v>2748</v>
       </c>
       <c r="F41" s="217" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G41" s="218">
         <f>C70</f>
@@ -7783,7 +7990,7 @@
         <v>4837</v>
       </c>
       <c r="F42" s="228" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G42" s="229">
         <f>C82</f>
@@ -7796,7 +8003,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="81" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -7807,21 +8014,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C45" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="F45" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -7853,20 +8060,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="161" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C49" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D49" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="289"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C50" s="98">
         <f>G31/Normalized_FCF!C8</f>
@@ -7880,7 +8087,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="94">
@@ -7894,19 +8101,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="161" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C53" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D53" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F53" s="289"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C54" s="94">
         <f>Normalized_FCF!C8/G35</f>
@@ -7920,7 +8127,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C55" s="94">
         <f>Normalized_FCF!C11/G40</f>
@@ -7937,19 +8144,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="161" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C57" s="268" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D57" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F57" s="289"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C58" s="101"/>
       <c r="D58" s="23">
@@ -7960,7 +8167,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C59" s="101"/>
       <c r="D59" s="94">
@@ -7974,19 +8181,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C61" s="268" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D61" s="224" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F61" s="289"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C62" s="94">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -7997,12 +8204,12 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B64" s="81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8013,21 +8220,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="16" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C65" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="F65" s="293" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8038,12 +8245,12 @@
         <v>42222.564948178719</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="108" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8053,7 +8260,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="108" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8063,7 +8270,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="108" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8073,7 +8280,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="82" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C70" s="83">
         <f>SUM(C66:C69)</f>
@@ -8086,19 +8293,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="C72" s="267" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D72" s="209" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F72" s="289"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8109,12 +8316,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8125,12 +8332,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8138,12 +8345,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8151,7 +8358,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8159,10 +8366,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="16" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C78" s="267" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D78" s="210" t="s">
         <v>35</v>
@@ -8171,7 +8378,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="108" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8185,7 +8392,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="108" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8199,7 +8406,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="108" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8213,7 +8420,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B82" s="82" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C82" s="83">
         <f>SUM(C79:C81)</f>
@@ -8227,7 +8434,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8238,15 +8445,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="D85" s="276" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8263,7 +8470,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8280,7 +8487,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B88" s="274" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" s="191">
         <f>Valuation_Model!C9*Exchange_Rate</f>
@@ -8297,7 +8504,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -8345,7 +8552,7 @@
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -8398,12 +8605,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -8421,7 +8628,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="110">
         <f>Data!C3</f>
@@ -8492,7 +8699,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C5" s="197">
         <f>C25</f>
@@ -8547,7 +8754,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="187">
         <f>C4+C5</f>
@@ -8602,7 +8809,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="197">
         <f>C35</f>
@@ -8657,7 +8864,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C8" s="198">
         <f>C6+C7</f>
@@ -8714,7 +8921,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" s="197">
         <f>BS!$G$39*BS!D58</f>
@@ -8769,7 +8976,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="197">
         <f>-C4*C78</f>
@@ -8824,7 +9031,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C11" s="199">
         <f>C63</f>
@@ -8881,7 +9088,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C12" s="197">
         <f>C50</f>
@@ -8936,7 +9143,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C13" s="187">
         <f>SUM(C8:C12)</f>
@@ -8991,7 +9198,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="197">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9046,7 +9253,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C15" s="197">
         <f>-C4*C83</f>
@@ -9103,7 +9310,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C16" s="200">
         <f>SUM(C13:C15)</f>
@@ -9160,7 +9367,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="197">
         <f>-C4*C85</f>
@@ -9168,7 +9375,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9186,14 +9393,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" s="197">
         <v>0</v>
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9211,7 +9418,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" s="187">
         <f>C16+C17</f>
@@ -9287,12 +9494,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9310,7 +9517,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="27"/>
@@ -9331,7 +9538,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="203">
         <f>-C4*C28</f>
@@ -9388,7 +9595,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10"/>
       <c r="B24" s="69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C24" s="197">
         <f>-C4*C29</f>
@@ -9445,7 +9652,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="187">
         <f>C23+C24</f>
@@ -9506,14 +9713,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E27" s="308"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="64">
         <f>AVERAGE(G28:H28)</f>
@@ -9521,7 +9728,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9581,7 +9788,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9632,7 +9839,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="10"/>
       <c r="B30" s="71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="72">
         <f>ABS(C25/$C$4)</f>
@@ -9691,21 +9898,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="10"/>
       <c r="B32" s="65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="308"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C33" s="204">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9755,7 +9962,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="204">
         <f>AVERAGE(G34:J34)</f>
@@ -9763,7 +9970,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -9814,7 +10021,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="10"/>
       <c r="B35" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="187">
         <f>C33+C34</f>
@@ -9875,7 +10082,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="10"/>
       <c r="B37" s="65" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E37" s="308"/>
     </row>
@@ -9998,7 +10205,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="10"/>
       <c r="B40" s="71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="72">
         <f>ABS(C35/$C$4)</f>
@@ -10057,21 +10264,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="10"/>
       <c r="B42" s="65" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E42" s="308"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C43" s="302">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10125,12 +10332,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10148,7 +10355,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="10"/>
       <c r="B46" s="65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E46" s="308"/>
     </row>
@@ -10210,7 +10417,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10265,7 +10472,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10322,7 +10529,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="10"/>
       <c r="B50" s="71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50" s="187">
         <f>C47+C48</f>
@@ -10381,23 +10588,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="10"/>
       <c r="B52" s="73" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E52" s="308"/>
       <c r="G52" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C53" s="89">
         <v>0.03</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10417,14 +10624,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C54" s="84">
         <f>G54</f>
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10444,7 +10651,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -10503,17 +10710,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="10"/>
       <c r="B57" s="65" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E57" s="308"/>
       <c r="G57" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C58" s="197">
         <f>BS!$C79*C66</f>
@@ -10568,7 +10775,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C59" s="197">
         <f>BS!$C68*C67</f>
@@ -10623,7 +10830,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C60" s="197">
         <f>BS!$C81*C68</f>
@@ -10678,7 +10885,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C61" s="187">
         <f>SUM(C58:C60)</f>
@@ -10733,13 +10940,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C62" s="303">
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -10789,7 +10996,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C63" s="187">
         <f>C61+C62</f>
@@ -10848,17 +11055,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="10"/>
       <c r="B65" s="99" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E65" s="308"/>
       <c r="G65" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C66" s="180">
         <f>G66</f>
@@ -10883,7 +11090,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="10"/>
       <c r="B67" s="108" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C67" s="180">
         <f>G67</f>
@@ -10908,7 +11115,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="10"/>
       <c r="B68" s="108" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C68" s="180">
         <f>G68</f>
@@ -10933,7 +11140,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C69" s="72">
         <f>C61/BS!C70</f>
@@ -10963,12 +11170,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -10986,7 +11193,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="10"/>
       <c r="B72" s="73" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C72" s="63"/>
       <c r="D72" s="27"/>
@@ -11007,7 +11214,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C73" s="79">
         <f>ABS(C5/C$4)</f>
@@ -11064,7 +11271,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C74" s="80">
         <f>ABS(C6/C$4)</f>
@@ -11121,7 +11328,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C75" s="79">
         <f>ABS(C7/C$4)</f>
@@ -11178,7 +11385,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C76" s="80">
         <f>ABS(C8/C$4)</f>
@@ -11235,7 +11442,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C77" s="79">
         <f>ABS(C9/C$4)</f>
@@ -11292,7 +11499,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C78" s="90">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -11300,7 +11507,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -11351,7 +11558,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C79" s="80">
         <f>ABS(C11/C$4)</f>
@@ -11408,7 +11615,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C80" s="79">
         <f>ABS(C12/C$4)</f>
@@ -11465,7 +11672,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="10"/>
       <c r="B81" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C81" s="80">
         <f>C13/C4</f>
@@ -11522,7 +11729,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C82" s="79">
         <f>ABS(C14/C$4)</f>
@@ -11637,7 +11844,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C84" s="80">
         <f>ABS(C16/C$4)</f>
@@ -11694,7 +11901,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C85" s="304">
         <v>0</v>
@@ -11720,7 +11927,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C86" s="79">
         <v>0</v>
@@ -11744,7 +11951,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C87" s="80">
         <f>ABS(C19/C$4)</f>
@@ -11805,7 +12012,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="10"/>
       <c r="B89" s="65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E89" s="308"/>
     </row>
@@ -11924,7 +12131,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*$C$3/Common_Shares)</f>
@@ -11979,7 +12186,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12038,7 +12245,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="10"/>
       <c r="B95" s="161" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C95" s="63"/>
       <c r="D95" s="27"/>
@@ -12059,7 +12266,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C96" s="79">
         <f>C4/G4-1</f>
@@ -12116,7 +12323,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="10"/>
       <c r="B97" s="71" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C97" s="79">
         <f>C13/G13-1</f>
@@ -12176,12 +12383,12 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12203,7 +12410,7 @@
       </c>
       <c r="E100" s="308"/>
       <c r="G100" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -12266,7 +12473,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="10"/>
       <c r="B102" s="95" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C102" s="206">
         <f>BS!C4</f>
@@ -12323,7 +12530,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="10"/>
       <c r="B103" s="95" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C103" s="206">
         <f>BS!C6+BS!C7</f>
@@ -12498,14 +12705,14 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="10"/>
       <c r="B107" s="93" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="309"/>
       <c r="F107" s="26"/>
       <c r="G107" s="100" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -12521,7 +12728,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C108" s="97">
         <f>C102/C$4</f>
@@ -12578,7 +12785,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C109" s="97">
         <f>C103/C$4</f>
@@ -12635,7 +12842,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C110" s="97">
         <f>BS!$G$38/C$4</f>
@@ -12720,7 +12927,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C113" s="23">
         <f>C81</f>
@@ -12774,7 +12981,7 @@
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B114" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C114" s="42">
         <f>C4/C101</f>
@@ -12828,7 +13035,7 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C115" s="15">
         <f>C101/C105</f>
@@ -12885,7 +13092,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="10"/>
       <c r="B116" s="71" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C116" s="105">
         <f>C8/C105</f>
@@ -12961,12 +13168,12 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A118" s="10"/>
       <c r="B118" s="54" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C118" s="54"/>
       <c r="D118" s="56"/>
       <c r="E118" s="67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F118" s="56"/>
       <c r="G118" s="37"/>
@@ -12984,7 +13191,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="10"/>
       <c r="B119" s="182" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C119" s="183"/>
       <c r="D119" s="27"/>
@@ -13063,7 +13270,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="10"/>
       <c r="B121" s="27" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13832,32 +14039,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="134" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="112" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C3" s="110">
         <f>Normalized_FCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="112" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H3" s="124"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="103" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C4" s="113">
         <f>Normalized_FCF!C19</f>
@@ -13868,17 +14075,17 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F4" s="138">
-        <f>Thesis!C75</f>
+        <f>Thesis!C76</f>
         <v>0</v>
       </c>
       <c r="H4" s="124"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="233" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" s="234">
         <f>Thesis!C70</f>
@@ -13889,7 +14096,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="153" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C6" s="238">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -13899,15 +14106,15 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="344" t="s">
-        <v>255</v>
-      </c>
-      <c r="F6" s="344"/>
+      <c r="E6" s="345" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6" s="345"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="152" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" s="232">
         <f>BS!G31</f>
@@ -13917,13 +14124,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="152" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="207">
         <f>BS!D66</f>
@@ -13933,13 +14140,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="233" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C9" s="235">
         <f>BS!H42</f>
@@ -13949,13 +14156,13 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B10" s="153" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C10" s="238">
         <f>C6-C7+C8+C9</f>
@@ -13969,7 +14176,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="236" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C11" s="237">
         <f>Exchange_Rate</f>
@@ -13983,7 +14190,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="B12" s="153" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C12" s="115">
         <f>(C10*C3)/Common_Shares*C11</f>
@@ -14000,7 +14207,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B14" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14010,13 +14217,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B15" s="123" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H15" s="124"/>
     </row>
     <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" s="165">
         <f>Scenarios!C65</f>
@@ -14026,7 +14233,7 @@
     </row>
     <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C17" s="166">
         <f>Scenarios!C64</f>
@@ -14036,7 +14243,7 @@
     </row>
     <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="157" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C18" s="144">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
@@ -14053,19 +14260,19 @@
     </row>
     <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="132" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="132" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="132" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="132" t="s">
+      <c r="F20" s="133" t="s">
         <v>112</v>
-      </c>
-      <c r="D20" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="132" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="133" t="s">
-        <v>114</v>
       </c>
       <c r="H20" s="124"/>
     </row>
@@ -14731,7 +14938,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B51" s="130" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C51" s="127">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -14754,7 +14961,7 @@
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C52" s="118"/>
       <c r="E52" s="131" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F52" s="141">
         <f>SUM(F21:F51)</f>
@@ -14768,7 +14975,7 @@
     </row>
     <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B54" s="123" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C54" s="140"/>
       <c r="D54" s="140"/>
@@ -14939,7 +15146,7 @@
     </row>
     <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="B63" s="123" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C63" s="118"/>
       <c r="D63" s="118"/>
@@ -15158,19 +15365,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B73" s="175" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="175" t="s">
+        <v>134</v>
+      </c>
+      <c r="D73" s="175" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" s="176" t="s">
+        <v>115</v>
+      </c>
+      <c r="F73" s="176" t="s">
         <v>121</v>
-      </c>
-      <c r="C73" s="175" t="s">
-        <v>136</v>
-      </c>
-      <c r="D73" s="175" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" s="176" t="s">
-        <v>117</v>
-      </c>
-      <c r="F73" s="176" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
@@ -15295,20 +15502,20 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C80" s="159" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C81" s="159" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C82" s="159" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="92" spans="3:3" x14ac:dyDescent="0.35">
@@ -15360,20 +15567,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B2" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="I2" s="284"/>
     </row>
     <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B3" s="163" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H3" s="282">
         <v>0</v>
@@ -15385,14 +15592,14 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" s="156" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4" s="124">
         <v>3</v>
       </c>
       <c r="D4" s="124"/>
       <c r="E4" s="159" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F4" s="159"/>
       <c r="H4" s="282">
@@ -15414,14 +15621,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B6" s="163" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6" s="110">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15434,7 +15641,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15444,11 +15651,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15459,7 +15666,7 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="118">
         <f>Normalized_FCF!G19</f>
@@ -15469,8 +15676,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15481,7 +15688,7 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" s="103" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9" s="207">
         <f>Normalized_FCF!C19</f>
@@ -15491,8 +15698,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15502,8 +15709,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15514,10 +15721,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>294</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>283</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15528,15 +15735,15 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" s="122" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12" s="162">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15547,14 +15754,14 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B13" s="152" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="162">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15565,18 +15772,18 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="103" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C14" s="162">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.34904529928871464</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -15585,38 +15792,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B17" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B18" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>360</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>345</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>329</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>315</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
@@ -15626,12 +15833,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15641,44 +15848,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F24" s="163"/>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B25" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C25" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C26" s="168">
         <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C27" s="164">
         <f>Valuation_Model!E76</f>
@@ -15688,55 +15895,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C28" s="169">
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E30" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F30" s="163"/>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B31" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C31" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C32" s="168">
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C33" s="164">
         <f>Valuation_Model!E77</f>
@@ -15746,55 +15953,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C34" s="169">
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E36" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F36" s="163"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C37" s="170">
         <f>C18</f>
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C38" s="168">
         <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C39" s="164">
         <f>Valuation_Model!E75</f>
@@ -15804,24 +16011,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C40" s="171">
         <f>1-C28-C34</f>
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C42" s="158">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -15834,7 +16041,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B44" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -15843,12 +16050,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B45" s="112" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B46" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C46" s="154">
         <v>15</v>
@@ -15863,39 +16070,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B48" s="163" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E48" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F48" s="163"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C49" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C50" s="168">
         <v>-0.2</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C51" s="164">
         <f>Valuation_Model!E78</f>
@@ -15905,55 +16112,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C52" s="169">
         <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="E54" s="163" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F54" s="163"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B55" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C55" s="170">
         <f>C46</f>
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C56" s="168">
         <v>0.05</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C57" s="164">
         <f>Valuation_Model!E74</f>
@@ -15963,23 +16170,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C58" s="169">
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C60" s="158">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -15990,7 +16197,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -15999,7 +16206,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16008,39 +16215,39 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B64" s="156" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C64" s="170">
         <v>10</v>
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B65" s="122" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C65" s="155">
         <v>-7.3000000000000001E-3</v>
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B66" s="103" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C66" s="164">
         <f>Valuation_Model!C18</f>
@@ -16051,20 +16258,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16074,19 +16281,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16096,14 +16303,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16112,7 +16319,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B74" s="36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -16121,12 +16328,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B75" s="112" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16136,7 +16343,7 @@
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B77" s="103" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C77" s="177">
         <f>Normalized_FCF!C90</f>
@@ -16149,21 +16356,21 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C80" s="171">
-        <f>Thesis!C121</f>
+        <f>Thesis!C123</f>
         <v>0.2</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B81" s="103" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -16175,7 +16382,7 @@
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B82" s="103" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
@@ -16185,7 +16392,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B83" s="114" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
@@ -16196,7 +16403,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="150" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
@@ -16208,12 +16415,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
@@ -16226,7 +16433,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16238,7 +16445,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16246,30 +16453,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F90" s="324" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BC1A2E-9867-4EEE-855A-6D7F0BF81681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8D7F74-6A3D-4951-87C4-C1B1AA39531B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1353,10 +1353,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>FCFE/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Latest FCFE =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2160,6 +2156,149 @@
   </si>
   <si>
     <t>CFI</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 6:  Risk Analysis</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Key Risk Factors</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Sustainable Revenue &amp; Margins</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Capital Expenditures</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Working Capital</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Accuracy of Normalized FCFE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, which is affacted by uncertainties include:</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- The extreme scenarios (“Snowball”, “Devil’s Advocate”) have low probabilities; if market conditions shift drastically, these might become more relevant than anticipated.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Appropriateness of Cost of Equity</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Reliability of Growth Scenarios</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Macroeconomic Sensitivity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Input Cost Volatility</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Intense Competition</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>External &amp; Company-Specific Risks</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normalized FCFE/Market Cap =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2839,7 +2978,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="351">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3543,23 +3682,29 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3849,7 +3994,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -3869,10 +4014,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="337" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F1" s="290" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -3901,13 +4046,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -3915,7 +4060,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.88</v>
+        <v>7.63</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -3934,7 +4079,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C8" s="285">
         <v>6</v>
@@ -3960,7 +4105,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64394.413895680002</v>
+        <v>62351.443911679999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -3970,24 +4115,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="341" t="s">
-        <v>377</v>
-      </c>
-      <c r="C12" s="341"/>
-      <c r="D12" s="341"/>
-      <c r="E12" s="341"/>
-      <c r="F12" s="341"/>
+      <c r="B12" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -3997,7 +4142,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4023,13 +4168,13 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C19" s="255">
         <v>0.2</v>
@@ -4046,7 +4191,7 @@
         <v>6.4883606756817951</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E20" s="336">
         <v>3</v>
@@ -4054,11 +4199,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11953198379323582</v>
+        <v>0.132459340913061</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4069,7 +4214,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="253" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4078,22 +4223,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="341" t="s">
-        <v>378</v>
-      </c>
-      <c r="C25" s="341"/>
-      <c r="D25" s="341"/>
-      <c r="E25" s="341"/>
-      <c r="F25" s="341"/>
+      <c r="B25" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="339" t="s">
-        <v>354</v>
-      </c>
-      <c r="C26" s="339"/>
-      <c r="D26" s="339"/>
-      <c r="E26" s="339"/>
-      <c r="F26" s="339"/>
+      <c r="B26" s="341" t="s">
+        <v>353</v>
+      </c>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4198,7 +4343,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C40" s="328">
         <f>Normalized_FCF!C48</f>
@@ -4213,7 +4358,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C41" s="328">
         <f>Normalized_FCF!C47</f>
@@ -4281,12 +4426,12 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="340" t="s">
-        <v>353</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
+        <v>352</v>
+      </c>
+      <c r="C50" s="343"/>
+      <c r="D50" s="343"/>
+      <c r="E50" s="343"/>
+      <c r="F50" s="343"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4302,26 +4447,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="341" t="s">
-        <v>358</v>
-      </c>
-      <c r="C53" s="341"/>
-      <c r="D53" s="341"/>
-      <c r="E53" s="341"/>
-      <c r="F53" s="341"/>
+      <c r="B53" s="339" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="341" t="s">
-        <v>379</v>
-      </c>
-      <c r="C54" s="341"/>
-      <c r="D54" s="341"/>
-      <c r="E54" s="341"/>
-      <c r="F54" s="341"/>
+      <c r="B54" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C56" s="191">
         <f>Normalized_FCF!G19</f>
@@ -4347,25 +4492,25 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="260" t="s">
-        <v>273</v>
+        <v>407</v>
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C121</f>
-        <v>3.9200301012977792E-2</v>
+        <v>4.0484714545513105E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="260" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>7.3604060913705582E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="253" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4378,22 +4523,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="341" t="s">
-        <v>380</v>
-      </c>
-      <c r="C63" s="341"/>
-      <c r="D63" s="341"/>
-      <c r="E63" s="341"/>
-      <c r="F63" s="341"/>
+      <c r="B63" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="339" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="339"/>
-      <c r="D64" s="339"/>
-      <c r="E64" s="339"/>
-      <c r="F64" s="339"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4402,7 +4547,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C67" s="317">
         <v>0.08</v>
@@ -4410,26 +4555,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C68" s="269">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D68" s="292" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C69" s="269">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="292" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4446,27 +4591,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="338" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="341" t="s">
+      <c r="B73" s="339" t="s">
+        <v>380</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="339" t="s">
         <v>381</v>
       </c>
-      <c r="C73" s="341"/>
-      <c r="D73" s="341"/>
-      <c r="E73" s="341"/>
-      <c r="F73" s="341"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="341" t="s">
-        <v>382</v>
-      </c>
-      <c r="C74" s="341"/>
-      <c r="D74" s="341"/>
-      <c r="E74" s="341"/>
-      <c r="F74" s="341"/>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4478,7 +4623,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C77" s="254">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4491,7 +4636,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="253" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4503,13 +4648,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="341" t="s">
-        <v>383</v>
-      </c>
-      <c r="C81" s="341"/>
-      <c r="D81" s="341"/>
-      <c r="E81" s="341"/>
-      <c r="F81" s="341"/>
+      <c r="B81" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4522,13 +4667,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="341" t="s">
-        <v>359</v>
-      </c>
-      <c r="C85" s="341"/>
-      <c r="D85" s="341"/>
-      <c r="E85" s="341"/>
-      <c r="F85" s="341"/>
+      <c r="B85" s="339" t="s">
+        <v>358</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4545,7 +4690,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C87" s="254">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4589,7 +4734,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C92" s="254">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4620,7 +4765,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" s="254">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4632,17 +4777,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="341" t="s">
-        <v>384</v>
-      </c>
-      <c r="C98" s="341"/>
-      <c r="D98" s="341"/>
-      <c r="E98" s="341"/>
-      <c r="F98" s="341"/>
+      <c r="B98" s="339" t="s">
+        <v>383</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C100" s="254">
         <f>Valuation_Model!C12</f>
@@ -4655,7 +4800,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="253" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4665,7 +4810,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="340" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C104" s="340"/>
       <c r="D104" s="340"/>
@@ -4813,17 +4958,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>388</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="B115" s="344" t="s">
+        <v>387</v>
+      </c>
+      <c r="C115" s="344"/>
+      <c r="D115" s="344"/>
+      <c r="E115" s="344"/>
+      <c r="F115" s="344"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4832,22 +4977,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="342" t="s">
+        <v>385</v>
+      </c>
+      <c r="C119" s="342"/>
+      <c r="D119" s="342"/>
+      <c r="E119" s="342"/>
+      <c r="F119" s="342"/>
+    </row>
+    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="339" t="s">
         <v>386</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="341" t="s">
-        <v>387</v>
-      </c>
-      <c r="C120" s="341"/>
-      <c r="D120" s="341"/>
-      <c r="E120" s="341"/>
-      <c r="F120" s="341"/>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -4865,7 +5010,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C123" s="256">
         <f>C19</f>
@@ -4910,7 +5055,7 @@
         <v>5.2666014164225361</v>
       </c>
     </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B129" s="82" t="s">
         <v>262</v>
       </c>
@@ -4923,7 +5068,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B130" s="244" t="s">
         <v>264</v>
       </c>
@@ -4932,8 +5077,124 @@
         <v>0.28704717576043881</v>
       </c>
     </row>
+    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A132" s="253" t="s">
+        <v>391</v>
+      </c>
+      <c r="B132" s="36"/>
+      <c r="C132" s="36"/>
+      <c r="D132" s="36"/>
+      <c r="E132" s="36"/>
+      <c r="F132" s="36"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="346" t="s">
+        <v>393</v>
+      </c>
+      <c r="C134" s="339"/>
+      <c r="D134" s="339"/>
+      <c r="E134" s="339"/>
+      <c r="F134" s="339"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="240" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="343" t="s">
+        <v>397</v>
+      </c>
+      <c r="C137" s="343"/>
+      <c r="D137" s="343"/>
+      <c r="E137" s="343"/>
+      <c r="F137" s="343"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="244" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="244" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="244" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B143" s="340" t="s">
+        <v>398</v>
+      </c>
+      <c r="C143" s="340"/>
+      <c r="D143" s="340"/>
+      <c r="E143" s="340"/>
+      <c r="F143" s="340"/>
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="345" t="s">
+        <v>399</v>
+      </c>
+      <c r="C146" s="345"/>
+      <c r="D146" s="345"/>
+      <c r="E146" s="345"/>
+      <c r="F146" s="345"/>
+    </row>
+    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="345" t="s">
+        <v>400</v>
+      </c>
+      <c r="C147" s="345"/>
+      <c r="D147" s="345"/>
+      <c r="E147" s="345"/>
+      <c r="F147" s="345"/>
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="244" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="244" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="244" t="s">
+        <v>405</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -4950,15 +5211,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5409,7 +5664,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C22" s="184"/>
       <c r="D22" s="184"/>
@@ -5425,7 +5680,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C23" s="184"/>
       <c r="D23" s="184"/>
@@ -5441,7 +5696,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C24" s="184"/>
       <c r="D24" s="184"/>
@@ -8014,13 +8269,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C45" s="267" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="209" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F45" s="293" t="s">
         <v>60</v>
@@ -8028,7 +8283,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C46" s="191">
         <f>G29</f>
@@ -8181,7 +8436,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="161" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C61" s="268" t="s">
         <v>139</v>
@@ -8204,7 +8459,7 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="289" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8226,7 +8481,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="210" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F65" s="293" t="s">
         <v>60</v>
@@ -8293,7 +8548,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="291" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C72" s="267" t="s">
         <v>97</v>
@@ -8305,7 +8560,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="108" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C73" s="191">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8316,12 +8571,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="294" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C74" s="295">
         <f>-$C$66/C73</f>
@@ -8332,12 +8587,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="289" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="82" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C75" s="299"/>
       <c r="D75" s="298">
@@ -8345,12 +8600,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="289" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="296" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C76" s="297"/>
       <c r="D76" s="333">
@@ -8358,7 +8613,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="289" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8434,7 +8689,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="81" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8445,15 +8700,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="D85" s="276" t="s">
         <v>301</v>
-      </c>
-      <c r="D85" s="276" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="273" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C86" s="191">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8470,7 +8725,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="273" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C87" s="191">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8504,7 +8759,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="82" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C89" s="190">
         <f>SUM(C86:C88)</f>
@@ -9375,7 +9630,7 @@
       </c>
       <c r="D17" s="59"/>
       <c r="E17" s="307" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="201"/>
@@ -9400,7 +9655,7 @@
       </c>
       <c r="D18" s="59"/>
       <c r="E18" s="307" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F18" s="59"/>
       <c r="G18" s="202"/>
@@ -9728,7 +9983,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -9788,7 +10043,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -9912,7 +10167,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G33" s="197">
         <f>Data!C41</f>
@@ -9970,7 +10225,7 @@
       </c>
       <c r="D34" s="59"/>
       <c r="E34" s="306" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F34" s="59"/>
       <c r="G34" s="186">
@@ -10278,7 +10533,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="305" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10417,7 +10672,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C48" s="197">
         <f>BS!D75*C53</f>
@@ -10472,7 +10727,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="329" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C49" s="330">
         <f>BS!$C$66*C53</f>
@@ -10604,7 +10859,7 @@
         <v>0.03</v>
       </c>
       <c r="E53" s="305" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10631,7 +10886,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="305" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -10946,7 +11201,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="306" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G62" s="197">
         <f>Data!C58</f>
@@ -11507,7 +11762,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="306" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12186,24 +12441,24 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.3604060913705582E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.3604060913705582E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3604060913705582E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.2335025380710655E-2</v>
+        <v>7.4705111402359109E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13274,30 +13529,30 @@
       </c>
       <c r="C121" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9200301012977792E-2</v>
+        <v>4.0484714545513105E-2</v>
       </c>
       <c r="D121" s="27"/>
       <c r="E121" s="305"/>
       <c r="F121" s="27"/>
       <c r="G121" s="79">
         <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>4.3059512471447625E-2</v>
+        <v>4.4470374610092699E-2</v>
       </c>
       <c r="H121" s="79">
         <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>6.9937116211553713E-2</v>
+        <v>7.2228633780739612E-2</v>
       </c>
       <c r="I121" s="79">
         <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>9.5062707610182304E-2</v>
+        <v>9.8177475225194835E-2</v>
       </c>
       <c r="J121" s="79">
         <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.15610499720660287</v>
+        <v>0.16121983984115734</v>
       </c>
       <c r="K121" s="79">
         <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>5.3576075800442199E-2</v>
+        <v>5.5331517340430472E-2</v>
       </c>
       <c r="L121" s="79" t="str">
         <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
@@ -14106,10 +14361,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="347" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="347"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14124,8 +14379,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="347"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14140,8 +14395,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14156,8 +14411,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15502,7 +15757,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="159" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C80" s="159" t="s">
         <v>107</v>
@@ -15574,7 +15829,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="283" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I2" s="284"/>
     </row>
@@ -15587,7 +15842,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-7.88</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15628,7 +15883,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F6" s="103"/>
       <c r="H6" s="282">
@@ -15641,7 +15896,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="103" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C7" s="118">
         <f>Normalized_FCF!G8</f>
@@ -15651,11 +15906,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="349" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15676,8 +15931,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15698,8 +15953,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15709,8 +15964,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="349"/>
+      <c r="F10" s="349"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15721,10 +15976,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="163" t="s">
-        <v>283</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>282</v>
+      </c>
+      <c r="E11" s="349"/>
+      <c r="F11" s="349"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15742,8 +15997,8 @@
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="349"/>
+      <c r="F12" s="349"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -15760,8 +16015,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="349"/>
+      <c r="F13" s="349"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -15778,8 +16033,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.34904529928871464</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="349"/>
+      <c r="F14" s="349"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -15795,7 +16050,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="163" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -15805,40 +16060,40 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>345</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="349" t="s">
+        <v>344</v>
+      </c>
+      <c r="F18" s="350"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="350"/>
+      <c r="F19" s="350"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
-        <v>315</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>314</v>
+      </c>
+      <c r="E20" s="350"/>
+      <c r="F20" s="350"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>7.88</v>
+        <v>7.63</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="350"/>
+      <c r="F21" s="350"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C22" s="164">
         <f>Valuation_Model!C12</f>
@@ -15848,8 +16103,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="350"/>
+      <c r="F22" s="350"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -15869,8 +16124,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="348"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -15880,8 +16135,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="348"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -15895,8 +16150,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="348"/>
+      <c r="F27" s="348"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -15906,8 +16161,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="348"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -15927,8 +16182,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -15938,8 +16193,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="348"/>
+      <c r="F32" s="348"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -15953,8 +16208,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="348"/>
+      <c r="F33" s="348"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -15964,8 +16219,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="348"/>
+      <c r="F34" s="348"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -15985,8 +16240,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -15996,8 +16251,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="348"/>
+      <c r="F38" s="348"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16011,8 +16266,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="348"/>
+      <c r="F39" s="348"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16023,8 +16278,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16086,8 +16341,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="348"/>
+      <c r="F49" s="348"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16097,8 +16352,8 @@
         <v>-0.2</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16112,8 +16367,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="348"/>
+      <c r="F51" s="348"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16123,12 +16378,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="348"/>
+      <c r="F52" s="348"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E54" s="163" t="s">
         <v>151</v>
@@ -16144,8 +16399,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="348"/>
+      <c r="F55" s="348"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16155,8 +16410,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="348"/>
+      <c r="F56" s="348"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16170,8 +16425,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="348"/>
+      <c r="F57" s="348"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16181,8 +16436,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16197,7 +16452,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="103" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F60" s="318">
         <f>Thesis!E20</f>
@@ -16206,7 +16461,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16215,10 +16470,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="112" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E63" s="288" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16230,7 +16485,7 @@
       </c>
       <c r="D64" s="154"/>
       <c r="E64" s="287" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16242,7 +16497,7 @@
       </c>
       <c r="D65" s="155"/>
       <c r="E65" s="287" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16258,20 +16513,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="287" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E68" s="288" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="103" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C69" s="279" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16281,19 +16536,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="103" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C70" s="279" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="287" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C71" s="279" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16303,14 +16558,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="103" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C72" s="278" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="138" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F72" s="335">
         <f>BS!D89/C60</f>
@@ -16333,7 +16588,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="281" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C76" s="280">
         <f>F60</f>
@@ -16356,12 +16611,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="112" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="152" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
@@ -16415,16 +16670,16 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="112" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="152" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>7.88</v>
+        <v>7.63</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16433,11 +16688,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="103" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11953198379323582</v>
+        <v>0.132459340913061</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16445,7 +16700,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="326" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F89" s="323"/>
       <c r="G89" s="2"/>
@@ -16453,30 +16708,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="319" t="s">
+        <v>339</v>
+      </c>
+      <c r="F90" s="324" t="s">
         <v>340</v>
-      </c>
-      <c r="F90" s="324" t="s">
-        <v>341</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="322"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="320" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F91" s="324" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="322"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="321" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F92" s="325" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="322"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8D7F74-6A3D-4951-87C4-C1B1AA39531B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD49E2E6-49EB-4870-B1A9-BFF0BC40B99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="414">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,6 +2302,18 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>CFO/Net Income</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFO/FCFE</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SINO LAND</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,7 +2350,7 @@
     <numFmt numFmtId="192" formatCode="0.0\x"/>
     <numFmt numFmtId="193" formatCode="0\x"/>
   </numFmts>
-  <fonts count="58" x14ac:knownFonts="1">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2771,6 +2783,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2978,7 +2997,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="351">
+  <cellXfs count="353">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3682,6 +3701,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4044,15 +4067,15 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>408</v>
+      <c r="C5" s="339" t="s">
+        <v>411</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4060,7 +4083,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.63</v>
+        <v>7.73</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4105,7 +4128,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>62351.443911679999</v>
+        <v>63168.63190528001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4115,13 +4138,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
+      <c r="B12" s="341" t="s">
         <v>376</v>
       </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="C12" s="341"/>
+      <c r="D12" s="341"/>
+      <c r="E12" s="341"/>
+      <c r="F12" s="341"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4168,7 +4191,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4203,7 +4226,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.132459340913061</v>
+        <v>0.12721857083761035</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4223,22 +4246,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
+      <c r="B25" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="C25" s="341"/>
+      <c r="D25" s="341"/>
+      <c r="E25" s="341"/>
+      <c r="F25" s="341"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="343" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="343"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4250,13 +4273,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="342" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="342"/>
+      <c r="D29" s="342"/>
+      <c r="E29" s="342"/>
+      <c r="F29" s="342"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4276,13 +4299,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="342" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="342"/>
+      <c r="D32" s="342"/>
+      <c r="E32" s="342"/>
+      <c r="F32" s="342"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4311,13 +4334,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="342" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="342"/>
+      <c r="D36" s="342"/>
+      <c r="E36" s="342"/>
+      <c r="F36" s="342"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4333,13 +4356,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="342" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="342"/>
+      <c r="D39" s="342"/>
+      <c r="E39" s="342"/>
+      <c r="F39" s="342"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4403,13 +4426,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="342" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="342"/>
+      <c r="D47" s="342"/>
+      <c r="E47" s="342"/>
+      <c r="F47" s="342"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4425,13 +4448,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
+      <c r="B50" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C50" s="343"/>
-      <c r="D50" s="343"/>
-      <c r="E50" s="343"/>
-      <c r="F50" s="343"/>
+      <c r="C50" s="345"/>
+      <c r="D50" s="345"/>
+      <c r="E50" s="345"/>
+      <c r="F50" s="345"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4447,22 +4470,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
+      <c r="B53" s="341" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="C53" s="341"/>
+      <c r="D53" s="341"/>
+      <c r="E53" s="341"/>
+      <c r="F53" s="341"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
+      <c r="B54" s="341" t="s">
         <v>378</v>
       </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="C54" s="341"/>
+      <c r="D54" s="341"/>
+      <c r="E54" s="341"/>
+      <c r="F54" s="341"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4495,8 +4518,8 @@
         <v>407</v>
       </c>
       <c r="C58" s="94">
-        <f>Normalized_FCF!C121</f>
-        <v>4.0484714545513105E-2</v>
+        <f>Normalized_FCF!C125</f>
+        <v>3.9960979557860932E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4505,7 +4528,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>7.6015727391874177E-2</v>
+        <v>7.5032341526520038E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4523,22 +4546,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
+      <c r="B63" s="341" t="s">
         <v>379</v>
       </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="C63" s="341"/>
+      <c r="D63" s="341"/>
+      <c r="E63" s="341"/>
+      <c r="F63" s="341"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="343" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="343"/>
+      <c r="D64" s="343"/>
+      <c r="E64" s="343"/>
+      <c r="F64" s="343"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4596,22 +4619,22 @@
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="341" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
+      <c r="C73" s="341"/>
+      <c r="D73" s="341"/>
+      <c r="E73" s="341"/>
+      <c r="F73" s="341"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
+      <c r="B74" s="341" t="s">
         <v>381</v>
       </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="341"/>
+      <c r="D74" s="341"/>
+      <c r="E74" s="341"/>
+      <c r="F74" s="341"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4648,13 +4671,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
+      <c r="B81" s="341" t="s">
         <v>382</v>
       </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="C81" s="341"/>
+      <c r="D81" s="341"/>
+      <c r="E81" s="341"/>
+      <c r="F81" s="341"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4667,13 +4690,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
+      <c r="B85" s="341" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="C85" s="341"/>
+      <c r="D85" s="341"/>
+      <c r="E85" s="341"/>
+      <c r="F85" s="341"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4777,13 +4800,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
+      <c r="B98" s="341" t="s">
         <v>383</v>
       </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
+      <c r="C98" s="341"/>
+      <c r="D98" s="341"/>
+      <c r="E98" s="341"/>
+      <c r="F98" s="341"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4809,13 +4832,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
+      <c r="B104" s="342" t="s">
         <v>384</v>
       </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
+      <c r="C104" s="342"/>
+      <c r="D104" s="342"/>
+      <c r="E104" s="342"/>
+      <c r="F104" s="342"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4958,13 +4981,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="344" t="s">
+      <c r="B115" s="346" t="s">
         <v>387</v>
       </c>
-      <c r="C115" s="344"/>
-      <c r="D115" s="344"/>
-      <c r="E115" s="344"/>
-      <c r="F115" s="344"/>
+      <c r="C115" s="346"/>
+      <c r="D115" s="346"/>
+      <c r="E115" s="346"/>
+      <c r="F115" s="346"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
@@ -4977,22 +5000,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="342" t="s">
+      <c r="B119" s="344" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="342"/>
-      <c r="D119" s="342"/>
-      <c r="E119" s="342"/>
-      <c r="F119" s="342"/>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
+      <c r="B120" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
+      <c r="C120" s="341"/>
+      <c r="D120" s="341"/>
+      <c r="E120" s="341"/>
+      <c r="F120" s="341"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5088,13 +5111,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>393</v>
       </c>
-      <c r="C134" s="339"/>
-      <c r="D134" s="339"/>
-      <c r="E134" s="339"/>
-      <c r="F134" s="339"/>
+      <c r="C134" s="341"/>
+      <c r="D134" s="341"/>
+      <c r="E134" s="341"/>
+      <c r="F134" s="341"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
@@ -5102,13 +5125,13 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="343" t="s">
+      <c r="B137" s="345" t="s">
         <v>397</v>
       </c>
-      <c r="C137" s="343"/>
-      <c r="D137" s="343"/>
-      <c r="E137" s="343"/>
-      <c r="F137" s="343"/>
+      <c r="C137" s="345"/>
+      <c r="D137" s="345"/>
+      <c r="E137" s="345"/>
+      <c r="F137" s="345"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="244" t="s">
@@ -5131,13 +5154,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="340" t="s">
+      <c r="B143" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="340"/>
-      <c r="D143" s="340"/>
-      <c r="E143" s="340"/>
-      <c r="F143" s="340"/>
+      <c r="C143" s="342"/>
+      <c r="D143" s="342"/>
+      <c r="E143" s="342"/>
+      <c r="F143" s="342"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5145,22 +5168,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="345" t="s">
+      <c r="B146" s="347" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="345"/>
-      <c r="D146" s="345"/>
-      <c r="E146" s="345"/>
-      <c r="F146" s="345"/>
+      <c r="C146" s="347"/>
+      <c r="D146" s="347"/>
+      <c r="E146" s="347"/>
+      <c r="F146" s="347"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="345" t="s">
+      <c r="B147" s="347" t="s">
         <v>400</v>
       </c>
-      <c r="C147" s="345"/>
-      <c r="D147" s="345"/>
-      <c r="E147" s="345"/>
-      <c r="F147" s="345"/>
+      <c r="C147" s="347"/>
+      <c r="D147" s="347"/>
+      <c r="E147" s="347"/>
+      <c r="F147" s="347"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5213,7 +5236,7 @@
     <mergeCell ref="B63:F63"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5225,7 +5248,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5234,7 +5257,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M79"/>
+  <dimension ref="B1:M80"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
@@ -5448,7 +5471,7 @@
       <c r="B10" s="40" t="s">
         <v>169</v>
       </c>
-      <c r="C10" s="193"/>
+      <c r="C10" s="184"/>
       <c r="D10" s="184"/>
       <c r="E10" s="184"/>
       <c r="F10" s="184"/>
@@ -5743,7 +5766,7 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="184"/>
       <c r="D28" s="184">
         <v>7251</v>
       </c>
@@ -5761,7 +5784,7 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="184"/>
       <c r="D29" s="184">
         <v>16389</v>
       </c>
@@ -6947,440 +6970,455 @@
       </c>
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C64" s="186">
+        <f>IF(C$4="","",C22+C23+C24)</f>
+        <v>0</v>
+      </c>
+      <c r="D64" s="186">
+        <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="F64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="G64" s="186">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="I64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="J64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="K64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="L64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="M64" s="186" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="C64" s="75">
-        <f t="shared" ref="C64:M64" si="32">IF(C$4="","",C25)</f>
+      <c r="C65" s="75">
+        <f t="shared" ref="C65:M65" si="33">IF(C$4="","",C25)</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="D64" s="75">
-        <f t="shared" si="32"/>
+      <c r="D65" s="75">
+        <f t="shared" si="33"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E64" s="75">
-        <f t="shared" si="32"/>
+      <c r="E65" s="75">
+        <f t="shared" si="33"/>
         <v>0.56999999999999995</v>
       </c>
-      <c r="F64" s="75">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="G64" s="75">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="I64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="J64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="K64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="L64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="M64" s="75" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B66" s="93" t="s">
+      <c r="F65" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="G65" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="H65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="I65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="J65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="K65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="L65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="M65" s="75" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B67" s="1" t="str">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
       </c>
-      <c r="C67" s="94">
-        <f t="shared" ref="C67:M67" si="33">IF(D$36="","",C36/D36-1)</f>
+      <c r="C68" s="94">
+        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C36/D36-1)</f>
         <v>-0.26226748590186011</v>
       </c>
-      <c r="D67" s="94">
-        <f t="shared" si="33"/>
+      <c r="D68" s="94">
+        <f t="shared" si="34"/>
         <v>-0.2408579989228844</v>
       </c>
-      <c r="E67" s="94">
-        <f t="shared" si="33"/>
+      <c r="E68" s="94">
+        <f t="shared" si="34"/>
         <v>-0.35945953217712834</v>
       </c>
-      <c r="F67" s="94">
-        <f t="shared" si="33"/>
+      <c r="F68" s="94">
+        <f t="shared" si="34"/>
         <v>3.150394387463904</v>
       </c>
-      <c r="G67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="H67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="I67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="J67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="K67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="L67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="M67" s="94" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B68" s="82" t="str">
+      <c r="G68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="H68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="I68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="J68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="K68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="L68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="M68" s="94" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B69" s="82" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
       </c>
-      <c r="C68" s="104">
-        <f t="shared" ref="C68:M68" si="34">IF(D$36="","",C37/D37-1)</f>
+      <c r="C69" s="104">
+        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C37/D37-1)</f>
         <v>-0.17683302526186073</v>
       </c>
-      <c r="D68" s="104">
-        <f t="shared" si="34"/>
+      <c r="D69" s="104">
+        <f t="shared" si="35"/>
         <v>-0.13241981462568664</v>
       </c>
-      <c r="E68" s="104">
-        <f t="shared" si="34"/>
+      <c r="E69" s="104">
+        <f t="shared" si="35"/>
         <v>-0.33170036321243324</v>
       </c>
-      <c r="F68" s="104">
-        <f t="shared" si="34"/>
+      <c r="F69" s="104">
+        <f t="shared" si="35"/>
         <v>3.5945410094378332</v>
       </c>
-      <c r="G68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="H68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="I68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="J68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="K68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="L68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-      <c r="M68" s="104" t="str">
-        <f t="shared" si="34"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="str">
+      <c r="G69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="H69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="I69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="J69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="K69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="L69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+      <c r="M69" s="104" t="str">
+        <f t="shared" si="35"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="str">
         <f>B58</f>
         <v>Other Non-operating Income</v>
       </c>
-      <c r="C69" s="94">
-        <f t="shared" ref="C69:M69" si="35">IF(D$36="","",C38/D38-1)</f>
+      <c r="C70" s="94">
+        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C38/D38-1)</f>
         <v>-0.36518834663202826</v>
       </c>
-      <c r="D69" s="94">
-        <f t="shared" si="35"/>
+      <c r="D70" s="94">
+        <f t="shared" si="36"/>
         <v>-0.34020444295840435</v>
       </c>
-      <c r="E69" s="94">
-        <f t="shared" si="35"/>
+      <c r="E70" s="94">
+        <f t="shared" si="36"/>
         <v>-0.38294135287844455</v>
       </c>
-      <c r="F69" s="94">
-        <f t="shared" si="35"/>
+      <c r="F70" s="94">
+        <f t="shared" si="36"/>
         <v>2.8366595127536236</v>
       </c>
-      <c r="G69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="H69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="I69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="J69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="K69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="L69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="M69" s="94" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="82" t="str">
+      <c r="G70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="H70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="I70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="J70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="K70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="L70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="M70" s="94" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B71" s="82" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
       </c>
-      <c r="C70" s="104">
-        <f t="shared" ref="C70:M70" si="36">IF(D$36="","",C39/D39-1)</f>
+      <c r="C71" s="104">
+        <f t="shared" ref="C71:M71" si="37">IF(D$36="","",C39/D39-1)</f>
         <v>-3.9858281665190454E-2</v>
       </c>
-      <c r="D70" s="104">
-        <f t="shared" si="36"/>
+      <c r="D71" s="104">
+        <f t="shared" si="37"/>
         <v>0.30146600785373745</v>
       </c>
-      <c r="E70" s="104">
-        <f t="shared" si="36"/>
+      <c r="E71" s="104">
+        <f t="shared" si="37"/>
         <v>5.3690029049281884E-2</v>
       </c>
-      <c r="F70" s="104" t="e">
-        <f t="shared" si="36"/>
+      <c r="F71" s="104" t="e">
+        <f t="shared" si="37"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="H70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="I70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="J70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="K70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="L70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="M70" s="104" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="1" t="str">
+      <c r="G71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="H71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="I71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="J71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="K71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="L71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="M71" s="104" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B72" s="1" t="str">
         <f>B48</f>
         <v>Non-controling Interests</v>
       </c>
-      <c r="C71" s="94">
-        <f>IF(D$36="","",C64/D64-1)</f>
-        <v>0</v>
-      </c>
-      <c r="D71" s="94">
-        <f t="shared" ref="D71:M71" si="37">IF(E$36="","",D64/E64-1)</f>
+      <c r="C72" s="94">
+        <f>IF(D$36="","",C65/D65-1)</f>
+        <v>0</v>
+      </c>
+      <c r="D72" s="94">
+        <f t="shared" ref="D72:M72" si="38">IF(E$36="","",D65/E65-1)</f>
         <v>1.7543859649122862E-2</v>
       </c>
-      <c r="E71" s="94" t="e">
-        <f t="shared" si="37"/>
+      <c r="E72" s="94" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="F71" s="94" t="e">
-        <f t="shared" si="37"/>
+      <c r="F72" s="94" t="e">
+        <f t="shared" si="38"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="G71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="H71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="I71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="J71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="K71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="L71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="M71" s="94" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="B73" s="36" t="s">
+      <c r="G72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="H72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="I72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="K72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="L72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="M72" s="94" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="B74" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="37"/>
-      <c r="I73" s="37"/>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
-      <c r="L73" s="37"/>
-      <c r="M73" s="37"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B74" s="16" t="s">
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
+      <c r="M74" s="37"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C74" s="9"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B75" s="26" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C75" s="78">
-        <f>IF(C$4="","",C78+C79)</f>
+      <c r="C76" s="78">
+        <f>IF(C$4="","",C79+C80)</f>
         <v>180344</v>
       </c>
-      <c r="D75" s="78">
-        <f t="shared" ref="D75:M75" si="38">IF(D$4="","",D78+D79)</f>
+      <c r="D76" s="78">
+        <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
         <v>174007</v>
       </c>
-      <c r="E75" s="78">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="F75" s="78">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="G75" s="78">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="H75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="I75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M75" s="78" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B76" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" s="74">
-        <f t="shared" ref="C76:H77" si="39">IF(C$4="","",C28)</f>
-        <v>0</v>
-      </c>
-      <c r="D76" s="74">
+      <c r="E76" s="78">
         <f t="shared" si="39"/>
-        <v>7251</v>
-      </c>
-      <c r="E76" s="74">
+        <v>0</v>
+      </c>
+      <c r="F76" s="78">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="F76" s="74">
+      <c r="G76" s="78">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="G76" s="74">
+      <c r="H76" s="78" t="str">
         <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="H76" s="74" t="str">
+        <v/>
+      </c>
+      <c r="I76" s="78" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="I76" s="96"/>
-      <c r="J76" s="96"/>
-      <c r="K76" s="96"/>
-      <c r="L76" s="96"/>
-      <c r="M76" s="96"/>
+      <c r="J76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="L76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="M76" s="78" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B77" s="95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>0</v>
       </c>
       <c r="D77" s="74">
-        <f t="shared" si="39"/>
-        <v>16389</v>
+        <f t="shared" si="40"/>
+        <v>7251</v>
       </c>
       <c r="E77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="F77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="G77" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="H77" s="74" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="I77" s="96"/>
@@ -7390,65 +7428,50 @@
       <c r="M77" s="96"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B78" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="58">
-        <f t="shared" ref="C78:M78" si="40">IF(C$4="","",C30)</f>
-        <v>14028</v>
-      </c>
-      <c r="D78" s="58">
+      <c r="B78" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>10902</v>
-      </c>
-      <c r="E78" s="58">
+        <v>0</v>
+      </c>
+      <c r="D78" s="74">
         <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="F78" s="58">
+        <v>16389</v>
+      </c>
+      <c r="E78" s="74">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="G78" s="58">
+      <c r="F78" s="74">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="H78" s="58" t="str">
+      <c r="G78" s="74">
         <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="I78" s="58" t="str">
+        <v>0</v>
+      </c>
+      <c r="H78" s="74" t="str">
         <f t="shared" si="40"/>
         <v/>
       </c>
-      <c r="J78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="K78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="L78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M78" s="58" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="I78" s="96"/>
+      <c r="J78" s="96"/>
+      <c r="K78" s="96"/>
+      <c r="L78" s="96"/>
+      <c r="M78" s="96"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B79" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C79" s="58">
-        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C31)</f>
-        <v>166316</v>
+        <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
+        <v>14028</v>
       </c>
       <c r="D79" s="58">
         <f t="shared" si="41"/>
-        <v>163105</v>
+        <v>10902</v>
       </c>
       <c r="E79" s="58">
         <f t="shared" si="41"/>
@@ -7487,9 +7510,58 @@
         <v/>
       </c>
     </row>
+    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B80" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" s="58">
+        <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
+        <v>166316</v>
+      </c>
+      <c r="D80" s="58">
+        <f t="shared" si="42"/>
+        <v>163105</v>
+      </c>
+      <c r="E80" s="58">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="F80" s="58">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="G80" s="58">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="H80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="I80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="J80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="K80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="L80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="M80" s="58" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C76:H77 C78:M79">
+  <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
     <cfRule type="expression" dxfId="5" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
@@ -7499,7 +7571,7 @@
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C36:M37 C61:M64">
+  <conditionalFormatting sqref="C36:M37 C61:M65">
     <cfRule type="expression" dxfId="3" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
@@ -8787,7 +8859,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q804"/>
+  <dimension ref="A1:Q808"/>
   <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
@@ -12283,47 +12355,47 @@
       </c>
       <c r="E90" s="308"/>
       <c r="G90" s="116">
-        <f>Data!C64</f>
+        <f>Data!C65</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="H90" s="116">
-        <f>Data!D64</f>
+        <f>Data!D65</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="I90" s="116">
-        <f>Data!E64</f>
+        <f>Data!E65</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="J90" s="116">
-        <f>Data!F64</f>
+        <f>Data!F65</f>
         <v>0</v>
       </c>
       <c r="K90" s="116">
-        <f>Data!G64</f>
+        <f>Data!G65</f>
         <v>0</v>
       </c>
       <c r="L90" s="116" t="str">
-        <f>Data!H64</f>
+        <f>Data!H65</f>
         <v/>
       </c>
       <c r="M90" s="116" t="str">
-        <f>Data!I64</f>
+        <f>Data!I65</f>
         <v/>
       </c>
       <c r="N90" s="116" t="str">
-        <f>Data!J64</f>
+        <f>Data!J65</f>
         <v/>
       </c>
       <c r="O90" s="116" t="str">
-        <f>Data!K64</f>
+        <f>Data!K65</f>
         <v/>
       </c>
       <c r="P90" s="116" t="str">
-        <f>Data!L64</f>
+        <f>Data!L65</f>
         <v/>
       </c>
       <c r="Q90" s="116" t="str">
-        <f>Data!M64</f>
+        <f>Data!M65</f>
         <v/>
       </c>
     </row>
@@ -12445,20 +12517,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.6015727391874177E-2</v>
+        <v>7.5032341526520038E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.6015727391874177E-2</v>
+        <v>7.5032341526520038E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6015727391874177E-2</v>
+        <v>7.5032341526520038E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4705111402359109E-2</v>
+        <v>7.3738680465717965E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -12738,47 +12810,47 @@
       <c r="E102" s="310"/>
       <c r="F102" s="91"/>
       <c r="G102" s="188">
-        <f>IF(G$4="","",Data!D76)</f>
+        <f>IF(G$4="","",Data!D77)</f>
         <v>7251</v>
       </c>
       <c r="H102" s="188">
-        <f>IF(H$4="","",Data!E76)</f>
+        <f>IF(H$4="","",Data!E77)</f>
         <v>0</v>
       </c>
       <c r="I102" s="188">
-        <f>IF(I$4="","",Data!F76)</f>
+        <f>IF(I$4="","",Data!F77)</f>
         <v>0</v>
       </c>
       <c r="J102" s="188">
-        <f>IF(J$4="","",Data!G76)</f>
+        <f>IF(J$4="","",Data!G77)</f>
         <v>0</v>
       </c>
       <c r="K102" s="188" t="str">
-        <f>IF(K$4="","",Data!H76)</f>
+        <f>IF(K$4="","",Data!H77)</f>
         <v/>
       </c>
       <c r="L102" s="188" t="str">
-        <f>IF(L$4="","",Data!I76)</f>
+        <f>IF(L$4="","",Data!I77)</f>
         <v/>
       </c>
       <c r="M102" s="188" t="str">
-        <f>IF(M$4="","",Data!J76)</f>
+        <f>IF(M$4="","",Data!J77)</f>
         <v/>
       </c>
       <c r="N102" s="188" t="str">
-        <f>IF(N$4="","",Data!K76)</f>
+        <f>IF(N$4="","",Data!K77)</f>
         <v/>
       </c>
       <c r="O102" s="188" t="str">
-        <f>IF(O$4="","",Data!L76)</f>
+        <f>IF(O$4="","",Data!L77)</f>
         <v/>
       </c>
       <c r="P102" s="188" t="str">
-        <f>IF(P$4="","",Data!M76)</f>
+        <f>IF(P$4="","",Data!M77)</f>
         <v/>
       </c>
       <c r="Q102" s="188" t="str">
-        <f>IF(Q$4="","",Data!N76)</f>
+        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
@@ -12795,47 +12867,47 @@
       <c r="E103" s="310"/>
       <c r="F103" s="91"/>
       <c r="G103" s="188">
-        <f>IF(G$4="","",Data!D77)</f>
+        <f>IF(G$4="","",Data!D78)</f>
         <v>16389</v>
       </c>
       <c r="H103" s="188">
-        <f>IF(H$4="","",Data!E77)</f>
+        <f>IF(H$4="","",Data!E78)</f>
         <v>0</v>
       </c>
       <c r="I103" s="188">
-        <f>IF(I$4="","",Data!F77)</f>
+        <f>IF(I$4="","",Data!F78)</f>
         <v>0</v>
       </c>
       <c r="J103" s="188">
-        <f>IF(J$4="","",Data!G77)</f>
+        <f>IF(J$4="","",Data!G78)</f>
         <v>0</v>
       </c>
       <c r="K103" s="188" t="str">
-        <f>IF(K$4="","",Data!H77)</f>
+        <f>IF(K$4="","",Data!H78)</f>
         <v/>
       </c>
       <c r="L103" s="188" t="str">
-        <f>IF(L$4="","",Data!I77)</f>
+        <f>IF(L$4="","",Data!I78)</f>
         <v/>
       </c>
       <c r="M103" s="188" t="str">
-        <f>IF(M$4="","",Data!J77)</f>
+        <f>IF(M$4="","",Data!J78)</f>
         <v/>
       </c>
       <c r="N103" s="188" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
+        <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
       <c r="O103" s="188" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
+        <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
       <c r="P103" s="188" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
+        <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
       <c r="Q103" s="188" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
+        <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
     </row>
@@ -12852,47 +12924,47 @@
       <c r="E104" s="309"/>
       <c r="F104" s="26"/>
       <c r="G104" s="186">
-        <f>Data!C78</f>
+        <f>Data!C79</f>
         <v>14028</v>
       </c>
       <c r="H104" s="186">
-        <f>Data!D78</f>
+        <f>Data!D79</f>
         <v>10902</v>
       </c>
       <c r="I104" s="186">
-        <f>Data!E78</f>
+        <f>Data!E79</f>
         <v>0</v>
       </c>
       <c r="J104" s="186">
-        <f>Data!F78</f>
+        <f>Data!F79</f>
         <v>0</v>
       </c>
       <c r="K104" s="186">
-        <f>Data!G78</f>
+        <f>Data!G79</f>
         <v>0</v>
       </c>
       <c r="L104" s="186" t="str">
-        <f>Data!H78</f>
+        <f>Data!H79</f>
         <v/>
       </c>
       <c r="M104" s="186" t="str">
-        <f>Data!I78</f>
+        <f>Data!I79</f>
         <v/>
       </c>
       <c r="N104" s="186" t="str">
-        <f>Data!J78</f>
+        <f>Data!J79</f>
         <v/>
       </c>
       <c r="O104" s="186" t="str">
-        <f>Data!K78</f>
+        <f>Data!K79</f>
         <v/>
       </c>
       <c r="P104" s="186" t="str">
-        <f>Data!L78</f>
+        <f>Data!L79</f>
         <v/>
       </c>
       <c r="Q104" s="186" t="str">
-        <f>Data!M78</f>
+        <f>Data!M79</f>
         <v/>
       </c>
     </row>
@@ -12909,47 +12981,47 @@
       <c r="E105" s="309"/>
       <c r="F105" s="26"/>
       <c r="G105" s="186">
-        <f>Data!C79</f>
+        <f>Data!C80</f>
         <v>166316</v>
       </c>
       <c r="H105" s="186">
-        <f>Data!D79</f>
+        <f>Data!D80</f>
         <v>163105</v>
       </c>
       <c r="I105" s="186">
-        <f>Data!E79</f>
+        <f>Data!E80</f>
         <v>0</v>
       </c>
       <c r="J105" s="186">
-        <f>Data!F79</f>
+        <f>Data!F80</f>
         <v>0</v>
       </c>
       <c r="K105" s="186">
-        <f>Data!G79</f>
+        <f>Data!G80</f>
         <v>0</v>
       </c>
       <c r="L105" s="186" t="str">
-        <f>Data!H79</f>
+        <f>Data!H80</f>
         <v/>
       </c>
       <c r="M105" s="186" t="str">
-        <f>Data!I79</f>
+        <f>Data!I80</f>
         <v/>
       </c>
       <c r="N105" s="186" t="str">
-        <f>Data!J79</f>
+        <f>Data!J80</f>
         <v/>
       </c>
       <c r="O105" s="186" t="str">
-        <f>Data!K79</f>
+        <f>Data!K80</f>
         <v/>
       </c>
       <c r="P105" s="186" t="str">
-        <f>Data!L79</f>
+        <f>Data!L80</f>
         <v/>
       </c>
       <c r="Q105" s="186" t="str">
-        <f>Data!M79</f>
+        <f>Data!M80</f>
         <v/>
       </c>
     </row>
@@ -13127,462 +13199,573 @@
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="10"/>
-      <c r="B112" s="93" t="s">
-        <v>38</v>
-      </c>
-      <c r="C112" s="55"/>
-      <c r="D112" s="55"/>
-      <c r="E112" s="311"/>
-      <c r="F112" s="55"/>
-      <c r="G112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G114*(1/#REF!)=G116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H114*(1/#REF!)=H116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I114*(1/#REF!)=I116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J114*(1/#REF!)=J116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K114*(1/#REF!)=K116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L114*(1/#REF!)=L116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M114*(1/#REF!)=M116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N114*(1/#REF!)=N116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O114*(1/#REF!)=O116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P114*(1/#REF!)=P116,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q112" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q114*(1/#REF!)=Q116,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="B112" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="E112" s="308"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C113" s="173"/>
+      <c r="E113" s="308"/>
+      <c r="G113" s="340">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>0</v>
+      </c>
+      <c r="H113" s="340">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>0</v>
+      </c>
+      <c r="I113" s="340">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>0</v>
+      </c>
+      <c r="J113" s="340">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0</v>
+      </c>
+      <c r="K113" s="340" t="e">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L113" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v/>
+      </c>
+      <c r="M113" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v/>
+      </c>
+      <c r="N113" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O113" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P113" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q113" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="10"/>
+      <c r="B114" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="173"/>
+      <c r="E114" s="308"/>
+      <c r="G114" s="340">
+        <f>IF(G$4="","",Data!C$22/G19)</f>
+        <v>0</v>
+      </c>
+      <c r="H114" s="340">
+        <f>IF(H$4="","",Data!D$22/H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I114" s="340">
+        <f>IF(I$4="","",Data!E$22/I19)</f>
+        <v>0</v>
+      </c>
+      <c r="J114" s="340">
+        <f>IF(J$4="","",Data!F$22/J19)</f>
+        <v>0</v>
+      </c>
+      <c r="K114" s="340">
+        <f>IF(K$4="","",Data!G$22/K19)</f>
+        <v>0</v>
+      </c>
+      <c r="L114" s="340" t="str">
+        <f>IF(L$4="","",Data!H$22/L19)</f>
+        <v/>
+      </c>
+      <c r="M114" s="340" t="str">
+        <f>IF(M$4="","",Data!I$22/M19)</f>
+        <v/>
+      </c>
+      <c r="N114" s="340" t="str">
+        <f>IF(N$4="","",Data!J$22/N19)</f>
+        <v/>
+      </c>
+      <c r="O114" s="340" t="str">
+        <f>IF(O$4="","",Data!K$22/O19)</f>
+        <v/>
+      </c>
+      <c r="P114" s="340" t="str">
+        <f>IF(P$4="","",Data!L$22/P19)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="340" t="str">
+        <f>IF(Q$4="","",Data!M$22/Q19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="10"/>
+      <c r="E115" s="308"/>
+    </row>
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="10"/>
+      <c r="B116" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="C116" s="55"/>
+      <c r="D116" s="55"/>
+      <c r="E116" s="311"/>
+      <c r="F116" s="55"/>
+      <c r="G116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q116" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="10"/>
+      <c r="B117" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C113" s="23">
+      <c r="C117" s="23">
         <f>C81</f>
         <v>0.38237459335905039</v>
       </c>
-      <c r="E113" s="308"/>
-      <c r="G113" s="23">
-        <f t="shared" ref="G113:Q113" si="45">G81</f>
+      <c r="E117" s="308"/>
+      <c r="G117" s="23">
+        <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.37556098895979384</v>
       </c>
-      <c r="H113" s="23">
+      <c r="H117" s="23">
         <f t="shared" si="45"/>
         <v>0.45411955525604425</v>
       </c>
-      <c r="I113" s="23">
+      <c r="I117" s="23">
         <f t="shared" si="45"/>
         <v>0.47733839702364145</v>
       </c>
-      <c r="J113" s="23">
+      <c r="J117" s="23">
         <f t="shared" si="45"/>
         <v>0.5149947971331873</v>
       </c>
-      <c r="K113" s="23">
+      <c r="K117" s="23">
         <f t="shared" si="45"/>
         <v>0.5860370307457109</v>
       </c>
-      <c r="L113" s="23" t="str">
+      <c r="L117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="M113" s="23" t="str">
+      <c r="M117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="N113" s="23" t="str">
+      <c r="N117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="O113" s="23" t="str">
+      <c r="O117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="P113" s="23" t="str">
+      <c r="P117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="Q113" s="23" t="str">
+      <c r="Q117" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B114" s="7" t="s">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C114" s="42">
+      <c r="C118" s="42">
         <f>C4/C101</f>
         <v>4.8426484563194767E-2</v>
       </c>
-      <c r="E114" s="308"/>
-      <c r="G114" s="42">
-        <f t="shared" ref="G114:Q114" si="46">IF(G4="","",G4/G101)</f>
+      <c r="E118" s="308"/>
+      <c r="G118" s="42">
+        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>4.8601561460320276E-2</v>
       </c>
-      <c r="H114" s="42">
+      <c r="H118" s="42">
         <f t="shared" si="46"/>
         <v>6.8278862344618316E-2</v>
       </c>
-      <c r="I114" s="42" t="e">
+      <c r="I118" s="42" t="e">
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J114" s="42" t="e">
+      <c r="J118" s="42" t="e">
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K114" s="42" t="e">
+      <c r="K118" s="42" t="e">
         <f t="shared" si="46"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L114" s="42" t="str">
+      <c r="L118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="M114" s="42" t="str">
+      <c r="M118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="N114" s="42" t="str">
+      <c r="N118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="O114" s="42" t="str">
+      <c r="O118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="P114" s="42" t="str">
+      <c r="P118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="Q114" s="42" t="str">
+      <c r="Q118" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C115" s="15">
+      <c r="C119" s="15">
         <f>C101/C105</f>
         <v>1.0831144117242246</v>
       </c>
-      <c r="D115" s="11"/>
-      <c r="E115" s="312"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="15">
-        <f t="shared" ref="G115:Q115" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D119" s="11"/>
+      <c r="E119" s="312"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="15">
+        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
         <v>1.0843454628538445</v>
       </c>
-      <c r="H115" s="15">
+      <c r="H119" s="15">
         <f t="shared" si="47"/>
         <v>1.0668403788970295</v>
       </c>
-      <c r="I115" s="15" t="e">
+      <c r="I119" s="15" t="e">
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J115" s="15" t="e">
+      <c r="J119" s="15" t="e">
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K115" s="15" t="e">
+      <c r="K119" s="15" t="e">
         <f t="shared" si="47"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L115" s="15" t="str">
+      <c r="L119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="M115" s="15" t="str">
+      <c r="M119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="N115" s="15" t="str">
+      <c r="N119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="O115" s="15" t="str">
+      <c r="O119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="P115" s="15" t="str">
+      <c r="P119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="Q115" s="15" t="str">
+      <c r="Q119" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="10"/>
-      <c r="B116" s="71" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="10"/>
+      <c r="B120" s="71" t="s">
         <v>224</v>
       </c>
-      <c r="C116" s="105">
+      <c r="C120" s="105">
         <f>C8/C105</f>
         <v>1.5509944282629921E-2</v>
       </c>
-      <c r="D116" s="106"/>
-      <c r="E116" s="311"/>
-      <c r="F116" s="106"/>
-      <c r="G116" s="105">
-        <f t="shared" ref="G116:Q116" si="48">IF(G$4="","",G8/G105)</f>
+      <c r="D120" s="106"/>
+      <c r="E120" s="311"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="105">
+        <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
         <v>1.4051564491690517E-2</v>
       </c>
-      <c r="H116" s="105">
+      <c r="H120" s="105">
         <f t="shared" si="48"/>
         <v>2.6118144753379726E-2</v>
       </c>
-      <c r="I116" s="105" t="e">
+      <c r="I120" s="105" t="e">
         <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J116" s="105" t="e">
+      <c r="J120" s="105" t="e">
         <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K116" s="105" t="e">
+      <c r="K120" s="105" t="e">
         <f t="shared" si="48"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="L116" s="105" t="str">
+      <c r="L120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="M116" s="105" t="str">
+      <c r="M120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="N116" s="105" t="str">
+      <c r="N120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="O116" s="105" t="str">
+      <c r="O120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="P116" s="105" t="str">
+      <c r="P120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="Q116" s="105" t="str">
+      <c r="Q120" s="105" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="10"/>
-      <c r="B117" s="27"/>
-      <c r="C117" s="63"/>
-      <c r="D117" s="27"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="27"/>
-      <c r="G117" s="12"/>
-      <c r="H117" s="12"/>
-      <c r="I117" s="12"/>
-      <c r="J117" s="12"/>
-      <c r="K117" s="12"/>
-      <c r="L117" s="12"/>
-      <c r="M117" s="12"/>
-      <c r="N117" s="12"/>
-      <c r="O117" s="12"/>
-      <c r="P117" s="12"/>
-      <c r="Q117" s="12"/>
-    </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A118" s="10"/>
-      <c r="B118" s="54" t="s">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
+      <c r="B121" s="27"/>
+      <c r="C121" s="63"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="68"/>
+      <c r="F121" s="27"/>
+      <c r="G121" s="12"/>
+      <c r="H121" s="12"/>
+      <c r="I121" s="12"/>
+      <c r="J121" s="12"/>
+      <c r="K121" s="12"/>
+      <c r="L121" s="12"/>
+      <c r="M121" s="12"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="12"/>
+    </row>
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A122" s="10"/>
+      <c r="B122" s="54" t="s">
         <v>225</v>
       </c>
-      <c r="C118" s="54"/>
-      <c r="D118" s="56"/>
-      <c r="E118" s="67" t="s">
+      <c r="C122" s="54"/>
+      <c r="D122" s="56"/>
+      <c r="E122" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="F118" s="56"/>
-      <c r="G118" s="37"/>
-      <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
-      <c r="J118" s="37"/>
-      <c r="K118" s="37"/>
-      <c r="L118" s="37"/>
-      <c r="M118" s="37"/>
-      <c r="N118" s="37"/>
-      <c r="O118" s="37"/>
-      <c r="P118" s="37"/>
-      <c r="Q118" s="37"/>
-    </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="10"/>
-      <c r="B119" s="182" t="s">
+      <c r="F122" s="56"/>
+      <c r="G122" s="37"/>
+      <c r="H122" s="37"/>
+      <c r="I122" s="37"/>
+      <c r="J122" s="37"/>
+      <c r="K122" s="37"/>
+      <c r="L122" s="37"/>
+      <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+    </row>
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="10"/>
+      <c r="B123" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="C119" s="183"/>
-      <c r="D119" s="27"/>
-      <c r="E119" s="305"/>
-      <c r="F119" s="27"/>
-      <c r="G119" s="12"/>
-      <c r="H119" s="12"/>
-      <c r="I119" s="12"/>
-      <c r="J119" s="12"/>
-      <c r="K119" s="12"/>
-      <c r="L119" s="12"/>
-      <c r="M119" s="12"/>
-      <c r="N119" s="12"/>
-      <c r="O119" s="12"/>
-      <c r="P119" s="12"/>
-      <c r="Q119" s="12"/>
-    </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="10"/>
-      <c r="B120" s="27" t="str">
+      <c r="C123" s="183"/>
+      <c r="D123" s="27"/>
+      <c r="E123" s="305"/>
+      <c r="F123" s="27"/>
+      <c r="G123" s="12"/>
+      <c r="H123" s="12"/>
+      <c r="I123" s="12"/>
+      <c r="J123" s="12"/>
+      <c r="K123" s="12"/>
+      <c r="L123" s="12"/>
+      <c r="M123" s="12"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="12"/>
+    </row>
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="10"/>
+      <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
         <v>FCFE per share (HKD)</v>
       </c>
-      <c r="C120" s="181">
+      <c r="C124" s="181">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
         <v>0.308898371982265</v>
       </c>
-      <c r="D120" s="27"/>
-      <c r="E120" s="305"/>
-      <c r="F120" s="27"/>
-      <c r="G120" s="181">
-        <f t="shared" ref="G120:Q120" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+      <c r="D124" s="27"/>
+      <c r="E124" s="305"/>
+      <c r="F124" s="27"/>
+      <c r="G124" s="181">
+        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
         <v>0.33930895827500729</v>
       </c>
-      <c r="H120" s="181">
+      <c r="H124" s="181">
         <f t="shared" si="49"/>
         <v>0.55110447574704324</v>
       </c>
-      <c r="I120" s="181">
+      <c r="I124" s="181">
         <f t="shared" si="49"/>
         <v>0.7490941359682366</v>
       </c>
-      <c r="J120" s="181">
+      <c r="J124" s="181">
         <f t="shared" si="49"/>
         <v>1.2301073779880305</v>
       </c>
-      <c r="K120" s="181">
+      <c r="K124" s="181">
         <f t="shared" si="49"/>
         <v>0.42217947730748451</v>
       </c>
-      <c r="L120" s="181" t="str">
+      <c r="L124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="M120" s="181" t="str">
+      <c r="M124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="N120" s="181" t="str">
+      <c r="N124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="O120" s="181" t="str">
+      <c r="O124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="P120" s="181" t="str">
+      <c r="P124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
-      <c r="Q120" s="181" t="str">
+      <c r="Q124" s="181" t="str">
         <f t="shared" si="49"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27" t="s">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="10"/>
+      <c r="B125" s="27" t="s">
         <v>272</v>
       </c>
-      <c r="C121" s="79">
+      <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.0484714545513105E-2</v>
-      </c>
-      <c r="D121" s="27"/>
-      <c r="E121" s="305"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="79">
-        <f t="shared" ref="G121" si="50">IF(G$4="","",G120/Market_Price)</f>
-        <v>4.4470374610092699E-2</v>
-      </c>
-      <c r="H121" s="79">
-        <f t="shared" ref="H121" si="51">IF(H$4="","",H120/Market_Price)</f>
-        <v>7.2228633780739612E-2</v>
-      </c>
-      <c r="I121" s="79">
-        <f t="shared" ref="I121" si="52">IF(I$4="","",I120/Market_Price)</f>
-        <v>9.8177475225194835E-2</v>
-      </c>
-      <c r="J121" s="79">
-        <f t="shared" ref="J121" si="53">IF(J$4="","",J120/Market_Price)</f>
-        <v>0.16121983984115734</v>
-      </c>
-      <c r="K121" s="79">
-        <f t="shared" ref="K121" si="54">IF(K$4="","",K120/Market_Price)</f>
-        <v>5.5331517340430472E-2</v>
-      </c>
-      <c r="L121" s="79" t="str">
-        <f t="shared" ref="L121" si="55">IF(L$4="","",L120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="M121" s="79" t="str">
-        <f t="shared" ref="M121" si="56">IF(M$4="","",M120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="N121" s="79" t="str">
-        <f t="shared" ref="N121" si="57">IF(N$4="","",N120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O121" s="79" t="str">
-        <f t="shared" ref="O121" si="58">IF(O$4="","",O120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P121" s="79" t="str">
-        <f t="shared" ref="P121" si="59">IF(P$4="","",P120/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q121" s="79" t="str">
-        <f t="shared" ref="Q121" si="60">IF(Q$4="","",Q120/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+        <v>3.9960979557860932E-2</v>
+      </c>
+      <c r="D125" s="27"/>
+      <c r="E125" s="305"/>
+      <c r="F125" s="27"/>
+      <c r="G125" s="79">
+        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+        <v>4.3895078690169113E-2</v>
+      </c>
+      <c r="H125" s="79">
+        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+        <v>7.1294240070768844E-2</v>
+      </c>
+      <c r="I125" s="79">
+        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+        <v>9.6907391457727879E-2</v>
+      </c>
+      <c r="J125" s="79">
+        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+        <v>0.15913420155084482</v>
+      </c>
+      <c r="K125" s="79">
+        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+        <v>5.4615715046246377E-2</v>
+      </c>
+      <c r="L125" s="79" t="str">
+        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="M125" s="79" t="str">
+        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="N125" s="79" t="str">
+        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O125" s="79" t="str">
+        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P125" s="79" t="str">
+        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q125" s="79" t="str">
+        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -14262,6 +14445,10 @@
     <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14361,10 +14548,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="347" t="s">
+      <c r="E6" s="349" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="347"/>
+      <c r="F6" s="349"/>
       <c r="H6" s="124"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14379,8 +14566,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347"/>
-      <c r="F7" s="347"/>
+      <c r="E7" s="349"/>
+      <c r="F7" s="349"/>
       <c r="H7" s="124"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14395,8 +14582,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="349"/>
+      <c r="F8" s="349"/>
       <c r="H8" s="124"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14411,8 +14598,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="349"/>
+      <c r="F9" s="349"/>
       <c r="H9" s="124"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -15842,7 +16029,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-7.63</v>
+        <v>-7.73</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -15906,11 +16093,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="349" t="str">
+      <c r="E7" s="351" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="349"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="282">
         <v>4</v>
       </c>
@@ -15931,8 +16118,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="349"/>
-      <c r="F8" s="349"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="282">
         <v>5</v>
       </c>
@@ -15953,8 +16140,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="349"/>
-      <c r="F9" s="349"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="282">
         <v>6</v>
       </c>
@@ -15964,8 +16151,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="349"/>
-      <c r="F10" s="349"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
       <c r="H10" s="282">
         <v>7</v>
       </c>
@@ -15978,8 +16165,8 @@
       <c r="B11" s="163" t="s">
         <v>282</v>
       </c>
-      <c r="E11" s="349"/>
-      <c r="F11" s="349"/>
+      <c r="E11" s="351"/>
+      <c r="F11" s="351"/>
       <c r="H11" s="282">
         <v>8</v>
       </c>
@@ -15997,8 +16184,8 @@
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="162"/>
-      <c r="E12" s="349"/>
-      <c r="F12" s="349"/>
+      <c r="E12" s="351"/>
+      <c r="F12" s="351"/>
       <c r="H12" s="282">
         <v>9</v>
       </c>
@@ -16015,8 +16202,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="349"/>
-      <c r="F13" s="349"/>
+      <c r="E13" s="351"/>
+      <c r="F13" s="351"/>
       <c r="H13" s="282">
         <v>10</v>
       </c>
@@ -16033,8 +16220,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.34904529928871464</v>
       </c>
-      <c r="E14" s="349"/>
-      <c r="F14" s="349"/>
+      <c r="E14" s="351"/>
+      <c r="F14" s="351"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16060,21 +16247,21 @@
       <c r="C18" s="154">
         <v>10</v>
       </c>
-      <c r="E18" s="349" t="s">
+      <c r="E18" s="351" t="s">
         <v>344</v>
       </c>
-      <c r="F18" s="350"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="350"/>
-      <c r="F19" s="350"/>
+      <c r="E19" s="352"/>
+      <c r="F19" s="352"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="163" t="s">
         <v>314</v>
       </c>
-      <c r="E20" s="350"/>
-      <c r="F20" s="350"/>
+      <c r="E20" s="352"/>
+      <c r="F20" s="352"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="103" t="s">
@@ -16082,14 +16269,14 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>7.63</v>
+        <v>7.73</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="350"/>
-      <c r="F21" s="350"/>
+      <c r="E21" s="352"/>
+      <c r="F21" s="352"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="103" t="s">
@@ -16103,8 +16290,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="350"/>
-      <c r="F22" s="350"/>
+      <c r="E22" s="352"/>
+      <c r="F22" s="352"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="163" t="s">
@@ -16124,8 +16311,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="167"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="348"/>
+      <c r="E25" s="350"/>
+      <c r="F25" s="350"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="122" t="s">
@@ -16135,8 +16322,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="168"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="348"/>
+      <c r="E26" s="350"/>
+      <c r="F26" s="350"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="103" t="s">
@@ -16150,8 +16337,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="348"/>
-      <c r="F27" s="348"/>
+      <c r="E27" s="350"/>
+      <c r="F27" s="350"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="103" t="s">
@@ -16161,8 +16348,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="169"/>
-      <c r="E28" s="348"/>
-      <c r="F28" s="348"/>
+      <c r="E28" s="350"/>
+      <c r="F28" s="350"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="163" t="s">
@@ -16182,8 +16369,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="167"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="E31" s="350"/>
+      <c r="F31" s="350"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="122" t="s">
@@ -16193,8 +16380,8 @@
         <v>-0.05</v>
       </c>
       <c r="D32" s="168"/>
-      <c r="E32" s="348"/>
-      <c r="F32" s="348"/>
+      <c r="E32" s="350"/>
+      <c r="F32" s="350"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="103" t="s">
@@ -16208,8 +16395,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="348"/>
-      <c r="F33" s="348"/>
+      <c r="E33" s="350"/>
+      <c r="F33" s="350"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="103" t="s">
@@ -16219,8 +16406,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="169"/>
-      <c r="E34" s="348"/>
-      <c r="F34" s="348"/>
+      <c r="E34" s="350"/>
+      <c r="F34" s="350"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="163" t="s">
@@ -16240,8 +16427,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="167"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="122" t="s">
@@ -16251,8 +16438,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="168"/>
-      <c r="E38" s="348"/>
-      <c r="F38" s="348"/>
+      <c r="E38" s="350"/>
+      <c r="F38" s="350"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="103" t="s">
@@ -16266,8 +16453,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="348"/>
-      <c r="F39" s="348"/>
+      <c r="E39" s="350"/>
+      <c r="F39" s="350"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="103" t="s">
@@ -16278,8 +16465,8 @@
         <v>0.24999999999999994</v>
       </c>
       <c r="D40" s="169"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="103" t="s">
@@ -16341,8 +16528,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="167"/>
-      <c r="E49" s="348"/>
-      <c r="F49" s="348"/>
+      <c r="E49" s="350"/>
+      <c r="F49" s="350"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="122" t="s">
@@ -16352,8 +16539,8 @@
         <v>-0.2</v>
       </c>
       <c r="D50" s="168"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="103" t="s">
@@ -16367,8 +16554,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="348"/>
-      <c r="F51" s="348"/>
+      <c r="E51" s="350"/>
+      <c r="F51" s="350"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="103" t="s">
@@ -16378,8 +16565,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="169"/>
-      <c r="E52" s="348"/>
-      <c r="F52" s="348"/>
+      <c r="E52" s="350"/>
+      <c r="F52" s="350"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="163" t="s">
@@ -16399,8 +16586,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="167"/>
-      <c r="E55" s="348"/>
-      <c r="F55" s="348"/>
+      <c r="E55" s="350"/>
+      <c r="F55" s="350"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="122" t="s">
@@ -16410,8 +16597,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="168"/>
-      <c r="E56" s="348"/>
-      <c r="F56" s="348"/>
+      <c r="E56" s="350"/>
+      <c r="F56" s="350"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="103" t="s">
@@ -16425,8 +16612,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="348"/>
-      <c r="F57" s="348"/>
+      <c r="E57" s="350"/>
+      <c r="F57" s="350"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="103" t="s">
@@ -16436,8 +16623,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="169"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="103" t="s">
@@ -16679,7 +16866,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>7.63</v>
+        <v>7.73</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16692,7 +16879,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.132459340913061</v>
+        <v>0.12721857083761035</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD49E2E6-49EB-4870-B1A9-BFF0BC40B99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B712278A-95AA-465A-82FB-42AFE9574E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="415">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2311,6 +2311,10 @@
   </si>
   <si>
     <t>Net Change in Cash</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net Income/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -4072,10 +4076,10 @@
         <v>328</v>
       </c>
       <c r="C5" s="339" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4191,7 +4195,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -5760,13 +5764,13 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="100"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="184"/>
+      <c r="C28" s="186"/>
       <c r="D28" s="184">
         <v>7251</v>
       </c>
@@ -5784,7 +5788,7 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="184"/>
+      <c r="C29" s="186"/>
       <c r="D29" s="184">
         <v>16389</v>
       </c>
@@ -5802,7 +5806,7 @@
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="185">
+      <c r="C30" s="189">
         <v>14028</v>
       </c>
       <c r="D30" s="185">
@@ -5822,7 +5826,7 @@
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="185">
+      <c r="C31" s="189">
         <v>166316</v>
       </c>
       <c r="D31" s="185">
@@ -5842,7 +5846,7 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="184"/>
+      <c r="C32" s="186"/>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -7576,7 +7580,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13766,7 +13770,56 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B126" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C126" s="173"/>
+      <c r="G126" s="23">
+        <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>6.7296059322200966E-2</v>
+      </c>
+      <c r="H126" s="23">
+        <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>9.3084175209254688E-2</v>
+      </c>
+      <c r="I126" s="23">
+        <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>9.0795009738379368E-2</v>
+      </c>
+      <c r="J126" s="23">
+        <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0.15270295871634554</v>
+      </c>
+      <c r="K126" s="23">
+        <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v>0</v>
+      </c>
+      <c r="L126" s="23" t="str">
+        <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="M126" s="23" t="str">
+        <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="N126" s="23" t="str">
+        <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="O126" s="23" t="str">
+        <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="P126" s="23" t="str">
+        <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+      <c r="Q126" s="23" t="str">
+        <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
+        <v/>
+      </c>
+    </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B712278A-95AA-465A-82FB-42AFE9574E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867CF741-E259-4E46-B988-01DD38F7DD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="416">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2328,6 +2328,9 @@
   <si>
     <t>RES_01</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
   </si>
 </sst>
 </file>
@@ -3709,29 +3712,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4087,7 +4090,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.73</v>
+        <v>7.69</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4109,7 +4112,7 @@
         <v>318</v>
       </c>
       <c r="C8" s="285">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
@@ -4120,7 +4123,7 @@
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45716</v>
+        <v>45900</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -4132,7 +4135,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>63168.63190528001</v>
+        <v>62841.756707840002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4142,13 +4145,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="341" t="s">
+      <c r="B12" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C12" s="341"/>
-      <c r="D12" s="341"/>
-      <c r="E12" s="341"/>
-      <c r="F12" s="341"/>
+      <c r="C12" s="343"/>
+      <c r="D12" s="343"/>
+      <c r="E12" s="343"/>
+      <c r="F12" s="343"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4204,7 +4207,7 @@
         <v>280</v>
       </c>
       <c r="C19" s="255">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="5"/>
     </row>
@@ -4215,7 +4218,7 @@
       </c>
       <c r="C20" s="258">
         <f>C129</f>
-        <v>6.4883606756817951</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4230,7 +4233,7 @@
       </c>
       <c r="C21" s="286">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12721857083761035</v>
+        <v>0.12930348429833716</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4250,22 +4253,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="341" t="s">
+      <c r="B25" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C25" s="341"/>
-      <c r="D25" s="341"/>
-      <c r="E25" s="341"/>
-      <c r="F25" s="341"/>
+      <c r="C25" s="343"/>
+      <c r="D25" s="343"/>
+      <c r="E25" s="343"/>
+      <c r="F25" s="343"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="343" t="s">
+      <c r="B26" s="346" t="s">
         <v>353</v>
       </c>
-      <c r="C26" s="343"/>
-      <c r="D26" s="343"/>
-      <c r="E26" s="343"/>
-      <c r="F26" s="343"/>
+      <c r="C26" s="346"/>
+      <c r="D26" s="346"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="240" t="s">
@@ -4277,13 +4280,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="342" t="s">
+      <c r="B29" s="344" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="342"/>
-      <c r="D29" s="342"/>
-      <c r="E29" s="342"/>
-      <c r="F29" s="342"/>
+      <c r="C29" s="344"/>
+      <c r="D29" s="344"/>
+      <c r="E29" s="344"/>
+      <c r="F29" s="344"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4303,13 +4306,13 @@
       <c r="C31" s="78"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="342" t="s">
+      <c r="B32" s="344" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="342"/>
-      <c r="D32" s="342"/>
-      <c r="E32" s="342"/>
-      <c r="F32" s="342"/>
+      <c r="C32" s="344"/>
+      <c r="D32" s="344"/>
+      <c r="E32" s="344"/>
+      <c r="F32" s="344"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4338,13 +4341,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="342" t="s">
+      <c r="B36" s="344" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="342"/>
-      <c r="D36" s="342"/>
-      <c r="E36" s="342"/>
-      <c r="F36" s="342"/>
+      <c r="C36" s="344"/>
+      <c r="D36" s="344"/>
+      <c r="E36" s="344"/>
+      <c r="F36" s="344"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4360,13 +4363,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="342" t="s">
+      <c r="B39" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="342"/>
-      <c r="D39" s="342"/>
-      <c r="E39" s="342"/>
-      <c r="F39" s="342"/>
+      <c r="C39" s="344"/>
+      <c r="D39" s="344"/>
+      <c r="E39" s="344"/>
+      <c r="F39" s="344"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4430,13 +4433,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="342" t="s">
+      <c r="B47" s="344" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="342"/>
-      <c r="D47" s="342"/>
-      <c r="E47" s="342"/>
-      <c r="F47" s="342"/>
+      <c r="C47" s="344"/>
+      <c r="D47" s="344"/>
+      <c r="E47" s="344"/>
+      <c r="F47" s="344"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4452,7 +4455,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="342" t="s">
+      <c r="B50" s="344" t="s">
         <v>352</v>
       </c>
       <c r="C50" s="345"/>
@@ -4474,22 +4477,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="341" t="s">
+      <c r="B53" s="343" t="s">
         <v>357</v>
       </c>
-      <c r="C53" s="341"/>
-      <c r="D53" s="341"/>
-      <c r="E53" s="341"/>
-      <c r="F53" s="341"/>
+      <c r="C53" s="343"/>
+      <c r="D53" s="343"/>
+      <c r="E53" s="343"/>
+      <c r="F53" s="343"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="341" t="s">
+      <c r="B54" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C54" s="341"/>
-      <c r="D54" s="341"/>
-      <c r="E54" s="341"/>
-      <c r="F54" s="341"/>
+      <c r="C54" s="343"/>
+      <c r="D54" s="343"/>
+      <c r="E54" s="343"/>
+      <c r="F54" s="343"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4523,7 +4526,7 @@
       </c>
       <c r="C58" s="94">
         <f>Normalized_FCF!C125</f>
-        <v>3.9960979557860932E-2</v>
+        <v>4.0168839009397266E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4532,7 +4535,7 @@
       </c>
       <c r="C59" s="94">
         <f>Normalized_FCF!C93</f>
-        <v>7.5032341526520038E-2</v>
+        <v>7.5422626788036407E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4550,22 +4553,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="341" t="s">
+      <c r="B63" s="343" t="s">
         <v>379</v>
       </c>
-      <c r="C63" s="341"/>
-      <c r="D63" s="341"/>
-      <c r="E63" s="341"/>
-      <c r="F63" s="341"/>
+      <c r="C63" s="343"/>
+      <c r="D63" s="343"/>
+      <c r="E63" s="343"/>
+      <c r="F63" s="343"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="343" t="s">
+      <c r="B64" s="346" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="343"/>
-      <c r="D64" s="343"/>
-      <c r="E64" s="343"/>
-      <c r="F64" s="343"/>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="240" t="s">
@@ -4623,22 +4626,22 @@
       <c r="C72" s="125"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="341" t="s">
+      <c r="B73" s="343" t="s">
         <v>380</v>
       </c>
-      <c r="C73" s="341"/>
-      <c r="D73" s="341"/>
-      <c r="E73" s="341"/>
-      <c r="F73" s="341"/>
+      <c r="C73" s="343"/>
+      <c r="D73" s="343"/>
+      <c r="E73" s="343"/>
+      <c r="F73" s="343"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="341" t="s">
+      <c r="B74" s="343" t="s">
         <v>381</v>
       </c>
-      <c r="C74" s="341"/>
-      <c r="D74" s="341"/>
-      <c r="E74" s="341"/>
-      <c r="F74" s="341"/>
+      <c r="C74" s="343"/>
+      <c r="D74" s="343"/>
+      <c r="E74" s="343"/>
+      <c r="F74" s="343"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4675,13 +4678,13 @@
       <c r="A80" s="239"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="341" t="s">
+      <c r="B81" s="343" t="s">
         <v>382</v>
       </c>
-      <c r="C81" s="341"/>
-      <c r="D81" s="341"/>
-      <c r="E81" s="341"/>
-      <c r="F81" s="341"/>
+      <c r="C81" s="343"/>
+      <c r="D81" s="343"/>
+      <c r="E81" s="343"/>
+      <c r="F81" s="343"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4694,13 +4697,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="341" t="s">
+      <c r="B85" s="343" t="s">
         <v>358</v>
       </c>
-      <c r="C85" s="341"/>
-      <c r="D85" s="341"/>
-      <c r="E85" s="341"/>
-      <c r="F85" s="341"/>
+      <c r="C85" s="343"/>
+      <c r="D85" s="343"/>
+      <c r="E85" s="343"/>
+      <c r="F85" s="343"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4804,13 +4807,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="341" t="s">
+      <c r="B98" s="343" t="s">
         <v>383</v>
       </c>
-      <c r="C98" s="341"/>
-      <c r="D98" s="341"/>
-      <c r="E98" s="341"/>
-      <c r="F98" s="341"/>
+      <c r="C98" s="343"/>
+      <c r="D98" s="343"/>
+      <c r="E98" s="343"/>
+      <c r="F98" s="343"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4836,13 +4839,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="342" t="s">
+      <c r="B104" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C104" s="342"/>
-      <c r="D104" s="342"/>
-      <c r="E104" s="342"/>
-      <c r="F104" s="342"/>
+      <c r="C104" s="344"/>
+      <c r="D104" s="344"/>
+      <c r="E104" s="344"/>
+      <c r="F104" s="344"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="266" t="s">
@@ -4985,13 +4988,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="346" t="s">
+      <c r="B115" s="347" t="s">
         <v>387</v>
       </c>
-      <c r="C115" s="346"/>
-      <c r="D115" s="346"/>
-      <c r="E115" s="346"/>
-      <c r="F115" s="346"/>
+      <c r="C115" s="347"/>
+      <c r="D115" s="347"/>
+      <c r="E115" s="347"/>
+      <c r="F115" s="347"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="253" t="s">
@@ -5004,22 +5007,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+      <c r="B119" s="348" t="s">
         <v>385</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
+      <c r="C119" s="348"/>
+      <c r="D119" s="348"/>
+      <c r="E119" s="348"/>
+      <c r="F119" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="341" t="s">
+      <c r="B120" s="343" t="s">
         <v>386</v>
       </c>
-      <c r="C120" s="341"/>
-      <c r="D120" s="341"/>
-      <c r="E120" s="341"/>
-      <c r="F120" s="341"/>
+      <c r="C120" s="343"/>
+      <c r="D120" s="343"/>
+      <c r="E120" s="343"/>
+      <c r="F120" s="343"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="240" t="s">
@@ -5041,7 +5044,7 @@
       </c>
       <c r="C123" s="256">
         <f>C19</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.35">
@@ -5069,7 +5072,7 @@
       </c>
       <c r="C127" s="246">
         <f>Scenarios!C81</f>
-        <v>1.2217592592592592</v>
+        <v>1.1321599999999998</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.35">
@@ -5079,7 +5082,7 @@
       </c>
       <c r="C128" s="246">
         <f>Scenarios!C82</f>
-        <v>5.2666014164225361</v>
+        <v>4.6595518707600085</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5088,7 +5091,7 @@
       </c>
       <c r="C129" s="245">
         <f>Scenarios!C83</f>
-        <v>6.4883606756817951</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5101,7 +5104,7 @@
       </c>
       <c r="C130" s="94">
         <f>Scenarios!F83</f>
-        <v>0.28704717576043881</v>
+        <v>0.36359620837412165</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5115,13 +5118,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="348" t="s">
+      <c r="B134" s="342" t="s">
         <v>393</v>
       </c>
-      <c r="C134" s="341"/>
-      <c r="D134" s="341"/>
-      <c r="E134" s="341"/>
-      <c r="F134" s="341"/>
+      <c r="C134" s="343"/>
+      <c r="D134" s="343"/>
+      <c r="E134" s="343"/>
+      <c r="F134" s="343"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="240" t="s">
@@ -5158,13 +5161,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="342" t="s">
+      <c r="B143" s="344" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="342"/>
-      <c r="D143" s="342"/>
-      <c r="E143" s="342"/>
-      <c r="F143" s="342"/>
+      <c r="C143" s="344"/>
+      <c r="D143" s="344"/>
+      <c r="E143" s="344"/>
+      <c r="F143" s="344"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5172,22 +5175,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="347" t="s">
+      <c r="B146" s="341" t="s">
         <v>399</v>
       </c>
-      <c r="C146" s="347"/>
-      <c r="D146" s="347"/>
-      <c r="E146" s="347"/>
-      <c r="F146" s="347"/>
+      <c r="C146" s="341"/>
+      <c r="D146" s="341"/>
+      <c r="E146" s="341"/>
+      <c r="F146" s="341"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="347" t="s">
+      <c r="B147" s="341" t="s">
         <v>400</v>
       </c>
-      <c r="C147" s="347"/>
-      <c r="D147" s="347"/>
-      <c r="E147" s="347"/>
-      <c r="F147" s="347"/>
+      <c r="C147" s="341"/>
+      <c r="D147" s="341"/>
+      <c r="E147" s="341"/>
+      <c r="F147" s="341"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5211,17 +5214,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5238,6 +5230,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5764,13 +5767,18 @@
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="100"/>
+      <c r="C27" s="100" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="186"/>
+      <c r="C28" s="186">
+        <f>BS!C4</f>
+        <v>8029</v>
+      </c>
       <c r="D28" s="184">
         <v>7251</v>
       </c>
@@ -5788,7 +5796,10 @@
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="186"/>
+      <c r="C29" s="186">
+        <f>BS!C6</f>
+        <v>9844</v>
+      </c>
       <c r="D29" s="184">
         <v>16389</v>
       </c>
@@ -5807,7 +5818,8 @@
         <v>40</v>
       </c>
       <c r="C30" s="189">
-        <v>14028</v>
+        <f>BS!C33+BS!C42</f>
+        <v>13889</v>
       </c>
       <c r="D30" s="185">
         <v>10902</v>
@@ -5827,7 +5839,8 @@
         <v>30</v>
       </c>
       <c r="C31" s="189">
-        <v>166316</v>
+        <f>BS!G27</f>
+        <v>167107</v>
       </c>
       <c r="D31" s="185">
         <v>163105</v>
@@ -5846,7 +5859,10 @@
       <c r="B32" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="186"/>
+      <c r="C32" s="186">
+        <f>BS!G28</f>
+        <v>519</v>
+      </c>
       <c r="D32" s="184"/>
       <c r="E32" s="184"/>
       <c r="F32" s="184"/>
@@ -7354,7 +7370,7 @@
       </c>
       <c r="C76" s="78">
         <f>IF(C$4="","",C79+C80)</f>
-        <v>180344</v>
+        <v>180996</v>
       </c>
       <c r="D76" s="78">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
@@ -7403,7 +7419,7 @@
       </c>
       <c r="C77" s="74">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
-        <v>0</v>
+        <v>8029</v>
       </c>
       <c r="D77" s="74">
         <f t="shared" si="40"/>
@@ -7437,7 +7453,7 @@
       </c>
       <c r="C78" s="74">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>9844</v>
       </c>
       <c r="D78" s="74">
         <f t="shared" si="40"/>
@@ -7471,7 +7487,7 @@
       </c>
       <c r="C79" s="58">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
-        <v>14028</v>
+        <v>13889</v>
       </c>
       <c r="D79" s="58">
         <f t="shared" si="41"/>
@@ -7520,7 +7536,7 @@
       </c>
       <c r="C80" s="58">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
-        <v>166316</v>
+        <v>167107</v>
       </c>
       <c r="D80" s="58">
         <f t="shared" si="42"/>
@@ -12521,20 +12537,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.5032341526520038E-2</v>
+        <v>7.5422626788036407E-2</v>
       </c>
       <c r="E93" s="308"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.5032341526520038E-2</v>
+        <v>7.5422626788036407E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.5032341526520038E-2</v>
+        <v>7.5422626788036407E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3738680465717965E-2</v>
+        <v>7.412223667100129E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -12758,7 +12774,7 @@
       <c r="F101" s="26"/>
       <c r="G101" s="186">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>180344</v>
+        <v>180996</v>
       </c>
       <c r="H101" s="186">
         <f t="shared" si="42"/>
@@ -12929,7 +12945,7 @@
       <c r="F104" s="26"/>
       <c r="G104" s="186">
         <f>Data!C79</f>
-        <v>14028</v>
+        <v>13889</v>
       </c>
       <c r="H104" s="186">
         <f>Data!D79</f>
@@ -12986,7 +13002,7 @@
       <c r="F105" s="26"/>
       <c r="G105" s="186">
         <f>Data!C80</f>
-        <v>166316</v>
+        <v>167107</v>
       </c>
       <c r="H105" s="186">
         <f>Data!D80</f>
@@ -13436,7 +13452,7 @@
       <c r="E118" s="308"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
-        <v>4.8601561460320276E-2</v>
+        <v>4.8426484563194767E-2</v>
       </c>
       <c r="H118" s="42">
         <f t="shared" si="46"/>
@@ -13492,7 +13508,7 @@
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.0843454628538445</v>
+        <v>1.0831144117242246</v>
       </c>
       <c r="H119" s="15">
         <f t="shared" si="47"/>
@@ -13549,7 +13565,7 @@
       <c r="F120" s="106"/>
       <c r="G120" s="105">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
-        <v>1.4051564491690517E-2</v>
+        <v>1.3985051493952976E-2</v>
       </c>
       <c r="H120" s="105">
         <f t="shared" si="48"/>
@@ -13720,30 +13736,30 @@
       </c>
       <c r="C125" s="79">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9960979557860932E-2</v>
+        <v>4.0168839009397266E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="305"/>
       <c r="F125" s="27"/>
       <c r="G125" s="79">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.3895078690169113E-2</v>
+        <v>4.4123401596229815E-2</v>
       </c>
       <c r="H125" s="79">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.1294240070768844E-2</v>
+        <v>7.1665081371527078E-2</v>
       </c>
       <c r="I125" s="79">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.6907391457727879E-2</v>
+        <v>9.7411461114205011E-2</v>
       </c>
       <c r="J125" s="79">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15913420155084482</v>
+        <v>0.15996194772276079</v>
       </c>
       <c r="K125" s="79">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4615715046246377E-2</v>
+        <v>5.4899801990570152E-2</v>
       </c>
       <c r="L125" s="79" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13777,19 +13793,19 @@
       <c r="C126" s="173"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7296059322200966E-2</v>
+        <v>6.7646103844032968E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3084175209254688E-2</v>
+        <v>9.356835817523261E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0795009738379368E-2</v>
+        <v>9.1267285471738957E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15270295871634554</v>
+        <v>0.15349725238977258</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16082,7 +16098,7 @@
       </c>
       <c r="I3" s="270">
         <f>-Market_Price</f>
-        <v>-7.73</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16322,7 +16338,7 @@
       </c>
       <c r="C21" s="164">
         <f>Market_Price</f>
-        <v>7.73</v>
+        <v>7.69</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16860,7 +16876,7 @@
       </c>
       <c r="C80" s="171">
         <f>Thesis!C123</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.35">
@@ -16869,7 +16885,7 @@
       </c>
       <c r="C81" s="120">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.2217592592592592</v>
+        <v>1.1321599999999998</v>
       </c>
       <c r="D81" s="120"/>
       <c r="E81" s="103"/>
@@ -16881,7 +16897,7 @@
       </c>
       <c r="C82" s="120">
         <f>C60/(1+C80)^C76</f>
-        <v>5.2666014164225361</v>
+        <v>4.6595518707600085</v>
       </c>
       <c r="D82" s="120"/>
     </row>
@@ -16891,7 +16907,7 @@
       </c>
       <c r="C83" s="115">
         <f>C81+C82</f>
-        <v>6.4883606756817951</v>
+        <v>5.7917118707600084</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16902,7 +16918,7 @@
       </c>
       <c r="F83" s="335">
         <f>(1-C83/C60)</f>
-        <v>0.28704717576043881</v>
+        <v>0.36359620837412165</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16919,7 +16935,7 @@
       </c>
       <c r="C86" s="272">
         <f>Market_Price</f>
-        <v>7.73</v>
+        <v>7.69</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16932,7 +16948,7 @@
       </c>
       <c r="C87" s="271">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12721857083761035</v>
+        <v>0.12930348429833716</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C2701DA-A150-4913-80B2-9383D80FAD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDB56DD-ABEB-417B-8CDB-9053AB66AB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -1557,10 +1557,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Always use 10yrs to identify the HGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Use Excel Goal Seek to find the HGR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2331,6 +2327,10 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F1" s="284" t="s">
         <v>291</v>
@@ -4061,13 +4061,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>411</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>412</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.47</v>
+        <v>7.63</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>61043.943121919998</v>
+        <v>62351.443911679999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="338" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C12" s="338"/>
       <c r="D12" s="338"/>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4183,7 +4183,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4214,11 +4214,11 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14104674835105913</v>
+        <v>0.132459340913061</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="338" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C25" s="338"/>
       <c r="D25" s="338"/>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="341" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C26" s="341"/>
       <c r="D26" s="341"/>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4373,7 +4373,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4441,7 +4441,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B50" s="339" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C50" s="340"/>
       <c r="D50" s="340"/>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="338" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C53" s="338"/>
       <c r="D53" s="338"/>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="338" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C54" s="338"/>
       <c r="D54" s="338"/>
@@ -4507,11 +4507,11 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.1351857025738292E-2</v>
+        <v>4.0484714545513105E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.7643908969210168E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4539,7 +4539,7 @@
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
       <c r="B63" s="338" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="338"/>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4606,13 +4606,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="338" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C73" s="338"/>
       <c r="D73" s="338"/>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="338" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C74" s="338"/>
       <c r="D74" s="338"/>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B81" s="338" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C81" s="338"/>
       <c r="D81" s="338"/>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="338" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C85" s="338"/>
       <c r="D85" s="338"/>
@@ -4793,7 +4793,7 @@
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B98" s="338" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C98" s="338"/>
       <c r="D98" s="338"/>
@@ -4815,7 +4815,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B104" s="339" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C104" s="339"/>
       <c r="D104" s="339"/>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B115" s="342" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C115" s="342"/>
       <c r="D115" s="342"/>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4993,7 +4993,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B119" s="343" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C119" s="343"/>
       <c r="D119" s="343"/>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B120" s="338" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C120" s="338"/>
       <c r="D120" s="338"/>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A132" s="247" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B134" s="337" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C134" s="338"/>
       <c r="D134" s="338"/>
@@ -5113,12 +5113,12 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B137" s="340" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C137" s="340"/>
       <c r="D137" s="340"/>
@@ -5127,27 +5127,27 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B138" s="238" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B139" s="238" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B140" s="238" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B142" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B143" s="339" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C143" s="339"/>
       <c r="D143" s="339"/>
@@ -5156,12 +5156,12 @@
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B146" s="336" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C146" s="336"/>
       <c r="D146" s="336"/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B147" s="336" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C147" s="336"/>
       <c r="D147" s="336"/>
@@ -5179,22 +5179,22 @@
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B150" s="238" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B151" s="238" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B152" s="238" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5679,7 +5679,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5695,7 +5695,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5711,7 +5711,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5753,7 +5753,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -6976,7 +6976,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8623,7 +8623,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8635,7 +8635,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8646,12 +8646,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8662,12 +8662,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8675,12 +8675,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8688,7 +8688,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9730,7 +9730,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10118,7 +10118,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10242,7 +10242,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10747,7 +10747,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10802,7 +10802,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10934,7 +10934,7 @@
         <v>0.03</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10961,7 +10961,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11276,7 +11276,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11837,7 +11837,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12520,20 +12520,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.7643908969210168E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.7643908969210168E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.7643908969210168E-2</v>
+        <v>7.6015727391874177E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6305220883534128E-2</v>
+        <v>7.4705111402359109E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13210,7 +13210,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13262,7 +13262,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13719,30 +13719,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.1351857025738292E-2</v>
+        <v>4.0484714545513105E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.5422885980590001E-2</v>
+        <v>4.4470374610092699E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.3775699564530561E-2</v>
+        <v>7.2228633780739612E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1002803394870464</v>
+        <v>9.8177475225194835E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16467300910147664</v>
+        <v>0.16121983984115734</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.6516663628846657E-2</v>
+        <v>5.5331517340430472E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13771,24 +13771,24 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9638358575718012E-2</v>
+        <v>6.8178052235991285E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6324052793512568E-2</v>
+        <v>9.4304151293255409E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3955210880545204E-2</v>
+        <v>9.1984983653692343E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15801792113485288</v>
+        <v>0.15470430810974456</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-7.47</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16289,7 +16289,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16300,7 +16300,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="346" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="347"/>
     </row>
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>7.47</v>
+        <v>7.63</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16622,7 +16622,7 @@
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16700,7 +16700,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16720,11 +16720,12 @@
         <v>135</v>
       </c>
       <c r="C64" s="167">
+        <f>C18</f>
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16736,7 +16737,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16752,15 +16753,15 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
@@ -16804,7 +16805,7 @@
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16918,7 +16919,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>7.47</v>
+        <v>7.63</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16931,7 +16932,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14104674835105913</v>
+        <v>0.132459340913061</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
@@ -16939,7 +16940,7 @@
     </row>
     <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E89" s="320" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F89" s="317"/>
       <c r="G89" s="2"/>
@@ -16947,30 +16948,30 @@
     </row>
     <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E90" s="313" t="s">
+        <v>338</v>
+      </c>
+      <c r="F90" s="318" t="s">
         <v>339</v>
-      </c>
-      <c r="F90" s="318" t="s">
-        <v>340</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="316"/>
     </row>
     <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E91" s="314" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F91" s="318" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="316"/>
     </row>
     <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E92" s="315" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F92" s="319" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G92" s="2"/>
       <c r="H92" s="316"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDB56DD-ABEB-417B-8CDB-9053AB66AB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC5077B-56AD-45CF-8B35-499826CAD55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2314,6 +2314,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SINO LAND</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2327,10 +2331,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,10 +4064,10 @@
         <v>327</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.63</v>
+        <v>7.6</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>62351.443911679999</v>
+        <v>62106.2875136</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4183,7 +4183,7 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.132459340913061</v>
+        <v>0.13405026456260738</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.0484714545513105E-2</v>
+        <v>4.0644522629245394E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.6015727391874177E-2</v>
+        <v>7.6315789473684212E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5753,7 +5753,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -10755,11 +10755,11 @@
       </c>
       <c r="E48" s="302"/>
       <c r="G48" s="328">
-        <f>IF(G$4="","",($C$48/$C$49)*G49)</f>
+        <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>267.79206823259295</v>
       </c>
       <c r="H48" s="328">
-        <f t="shared" ref="H48:Q48" si="19">IF(H$4="","",($C$48/$C$49)*H49)</f>
+        <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>159.16980399706225</v>
       </c>
       <c r="I48" s="328">
@@ -11053,7 +11053,7 @@
         <v>169</v>
       </c>
       <c r="C58" s="191">
-        <f>BS!$C79*C66</f>
+        <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="302"/>
@@ -11163,7 +11163,7 @@
         <v>160</v>
       </c>
       <c r="C60" s="191">
-        <f>BS!$C81*C68</f>
+        <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="302"/>
@@ -11453,7 +11453,7 @@
       </c>
       <c r="E68" s="302"/>
       <c r="G68" s="23">
-        <f>IFERROR(G60/BS!$C$81,0)</f>
+        <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
       </c>
       <c r="H68" s="176"/>
@@ -12520,20 +12520,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.6015727391874177E-2</v>
+        <v>7.6315789473684212E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.6015727391874177E-2</v>
+        <v>7.6315789473684212E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6015727391874177E-2</v>
+        <v>7.6315789473684212E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4705111402359109E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13719,30 +13719,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.0484714545513105E-2</v>
+        <v>4.0644522629245394E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.4470374610092699E-2</v>
+        <v>4.4645915562500964E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.2228633780739612E-2</v>
+        <v>7.2513746808821486E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.8177475225194835E-2</v>
+        <v>9.8565017890557452E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16121983984115734</v>
+        <v>0.16185623394579349</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5331517340430472E-2</v>
+        <v>5.5549931224669016E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13776,19 +13776,19 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8178052235991285E-2</v>
+        <v>6.8447176126396517E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4304151293255409E-2</v>
+        <v>9.467640452204458E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1984983653692343E-2</v>
+        <v>9.2348082273377971E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15470430810974456</v>
+        <v>0.15531498301017777</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-7.63</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>7.63</v>
+        <v>7.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16919,7 +16919,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>7.63</v>
+        <v>7.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.132459340913061</v>
+        <v>0.13405026456260738</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC5077B-56AD-45CF-8B35-499826CAD55D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A44D681-9A7C-44AD-83F9-E33FC5D3DA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.6</v>
+        <v>7.81</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>62106.2875136</v>
+        <v>63822.382300159996</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13405026456260738</v>
+        <v>0.12309347362957457</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.0644522629245394E-2</v>
+        <v>3.9551648141135085E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.6315789473684212E-2</v>
+        <v>7.4263764404609467E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,17 +5199,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5226,6 +5215,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12520,20 +12520,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.6315789473684212E-2</v>
+        <v>7.4263764404609467E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.6315789473684212E-2</v>
+        <v>7.4263764404609467E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.6315789473684212E-2</v>
+        <v>7.4263764404609467E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4999999999999997E-2</v>
+        <v>7.298335467349551E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13719,30 +13719,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.0644522629245394E-2</v>
+        <v>3.9551648141135085E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.4645915562500964E-2</v>
+        <v>4.3445449202945879E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.2513746808821486E-2</v>
+        <v>7.0563953360696957E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.8565017890557452E-2</v>
+        <v>9.5914742121413141E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16185623394579349</v>
+        <v>0.15750414570909482</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.5549931224669016E-2</v>
+        <v>5.4056271102110698E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13776,19 +13776,19 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8447176126396517E-2</v>
+        <v>6.6606727088426826E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.467640452204458E-2</v>
+        <v>9.2130688139249531E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2348082273377971E-2</v>
+        <v>8.9864971226334522E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15531498301017777</v>
+        <v>0.15113877988186314</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-7.6</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>7.6</v>
+        <v>7.81</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>7.6</v>
+        <v>7.81</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13405026456260738</v>
+        <v>0.12309347362957457</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A44D681-9A7C-44AD-83F9-E33FC5D3DA2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBD631D-3DA5-4730-B866-85FA01F00504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4075,7 +4075,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>7.81</v>
+        <v>7.85</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>63822.382300159996</v>
+        <v>64149.257497599996</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12309347362957457</v>
+        <v>0.12105292184429062</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.9551648141135085E-2</v>
+        <v>3.9350111080543315E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.4263764404609467E-2</v>
+        <v>7.3885350318471335E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,6 +5199,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5215,17 +5226,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12520,20 +12520,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.4263764404609467E-2</v>
+        <v>7.3885350318471335E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.4263764404609467E-2</v>
+        <v>7.3885350318471335E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.4263764404609467E-2</v>
+        <v>7.3885350318471335E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.298335467349551E-2</v>
+        <v>7.2611464968152864E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13719,30 +13719,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9551648141135085E-2</v>
+        <v>3.9350111080543315E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.3445449202945879E-2</v>
+        <v>4.3224071117835328E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.0563953360696957E-2</v>
+        <v>7.0204391814909964E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.5914742121413141E-2</v>
+        <v>9.5426004581940976E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15750414570909482</v>
+        <v>0.15670157681376184</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.4056271102110698E-2</v>
+        <v>5.3780825134711406E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13776,19 +13776,19 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6606727088426826E-2</v>
+        <v>6.6267329752944401E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2130688139249531E-2</v>
+        <v>9.1661232403508139E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9864971226334522E-2</v>
+        <v>8.9407060544926448E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15113877988186314</v>
+        <v>0.15036864597163707</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-7.81</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16321,7 +16321,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>7.81</v>
+        <v>7.85</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>7.81</v>
+        <v>7.85</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12309347362957457</v>
+        <v>0.12105292184429062</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BBD631D-3DA5-4730-B866-85FA01F00504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8B2460-D251-47D8-B4D8-743BCB41F48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3697,29 +3697,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4130,13 +4130,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>5.7917118707600084</v>
+        <v>5.8235187175367322</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12105292184429062</v>
+        <v>0.12328963999428066</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4238,22 +4238,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4265,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4291,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,13 +4348,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4418,13 +4418,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,7 +4440,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4462,22 +4462,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4538,22 +4538,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4611,22 +4611,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4663,13 +4663,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4792,13 +4792,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4824,13 +4824,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
-        <v>0.22499999999999992</v>
+        <v>0.17999999999999994</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C110" s="243">
         <f>Valuation_Model!C77</f>
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D110" s="244">
         <f>Valuation_Model!D77</f>
@@ -4930,11 +4930,11 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>8.69 HKD</v>
+        <v>8.97 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
-        <v>0.18</v>
+        <v>0.22499999999999998</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.35">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="C111" s="243">
         <f>Valuation_Model!C78</f>
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D111" s="244">
         <f>Valuation_Model!D78</f>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>7.34 HKD</v>
+        <v>7.97 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>9.1006872475781417</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4973,13 +4973,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4992,22 +4992,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>4.6595518707600085</v>
+        <v>4.6913587175367324</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>5.7917118707600084</v>
+        <v>5.8235187175367322</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="C130" s="92">
         <f>Scenarios!F83</f>
-        <v>0.36359620837412165</v>
+        <v>0.3644396510901724</v>
       </c>
     </row>
     <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -5103,13 +5103,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5146,13 +5146,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5160,22 +5160,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5199,17 +5199,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5226,6 +5215,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>9.0981264288878361</v>
+        <v>9.1600300006768141</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -14776,11 +14776,11 @@
       </c>
       <c r="C21" s="124">
         <f>C4*(1+D21)</f>
-        <v>2505.8531612846018</v>
+        <v>2520.4094479092696</v>
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2298.947854389543</v>
+        <v>2312.3022457883208</v>
       </c>
       <c r="H21" s="121"/>
     </row>
@@ -14798,11 +14798,11 @@
       </c>
       <c r="C22" s="124">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2487.5604332072244</v>
+        <v>2516.5444236350409</v>
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2093.7298486720174</v>
+        <v>2118.1250935401404</v>
       </c>
       <c r="H22" s="121"/>
     </row>
@@ -14820,11 +14820,11 @@
       </c>
       <c r="C23" s="124">
         <f t="shared" si="2"/>
-        <v>2469.4012420448116</v>
+        <v>2512.6853263393245</v>
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>1906.830844749277</v>
+        <v>1940.2540995910704</v>
       </c>
       <c r="H23" s="121"/>
     </row>
@@ -14842,11 +14842,11 @@
       </c>
       <c r="C24" s="124">
         <f t="shared" si="2"/>
-        <v>2451.3746129778847</v>
+        <v>2508.8321469331549</v>
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>1736.6155775987222</v>
+        <v>1777.3199432182701</v>
       </c>
       <c r="H24" s="121"/>
     </row>
@@ -14864,11 +14864,11 @@
       </c>
       <c r="C25" s="124">
         <f t="shared" si="2"/>
-        <v>2433.4795783031459</v>
+        <v>2504.9848763415034</v>
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>1581.5947558552762</v>
+        <v>1628.0682933370222</v>
       </c>
       <c r="H25" s="121"/>
     </row>
@@ -14886,11 +14886,11 @@
       </c>
       <c r="C26" s="124">
         <f t="shared" si="2"/>
-        <v>2415.7151773815331</v>
+        <v>2501.1435055032584</v>
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -14898,7 +14898,7 @@
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>1440.4120313188373</v>
+        <v>1491.350152167739</v>
       </c>
       <c r="H26" s="121"/>
     </row>
@@ -14908,11 +14908,11 @@
       </c>
       <c r="C27" s="124">
         <f t="shared" si="2"/>
-        <v>2398.0804565866479</v>
+        <v>2497.3080253712037</v>
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>1311.8321316423944</v>
+        <v>1366.1130098000924</v>
       </c>
       <c r="H27" s="121"/>
     </row>
@@ -14930,11 +14930,11 @@
       </c>
       <c r="C28" s="124">
         <f t="shared" si="2"/>
-        <v>2380.5744692535654</v>
+        <v>2493.4784269119959</v>
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -14942,7 +14942,7 @@
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1194.7300523682613</v>
+        <v>1251.3927415586295</v>
       </c>
       <c r="H28" s="121"/>
     </row>
@@ -14952,11 +14952,11 @@
       </c>
       <c r="C29" s="124">
         <f t="shared" si="2"/>
-        <v>2363.1962756280145</v>
+        <v>2489.6547011061448</v>
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1088.0812137485991</v>
+        <v>1146.3061857926223</v>
       </c>
       <c r="H29" s="121"/>
     </row>
@@ -14974,11 +14974,11 @@
       </c>
       <c r="C30" s="124">
         <f t="shared" si="2"/>
-        <v>2345.9449428159301</v>
+        <v>2485.8368389479924</v>
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>990.95249622773781</v>
+        <v>1050.0443449510503</v>
       </c>
       <c r="H30" s="121"/>
     </row>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>27842.812903162245</v>
+        <v>28004.549421214109</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>11761.105064670463</v>
+        <v>11829.42431776525</v>
       </c>
       <c r="H51" s="121"/>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>27404.831871241127</v>
+        <v>27910.700427510208</v>
       </c>
       <c r="H52" s="121"/>
     </row>
@@ -15480,15 +15480,15 @@
     <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>27404.831871241127</v>
+        <v>27910.700427510208</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C55" s="132">
         <f>C77</f>
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D55" s="132">
         <f>C76</f>
@@ -15510,10 +15510,10 @@
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>20063.703772414767</v>
+        <v>23774.32983700114</v>
       </c>
       <c r="C56" s="124">
-        <v>25832.311334807477</v>
+        <v>27141.444000157735</v>
       </c>
       <c r="D56" s="124">
         <v>28047.560091832616</v>
@@ -15531,10 +15531,10 @@
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>16125.768083282397</v>
+        <v>20858.840408788732</v>
       </c>
       <c r="C57" s="124">
-        <v>24052.100970487048</v>
+        <v>26337.807128432454</v>
       </c>
       <c r="D57" s="124">
         <v>28047.560091832609</v>
@@ -15552,10 +15552,10 @@
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>13056.366048742024</v>
+        <v>18211.352254376201</v>
       </c>
       <c r="C58" s="124">
-        <v>22265.500140079126</v>
+        <v>25475.165391277165</v>
       </c>
       <c r="D58" s="124">
         <v>28047.560091832613</v>
@@ -15573,10 +15573,10 @@
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>10952.84788723816</v>
+        <v>16201.827595104349</v>
       </c>
       <c r="C59" s="124">
-        <v>20787.710421208605</v>
+        <v>24714.566461598573</v>
       </c>
       <c r="D59" s="124">
         <v>28047.560091832613</v>
@@ -15594,10 +15594,10 @@
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>9562.5732082856211</v>
+        <v>14784.924393359493</v>
       </c>
       <c r="C60" s="124">
-        <v>19668.01798494067</v>
+        <v>24102.766713332425</v>
       </c>
       <c r="D60" s="124">
         <v>28047.560091832605</v>
@@ -15615,10 +15615,10 @@
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>8654.0636045229312</v>
+        <v>13821.492720860644</v>
       </c>
       <c r="C61" s="124">
-        <v>18860.216981993442</v>
+        <v>23636.131144957148</v>
       </c>
       <c r="D61" s="124">
         <v>28047.560091832605</v>
@@ -15651,11 +15651,11 @@
     <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B64" s="133">
         <f>B55</f>
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C64" s="133">
         <f>C55</f>
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D64" s="133">
         <f>D55</f>
@@ -15704,11 +15704,11 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>8.1997862481313746</v>
+        <v>8.6538587618793734</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>8.9056957337786056</v>
+        <v>9.0658954278028752</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
@@ -15731,11 +15731,11 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>7.7178976594622748</v>
+        <v>8.2970878045175738</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>8.6878498551971095</v>
+        <v>8.9675536902811377</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
@@ -15758,11 +15758,11 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>7.3422922836394369</v>
+        <v>7.9731123943124613</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>8.4692219697655933</v>
+        <v>8.8619914764562537</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
@@ -15785,11 +15785,11 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>7.0848829509059597</v>
+        <v>7.727205127562347</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>8.2883835665530903</v>
+        <v>8.7689163290439822</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
@@ -15812,11 +15812,11 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>6.9147538386526222</v>
+        <v>7.5538174599948267</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>8.1513658368462085</v>
+        <v>8.6940498658730085</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
@@ -15838,11 +15838,11 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>6.8035787344075898</v>
+        <v>7.4359214948014829</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>8.0525145309932462</v>
+        <v>8.6369472686701805</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
-        <v>0.22499999999999992</v>
+        <v>0.17999999999999994</v>
       </c>
       <c r="H75" s="121"/>
     </row>
@@ -15949,7 +15949,7 @@
       </c>
       <c r="C77" s="143">
         <f>Scenarios!C32</f>
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D77" s="146">
         <f>Scenarios!C31</f>
@@ -15957,11 +15957,11 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>8.6878498551971095</v>
+        <v>8.9675536902811377</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
-        <v>0.18</v>
+        <v>0.22499999999999998</v>
       </c>
       <c r="H77" s="121"/>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C78" s="143">
         <f>Scenarios!C50</f>
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D78" s="146">
         <f>Scenarios!C49</f>
@@ -15980,7 +15980,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>7.3422922836394369</v>
+        <v>7.9731123943124613</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>9.6806872475781418</v>
+        <v>9.7428099951889298</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16429,7 +16429,7 @@
         <v>136</v>
       </c>
       <c r="C32" s="165">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="D32" s="165"/>
       <c r="E32" s="345"/>
@@ -16441,7 +16441,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>8.6878498551971095</v>
+        <v>8.9675536902811377</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16455,7 +16455,7 @@
         <v>149</v>
       </c>
       <c r="C34" s="166">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
       <c r="E34" s="345"/>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="C40" s="168">
         <f>1-C28-C34</f>
-        <v>0.24999999999999994</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="D40" s="166"/>
       <c r="E40" s="345"/>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>9.1364913613480141</v>
+        <v>9.1704710747670557</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16588,7 +16588,7 @@
         <v>136</v>
       </c>
       <c r="C50" s="165">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="D50" s="165"/>
       <c r="E50" s="345"/>
@@ -16600,7 +16600,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>7.3422922836394369</v>
+        <v>7.9731123943124613</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16684,7 +16684,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>9.1006872475781417</v>
+        <v>9.1628099951889297</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16733,7 +16733,7 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>-7.3000000000000001E-3</v>
+        <v>-1.533490630831739E-3</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>9.0981264288878361</v>
+        <v>9.1600300006768141</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -16809,7 +16809,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>0.63122414236360114</v>
+        <v>0.6269445187435021</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.6595518707600085</v>
+        <v>4.6913587175367324</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -16891,7 +16891,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>5.7917118707600084</v>
+        <v>5.8235187175367322</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -16902,7 +16902,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.36359620837412165</v>
+        <v>0.3644396510901724</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.35">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12105292184429062</v>
+        <v>0.12328963999428066</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8B2460-D251-47D8-B4D8-743BCB41F48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94B0C6D-1343-4787-9AEB-FA4EC7C3818E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1825,14 +1821,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2315,6 +2303,45 @@
   </si>
   <si>
     <t xml:space="preserve">Use general Scenarios' HGP assumption </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3004,7 +3031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3697,6 +3724,9 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4009,7 +4039,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4029,15 +4059,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4061,13 +4091,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4094,7 +4124,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="279">
         <v>12</v>
@@ -4104,7 +4134,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4130,24 +4160,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>375</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4157,7 +4187,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4183,18 +4213,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4206,7 +4241,7 @@
         <v>5.8235187175367322</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4214,7 +4249,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4229,7 +4264,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4238,22 +4273,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="B25" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="B26" s="342" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4265,13 +4300,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="340" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4291,13 +4326,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="340" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4326,13 +4361,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4348,17 +4383,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4373,7 +4408,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4406,7 +4441,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4418,13 +4453,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4440,13 +4475,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4462,26 +4497,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>377</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4507,7 +4542,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4516,7 +4551,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4525,7 +4560,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4538,22 +4573,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
-        <v>378</v>
-      </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="B63" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="342" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4562,7 +4597,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4570,26 +4605,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4606,27 +4641,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>379</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="B73" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
-        <v>380</v>
-      </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="B74" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4638,7 +4673,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4651,7 +4686,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4663,13 +4698,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
-        <v>381</v>
-      </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="B81" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4682,13 +4717,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
-        <v>357</v>
-      </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="B85" s="339" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4705,7 +4740,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4723,7 +4758,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4736,7 +4771,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4749,7 +4784,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4780,7 +4815,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4792,17 +4827,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
-        <v>382</v>
-      </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="B98" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
@@ -4815,7 +4850,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4824,13 +4859,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="B104" s="340" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4973,17 +5008,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>386</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="B115" s="343" t="s">
+        <v>383</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>373</v>
+        <v>418</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4992,22 +5027,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
-        <v>384</v>
-      </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="B119" s="344" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
-        <v>385</v>
-      </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="B120" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5016,7 +5051,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5025,7 +5060,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5047,7 +5082,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>415</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5092,109 +5127,156 @@
         <v>0.3644396510901724</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>1.6265026918138714</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>8.2763185094983989</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>9.9028212013122712</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>-8.0762474231365289E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>389</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>393</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>395</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
-        <v>397</v>
-      </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
-        <v>398</v>
-      </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
-        <v>399</v>
-      </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5221,14 +5303,14 @@
     <mergeCell ref="B115:F115"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5679,7 +5761,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5695,7 +5777,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5711,7 +5793,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5753,7 +5835,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -6976,7 +7058,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8344,13 +8426,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8358,7 +8440,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8511,7 +8593,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8534,7 +8616,7 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8556,7 +8638,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8623,7 +8705,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8635,7 +8717,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8646,12 +8728,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8662,12 +8744,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8675,12 +8757,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8688,7 +8770,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8764,7 +8846,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8775,15 +8857,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8800,7 +8882,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8834,7 +8916,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9705,7 +9787,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9730,7 +9812,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10058,7 +10140,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10118,7 +10200,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10242,7 +10324,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10300,7 +10382,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10608,7 +10690,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10747,7 +10829,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10802,7 +10884,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10934,7 +11016,7 @@
         <v>0.03</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -10961,7 +11043,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11276,7 +11358,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11837,7 +11919,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12516,7 +12598,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13210,7 +13292,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13262,7 +13344,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13715,7 +13797,7 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13771,7 +13853,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14600,10 +14682,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14618,8 +14700,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14634,8 +14716,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14650,8 +14732,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -14721,7 +14803,7 @@
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="H16" s="121"/>
     </row>
@@ -14780,7 +14862,7 @@
       </c>
       <c r="D21" s="139">
         <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -14802,7 +14884,7 @@
       </c>
       <c r="D22" s="139">
         <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
@@ -14824,7 +14906,7 @@
       </c>
       <c r="D23" s="139">
         <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
@@ -14846,7 +14928,7 @@
       </c>
       <c r="D24" s="139">
         <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
@@ -14868,7 +14950,7 @@
       </c>
       <c r="D25" s="139">
         <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
@@ -14890,7 +14972,7 @@
       </c>
       <c r="D26" s="139">
         <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
@@ -14912,7 +14994,7 @@
       </c>
       <c r="D27" s="139">
         <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
@@ -14934,7 +15016,7 @@
       </c>
       <c r="D28" s="139">
         <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
@@ -14956,7 +15038,7 @@
       </c>
       <c r="D29" s="139">
         <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
@@ -14978,7 +15060,7 @@
       </c>
       <c r="D30" s="139">
         <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
@@ -15996,7 +16078,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16048,7 +16130,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16068,7 +16150,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16122,7 +16204,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16135,7 +16217,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16145,11 +16227,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16170,8 +16252,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16192,8 +16274,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16203,8 +16285,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16215,10 +16297,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16236,8 +16318,8 @@
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16254,8 +16336,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16272,8 +16354,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.34904529928871464</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16289,7 +16371,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16299,25 +16381,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16327,12 +16409,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16342,8 +16424,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16363,8 +16445,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16374,8 +16456,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16389,8 +16471,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16400,8 +16482,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16421,8 +16503,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16432,8 +16514,8 @@
         <v>-0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16447,8 +16529,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16458,8 +16540,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16479,8 +16561,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16490,8 +16572,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16505,8 +16587,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16517,8 +16599,8 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16580,8 +16662,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16591,8 +16673,8 @@
         <v>-0.1</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16606,8 +16688,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16617,12 +16699,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16638,8 +16720,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16649,8 +16731,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16664,8 +16746,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16675,8 +16757,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16691,7 +16773,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16700,7 +16782,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16709,10 +16791,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16725,7 +16807,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16733,11 +16815,11 @@
         <v>136</v>
       </c>
       <c r="C65" s="152">
-        <v>-1.533490630831739E-3</v>
+        <v>-1.5334906308317399E-3</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16753,20 +16835,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16776,19 +16858,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16798,14 +16880,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16828,7 +16910,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16851,12 +16933,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -16910,12 +16992,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -16928,7 +17010,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -16938,43 +17020,99 @@
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>1.6265026918138714</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>8.2763185094983989</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>413</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>9.9028212013122712</v>
+      </c>
+      <c r="D93" t="s">
+        <v>410</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>-8.0762474231365289E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>337</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>337</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>338</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>341</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94B0C6D-1343-4787-9AEB-FA4EC7C3818E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D683C52-DDF4-41E2-AFCF-92A3BF87CA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2317,31 +2313,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3031,7 +3043,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3727,6 +3739,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4039,7 +4056,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4059,10 +4076,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4091,13 +4108,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4124,7 +4141,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>12</v>
@@ -4160,24 +4177,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4187,7 +4204,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
         <v>41</v>
@@ -4213,19 +4230,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4237,11 +4254,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>5.8235187175367322</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4249,7 +4266,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4264,7 +4281,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4273,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4300,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4326,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4361,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4383,17 +4400,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4408,7 +4425,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4453,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4475,13 +4492,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4497,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4542,7 +4559,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4551,7 +4568,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4560,7 +4577,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4573,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>375</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4597,7 +4614,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4605,26 +4622,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4641,27 +4658,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4673,7 +4690,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4686,7 +4703,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4698,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4717,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4740,7 +4757,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4751,537 +4768,577 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>418</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>8.3114411724224596E-2</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>1.8509098960546238E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>421</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>1.1933697905849452</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>47679</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>42222.564948178719</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>5.1668117102618574</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>7814.4</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>378</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>9.1767776359081505</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>371</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>380</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>11.511512740854835</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>370</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>379</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.05</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>10.21 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.02</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>9.41 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.17999999999999994</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>9.18 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.495</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>-0.02</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>8.97 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>-0.1</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>7.97 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>9.1628099951889297</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>383</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>418</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>382</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>416</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>380</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>381</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>1.1321599999999998</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>4.6913587175367324</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>5.8235187175367322</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.3644396510901724</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.6265026918138714</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>1.5582689315271454</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>8.2763185094983989</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>417</v>
-      </c>
-      <c r="C135" s="239">
+        <v>7.7534608700654166</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>415</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>9.9028212013122712</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>9.3117298015925627</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-8.0762474231365289E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>-1.6252634997541815E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>388</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>387</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>392</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>393</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>396</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>395</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5290,24 +5347,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5761,7 +5818,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5777,7 +5834,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5793,7 +5850,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5835,7 +5892,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7058,7 +7115,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8432,7 +8489,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>420</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8440,7 +8497,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8593,7 +8650,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8616,7 +8673,7 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8638,7 +8695,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8705,7 +8762,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8717,7 +8774,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8728,12 +8785,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8744,12 +8801,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8757,12 +8814,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8770,7 +8827,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8846,7 +8903,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8857,15 +8914,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -8882,7 +8939,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -8916,7 +8973,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9787,7 +9844,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9812,7 +9869,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10140,7 +10197,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10200,7 +10257,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10324,7 +10381,7 @@
         <v>-1106.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10382,7 +10439,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10690,7 +10747,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10829,7 +10886,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10884,7 +10941,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11016,7 +11073,7 @@
         <v>0.03</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11043,7 +11100,7 @@
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11358,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11919,7 +11976,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12598,7 +12655,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13292,7 +13349,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13344,7 +13401,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13853,7 +13910,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14682,10 +14739,10 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14700,8 +14757,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14716,8 +14773,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14732,8 +14789,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16078,7 +16135,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16150,7 +16207,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16204,7 +16261,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16217,7 +16274,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16227,11 +16284,11 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for SINO LAND(0083.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16252,8 +16309,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16274,8 +16331,8 @@
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16285,8 +16342,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16297,10 +16354,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16318,8 +16375,8 @@
         <v>-0.28945840615733698</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16336,8 +16393,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.42686307479092267</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16354,8 +16411,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.34904529928871464</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16371,7 +16428,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16381,25 +16438,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16409,12 +16466,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16424,8 +16481,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16445,8 +16502,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16456,8 +16513,8 @@
         <v>0</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16471,8 +16528,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16482,8 +16539,8 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16503,8 +16560,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16514,8 +16571,8 @@
         <v>-0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16529,8 +16586,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16540,8 +16597,8 @@
         <v>0.25</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16561,8 +16618,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16572,8 +16629,8 @@
         <v>0.02</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16587,8 +16644,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16599,8 +16656,8 @@
         <v>0.19999999999999996</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16662,8 +16719,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16673,8 +16730,8 @@
         <v>-0.1</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16688,8 +16745,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16699,12 +16756,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16720,8 +16777,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16731,8 +16788,8 @@
         <v>0.05</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16746,8 +16803,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16757,8 +16814,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16773,7 +16830,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16782,7 +16839,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16791,10 +16848,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16807,7 +16864,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16819,7 +16876,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16835,20 +16892,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16858,19 +16915,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16880,14 +16937,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -16910,7 +16967,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16933,15 +16990,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -16992,12 +17049,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17010,7 +17067,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17022,16 +17079,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17040,7 +17097,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.6265026918138714</v>
+        <v>1.5582689315271454</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17050,27 +17107,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>8.2763185094983989</v>
+        <v>7.7534608700654166</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>9.9028212013122712</v>
+        <v>9.3117298015925627</v>
       </c>
       <c r="D93" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>-8.0762474231365289E-2</v>
+        <v>-1.6252634997541815E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17078,7 +17135,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17086,30 +17143,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>336</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>337</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>338</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D683C52-DDF4-41E2-AFCF-92A3BF87CA69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095C24DB-F554-455A-A233-C1281589B504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -180,10 +181,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1417,10 +1414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1582,10 +1575,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1793,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2357,19 +2342,34 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>SINO LAND</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0083.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>RES_01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -2377,26 +2377,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3071,7 +3071,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3113,23 +3113,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3138,13 +3138,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3215,10 +3215,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3229,7 +3229,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3267,7 +3267,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3277,7 +3277,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3288,29 +3288,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3326,7 +3326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3340,38 +3340,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3391,17 +3391,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3416,11 +3416,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3429,51 +3429,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3489,7 +3489,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3523,21 +3523,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3546,7 +3546,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3556,13 +3556,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3573,7 +3573,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3592,9 +3592,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3603,23 +3603,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3637,13 +3637,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3651,7 +3651,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3688,7 +3688,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3710,21 +3710,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3735,7 +3735,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3743,30 +3743,30 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4057,7 +4057,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4067,24 +4067,24 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="44">
         <v>45730</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4096,7 +4096,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>0083.HK Stock Information</v>
@@ -4106,30 +4106,30 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>421</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D5" s="49" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="50">
         <v>7.85</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4139,9 +4139,9 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C8" s="279">
         <v>12</v>
@@ -4149,9 +4149,9 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4160,7 +4160,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (HKD):</v>
@@ -4172,29 +4172,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
+      <c r="B12" s="340" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
@@ -4225,30 +4225,30 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
@@ -4258,15 +4258,15 @@
         <v>5.8235187175367322</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4275,13 +4275,13 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4289,45 +4289,45 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="345" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B25" s="340" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B26" s="342" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="108">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="108">
-        <f>Data!C3</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="343" t="s">
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="47" t="s">
         <v>233</v>
-      </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="C30" s="188">
         <f>Normalized_FCF!C8</f>
@@ -4338,22 +4338,22 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="343" t="s">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B32" s="341" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="47" t="s">
         <v>235</v>
-      </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="47" t="s">
-        <v>236</v>
       </c>
       <c r="C33" s="188">
         <f>Normalized_FCF!C9</f>
@@ -4364,9 +4364,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C34" s="188">
         <f>Normalized_FCF!C10</f>
@@ -4377,18 +4377,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="341" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="47" t="s">
         <v>238</v>
-      </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="47" t="s">
-        <v>239</v>
       </c>
       <c r="C37" s="188">
         <f>Normalized_FCF!C11</f>
@@ -4399,18 +4399,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="343" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
+      <c r="B39" s="341" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4423,9 +4423,9 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4438,9 +4438,9 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
@@ -4451,14 +4451,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4469,18 +4469,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="343" t="s">
-        <v>243</v>
-      </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6">
+      <c r="B47" s="341" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
@@ -4491,18 +4491,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="343" t="s">
-        <v>349</v>
+    <row r="50" spans="1:6">
+      <c r="B50" s="341" t="s">
+        <v>346</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
       <c r="E50" s="344"/>
       <c r="F50" s="344"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4513,27 +4513,27 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B53" s="340" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B54" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4544,9 +4544,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
@@ -4557,27 +4557,27 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
         <v>3.9350111080543315E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
         <v>7.3885350318471335E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4585,115 +4585,115 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="345" t="s">
-        <v>254</v>
-      </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B63" s="340" t="s">
+        <v>370</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="342" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0.01</v>
       </c>
       <c r="D68" s="286" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="1" t="s">
         <v>289</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B69" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C70" s="263">
         <f>SUM(C67:C69)</f>
         <v>0.09</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B73" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" s="263">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>3.432204133136278</v>
       </c>
       <c r="D77" s="1" t="str">
@@ -4701,9 +4701,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4711,40 +4711,40 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6">
+      <c r="B81" s="340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="342" t="s">
-        <v>355</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B85" s="340" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C86" s="188">
         <f>Valuation_Model!C7</f>
@@ -4755,12 +4755,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.37849307922088393</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4768,41 +4768,41 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6">
       <c r="B88" s="337" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>8.3114411724224596E-2</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6">
       <c r="B89" s="337" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>1.8509098960546238E-2</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6">
       <c r="B90" s="337" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
         <v>1.1933697905849452</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C93" s="188">
         <f>BS!C66</f>
@@ -4813,9 +4813,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
@@ -4826,12 +4826,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>5.1668117102618574</v>
       </c>
       <c r="D95" s="1" t="str">
@@ -4839,14 +4839,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B98" s="47" t="s">
-        <v>259</v>
       </c>
       <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
@@ -4857,12 +4857,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -4870,18 +4870,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="342" t="s">
-        <v>378</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B101" s="340" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
@@ -4892,9 +4892,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="B104" s="337" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4905,9 +4905,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4915,33 +4915,33 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="343" t="s">
-        <v>379</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B108" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" s="260" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D110" s="260" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E110" s="260" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F110" s="260" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4963,7 +4963,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4985,7 +4985,7 @@
         <v>0.17999999999999994</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5007,7 +5007,7 @@
         <v>0.495</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5029,7 +5029,7 @@
         <v>0.22499999999999998</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5051,9 +5051,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
@@ -5064,18 +5064,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="346" t="s">
-        <v>382</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B119" s="345" t="s">
+        <v>378</v>
+      </c>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5083,50 +5083,50 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="347" t="s">
-        <v>380</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="342" t="s">
-        <v>381</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
+      <c r="B123" s="343" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="340" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
@@ -5137,12 +5137,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5152,7 +5159,7 @@
         <v>1.1321599999999998</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5162,9 +5169,9 @@
         <v>4.6913587175367324</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
@@ -5175,65 +5182,72 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.3644396510901724</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.5582689315271454</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.5503469306877509</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>7.7534608700654166</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>7.693271958721736</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>9.3117298015925627</v>
+        <v>9.2436188894094862</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-1.6252634997541815E-2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>-8.8192262267783317E-3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5241,103 +5255,114 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="341" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="347" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
+    </row>
+    <row r="146" spans="2:6">
+      <c r="B146" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
+      <c r="B147" s="344" t="s">
         <v>388</v>
-      </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B147" s="344" t="s">
-        <v>392</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
       <c r="E147" s="344"/>
       <c r="F147" s="344"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
+      <c r="B149" s="238" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
+      <c r="B152" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="238" t="s">
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
+    </row>
+    <row r="155" spans="2:6">
+      <c r="B155" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
+    </row>
+    <row r="159" spans="2:6">
+      <c r="B159" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
+      <c r="B160" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="238" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>393</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B155" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="340" t="s">
-        <v>395</v>
-      </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B159" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B160" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B161" s="238" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B162" s="238" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5354,17 +5379,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5389,7 +5403,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5397,7 +5411,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>HKD</v>
@@ -5446,9 +5460,9 @@
         <v>41820</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -5462,7 +5476,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5470,7 +5484,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5496,9 +5510,9 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="181">
         <v>5344</v>
@@ -5522,9 +5536,9 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="181">
         <v>1084</v>
@@ -5546,9 +5560,9 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="189"/>
       <c r="D7" s="189"/>
@@ -5562,9 +5576,9 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="181"/>
       <c r="D8" s="181"/>
@@ -5578,9 +5592,9 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="181">
         <v>639</v>
@@ -5598,9 +5612,9 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="181"/>
       <c r="D10" s="181"/>
@@ -5614,9 +5628,9 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="181"/>
       <c r="D11" s="181"/>
@@ -5630,7 +5644,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5654,9 +5668,9 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="181">
         <v>2340</v>
@@ -5678,9 +5692,9 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="181">
         <v>519</v>
@@ -5702,9 +5716,9 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="182">
         <v>4251</v>
@@ -5726,9 +5740,9 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="181">
         <v>-151</v>
@@ -5746,15 +5760,15 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="181">
         <v>160</v>
@@ -5776,9 +5790,9 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="181">
         <v>69</v>
@@ -5796,9 +5810,9 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="181">
         <v>910</v>
@@ -5816,9 +5830,9 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181"/>
       <c r="D22" s="181"/>
@@ -5832,9 +5846,9 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181"/>
       <c r="D23" s="181"/>
@@ -5848,9 +5862,9 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181"/>
       <c r="D24" s="181"/>
@@ -5864,7 +5878,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -5887,7 +5901,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -5895,7 +5909,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -5916,7 +5930,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -5937,7 +5951,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -5958,7 +5972,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -5979,9 +5993,9 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C32" s="183">
         <f>BS!G28</f>
@@ -5998,9 +6012,9 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6014,12 +6028,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6068,9 +6082,9 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="183">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -6117,9 +6131,9 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" s="184">
         <f>IF(C36="","",C36+C37)</f>
@@ -6166,9 +6180,9 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="183">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -6215,9 +6229,9 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="185">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -6264,9 +6278,9 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" s="185">
         <f>IF(C$4="","",C39-C40)</f>
@@ -6313,9 +6327,9 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" s="183">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -6362,9 +6376,9 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="186">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6411,9 +6425,9 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C44" s="187">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -6460,9 +6474,9 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45" s="188">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -6509,9 +6523,9 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="183">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -6558,9 +6572,9 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="186">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -6607,9 +6621,9 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="183">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6656,12 +6670,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6710,9 +6724,9 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="183">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6759,14 +6773,14 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C55" s="188">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -6813,9 +6827,9 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C56" s="188">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -6862,9 +6876,9 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" s="188">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -6911,9 +6925,9 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -6960,15 +6974,15 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C61" s="183">
         <f>IF(C$4="","",-C19)</f>
@@ -7015,9 +7029,9 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="183">
         <f>IF(C$4="","",-C20)</f>
@@ -7064,9 +7078,9 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="183">
         <f>IF(C$4="","",-C21)</f>
@@ -7113,9 +7127,9 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7162,7 +7176,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7211,12 +7225,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7266,9 +7280,9 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -7315,7 +7329,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7365,9 +7379,9 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -7414,7 +7428,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7464,9 +7478,9 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -7480,13 +7494,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7535,9 +7549,9 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" s="185">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -7569,9 +7583,9 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" s="185">
         <f t="shared" si="40"/>
@@ -7603,7 +7617,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7652,7 +7666,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7733,7 +7747,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7744,7 +7758,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7756,13 +7770,13 @@
         <v>FY Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7771,27 +7785,27 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H3" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -7803,7 +7817,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="19">
         <v>45665</v>
@@ -7812,7 +7826,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7833,7 +7847,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -7845,7 +7859,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G6" s="19">
         <v>156</v>
@@ -7854,9 +7868,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="19">
         <v>5466</v>
@@ -7866,7 +7880,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -7875,9 +7889,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -7887,7 +7901,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -7896,7 +7910,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -7908,7 +7922,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -7917,7 +7931,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -7929,7 +7943,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7941,9 +7955,9 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -7954,7 +7968,7 @@
         <v>13028</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -7965,34 +7979,34 @@
         <v>42601.9</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H14" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="19">
         <v>2757</v>
@@ -8001,7 +8015,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8010,7 +8024,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8021,7 +8035,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G16" s="19">
         <v>1373</v>
@@ -8030,9 +8044,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="19">
         <v>67668</v>
@@ -8041,7 +8055,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G17" s="19">
         <v>13024</v>
@@ -8050,9 +8064,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8061,7 +8075,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G18" s="19">
         <v>23696</v>
@@ -8070,7 +8084,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8081,7 +8095,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8090,7 +8104,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8101,7 +8115,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8110,7 +8124,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8121,7 +8135,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8130,7 +8144,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8142,7 +8156,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8154,9 +8168,9 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -8167,7 +8181,7 @@
         <v>41841</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -8178,24 +8192,24 @@
         <v>11007.8</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" s="205" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G26" s="206" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H26" s="207" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8214,7 +8228,7 @@
         <v>94589.7</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8222,14 +8236,14 @@
         <v>37</v>
       </c>
       <c r="F28" s="210" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G28" s="181">
         <v>519</v>
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8237,7 +8251,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="211" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -8248,7 +8262,7 @@
         <v>94070.7</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8264,16 +8278,16 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>1004</v>
       </c>
       <c r="F31" s="211" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="212">
         <f>C31+C40</f>
@@ -8281,7 +8295,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8290,7 +8304,7 @@
         <v>8048</v>
       </c>
       <c r="F32" s="213" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" s="214">
         <f>G35+G40</f>
@@ -8301,7 +8315,7 @@
         <v>108478.7</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8312,25 +8326,25 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G34" s="218" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H34" s="219" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="220" t="s">
         <v>31</v>
@@ -8344,7 +8358,7 @@
         <v>54869</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8352,7 +8366,7 @@
         <v>832</v>
       </c>
       <c r="F36" s="211" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G36" s="212">
         <f>C4+C15</f>
@@ -8360,7 +8374,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8368,7 +8382,7 @@
         <v>27</v>
       </c>
       <c r="F37" s="211" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="212">
         <f>C6</f>
@@ -8376,7 +8390,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8384,7 +8398,7 @@
         <v>1230</v>
       </c>
       <c r="F38" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G38" s="212">
         <f>C7+C17</f>
@@ -8392,7 +8406,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8400,7 +8414,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="211" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G39" s="212">
         <f>C7+C17+C19+C20</f>
@@ -8411,16 +8425,16 @@
         <v>44008.799999999996</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>2089</v>
       </c>
       <c r="F40" s="220" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G40" s="214">
         <f>G12+G24</f>
@@ -8431,7 +8445,7 @@
         <v>53609.7</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8440,7 +8454,7 @@
         <v>2748</v>
       </c>
       <c r="F41" s="211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G41" s="212">
         <f>C70</f>
@@ -8451,7 +8465,7 @@
         <v>45795.299999999996</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8459,7 +8473,7 @@
         <v>4837</v>
       </c>
       <c r="F42" s="222" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G42" s="223">
         <f>C82</f>
@@ -8470,9 +8484,9 @@
         <v>7814.4</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8481,23 +8495,23 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8509,7 +8523,7 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -8524,25 +8538,25 @@
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -8554,9 +8568,9 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" s="202"/>
       <c r="D51" s="92">
@@ -8565,24 +8579,24 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -8594,9 +8608,9 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -8608,24 +8622,24 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C57" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -8634,9 +8648,9 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -8645,24 +8659,24 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="262" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8673,12 +8687,12 @@
         <v>3.1154705020769802E-3</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8687,23 +8701,23 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C65" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8714,12 +8728,12 @@
         <v>42222.564948178719</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8727,9 +8741,9 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8737,9 +8751,9 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8747,9 +8761,9 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -8757,24 +8771,24 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8785,12 +8799,12 @@
         <v>-909.4058419702136</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8801,12 +8815,12 @@
         <v>52.428737313479523</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8814,12 +8828,12 @@
         <v>5456.4350518212814</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8827,27 +8841,27 @@
         <v>6</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C78" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -8859,9 +8873,9 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -8873,9 +8887,9 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -8887,9 +8901,9 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -8901,9 +8915,9 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8912,24 +8926,24 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D85" s="270" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-3093</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
+        <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.37849307922088393</v>
       </c>
       <c r="E86" s="269" t="str">
@@ -8937,16 +8951,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>42222.564948178719</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
+        <f>C87*scaling_factor/Common_Shares</f>
         <v>5.1668117102618574</v>
       </c>
       <c r="E87" s="269" t="str">
@@ -8954,16 +8968,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>7814.4</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
+        <f>C88*scaling_factor/Common_Shares</f>
         <v>0.95625487173090062</v>
       </c>
       <c r="E88" s="269" t="str">
@@ -8971,9 +8985,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9002,7 +9016,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -9014,14 +9028,14 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>HKD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9071,15 +9085,15 @@
         <v>41820</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9094,13 +9108,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
@@ -9108,7 +9122,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9165,10 +9179,10 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="191">
         <f>C25</f>
@@ -9220,10 +9234,10 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
@@ -9275,10 +9289,10 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="191">
         <f>C35</f>
@@ -9330,10 +9344,10 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
@@ -9387,10 +9401,10 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="191">
         <f>BS!$G$39*BS!D58</f>
@@ -9442,10 +9456,10 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="191">
         <f>-C4*C78</f>
@@ -9497,10 +9511,10 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C11" s="193">
         <f>C63</f>
@@ -9554,10 +9568,10 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="191">
         <f>C50</f>
@@ -9609,10 +9623,10 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
@@ -9664,10 +9678,10 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9719,10 +9733,10 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C15" s="191">
         <f>-C4*C83</f>
@@ -9776,10 +9790,10 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
@@ -9833,10 +9847,10 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="191">
         <f>-C4*C85</f>
@@ -9844,7 +9858,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9859,17 +9873,17 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="191">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -9884,10 +9898,10 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
@@ -9941,7 +9955,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -9960,15 +9974,15 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -9983,10 +9997,10 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10004,10 +10018,10 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="197">
         <f>-C4*C28</f>
@@ -10061,10 +10075,10 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="191">
         <f>-C4*C29</f>
@@ -10118,10 +10132,10 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
@@ -10175,21 +10189,21 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:H28)</f>
@@ -10197,7 +10211,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10245,7 +10259,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10257,7 +10271,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10305,10 +10319,10 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -10360,28 +10374,28 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C33" s="198">
         <f>AVERAGE(G33:H33)</f>
         <v>-1106.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10428,10 +10442,10 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="198">
         <f>AVERAGE(G34:J34)</f>
@@ -10439,7 +10453,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10487,10 +10501,10 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
@@ -10544,18 +10558,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10613,7 +10627,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10671,10 +10685,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -10726,28 +10740,28 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C43" s="296">
         <v>0.24</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10795,18 +10809,18 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -10821,14 +10835,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -10883,10 +10897,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -10938,10 +10952,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -10995,10 +11009,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
@@ -11050,30 +11064,30 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E52" s="302"/>
       <c r="G52" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="87">
         <v>0.03</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11090,17 +11104,17 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>1.3902360168121564E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11117,10 +11131,10 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -11172,24 +11186,24 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57" s="302"/>
       <c r="G57" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="191">
         <f>BS!$C67*C66</f>
@@ -11241,10 +11255,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C59" s="191">
         <f>BS!$C68*C67</f>
@@ -11296,10 +11310,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" s="191">
         <f>BS!$C69*C68</f>
@@ -11351,10 +11365,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C61" s="184">
         <f>SUM(C58:C60)</f>
@@ -11406,16 +11420,16 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" s="297">
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11462,10 +11476,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C63" s="184">
         <f>C61+C62</f>
@@ -11517,24 +11531,24 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65" s="302"/>
       <c r="G65" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C66" s="177">
         <f>G66</f>
@@ -11556,10 +11570,10 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" s="177">
         <f>G67</f>
@@ -11581,10 +11595,10 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C68" s="177">
         <f>G68</f>
@@ -11606,10 +11620,10 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -11633,18 +11647,18 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>60</v>
+        <v>426</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11659,10 +11673,10 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -11680,10 +11694,10 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -11737,10 +11751,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -11794,10 +11808,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -11851,10 +11865,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -11908,10 +11922,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -11965,10 +11979,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -11976,7 +11990,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12024,10 +12038,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12081,10 +12095,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -12138,10 +12152,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -12195,10 +12209,10 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -12252,7 +12266,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12310,10 +12324,10 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -12367,10 +12381,10 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C85" s="298">
         <v>0</v>
@@ -12393,10 +12407,10 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -12417,10 +12431,10 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -12474,18 +12488,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12541,19 +12555,19 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (HKD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
+        <f>C90*Common_Shares/scaling_factor</f>
         <v>4739.6903628800001</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>4739.6903628800001</v>
       </c>
       <c r="H91" s="74">
@@ -12597,18 +12611,18 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>1.8776401969295582</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>1.7093565785843898</v>
       </c>
       <c r="H92" s="171">
@@ -12652,10 +12666,10 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12707,14 +12721,14 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
@@ -12732,10 +12746,10 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" s="77">
         <f>C4/G4-1</f>
@@ -12789,10 +12803,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
@@ -12846,18 +12860,18 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -12872,17 +12886,17 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="302"/>
       <c r="G100" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -12939,10 +12953,10 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C102" s="200">
         <f>BS!C4</f>
@@ -12996,10 +13010,10 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C103" s="200">
         <f>BS!C6+BS!C7</f>
@@ -13053,7 +13067,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13110,7 +13124,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13167,21 +13181,21 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="303"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -13194,10 +13208,10 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C108" s="94">
         <f>C102/C$4</f>
@@ -13251,10 +13265,10 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -13308,10 +13322,10 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C110" s="94">
         <f>BS!$G$38/C$4</f>
@@ -13335,21 +13349,21 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13398,10 +13412,10 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13450,11 +13464,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13508,10 +13522,10 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C117" s="23">
         <f>C81</f>
@@ -13563,9 +13577,9 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
@@ -13617,9 +13631,9 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
@@ -13673,10 +13687,10 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
@@ -13730,7 +13744,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13749,15 +13763,15 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C122" s="54"/>
       <c r="D122" s="56"/>
       <c r="E122" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F122" s="56"/>
       <c r="G122" s="37"/>
@@ -13772,10 +13786,10 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
@@ -13793,7 +13807,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -13851,10 +13865,10 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13908,9 +13922,9 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -13958,688 +13972,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14661,7 +14675,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
@@ -14670,34 +14684,34 @@
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="107">
-        <f>Normalized_FCF!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
@@ -14708,7 +14722,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F4" s="135">
         <f>Thesis!C76</f>
@@ -14716,9 +14730,9 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" s="227" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="228">
         <f>Thesis!C70</f>
@@ -14727,9 +14741,9 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -14740,14 +14754,14 @@
         <v>HKD</v>
       </c>
       <c r="E6" s="348" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="226">
         <f>BS!G31</f>
@@ -14761,9 +14775,9 @@
       <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
@@ -14777,9 +14791,9 @@
       <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" s="227" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="229">
         <f>BS!H42</f>
@@ -14793,9 +14807,9 @@
       <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
@@ -14807,9 +14821,9 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="230" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
@@ -14821,12 +14835,12 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="112">
-        <f>(C10*C3)/Common_Shares*C11</f>
+        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
         <v>9.1767776359081505</v>
       </c>
       <c r="D12" t="str">
@@ -14835,12 +14849,12 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -14848,15 +14862,15 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
@@ -14864,9 +14878,9 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
@@ -14874,12 +14888,12 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
+        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
         <v>9.1600300006768141</v>
       </c>
       <c r="D18" t="str">
@@ -14888,28 +14902,28 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="129" t="s">
+      <c r="D20" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="129" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="129" t="s">
+      <c r="F20" s="130" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="130" t="s">
-        <v>112</v>
-      </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -14931,7 +14945,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -14953,7 +14967,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -14975,7 +14989,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -14997,7 +15011,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15019,7 +15033,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15041,7 +15055,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15063,7 +15077,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15085,7 +15099,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15107,7 +15121,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15129,7 +15143,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15151,7 +15165,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15173,7 +15187,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15195,7 +15209,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15217,7 +15231,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15239,7 +15253,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15261,7 +15275,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15283,7 +15297,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15305,7 +15319,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15327,7 +15341,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15349,7 +15363,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15371,7 +15385,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -15393,7 +15407,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -15415,7 +15429,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -15437,7 +15451,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -15459,7 +15473,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -15481,7 +15495,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -15503,7 +15517,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -15525,7 +15539,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -15547,7 +15561,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -15569,9 +15583,9 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -15591,10 +15605,10 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
@@ -15602,13 +15616,13 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" s="137"/>
       <c r="D54" s="137"/>
@@ -15616,7 +15630,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>27910.700427510208</v>
@@ -15643,7 +15657,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -15665,7 +15679,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -15686,7 +15700,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -15707,7 +15721,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -15728,7 +15742,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -15749,7 +15763,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -15770,16 +15784,16 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="115"/>
       <c r="D63" s="115"/>
@@ -15787,7 +15801,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>-0.1</v>
@@ -15810,7 +15824,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -15836,7 +15850,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -15863,7 +15877,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -15890,7 +15904,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -15917,7 +15931,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -15944,7 +15958,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -15970,7 +15984,7 @@
         <v>11.086775141303123</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -15996,24 +16010,24 @@
         <v>11.483411050862937</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C73" s="172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D73" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="173" t="s">
         <v>114</v>
       </c>
-      <c r="E73" s="173" t="s">
-        <v>115</v>
-      </c>
       <c r="F73" s="173" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16035,7 +16049,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16058,7 +16072,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16081,7 +16095,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16104,7 +16118,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16126,38 +16140,38 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16188,7 +16202,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I98"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -16198,22 +16212,22 @@
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="276">
         <v>0</v>
@@ -16223,16 +16237,16 @@
         <v>-7.85</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="121">
         <v>3</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" s="156"/>
       <c r="H4" s="276">
@@ -16243,7 +16257,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9">
       <c r="H5" s="276">
         <v>2</v>
       </c>
@@ -16252,16 +16266,16 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="107">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16272,9 +16286,9 @@
         <v>9.7428099951889298</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16297,9 +16311,9 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
@@ -16319,9 +16333,9 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
@@ -16341,7 +16355,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9">
       <c r="E10" s="350"/>
       <c r="F10" s="350"/>
       <c r="H10" s="276">
@@ -16352,9 +16366,9 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11" s="350"/>
       <c r="F11" s="350"/>
@@ -16366,9 +16380,9 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="159">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16385,9 +16399,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="159">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16403,9 +16417,9 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16414,49 +16428,49 @@
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="151">
         <v>10</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F18" s="351"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="E19" s="351"/>
       <c r="F19" s="351"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16469,9 +16483,9 @@
       <c r="E21" s="351"/>
       <c r="F21" s="351"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16484,18 +16498,18 @@
       <c r="E22" s="351"/>
       <c r="F22" s="351"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="167">
         <f>C18</f>
@@ -16505,9 +16519,9 @@
       <c r="E25" s="349"/>
       <c r="F25" s="349"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="165">
         <v>0</v>
@@ -16516,9 +16530,9 @@
       <c r="E26" s="349"/>
       <c r="F26" s="349"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
@@ -16531,9 +16545,9 @@
       <c r="E27" s="349"/>
       <c r="F27" s="349"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="166">
         <v>0.55000000000000004</v>
@@ -16542,18 +16556,18 @@
       <c r="E28" s="349"/>
       <c r="F28" s="349"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="167">
         <f>C18</f>
@@ -16563,9 +16577,9 @@
       <c r="E31" s="349"/>
       <c r="F31" s="349"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C32" s="165">
         <v>-0.02</v>
@@ -16574,9 +16588,9 @@
       <c r="E32" s="349"/>
       <c r="F32" s="349"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
@@ -16589,9 +16603,9 @@
       <c r="E33" s="349"/>
       <c r="F33" s="349"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="166">
         <v>0.25</v>
@@ -16600,18 +16614,18 @@
       <c r="E34" s="349"/>
       <c r="F34" s="349"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="167">
         <f>C18</f>
@@ -16621,9 +16635,9 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="165">
         <v>0.02</v>
@@ -16632,9 +16646,9 @@
       <c r="E38" s="349"/>
       <c r="F38" s="349"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
@@ -16647,9 +16661,9 @@
       <c r="E39" s="349"/>
       <c r="F39" s="349"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="168">
         <f>1-C28-C34</f>
@@ -16659,9 +16673,9 @@
       <c r="E40" s="349"/>
       <c r="F40" s="349"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -16672,23 +16686,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="151">
         <v>15</v>
@@ -16696,23 +16710,23 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="167">
         <f>C46</f>
@@ -16722,9 +16736,9 @@
       <c r="E49" s="349"/>
       <c r="F49" s="349"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50" s="165">
         <v>-0.1</v>
@@ -16733,9 +16747,9 @@
       <c r="E50" s="349"/>
       <c r="F50" s="349"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
@@ -16748,9 +16762,9 @@
       <c r="E51" s="349"/>
       <c r="F51" s="349"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" s="166">
         <v>0.05</v>
@@ -16759,18 +16773,18 @@
       <c r="E52" s="349"/>
       <c r="F52" s="349"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55" s="167">
         <f>C46</f>
@@ -16780,9 +16794,9 @@
       <c r="E55" s="349"/>
       <c r="F55" s="349"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56" s="165">
         <v>0.05</v>
@@ -16791,9 +16805,9 @@
       <c r="E56" s="349"/>
       <c r="F56" s="349"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
@@ -16806,9 +16820,9 @@
       <c r="E57" s="349"/>
       <c r="F57" s="349"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="166">
         <v>0.05</v>
@@ -16817,9 +16831,9 @@
       <c r="E58" s="349"/>
       <c r="F58" s="349"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -16830,33 +16844,33 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64" s="167">
         <f>C18</f>
@@ -16864,24 +16878,24 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65" s="152">
         <v>-1.5334906308317399E-3</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
@@ -16892,20 +16906,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16913,21 +16927,21 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -16935,39 +16949,39 @@
       </c>
       <c r="E71" s="281"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>Y</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
         <v>0.6269445187435021</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -16975,9 +16989,9 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
@@ -16988,23 +17002,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -17014,9 +17028,9 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
@@ -17024,9 +17038,9 @@
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
@@ -17037,24 +17051,24 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
         <v>0.3644396510901724</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17065,108 +17079,108 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.12328963999428066</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>(Thesis!E19+Thesis!C67)/2</f>
-        <v>5.7250000000000002E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.5582689315271454</v>
+        <v>1.5503469306877509</v>
       </c>
       <c r="D91" s="117"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>7.7534608700654166</v>
+        <v>7.693271958721736</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>9.3117298015925627</v>
+        <v>9.2436188894094862</v>
       </c>
       <c r="D93" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E93" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>-1.6252634997541815E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+        <v>-8.8192262267783317E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="100"/>
     </row>
-    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="14.65">
       <c r="E95" s="320" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="13.9">
       <c r="E96" s="313" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F96" s="318" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:8" ht="13.9">
       <c r="E97" s="314" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="98" spans="5:8" ht="13.9">
       <c r="E98" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>336</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095C24DB-F554-455A-A233-C1281589B504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F123907C-4051-4772-B4E9-B64930E7627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F123907C-4051-4772-B4E9-B64930E7627E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB83877-1DB5-48AF-AC2F-E16DE7B74B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3744,29 +3744,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4177,13 +4177,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4290,22 +4290,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4317,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4343,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4378,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4470,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4492,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4514,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4590,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4663,22 +4663,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4715,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4734,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4871,13 +4871,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4916,13 +4916,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,13 +5065,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5084,22 +5084,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>1.5503469306877509</v>
+        <v>1.4947162526037703</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>7.693271958721736</v>
+        <v>7.2737339925228373</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>9.2436188894094862</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>-8.8192262267783317E-3</v>
+        <v>4.3039171418962741E-2</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5256,13 +5256,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5299,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5313,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,17 +5352,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5379,6 +5368,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17101,8 +17101,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.5503469306877509</v>
+        <v>1.4947162526037703</v>
       </c>
       <c r="D91" s="117"/>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>7.693271958721736</v>
+        <v>7.2737339925228373</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>9.2436188894094862</v>
+        <v>8.7684502451266084</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>-8.8192262267783317E-3</v>
+        <v>4.3039171418962741E-2</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB83877-1DB5-48AF-AC2F-E16DE7B74B5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6673F110-07C2-4AA5-A04B-FA23F9F55E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3736,37 +3741,37 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4084,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4111,10 +4116,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4125,7 +4130,7 @@
         <v>7.85</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4177,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4207,7 +4212,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4230,7 +4235,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4242,10 +4247,10 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4266,7 +4271,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4290,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4317,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4343,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4378,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4400,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4470,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4492,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4514,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4590,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4629,7 +4634,7 @@
         <v>0.01</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4641,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4663,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4715,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4734,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,28 +4774,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>8.3114411724224596E-2</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>1.8509098960546238E-2</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>1.1933697905849452</v>
       </c>
@@ -4871,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,8 +4898,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4916,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5065,17 +5070,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5084,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5139,14 +5144,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
         <v>0.25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5193,14 +5198,14 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5209,7 +5214,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>1.4947162526037703</v>
       </c>
     </row>
@@ -5219,16 +5224,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>7.2737339925228373</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>8.7684502451266084</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5241,7 +5246,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>4.3039171418962741E-2</v>
       </c>
     </row>
@@ -5256,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5299,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5313,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5352,6 +5357,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5368,17 +5384,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5906,7 +5911,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8503,7 +8508,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11658,7 +11663,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11990,7 +11995,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16201,7 +16206,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17093,16 +17098,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17111,9 +17116,11 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>1.4947162526037703</v>
+        <v>1.2217592592592592</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17121,69 +17128,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>7.2737339925228373</v>
+        <v>5.3025520805491491</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>8.7684502451266084</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>6.5243113398084081</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>4.3039171418962741E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.28795736862009635</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>1.4947162526037703</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>7.2737339925228373</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>8.7684502451266084</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>4.3039171418962741E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6673F110-07C2-4AA5-A04B-FA23F9F55E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C480474B-6A41-495B-BF93-8F1511BDAC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3749,29 +3749,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4182,13 +4182,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4244,7 +4244,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>419</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>5.8235187175367322</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4295,22 +4295,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4322,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4348,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4383,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4405,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4475,13 +4475,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4497,7 +4497,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4519,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4595,22 +4595,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4668,22 +4668,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4720,13 +4720,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4739,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4876,13 +4876,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4921,13 +4921,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5070,13 +5070,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5089,22 +5089,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>418</v>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>1.1321599999999998</v>
+        <v>1.0533454710969505</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>4.6913587175367324</v>
+        <v>4.1706008171092073</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>5.8235187175367322</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.3644396510901724</v>
+        <v>0.42987508297683041</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5261,13 +5261,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5304,13 +5304,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5318,22 +5318,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5357,17 +5357,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5384,6 +5373,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>1.1321599999999998</v>
+        <v>1.0533454710969505</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>4.6913587175367324</v>
+        <v>4.1706008171092073</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>5.8235187175367322</v>
+        <v>5.2239462882061574</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.3644396510901724</v>
+        <v>0.42987508297683041</v>
       </c>
     </row>
     <row r="84" spans="2:8">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C480474B-6A41-495B-BF93-8F1511BDAC14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD304936-D26E-4F61-ABD8-0C5F5A6B53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3749,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4061,7 +4063,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4084,7 +4086,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4116,10 +4118,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4182,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4235,7 +4237,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4247,7 +4249,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4295,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4322,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4348,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4383,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4405,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4475,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4497,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4519,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4595,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4634,7 +4636,7 @@
         <v>0.01</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4646,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4668,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4720,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4739,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4775,7 +4777,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4784,7 +4786,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4793,7 +4795,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4876,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4899,7 +4901,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4921,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5070,17 +5072,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5089,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5142,19 +5144,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5164,7 +5166,7 @@
         <v>1.0533454710969505</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5174,7 +5176,7 @@
         <v>4.1706008171092073</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
@@ -5187,7 +5189,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
@@ -5196,167 +5198,232 @@
         <v>0.42987508297683041</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>1.4947162526037703</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>1.2217592592592592</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
+        <f>Scenarios!C92</f>
+        <v>5.3025520805491491</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
+      <c r="B139" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="C139" s="239">
+        <f>Scenarios!C93</f>
+        <v>6.5243113398084081</v>
+      </c>
+      <c r="D139" s="47" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4">
+      <c r="B140" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.28795736862009635</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>1.4947162526037703</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
         <f>Scenarios!C98</f>
         <v>7.2737339925228373</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
-      <c r="B139" s="80" t="s">
-        <v>410</v>
-      </c>
-      <c r="C139" s="239">
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
         <f>Scenarios!C99</f>
         <v>8.7684502451266084</v>
       </c>
-      <c r="D139" s="101" t="str">
+      <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
-      <c r="B140" s="238" t="s">
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
         <v>4.3039171418962741E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5373,20 +5440,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5911,7 +5967,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8508,7 +8564,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11663,7 +11719,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11995,7 +12051,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17098,12 +17154,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17161,7 +17217,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD304936-D26E-4F61-ABD8-0C5F5A6B53E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28387581-8FCB-42E3-BC67-0CCE7E686941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3751,29 +3751,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4129,7 +4129,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64149.257497599996</v>
+        <v>64884.726691840006</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4184,13 +4184,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.12328963999428066</v>
+        <v>0.11874261404950959</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4297,22 +4297,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4324,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4350,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4385,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4407,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4477,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4499,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4521,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.9350111080543315E-2</v>
+        <v>3.8904077075852014E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.3885350318471335E-2</v>
+        <v>7.3047858942065488E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4597,22 +4597,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4670,22 +4670,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4722,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4741,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4878,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4923,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5072,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5091,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5317,13 +5317,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5360,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5374,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,17 +5413,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5440,6 +5429,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12734,20 +12734,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.3885350318471335E-2</v>
+        <v>7.3047858942065488E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.3885350318471335E-2</v>
+        <v>7.3047858942065488E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3885350318471335E-2</v>
+        <v>7.3047858942065488E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.2611464968152864E-2</v>
+        <v>7.1788413098236761E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13933,30 +13933,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.9350111080543315E-2</v>
+        <v>3.8904077075852014E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.3224071117835328E-2</v>
+        <v>4.2734125727330888E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>7.0204391814909964E-2</v>
+        <v>6.9408624149501663E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.5426004581940976E-2</v>
+        <v>9.4344349618165818E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15670157681376184</v>
+        <v>0.15492536246700636</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.3780825134711406E-2</v>
+        <v>5.3171218804469081E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13990,19 +13990,19 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6267329752944401E-2</v>
+        <v>6.5516188735593645E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1661232403508139E-2</v>
+        <v>9.062225117979078E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.9407060544926448E-2</v>
+        <v>8.839363038761619E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.15036864597163707</v>
+        <v>0.14866421547573691</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-7.85</v>
+        <v>-7.94</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.12328963999428066</v>
+        <v>0.11874261404950959</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28387581-8FCB-42E3-BC67-0CCE7E686941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2D7A2D-7516-480E-BC5C-DEE329F2469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3751,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4086,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4118,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4184,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4237,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4297,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4324,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4350,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4385,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4407,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4477,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4499,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4521,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4597,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4636,7 +4639,7 @@
         <v>0.01</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4648,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4670,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4722,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4741,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4878,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4923,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5072,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5091,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5146,7 +5149,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5200,14 +5203,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5261,7 +5264,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5317,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5360,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5374,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5413,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5429,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -5967,7 +5970,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -11719,7 +11722,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12051,7 +12054,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -17154,12 +17157,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2D7A2D-7516-480E-BC5C-DEE329F2469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F594288-28EF-44E8-9309-BDB98EA29A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>7.94</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>64884.726691840006</v>
+        <v>67172.853073920007</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11874261404950959</v>
+        <v>0.10504291417240008</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.8904077075852014E-2</v>
+        <v>3.7578877370105228E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.3047858942065488E-2</v>
+        <v>7.055961070559609E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12737,20 +12737,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.3047858942065488E-2</v>
+        <v>7.055961070559609E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.3047858942065488E-2</v>
+        <v>7.055961070559609E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.3047858942065488E-2</v>
+        <v>7.055961070559609E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.1788413098236761E-2</v>
+        <v>6.9343065693430642E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13936,30 +13936,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.8904077075852014E-2</v>
+        <v>3.7578877370105228E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.2734125727330888E-2</v>
+        <v>4.1278462077251492E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.9408624149501663E-2</v>
+        <v>6.704434011521207E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.4344349618165818E-2</v>
+        <v>9.113067347545456E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15492536246700636</v>
+        <v>0.14964809951192584</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.3171218804469081E-2</v>
+        <v>5.1360033735703706E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13993,19 +13993,19 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5516188735593645E-2</v>
+        <v>6.3284493742167089E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.062225117979078E-2</v>
+        <v>8.7535361845199361E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.839363038761619E-2</v>
+        <v>8.5382655143269162E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14866421547573691</v>
+        <v>0.14360022760065097</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-7.94</v>
+        <v>-8.2200000000000006</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>7.94</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>7.94</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11874261404950959</v>
+        <v>0.10504291417240008</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F594288-28EF-44E8-9309-BDB98EA29A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A7D62D-DC5F-4BE7-BC11-D576568771B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>8.2200000000000006</v>
+        <v>8.1</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>67172.853073920007</v>
+        <v>66192.227481599999</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10504291417240008</v>
+        <v>0.11083350655450119</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.7578877370105228E-2</v>
+        <v>3.8135601479291979E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.055961070559609E-2</v>
+        <v>7.160493827160494E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5416,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5443,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12737,20 +12737,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.055961070559609E-2</v>
+        <v>7.160493827160494E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.055961070559609E-2</v>
+        <v>7.160493827160494E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.055961070559609E-2</v>
+        <v>7.160493827160494E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>6.9343065693430642E-2</v>
+        <v>7.0370370370370361E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13936,30 +13936,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.7578877370105228E-2</v>
+        <v>3.8135601479291979E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.1278462077251492E-2</v>
+        <v>4.1889994848766335E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.704434011521207E-2</v>
+        <v>6.8037589598400408E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.113067347545456E-2</v>
+        <v>9.2480757526942792E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.14964809951192584</v>
+        <v>0.15186510839358403</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.1360033735703706E-2</v>
+        <v>5.2120923124380804E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13993,19 +13993,19 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3284493742167089E-2</v>
+        <v>6.4222041797606613E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7535361845199361E-2</v>
+        <v>8.8832182020683811E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5382655143269162E-2</v>
+        <v>8.6647583367613898E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14360022760065097</v>
+        <v>0.14572763837991989</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-8.2200000000000006</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>8.2200000000000006</v>
+        <v>8.1</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>8.2200000000000006</v>
+        <v>8.1</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10504291417240008</v>
+        <v>0.11083350655450119</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A7D62D-DC5F-4BE7-BC11-D576568771B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A2AA47-2AB0-4FFD-ADF8-8BB767FF1CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>66192.227481599999</v>
+        <v>66600.821478400001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.11083350655450119</v>
+        <v>0.10840635294497614</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.8135601479291979E-2</v>
+        <v>3.7901640734020248E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>7.160493827160494E-2</v>
+        <v>7.1165644171779133E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12737,20 +12737,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>7.160493827160494E-2</v>
+        <v>7.1165644171779133E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>7.160493827160494E-2</v>
+        <v>7.1165644171779133E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>7.160493827160494E-2</v>
+        <v>7.1165644171779133E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>7.0370370370370361E-2</v>
+        <v>6.9938650306748451E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -13936,30 +13936,30 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.8135601479291979E-2</v>
+        <v>3.7901640734020248E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>4.1889994848766335E-2</v>
+        <v>4.1633001015338317E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>6.8037589598400408E-2</v>
+        <v>6.7620181073256833E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.2480757526942792E-2</v>
+        <v>9.1913390916348051E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15186510839358403</v>
+        <v>0.15093342061202827</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>5.2120923124380804E-2</v>
+        <v>5.1801162859814051E-2</v>
       </c>
       <c r="L125" s="77" t="str">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
@@ -13993,19 +13993,19 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4222041797606613E-2</v>
+        <v>6.3828041541179575E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.8832182020683811E-2</v>
+        <v>8.8287199308900471E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6647583367613898E-2</v>
+        <v>8.6116003101554914E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.14572763837991989</v>
+        <v>0.14483360378863203</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-8.1</v>
+        <v>-8.15</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.11083350655450119</v>
+        <v>0.10840635294497614</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0083.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0083.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76A2AA47-2AB0-4FFD-ADF8-8BB767FF1CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453C7C53-5AB2-449A-AA55-DDC4E70F15FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,6 +2358,24 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -2365,6 +2383,9 @@
   </si>
   <si>
     <t>0083.HK</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>RES_01</t>
@@ -3053,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3754,29 +3775,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4066,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4089,7 +4116,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4107,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>0083.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>424</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4121,340 +4147,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>8171879936</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>12</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>8.15</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>8171879936</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>12</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45900</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>66600.821478400001</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v>Negative Growth Asset Play</v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C22" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>5.2239462882061574</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.10840635294497614</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>2591.8202592374382</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>159.99999999999997</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-159.99999999999997</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C37" s="188">
+      <c r="C42" s="188">
         <f>Normalized_FCF!C11</f>
         <v>639</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>163.69305155463843</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-43</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>239</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>120.69305155463843</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4462,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-22.869707937042335</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>163.69305155463843</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-43</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>120.69305155463843</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-22.869707937042335</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-804.36319459009837</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>2772.792068232593</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>2772.792068232593</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>2524.2804082649359</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>3.7901640734020248E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>7.1165644171779133E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
         <v>0.01</v>
       </c>
-      <c r="D68" s="286" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="D73" s="286" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.09</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>3.432204133136278</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>3093</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.37849307922088393</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>8.3114411724224596E-2</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>1.8509098960546238E-2</v>
       </